--- a/data/REC.MI.xlsx
+++ b/data/REC.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2174" uniqueCount="2174">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2175" uniqueCount="2175">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,7 +38,7 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">18.3691120147705</t>
+    <t xml:space="preserve">18.3691082000732</t>
   </si>
   <si>
     <t xml:space="preserve">REC.MI</t>
@@ -47,37 +47,37 @@
     <t xml:space="preserve">18.9363460540771</t>
   </si>
   <si>
-    <t xml:space="preserve">18.6177597045898</t>
+    <t xml:space="preserve">18.6177635192871</t>
   </si>
   <si>
     <t xml:space="preserve">18.2680969238281</t>
   </si>
   <si>
-    <t xml:space="preserve">18.1204605102539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9728221893311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0116748809814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4444446563721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.5609970092773</t>
+    <t xml:space="preserve">18.1204643249512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9728260040283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0116767883301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4444408416748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.560998916626</t>
   </si>
   <si>
     <t xml:space="preserve">16.9626808166504</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9005184173584</t>
+    <t xml:space="preserve">16.9005165100098</t>
   </si>
   <si>
     <t xml:space="preserve">16.8849716186523</t>
   </si>
   <si>
-    <t xml:space="preserve">17.6231575012207</t>
+    <t xml:space="preserve">17.6231632232666</t>
   </si>
   <si>
     <t xml:space="preserve">17.8484973907471</t>
@@ -89,148 +89,148 @@
     <t xml:space="preserve">18.1359996795654</t>
   </si>
   <si>
-    <t xml:space="preserve">17.3667373657227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.7164039611816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0660705566406</t>
+    <t xml:space="preserve">17.366735458374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.7164001464844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.066068649292</t>
   </si>
   <si>
     <t xml:space="preserve">17.4677486419678</t>
   </si>
   <si>
-    <t xml:space="preserve">17.2424068450928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6440963745117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5407047271729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0977935791016</t>
+    <t xml:space="preserve">17.24241065979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6440944671631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5407037734985</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0977964401245</t>
   </si>
   <si>
     <t xml:space="preserve">15.2143478393555</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7815799713135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9136791229248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5042304992676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1647090911865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0326099395752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.3511943817139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.7474803924561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.7707958221436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.034984588623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4342956542969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3798999786377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8772010803223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0403823852539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2579517364502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4055919647217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0248394012451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7995014190674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7295703887939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5508499145508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8616676330566</t>
+    <t xml:space="preserve">15.7815866470337</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9136800765991</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5042266845703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1647109985352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0326118469238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3511981964111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.7474822998047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.7707939147949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0349884033203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4342918395996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3799018859863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8772048950195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0403804779053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2579498291016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4055881500244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0248413085938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7995052337646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7295665740967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5508480072021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8616619110107</t>
   </si>
   <si>
     <t xml:space="preserve">16.5353107452393</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8072700500488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9082870483398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9937648773193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9315967559814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7217960357666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7684211730957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8694343566895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6829471588135</t>
+    <t xml:space="preserve">16.8072681427002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9082851409912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9937591552734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9316005706787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7217998504639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7684173583984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8694305419922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6829452514648</t>
   </si>
   <si>
     <t xml:space="preserve">16.9782199859619</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0947742462158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1025428771973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2190971374512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1336288452148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4832916259766</t>
+    <t xml:space="preserve">17.0947704315186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1025447845459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2191009521484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1336231231689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4832935333252</t>
   </si>
   <si>
     <t xml:space="preserve">17.5454521179199</t>
   </si>
   <si>
-    <t xml:space="preserve">17.459981918335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.436674118042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4522094726562</t>
+    <t xml:space="preserve">17.4599781036377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4366703033447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4522075653076</t>
   </si>
   <si>
     <t xml:space="preserve">17.3822784423828</t>
@@ -248,166 +248,166 @@
     <t xml:space="preserve">17.5314960479736</t>
   </si>
   <si>
-    <t xml:space="preserve">17.6102542877197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.3818607330322</t>
+    <t xml:space="preserve">17.6102504730225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3818531036377</t>
   </si>
   <si>
     <t xml:space="preserve">17.4448623657227</t>
   </si>
   <si>
-    <t xml:space="preserve">17.5078678131104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6811370849609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4763660430908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4291095733643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6023807525635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.8937797546387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9804153442383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.6734828948975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.9648838043213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.9018802642822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.7286148071289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.0436420440674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.02001953125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.067268371582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.2169094085693</t>
+    <t xml:space="preserve">17.507869720459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6811351776123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4763679504395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4291133880615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6023750305176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.8937816619873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9804134368896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6734809875488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.9648876190186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.9018821716309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.7286109924316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.0436496734619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.0200214385986</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.0672740936279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.216911315918</t>
   </si>
   <si>
     <t xml:space="preserve">19.2720413208008</t>
   </si>
   <si>
-    <t xml:space="preserve">20.0911273956299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.2328910827637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.421911239624</t>
+    <t xml:space="preserve">20.0911235809326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.232889175415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.4219131469727</t>
   </si>
   <si>
     <t xml:space="preserve">20.3273983001709</t>
   </si>
   <si>
-    <t xml:space="preserve">20.469165802002</t>
+    <t xml:space="preserve">20.4691638946533</t>
   </si>
   <si>
     <t xml:space="preserve">20.7605686187744</t>
   </si>
   <si>
-    <t xml:space="preserve">20.894458770752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.9023323059082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.2488632202148</t>
+    <t xml:space="preserve">20.8944549560547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.9023361206055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.2488670349121</t>
   </si>
   <si>
     <t xml:space="preserve">21.4142589569092</t>
   </si>
   <si>
-    <t xml:space="preserve">21.0677185058594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.9968433380127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.4930171966553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.4536380767822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.1464824676514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.4770374298096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.4297828674316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.6266803741455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3667812347412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.9729881286621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.6424293518066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.9102077484131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.8156986236572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.1386070251465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.0438709259033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.8708229064941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.1543579101562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.2646217346191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.2882461547852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.2803745269775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.1858577728271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.0519676208496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.3748817443848</t>
+    <t xml:space="preserve">21.067720413208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.9968395233154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.493013381958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.453634262085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.1464786529541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.4770412445068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.4297885894775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.6266765594482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3667774200439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.9729919433594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.6424312591553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.9102058410645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.81569480896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.1386089324951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.0438766479492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.8708305358887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.154354095459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.2646160125732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.2882442474365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.280366897583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.1858615875244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.0519695281982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.3748779296875</t>
   </si>
   <si>
     <t xml:space="preserve">22.0758266448975</t>
   </si>
   <si>
-    <t xml:space="preserve">22.2884654998779</t>
+    <t xml:space="preserve">22.2884674072266</t>
   </si>
   <si>
     <t xml:space="preserve">22.1545791625977</t>
@@ -416,73 +416,73 @@
     <t xml:space="preserve">21.918306350708</t>
   </si>
   <si>
-    <t xml:space="preserve">21.7292881011963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.9104328155518</t>
+    <t xml:space="preserve">21.7292861938477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.9104309082031</t>
   </si>
   <si>
     <t xml:space="preserve">21.8001708984375</t>
   </si>
   <si>
-    <t xml:space="preserve">22.2175846099854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.6507549285889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.6192493438721</t>
+    <t xml:space="preserve">22.217586517334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.6507587432861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.6192512512207</t>
   </si>
   <si>
     <t xml:space="preserve">22.6586322784424</t>
   </si>
   <si>
-    <t xml:space="preserve">22.3751087188721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.8161430358887</t>
+    <t xml:space="preserve">22.3751010894775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.8161468505859</t>
   </si>
   <si>
     <t xml:space="preserve">22.7925186157227</t>
   </si>
   <si>
-    <t xml:space="preserve">22.66650390625</t>
+    <t xml:space="preserve">22.6665077209473</t>
   </si>
   <si>
     <t xml:space="preserve">22.8476486206055</t>
   </si>
   <si>
-    <t xml:space="preserve">23.1233062744141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.7216377258301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.1230812072754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.4932422637939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.2412166595459</t>
+    <t xml:space="preserve">23.1233024597168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.7216396331787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.1230754852295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.4932384490967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.2412128448486</t>
   </si>
   <si>
     <t xml:space="preserve">22.1782093048096</t>
   </si>
   <si>
-    <t xml:space="preserve">22.406608581543</t>
+    <t xml:space="preserve">22.4066066741943</t>
   </si>
   <si>
     <t xml:space="preserve">22.3672275543213</t>
   </si>
   <si>
-    <t xml:space="preserve">22.5168704986572</t>
+    <t xml:space="preserve">22.51686668396</t>
   </si>
   <si>
     <t xml:space="preserve">21.9025592803955</t>
   </si>
   <si>
-    <t xml:space="preserve">21.8946800231934</t>
+    <t xml:space="preserve">21.894681930542</t>
   </si>
   <si>
     <t xml:space="preserve">21.4772644042969</t>
@@ -491,49 +491,49 @@
     <t xml:space="preserve">21.6111526489258</t>
   </si>
   <si>
-    <t xml:space="preserve">21.3355007171631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.4851417541504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.6032772064209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.6977825164795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.2094841003418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.2331142425537</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.5402698516846</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.3591251373291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.1228580474854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.3827514648438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.272497177124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.9655609130859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.6899070739746</t>
+    <t xml:space="preserve">21.3354988098145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.4851398468018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.6032733917236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.6977863311768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.2094898223877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.2331123352051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.5402717590332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.3591289520264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.1228523254395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.3827476501465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.2724895477295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.9655628204346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.6899089813232</t>
   </si>
   <si>
     <t xml:space="preserve">21.083475112915</t>
   </si>
   <si>
-    <t xml:space="preserve">21.0047187805176</t>
+    <t xml:space="preserve">21.0047130584717</t>
   </si>
   <si>
     <t xml:space="preserve">20.9495868682861</t>
@@ -542,112 +542,112 @@
     <t xml:space="preserve">21.3985080718994</t>
   </si>
   <si>
-    <t xml:space="preserve">21.5481472015381</t>
+    <t xml:space="preserve">21.5481491088867</t>
   </si>
   <si>
     <t xml:space="preserve">21.1779842376709</t>
   </si>
   <si>
-    <t xml:space="preserve">21.3906307220459</t>
+    <t xml:space="preserve">21.3906288146973</t>
   </si>
   <si>
     <t xml:space="preserve">21.4063816070557</t>
   </si>
   <si>
-    <t xml:space="preserve">21.6190280914307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.6584072113037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.3908596038818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.5956249237061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.5326194763184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.4223556518555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.3514747619629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.304220199585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.1860828399658</t>
+    <t xml:space="preserve">21.619026184082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.6584091186523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.3908538818359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.5956230163574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.5326232910156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.4223575592041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.3514766693115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.3042259216309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.1860866546631</t>
   </si>
   <si>
     <t xml:space="preserve">22.083703994751</t>
   </si>
   <si>
-    <t xml:space="preserve">22.2648391723633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.5166397094727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.6820316314697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.2252349853516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.3512516021729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.2567405700684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.1071033477783</t>
+    <t xml:space="preserve">22.2648429870605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.5166416168213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.6820335388184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.2252388000488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.3512535095215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.256742477417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.1071014404297</t>
   </si>
   <si>
     <t xml:space="preserve">21.0913467407227</t>
   </si>
   <si>
-    <t xml:space="preserve">20.3037719726562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.8627281188965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.1620044708252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.256519317627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.8154697418213</t>
+    <t xml:space="preserve">20.3037757873535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.8627262115479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.1620082855225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.2565155029297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.8154754638672</t>
   </si>
   <si>
     <t xml:space="preserve">20.3116455078125</t>
   </si>
   <si>
-    <t xml:space="preserve">21.193733215332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.5164184570312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.5557956695557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.1383781433105</t>
+    <t xml:space="preserve">21.1937389373779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.5164203643799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.5557975769043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.1383819580078</t>
   </si>
   <si>
     <t xml:space="preserve">20.0202465057373</t>
   </si>
   <si>
-    <t xml:space="preserve">20.2643947601318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.2164859771729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.7134704589844</t>
+    <t xml:space="preserve">20.2643966674805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.2164897918701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.7134666442871</t>
   </si>
   <si>
     <t xml:space="preserve">20.0168743133545</t>
@@ -662,22 +662,22 @@
     <t xml:space="preserve">20.088737487793</t>
   </si>
   <si>
-    <t xml:space="preserve">20.3602027893066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.5119113922119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.8092842102051</t>
+    <t xml:space="preserve">20.3602085113525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.5119075775146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.8092823028564</t>
   </si>
   <si>
     <t xml:space="preserve">20.1286582946777</t>
   </si>
   <si>
-    <t xml:space="preserve">20.3442344665527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.5598163604736</t>
+    <t xml:space="preserve">20.3442325592041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.5598125457764</t>
   </si>
   <si>
     <t xml:space="preserve">20.5039253234863</t>
@@ -686,49 +686,49 @@
     <t xml:space="preserve">20.3841609954834</t>
   </si>
   <si>
-    <t xml:space="preserve">20.7594223022461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.4719829559326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.7354698181152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.4240798950195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.1107387542725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.3582515716553</t>
+    <t xml:space="preserve">20.759428024292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.4719905853271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.7354755401611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.4240818023682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.1107368469238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.3582572937012</t>
   </si>
   <si>
     <t xml:space="preserve">21.5179424285889</t>
   </si>
   <si>
-    <t xml:space="preserve">21.2943801879883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.1027584075928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.927095413208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.501974105835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.6057682037354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.3502712249756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.493989944458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.8053798675537</t>
+    <t xml:space="preserve">21.294376373291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.1027507781982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.9271011352539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.5019760131836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.6057720184326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.350269317627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.4939861297607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.8053779602051</t>
   </si>
   <si>
     <t xml:space="preserve">21.7335224151611</t>
@@ -743,79 +743,79 @@
     <t xml:space="preserve">22.1806488037109</t>
   </si>
   <si>
-    <t xml:space="preserve">21.7095642089844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.2205657958984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.7894153594971</t>
+    <t xml:space="preserve">21.7095680236816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.2205677032471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.7894096374512</t>
   </si>
   <si>
     <t xml:space="preserve">22.1087913513184</t>
   </si>
   <si>
-    <t xml:space="preserve">21.9570827484131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.9890213012695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.7734432220459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.7814292907715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.7494926452637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.4620494842529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.6377086639404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.6137580871582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.0069446563721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.0867881774902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.2544612884521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.4380950927734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.0708160400391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.4540710449219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.5578651428223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.428165435791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.539945602417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.595832824707</t>
+    <t xml:space="preserve">21.9570846557617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.9890232086182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.7734470367432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.7814273834229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.7494888305664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.4620513916016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.6377067565918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.6137561798096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.0069427490234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.0867900848389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.2544593811035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.4381008148193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.0708179473877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.4540672302246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.5578632354736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.4281616210938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.5399475097656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.5958347320557</t>
   </si>
   <si>
     <t xml:space="preserve">22.8193969726562</t>
   </si>
   <si>
-    <t xml:space="preserve">22.5638961791992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.0509452819824</t>
+    <t xml:space="preserve">22.5638999938965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.0509471893311</t>
   </si>
   <si>
     <t xml:space="preserve">23.1467609405518</t>
@@ -824,31 +824,31 @@
     <t xml:space="preserve">23.5539646148682</t>
   </si>
   <si>
-    <t xml:space="preserve">23.5220279693604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.4501609802246</t>
+    <t xml:space="preserve">23.5220241546631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.4501667022705</t>
   </si>
   <si>
     <t xml:space="preserve">23.8733367919922</t>
   </si>
   <si>
-    <t xml:space="preserve">23.9292240142822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.8653526306152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.1687622070312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.2326354980469</t>
+    <t xml:space="preserve">23.9292297363281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.8653564453125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.168758392334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.2326374053955</t>
   </si>
   <si>
     <t xml:space="preserve">24.0889167785645</t>
   </si>
   <si>
-    <t xml:space="preserve">24.1847305297852</t>
+    <t xml:space="preserve">24.1847343444824</t>
   </si>
   <si>
     <t xml:space="preserve">24.3444156646729</t>
@@ -857,343 +857,343 @@
     <t xml:space="preserve">24.6158847808838</t>
   </si>
   <si>
-    <t xml:space="preserve">24.6079006195068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.8554191589355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.9751892089844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.2466602325439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.4382839202881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.4702167510986</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.0071201324463</t>
+    <t xml:space="preserve">24.6079044342041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.8554172515869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.9751834869385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.2466526031494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.4382820129395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.47021484375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.0071239471436</t>
   </si>
   <si>
     <t xml:space="preserve">24.9272804260254</t>
   </si>
   <si>
-    <t xml:space="preserve">25.1668148040771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.3344802856445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.2785930633545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.6298999786377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.3983592987061</t>
+    <t xml:space="preserve">25.1668109893799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.3344841003418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.2785911560059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.6299018859863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.3983573913574</t>
   </si>
   <si>
     <t xml:space="preserve">25.206729888916</t>
   </si>
   <si>
-    <t xml:space="preserve">25.2865791320801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.3664245605469</t>
+    <t xml:space="preserve">25.2865734100342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.3664226531982</t>
   </si>
   <si>
     <t xml:space="preserve">25.5899829864502</t>
   </si>
   <si>
-    <t xml:space="preserve">25.9492797851562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.9652519226074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.2207469940186</t>
+    <t xml:space="preserve">25.9492778778076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.9652500152588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.2207489013672</t>
   </si>
   <si>
     <t xml:space="preserve">26.0450973510742</t>
   </si>
   <si>
-    <t xml:space="preserve">26.0211391448975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.4043960571289</t>
+    <t xml:space="preserve">26.0211372375488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.4043865203857</t>
   </si>
   <si>
     <t xml:space="preserve">26.6598949432373</t>
   </si>
   <si>
-    <t xml:space="preserve">26.6119899749756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.3804359436035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.6439247131348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.0351619720459</t>
+    <t xml:space="preserve">26.6119918823242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.3804397583008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.6439228057861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.0351600646973</t>
   </si>
   <si>
     <t xml:space="preserve">26.5002059936523</t>
   </si>
   <si>
-    <t xml:space="preserve">27.6864242553711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.468542098999</t>
+    <t xml:space="preserve">27.6864223480225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.4685440063477</t>
   </si>
   <si>
     <t xml:space="preserve">27.4362640380859</t>
   </si>
   <si>
-    <t xml:space="preserve">27.7186985015869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.4443359375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.7832508087158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.5573120117188</t>
+    <t xml:space="preserve">27.7187004089355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.4443378448486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.7832527160645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.5573062896729</t>
   </si>
   <si>
     <t xml:space="preserve">27.621862411499</t>
   </si>
   <si>
-    <t xml:space="preserve">28.3481140136719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.7435207366943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.7193164825439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.4455680847168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.5343360900879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.453634262085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.6628227233887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.8403625488281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.9291191101074</t>
+    <t xml:space="preserve">28.3481197357178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.743522644043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.719310760498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.4455718994141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.5343341827393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.4536380767822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.6628284454346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.8403549194336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.9291210174561</t>
   </si>
   <si>
     <t xml:space="preserve">28.8322906494141</t>
   </si>
   <si>
-    <t xml:space="preserve">28.7758007049561</t>
+    <t xml:space="preserve">28.7757968902588</t>
   </si>
   <si>
     <t xml:space="preserve">28.9452571868896</t>
   </si>
   <si>
-    <t xml:space="preserve">28.8000087738037</t>
+    <t xml:space="preserve">28.8000068664551</t>
   </si>
   <si>
     <t xml:space="preserve">29.1389350891113</t>
   </si>
   <si>
-    <t xml:space="preserve">28.3884716033936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.4852981567383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.896842956543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.583366394043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.6230983734131</t>
+    <t xml:space="preserve">28.3884620666504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.4852962493896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.8968486785889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.5833721160889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.6231002807617</t>
   </si>
   <si>
     <t xml:space="preserve">29.7441425323486</t>
   </si>
   <si>
-    <t xml:space="preserve">29.2680377960205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.4375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.469783782959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.9371929168701</t>
+    <t xml:space="preserve">29.2680416107178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.4374980926514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.4697799682617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.9371910095215</t>
   </si>
   <si>
     <t xml:space="preserve">29.405216217041</t>
   </si>
   <si>
-    <t xml:space="preserve">30.0749855041504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.8893909454346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.1072673797607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.3412742614746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.0265712738037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.1798915863037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.2519016265869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.4610919952393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.0818271636963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.5659999847412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.6386203765869</t>
+    <t xml:space="preserve">30.0749950408936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.8893966674805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.1072692871094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.3412799835205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.026575088501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.1798934936523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.2519073486328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.4610939025879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.0818252563477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.5659980773926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.6386241912842</t>
   </si>
   <si>
     <t xml:space="preserve">28.2109375</t>
   </si>
   <si>
-    <t xml:space="preserve">28.1544532775879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.4368839263916</t>
+    <t xml:space="preserve">28.154447555542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.4368858337402</t>
   </si>
   <si>
     <t xml:space="preserve">28.2593517303467</t>
   </si>
   <si>
-    <t xml:space="preserve">28.6063499450684</t>
+    <t xml:space="preserve">28.6063385009766</t>
   </si>
   <si>
     <t xml:space="preserve">28.3158416748047</t>
   </si>
   <si>
-    <t xml:space="preserve">28.590202331543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.6547546386719</t>
+    <t xml:space="preserve">28.5902004241943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.6547565460205</t>
   </si>
   <si>
     <t xml:space="preserve">29.1147193908691</t>
   </si>
   <si>
-    <t xml:space="preserve">29.1308650970459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.0662994384766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.808084487915</t>
+    <t xml:space="preserve">29.1308555603027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.0663051605225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.8080768585205</t>
   </si>
   <si>
     <t xml:space="preserve">28.6789703369141</t>
   </si>
   <si>
-    <t xml:space="preserve">28.8564929962158</t>
+    <t xml:space="preserve">28.8564968109131</t>
   </si>
   <si>
     <t xml:space="preserve">28.6951084136963</t>
   </si>
   <si>
-    <t xml:space="preserve">28.6305503845215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.7596569061279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.2512855529785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.9769287109375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.3561859130859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.4126739501953</t>
+    <t xml:space="preserve">28.6305541992188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.7596626281738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.2512798309326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.976921081543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.3561878204346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.412670135498</t>
   </si>
   <si>
     <t xml:space="preserve">28.1786575317383</t>
   </si>
   <si>
-    <t xml:space="preserve">28.2028675079346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.5337219238281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.2835674285889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.5982723236084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.5014381408691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.3803997039795</t>
+    <t xml:space="preserve">28.2028713226318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.5337162017822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.2835597991943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.5982685089111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.5014362335205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.3803901672363</t>
   </si>
   <si>
     <t xml:space="preserve">28.7677345275879</t>
   </si>
   <si>
-    <t xml:space="preserve">29.0340213775635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.3325939178467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.211555480957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.1873416900635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.3971500396729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.840970993042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.0346374511719</t>
+    <t xml:space="preserve">29.034029006958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.3325977325439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.2115573883057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.187349319458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.3971576690674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.8409748077393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.0346393585205</t>
   </si>
   <si>
     <t xml:space="preserve">29.9942970275879</t>
   </si>
   <si>
-    <t xml:space="preserve">30.0991954803467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.2202396392822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.8490467071533</t>
+    <t xml:space="preserve">30.0992031097412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.2202434539795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.849048614502</t>
   </si>
   <si>
     <t xml:space="preserve">30.0830593109131</t>
@@ -1202,61 +1202,61 @@
     <t xml:space="preserve">30.4058399200439</t>
   </si>
   <si>
-    <t xml:space="preserve">30.5995006561279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.0352535247803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.527494430542</t>
+    <t xml:space="preserve">30.5995063781738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.0352592468262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.5274963378906</t>
   </si>
   <si>
     <t xml:space="preserve">31.4387321472168</t>
   </si>
   <si>
-    <t xml:space="preserve">31.349967956543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.7937850952148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.4710121154785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.7695827484131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.583984375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.8018627166748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.9067687988281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.930965423584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.1649894714355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.1407775878906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.3425178527832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.1084899902344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.3586578369141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.9632568359375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.0116691589355</t>
+    <t xml:space="preserve">31.3499717712402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.793794631958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.4710083007812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.7695789337158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.5839805603027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.8018569946289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.9067668914795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.9309749603271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.164981842041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.1407737731934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.3425102233887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.1085014343262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.3586463928223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.963249206543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.011661529541</t>
   </si>
   <si>
     <t xml:space="preserve">31.8986930847168</t>
@@ -1265,118 +1265,118 @@
     <t xml:space="preserve">32.0439453125</t>
   </si>
   <si>
-    <t xml:space="preserve">32.2295417785645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.423210144043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.9551734924316</t>
+    <t xml:space="preserve">32.2295341491699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.4232139587402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.955171585083</t>
   </si>
   <si>
     <t xml:space="preserve">32.0358734130859</t>
   </si>
   <si>
-    <t xml:space="preserve">32.1891937255859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.3667297363281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.2053413391113</t>
+    <t xml:space="preserve">32.1891860961914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.3667259216309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.2053298950195</t>
   </si>
   <si>
     <t xml:space="preserve">32.4877662658691</t>
   </si>
   <si>
-    <t xml:space="preserve">32.124641418457</t>
+    <t xml:space="preserve">32.1246337890625</t>
   </si>
   <si>
     <t xml:space="preserve">32.7621307373047</t>
   </si>
   <si>
-    <t xml:space="preserve">32.6491584777832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.1004333496094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.277961730957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.4064502716064</t>
+    <t xml:space="preserve">32.6491546630859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.1004295349121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.2779655456543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.4064521789551</t>
   </si>
   <si>
     <t xml:space="preserve">31.3176937103271</t>
   </si>
   <si>
-    <t xml:space="preserve">31.1562995910645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.414529800415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.8012390136719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.1805095672607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.6963386535645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.2348690032959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.2756614685059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.1614379882812</t>
+    <t xml:space="preserve">31.1563091278076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.4145240783691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.8012428283691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.1805114746094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.6963424682617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.2348728179932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.2756805419922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.1614322662354</t>
   </si>
   <si>
     <t xml:space="preserve">31.2103939056396</t>
   </si>
   <si>
-    <t xml:space="preserve">30.9982433319092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.9900875091553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.6963367462158</t>
+    <t xml:space="preserve">30.9982471466064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.9900817871094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.6963329315186</t>
   </si>
   <si>
     <t xml:space="preserve">30.8432102203369</t>
   </si>
   <si>
-    <t xml:space="preserve">30.704496383667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.9166469573975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.6020450592041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.2593574523926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.0471954345703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.5612506866455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.5204544067383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.5857334136963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.8350524902344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.2067623138428</t>
+    <t xml:space="preserve">30.7045059204102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.916654586792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.6020545959473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.2593536376953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.0471992492676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.5612545013428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.5204524993896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.5857372283936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.8350582122803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.2067699432373</t>
   </si>
   <si>
     <t xml:space="preserve">29.8395805358887</t>
@@ -1388,133 +1388,133 @@
     <t xml:space="preserve">30.3781127929688</t>
   </si>
   <si>
-    <t xml:space="preserve">29.8477478027344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.7416610717773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.1904468536377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.4597091674805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.5086688995361</t>
+    <t xml:space="preserve">29.8477439880371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.7416725158691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.1904449462891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.4597148895264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.5086669921875</t>
   </si>
   <si>
     <t xml:space="preserve">30.2394065856934</t>
   </si>
   <si>
-    <t xml:space="preserve">30.4352321624756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.2883605957031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.7616176605225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.3001518249512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.430700302124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.5775775909424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.349100112915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.1696033477783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.495979309082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.1043128967285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.9411239624023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.549467086792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.7942562103271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.4633369445801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.8595294952393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.3327884674072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.3128452301025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.9211750030518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.5539970397949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.7870006561279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.1505527496338</t>
+    <t xml:space="preserve">30.4352397918701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.2883625030518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.7616157531738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.3001480102539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.4307041168213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.5775718688965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.3490943908691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.1695995330811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.4959735870361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.1043224334717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.941125869751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.5494613647461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.7942600250244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.4633407592773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.8595314025879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.3327808380127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.3128471374512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.9211826324463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.5540046691895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.7869911193848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.1505546569824</t>
   </si>
   <si>
     <t xml:space="preserve">27.1550807952881</t>
   </si>
   <si>
-    <t xml:space="preserve">28.362699508667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.0780200958252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.1886196136475</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.6337757110596</t>
+    <t xml:space="preserve">28.3626976013184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.0780181884766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.1886215209961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.633768081665</t>
   </si>
   <si>
     <t xml:space="preserve">24.1686763763428</t>
   </si>
   <si>
-    <t xml:space="preserve">25.3518142700195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.0335941314697</t>
+    <t xml:space="preserve">25.3518104553223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.0335903167725</t>
   </si>
   <si>
     <t xml:space="preserve">25.4007720947266</t>
   </si>
   <si>
-    <t xml:space="preserve">24.495059967041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.0707626342773</t>
+    <t xml:space="preserve">24.4950580596924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.0707607269287</t>
   </si>
   <si>
     <t xml:space="preserve">23.9075679779053</t>
   </si>
   <si>
-    <t xml:space="preserve">23.7117404937744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.3971424102783</t>
+    <t xml:space="preserve">23.7117385864258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.397144317627</t>
   </si>
   <si>
     <t xml:space="preserve">24.2339515686035</t>
   </si>
   <si>
-    <t xml:space="preserve">24.0299644470215</t>
+    <t xml:space="preserve">24.0299606323242</t>
   </si>
   <si>
     <t xml:space="preserve">23.719898223877</t>
@@ -1523,115 +1523,115 @@
     <t xml:space="preserve">23.1405696868896</t>
   </si>
   <si>
-    <t xml:space="preserve">23.5730266571045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.6464614868164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.4216194152832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.3155479431152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.552173614502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.2013149261475</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.7933330535889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.0626029968262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.9238891601562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.703577041626</t>
+    <t xml:space="preserve">23.5730247497559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.646463394165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.4216251373291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.3155460357666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.5521755218506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.2013168334961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.7933349609375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.0625991821289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.9238872528076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.7035789489746</t>
   </si>
   <si>
     <t xml:space="preserve">23.3363990783691</t>
   </si>
   <si>
-    <t xml:space="preserve">23.2384853363037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.189525604248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.1568870544434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.4551639556885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.8468208312988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.548547744751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.4624176025391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.0870780944824</t>
+    <t xml:space="preserve">23.2384834289551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.1895275115967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.1568851470947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.4551620483398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.8468227386475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.5485458374023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.4624195098877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.0870819091797</t>
   </si>
   <si>
     <t xml:space="preserve">24.3808250427246</t>
   </si>
   <si>
-    <t xml:space="preserve">24.3563480377197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.0952396392822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.1278781890869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.9157257080078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.2094707489014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.1523571014404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.3481864929199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.5551605224609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.2902374267578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.5054874420166</t>
+    <t xml:space="preserve">24.3563423156738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.0952377319336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.1278762817383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.9157238006592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.20947265625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.1523532867432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.3481845855713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.5551624298096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.2902336120605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.505485534668</t>
   </si>
   <si>
     <t xml:space="preserve">24.4558124542236</t>
   </si>
   <si>
-    <t xml:space="preserve">24.5468769073486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.5403442382812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.3085346221924</t>
+    <t xml:space="preserve">24.5468826293945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.5403499603271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.3085384368896</t>
   </si>
   <si>
     <t xml:space="preserve">25.3747692108154</t>
   </si>
   <si>
-    <t xml:space="preserve">25.5982971191406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.3333721160889</t>
+    <t xml:space="preserve">25.5982990264893</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.3333759307861</t>
   </si>
   <si>
     <t xml:space="preserve">25.4244422912598</t>
@@ -1640,67 +1640,67 @@
     <t xml:space="preserve">25.1512393951416</t>
   </si>
   <si>
-    <t xml:space="preserve">25.2505836486816</t>
+    <t xml:space="preserve">25.250581741333</t>
   </si>
   <si>
     <t xml:space="preserve">25.5320663452148</t>
   </si>
   <si>
-    <t xml:space="preserve">25.416166305542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.9277114868164</t>
+    <t xml:space="preserve">25.4161624908447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.9277095794678</t>
   </si>
   <si>
     <t xml:space="preserve">26.6248779296875</t>
   </si>
   <si>
-    <t xml:space="preserve">26.4261837005615</t>
+    <t xml:space="preserve">26.4261875152588</t>
   </si>
   <si>
     <t xml:space="preserve">26.6828308105469</t>
   </si>
   <si>
-    <t xml:space="preserve">26.5503692626953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.508975982666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.5669288635254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.6000461578369</t>
+    <t xml:space="preserve">26.5503711700439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.5089740753174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.5669250488281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.6000385284424</t>
   </si>
   <si>
     <t xml:space="preserve">26.2440528869629</t>
   </si>
   <si>
-    <t xml:space="preserve">26.1115913391113</t>
+    <t xml:space="preserve">26.1115875244141</t>
   </si>
   <si>
     <t xml:space="preserve">26.2606067657471</t>
   </si>
   <si>
-    <t xml:space="preserve">26.3433952331543</t>
+    <t xml:space="preserve">26.3433933258057</t>
   </si>
   <si>
     <t xml:space="preserve">26.2937240600586</t>
   </si>
   <si>
-    <t xml:space="preserve">27.254077911377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.3203067779541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.2789134979248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.9477519989014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.1298923492432</t>
+    <t xml:space="preserve">27.2540721893311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.3203048706055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.2789096832275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.9477577209473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.1298885345459</t>
   </si>
   <si>
     <t xml:space="preserve">27.1878433227539</t>
@@ -1709,97 +1709,97 @@
     <t xml:space="preserve">27.5686721801758</t>
   </si>
   <si>
-    <t xml:space="preserve">27.1961212158203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.0636577606201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.7839221954346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.545581817627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.2806606292725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.3468856811523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.50244140625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.4527683258057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.8004779815674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.7673606872559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.1978626251221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.6876220703125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.7024345397949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.0418701171875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.3399085998535</t>
+    <t xml:space="preserve">27.1961193084717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.0636596679688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.7839202880859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.5455799102783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.2806510925293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.3468894958496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.5024433135986</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.452766418457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.800479888916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.7673645019531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.197868347168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.6876163482666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.7024307250977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.0418682098389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.3399066925049</t>
   </si>
   <si>
     <t xml:space="preserve">24.8035259246826</t>
   </si>
   <si>
-    <t xml:space="preserve">25.0436153411865</t>
+    <t xml:space="preserve">25.0436115264893</t>
   </si>
   <si>
     <t xml:space="preserve">25.6645278930664</t>
   </si>
   <si>
-    <t xml:space="preserve">25.6728076934814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.358211517334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.4492740631104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.8780326843262</t>
+    <t xml:space="preserve">25.6728057861328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.3582096099854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.449275970459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.8780345916748</t>
   </si>
   <si>
     <t xml:space="preserve">24.7538509368896</t>
   </si>
   <si>
-    <t xml:space="preserve">24.8614807128906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.8301048278809</t>
+    <t xml:space="preserve">24.861478805542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.8301086425781</t>
   </si>
   <si>
     <t xml:space="preserve">25.6893653869629</t>
   </si>
   <si>
-    <t xml:space="preserve">25.904613494873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.0619125366211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.0453548431396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.7555961608887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.9128932952881</t>
+    <t xml:space="preserve">25.9046192169189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.0619144439697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.045352935791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.7555999755859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.9128952026367</t>
   </si>
   <si>
     <t xml:space="preserve">26.4758586883545</t>
@@ -1814,25 +1814,25 @@
     <t xml:space="preserve">26.5752048492432</t>
   </si>
   <si>
-    <t xml:space="preserve">26.6993865966797</t>
+    <t xml:space="preserve">26.6993885040283</t>
   </si>
   <si>
     <t xml:space="preserve">26.9725933074951</t>
   </si>
   <si>
-    <t xml:space="preserve">26.9891471862793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.8732452392578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.4924182891846</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.2274913787842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.6396865844727</t>
+    <t xml:space="preserve">26.9891452789307</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.8732471466064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.4924163818359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.2274951934814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.6396884918213</t>
   </si>
   <si>
     <t xml:space="preserve">25.2754230499268</t>
@@ -1844,115 +1844,115 @@
     <t xml:space="preserve">25.4327201843262</t>
   </si>
   <si>
-    <t xml:space="preserve">25.1926345825195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.9773788452148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.0022163391113</t>
+    <t xml:space="preserve">25.1926326751709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.9773826599121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.0022201538086</t>
   </si>
   <si>
     <t xml:space="preserve">25.1098461151123</t>
   </si>
   <si>
-    <t xml:space="preserve">24.9691009521484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.2423057556152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.1595191955566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.2919769287109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.8863124847412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.258861541748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.8118019104004</t>
+    <t xml:space="preserve">24.9691047668457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.242301940918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.159517288208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.2919788360596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.8863162994385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.2588634490967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.811803817749</t>
   </si>
   <si>
     <t xml:space="preserve">24.6296672821045</t>
   </si>
   <si>
-    <t xml:space="preserve">24.6710643768311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.5634346008301</t>
+    <t xml:space="preserve">24.6710624694824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.5634384155273</t>
   </si>
   <si>
     <t xml:space="preserve">24.3895797729492</t>
   </si>
   <si>
-    <t xml:space="preserve">24.2985153198242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.1081008911133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.3067893981934</t>
+    <t xml:space="preserve">24.298511505127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.1080989837646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.306791305542</t>
   </si>
   <si>
     <t xml:space="preserve">24.4475326538086</t>
   </si>
   <si>
-    <t xml:space="preserve">24.613109588623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.1412124633789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.356466293335</t>
+    <t xml:space="preserve">24.6131076812744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.1412143707275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.3564682006836</t>
   </si>
   <si>
     <t xml:space="preserve">24.4889259338379</t>
   </si>
   <si>
-    <t xml:space="preserve">25.3830490112305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.1181240081787</t>
+    <t xml:space="preserve">25.3830451965332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.1181259155273</t>
   </si>
   <si>
     <t xml:space="preserve">24.720739364624</t>
   </si>
   <si>
-    <t xml:space="preserve">24.8531970977783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.0187721252441</t>
+    <t xml:space="preserve">24.853199005127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.0187759399414</t>
   </si>
   <si>
     <t xml:space="preserve">24.0915412902832</t>
   </si>
   <si>
-    <t xml:space="preserve">23.950798034668</t>
+    <t xml:space="preserve">23.9508018493652</t>
   </si>
   <si>
     <t xml:space="preserve">23.818338394165</t>
   </si>
   <si>
-    <t xml:space="preserve">24.0004730224609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.1494903564453</t>
+    <t xml:space="preserve">24.0004749298096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.1494941711426</t>
   </si>
   <si>
     <t xml:space="preserve">24.522045135498</t>
   </si>
   <si>
-    <t xml:space="preserve">24.8283653259277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.5882740020752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.6627864837646</t>
+    <t xml:space="preserve">24.8283615112305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.5882720947266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.662784576416</t>
   </si>
   <si>
     <t xml:space="preserve">24.2488403320312</t>
@@ -1961,31 +1961,31 @@
     <t xml:space="preserve">25.0850048065186</t>
   </si>
   <si>
-    <t xml:space="preserve">25.606575012207</t>
+    <t xml:space="preserve">25.6065769195557</t>
   </si>
   <si>
     <t xml:space="preserve">24.7704086303711</t>
   </si>
   <si>
-    <t xml:space="preserve">24.9111499786377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.9608211517334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.7952461242676</t>
+    <t xml:space="preserve">24.9111518859863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.9608287811279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.7952499389648</t>
   </si>
   <si>
     <t xml:space="preserve">24.9194316864014</t>
   </si>
   <si>
-    <t xml:space="preserve">24.6958980560303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.0270576477051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.712459564209</t>
+    <t xml:space="preserve">24.6958999633789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.0270538330078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.7124557495117</t>
   </si>
   <si>
     <t xml:space="preserve">24.5303192138672</t>
@@ -1994,7 +1994,7 @@
     <t xml:space="preserve">23.9425201416016</t>
   </si>
   <si>
-    <t xml:space="preserve">24.008752822876</t>
+    <t xml:space="preserve">24.0087509155273</t>
   </si>
   <si>
     <t xml:space="preserve">24.1246566772461</t>
@@ -2006,16 +2006,16 @@
     <t xml:space="preserve">23.8639831542969</t>
   </si>
   <si>
-    <t xml:space="preserve">23.8555736541748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.4855899810791</t>
+    <t xml:space="preserve">23.8555774688721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.485595703125</t>
   </si>
   <si>
     <t xml:space="preserve">23.4771823883057</t>
   </si>
   <si>
-    <t xml:space="preserve">23.5360450744629</t>
+    <t xml:space="preserve">23.5360431671143</t>
   </si>
   <si>
     <t xml:space="preserve">23.3426456451416</t>
@@ -2024,130 +2024,130 @@
     <t xml:space="preserve">23.8892116546631</t>
   </si>
   <si>
-    <t xml:space="preserve">24.2171516418457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.1919250488281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.0489768981934</t>
+    <t xml:space="preserve">24.2171497344971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.1919269561768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.048978805542</t>
   </si>
   <si>
     <t xml:space="preserve">23.5444526672363</t>
   </si>
   <si>
-    <t xml:space="preserve">23.6285400390625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.4940013885498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.4603672027588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.9060306549072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.880802154541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.1330661773682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.3853282928467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.553503036499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.9318923950195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.4784603118896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.0754833221436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.4700584411621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.2430171966553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.0580272674561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.3271026611328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.0159797668457</t>
+    <t xml:space="preserve">23.6285419464111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.4940052032471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.4603652954102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.9060287475586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.8808040618896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.1330642700195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.3853302001953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.5534992218018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.9318943023682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.4784564971924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.0754852294922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.4700546264648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.2430152893066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.0580234527588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.3271064758301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.0159816741943</t>
   </si>
   <si>
     <t xml:space="preserve">24.8898525238037</t>
   </si>
   <si>
-    <t xml:space="preserve">25.1589298248291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.915075302124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.7979965209961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.8568553924561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.9913959503174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.5884170532227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.2352485656738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.8148155212402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.3691463470459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.1757507324219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.2009735107422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.2766513824463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.5877780914307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.6052341461182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.386604309082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.0004444122314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.8749523162842</t>
+    <t xml:space="preserve">25.1589279174805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.9150733947754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.7979946136475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.8568534851074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.9913940429688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.5884132385254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.2352542877197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.8148136138916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.3691501617432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.1757488250732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.2009754180908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.2766532897949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.587776184082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.6052303314209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.3866004943848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.0004425048828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.8749580383301</t>
   </si>
   <si>
     <t xml:space="preserve">27.8329048156738</t>
   </si>
   <si>
-    <t xml:space="preserve">27.1433906555176</t>
+    <t xml:space="preserve">27.1433925628662</t>
   </si>
   <si>
     <t xml:space="preserve">26.6556873321533</t>
   </si>
   <si>
-    <t xml:space="preserve">26.9415836334229</t>
+    <t xml:space="preserve">26.9415817260742</t>
   </si>
   <si>
     <t xml:space="preserve">27.3115653991699</t>
@@ -2156,172 +2156,172 @@
     <t xml:space="preserve">28.1188011169434</t>
   </si>
   <si>
-    <t xml:space="preserve">28.1860771179199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.4467468261719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.5560550689697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.0431270599365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.1944828033447</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.7992782592773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.6058712005615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.5806465148926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.8160915374756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.6815528869629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.8076820373535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.0094966888428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.4635639190674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.5896911621094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.5308361053467</t>
+    <t xml:space="preserve">28.1860809326172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.4467449188232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.556058883667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.0431213378906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.1944847106934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.7992725372314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.6058750152588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.5806407928467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.8160877227783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.681547164917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.8076782226562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.0094947814941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.4635581970215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.589693069458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.5308322906494</t>
   </si>
   <si>
     <t xml:space="preserve">28.396297454834</t>
   </si>
   <si>
-    <t xml:space="preserve">28.3626594543457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.9008159637451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.0269508361816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.3801136016846</t>
+    <t xml:space="preserve">28.3626556396484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.900821685791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.026948928833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.3801116943359</t>
   </si>
   <si>
     <t xml:space="preserve">30.2966651916504</t>
   </si>
   <si>
-    <t xml:space="preserve">30.4143848419189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.8348217010498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.9020957946777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.7423362731934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.9687232971191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.0612239837646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.1789379119873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.9014587402344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.8671779632568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.1867141723633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.3885250091553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.9266815185547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.1368999481201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.8341846466064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.3471183776855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.3891620635986</t>
+    <t xml:space="preserve">30.4143905639648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.8348255157471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.9020977020264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.7423286437988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.9687252044678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.0612201690674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.1789493560791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.9014549255371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.8671836853027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.1867122650146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.3885231018066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.9266834259033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.1369037628174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.8341865539551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.3471221923828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.3891639709473</t>
   </si>
   <si>
     <t xml:space="preserve">30.1200828552246</t>
   </si>
   <si>
-    <t xml:space="preserve">30.3218955993652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.4059791564941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.5152969360352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.3555335998535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.8510036468506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.6181678771973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.2602653503418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.2858352661133</t>
+    <t xml:space="preserve">30.3218975067139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.4059772491455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.5152950286865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.355525970459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.8510074615479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.6181774139404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.2602691650391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.285831451416</t>
   </si>
   <si>
     <t xml:space="preserve">30.8567790985107</t>
   </si>
   <si>
-    <t xml:space="preserve">30.6522579193115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.6693019866943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.8226890563965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.8397369384766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.2091407775879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.3880920410156</t>
+    <t xml:space="preserve">30.6522655487061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.6693077087402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.8226928710938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.8397388458252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.2091426849365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.3880882263184</t>
   </si>
   <si>
     <t xml:space="preserve">31.0783405303955</t>
   </si>
   <si>
-    <t xml:space="preserve">30.1409664154053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.9705352783203</t>
+    <t xml:space="preserve">30.1409645080566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.9705238342285</t>
   </si>
   <si>
     <t xml:space="preserve">28.862720489502</t>
@@ -2330,64 +2330,64 @@
     <t xml:space="preserve">29.4081020355225</t>
   </si>
   <si>
-    <t xml:space="preserve">30.1068801879883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.172082901001</t>
+    <t xml:space="preserve">30.1068820953369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.1720809936523</t>
   </si>
   <si>
     <t xml:space="preserve">31.1379947662354</t>
   </si>
   <si>
-    <t xml:space="preserve">31.1465148925781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.598165512085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.2572956085205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.8312149047852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.2658176422119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.9760799407959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.206169128418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.4021625518799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.4959030151367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.5299892425537</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.9731063842773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.9645862579346</t>
+    <t xml:space="preserve">31.1465225219727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.5981597900391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.2573013305664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.8312168121338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.2658157348633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.9760837554932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.2061634063721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.4021606445312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.4958972930908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.5299835205078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.9731140136719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.9645900726318</t>
   </si>
   <si>
     <t xml:space="preserve">32.382152557373</t>
   </si>
   <si>
-    <t xml:space="preserve">32.3480644226074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.4673690795898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.450325012207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.0668487548828</t>
+    <t xml:space="preserve">32.3480567932129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.4673652648926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.4503211975098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.0668563842773</t>
   </si>
   <si>
     <t xml:space="preserve">32.0498046875</t>
@@ -2396,49 +2396,49 @@
     <t xml:space="preserve">31.8708534240723</t>
   </si>
   <si>
-    <t xml:space="preserve">31.5725994110107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.052770614624</t>
+    <t xml:space="preserve">31.5725955963135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.0527667999268</t>
   </si>
   <si>
     <t xml:space="preserve">31.5129432678223</t>
   </si>
   <si>
-    <t xml:space="preserve">31.7856407165527</t>
+    <t xml:space="preserve">31.7856369018555</t>
   </si>
   <si>
     <t xml:space="preserve">31.8623332977295</t>
   </si>
   <si>
-    <t xml:space="preserve">30.9420013427734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.7630462646484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.2402496337891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.3510360717773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.6918983459473</t>
+    <t xml:space="preserve">30.9419994354248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.7630443572998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.2402591705322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.351037979126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.6919002532959</t>
   </si>
   <si>
     <t xml:space="preserve">32.0327568054199</t>
   </si>
   <si>
-    <t xml:space="preserve">32.1520652770996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.5951881408691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.1435432434082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.8252792358398</t>
+    <t xml:space="preserve">32.1520614624023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.5951919555664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.1435356140137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.8252754211426</t>
   </si>
   <si>
     <t xml:space="preserve">32.8082313537598</t>
@@ -2447,67 +2447,67 @@
     <t xml:space="preserve">33.4899559020996</t>
   </si>
   <si>
-    <t xml:space="preserve">33.5155258178711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.4132614135742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.7882232666016</t>
+    <t xml:space="preserve">33.5155296325684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.4132652282715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.7882118225098</t>
   </si>
   <si>
     <t xml:space="preserve">33.7626495361328</t>
   </si>
   <si>
-    <t xml:space="preserve">33.8904800415039</t>
+    <t xml:space="preserve">33.8904838562012</t>
   </si>
   <si>
     <t xml:space="preserve">34.0268249511719</t>
   </si>
   <si>
-    <t xml:space="preserve">34.4188232421875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.171688079834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.2483863830566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.2057762145996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.9075164794922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.5381164550781</t>
+    <t xml:space="preserve">34.4188194274902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.1716918945312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.2483787536621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.2057800292969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.9075202941895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.5381240844727</t>
   </si>
   <si>
     <t xml:space="preserve">34.5551643371582</t>
   </si>
   <si>
-    <t xml:space="preserve">33.7541351318359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.0894470214844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.1746597290039</t>
+    <t xml:space="preserve">33.7541313171387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.0894432067871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.1746559143066</t>
   </si>
   <si>
     <t xml:space="preserve">33.8308296203613</t>
   </si>
   <si>
-    <t xml:space="preserve">33.992733001709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.3876953125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.1150131225586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.5525856018066</t>
+    <t xml:space="preserve">33.9927291870117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.3877067565918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.1150093078613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.5525779724121</t>
   </si>
   <si>
     <t xml:space="preserve">33.0638809204102</t>
@@ -2516,7 +2516,7 @@
     <t xml:space="preserve">33.2854423522949</t>
   </si>
   <si>
-    <t xml:space="preserve">32.9275283813477</t>
+    <t xml:space="preserve">32.9275321960449</t>
   </si>
   <si>
     <t xml:space="preserve">33.9586486816406</t>
@@ -2525,40 +2525,40 @@
     <t xml:space="preserve">33.6689109802246</t>
   </si>
   <si>
-    <t xml:space="preserve">34.0694274902344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.0012588500977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.9130706787109</t>
+    <t xml:space="preserve">34.0694313049316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.0012550354004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.9130668640137</t>
   </si>
   <si>
     <t xml:space="preserve">34.2995109558105</t>
   </si>
   <si>
-    <t xml:space="preserve">33.967170715332</t>
+    <t xml:space="preserve">33.9671669006348</t>
   </si>
   <si>
     <t xml:space="preserve">34.5977745056152</t>
   </si>
   <si>
-    <t xml:space="preserve">34.4784736633301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.529598236084</t>
+    <t xml:space="preserve">34.4784698486328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.5296020507812</t>
   </si>
   <si>
     <t xml:space="preserve">34.035343170166</t>
   </si>
   <si>
-    <t xml:space="preserve">34.0523872375488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.5696258544922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.6263084411621</t>
+    <t xml:space="preserve">34.0523834228516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.5696334838867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.6263046264648</t>
   </si>
   <si>
     <t xml:space="preserve">32.544059753418</t>
@@ -2567,175 +2567,175 @@
     <t xml:space="preserve">33.1064872741699</t>
   </si>
   <si>
-    <t xml:space="preserve">33.6177864074707</t>
+    <t xml:space="preserve">33.617790222168</t>
   </si>
   <si>
     <t xml:space="preserve">33.8393440246582</t>
   </si>
   <si>
-    <t xml:space="preserve">33.9160346984863</t>
+    <t xml:space="preserve">33.9160461425781</t>
   </si>
   <si>
     <t xml:space="preserve">33.3024864196777</t>
   </si>
   <si>
-    <t xml:space="preserve">33.6433448791504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.5325698852539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.5410957336426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.9360542297363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.6578140258789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.8282451629639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.3765926361084</t>
+    <t xml:space="preserve">33.6433486938477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.5325660705566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.5410919189453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.9360504150391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.6578197479248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.8282432556152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.3765983581543</t>
   </si>
   <si>
     <t xml:space="preserve">31.8112010955811</t>
   </si>
   <si>
-    <t xml:space="preserve">31.2743358612061</t>
+    <t xml:space="preserve">31.274341583252</t>
   </si>
   <si>
     <t xml:space="preserve">31.5811195373535</t>
   </si>
   <si>
-    <t xml:space="preserve">31.9305019378662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.5270118713379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.9219856262207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.1265029907227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.34250831604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.1294727325439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.1550407409668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.4106845855713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.6066780090332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.3991966247559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.1009330749512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.1891269683838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.7174644470215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.4618186950684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.9390316009521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.8964157104492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.2372817993164</t>
+    <t xml:space="preserve">31.9305000305176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.5270156860352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.9219818115234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.1264991760254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.3425178527832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.129467010498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.1550312042236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.4106922149658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.6066837310791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.3992004394531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.1009292602539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.1891212463379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.7174682617188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.4618129730225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.9390201568604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.8964176177979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.2372856140137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.2969398498535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.0725288391113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.9344329833984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.8752098083496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.7112159729004</t>
   </si>
   <si>
     <t xml:space="preserve">32.2969360351562</t>
   </si>
   <si>
-    <t xml:space="preserve">32.0725326538086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.9344310760498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.8752059936523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.7112236022949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.296932220459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.0897941589355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.3055686950684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.616283416748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.2106285095215</t>
+    <t xml:space="preserve">32.0897903442383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.3055648803711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.6162719726562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.2106246948242</t>
   </si>
   <si>
     <t xml:space="preserve">32.8579444885254</t>
   </si>
   <si>
-    <t xml:space="preserve">31.2094326019287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.6841373443604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.7445583343506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.5891933441162</t>
+    <t xml:space="preserve">31.2094345092773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.6841411590576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.7445507049561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.5891971588135</t>
   </si>
   <si>
     <t xml:space="preserve">31.5287837982178</t>
   </si>
   <si>
-    <t xml:space="preserve">30.579381942749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.0972385406494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.2871131896973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.4597320556641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.4079437255859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.9862270355225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.5731201171875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.7543792724609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.4350318908691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.9701499938965</t>
+    <t xml:space="preserve">30.5793800354004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.097240447998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.287109375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.4597358703613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.4079494476318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.9862251281738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.5731239318848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.7543754577637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.4350204467773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.9701461791992</t>
   </si>
   <si>
     <t xml:space="preserve">32.7630004882812</t>
@@ -2744,13 +2744,13 @@
     <t xml:space="preserve">32.4264030456543</t>
   </si>
   <si>
-    <t xml:space="preserve">33.0823516845703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.5903854370117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.7025871276855</t>
+    <t xml:space="preserve">33.0823440551758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.5903816223145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.7025909423828</t>
   </si>
   <si>
     <t xml:space="preserve">33.4793739318848</t>
@@ -2762,34 +2762,34 @@
     <t xml:space="preserve">33.4534797668457</t>
   </si>
   <si>
-    <t xml:space="preserve">33.8504981994629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.3856163024902</t>
+    <t xml:space="preserve">33.8505058288574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.3856239318848</t>
   </si>
   <si>
     <t xml:space="preserve">33.6778869628906</t>
   </si>
   <si>
-    <t xml:space="preserve">34.0835304260254</t>
+    <t xml:space="preserve">34.0835380554199</t>
   </si>
   <si>
     <t xml:space="preserve">34.1612167358398</t>
   </si>
   <si>
-    <t xml:space="preserve">34.5237197875977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.7999000549316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.7740173339844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.4632949829102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.2832412719727</t>
+    <t xml:space="preserve">34.5237121582031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.7999038696289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.7740135192871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.4633026123047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.2832374572754</t>
   </si>
   <si>
     <t xml:space="preserve">34.2561531066895</t>
@@ -2798,19 +2798,19 @@
     <t xml:space="preserve">33.3412742614746</t>
   </si>
   <si>
-    <t xml:space="preserve">33.9540710449219</t>
+    <t xml:space="preserve">33.9540786743164</t>
   </si>
   <si>
     <t xml:space="preserve">34.5496063232422</t>
   </si>
   <si>
-    <t xml:space="preserve">34.5409774780273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.9552612304688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.6876983642578</t>
+    <t xml:space="preserve">34.5409736633301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.9552574157715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.6876945495605</t>
   </si>
   <si>
     <t xml:space="preserve">35.0329399108887</t>
@@ -2819,127 +2819,127 @@
     <t xml:space="preserve">35.317756652832</t>
   </si>
   <si>
-    <t xml:space="preserve">35.6543655395508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.3868064880371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.8257904052734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.4731140136719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.8442459106445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36.3880004882812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.0674667358398</t>
+    <t xml:space="preserve">35.654369354248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.3868103027344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.825798034668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.4731178283691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.8442420959473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.3879928588867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.0674629211426</t>
   </si>
   <si>
     <t xml:space="preserve">33.2204437255859</t>
   </si>
   <si>
-    <t xml:space="preserve">33.349910736084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.3424644470215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.3597259521484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.3844375610352</t>
+    <t xml:space="preserve">33.3499069213867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.3424606323242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.3597297668457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.3844299316406</t>
   </si>
   <si>
     <t xml:space="preserve">33.203182220459</t>
   </si>
   <si>
-    <t xml:space="preserve">33.8677673339844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.9713287353516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.3067474365234</t>
+    <t xml:space="preserve">33.8677635192871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.9713363647461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.3067588806152</t>
   </si>
   <si>
     <t xml:space="preserve">31.77907371521</t>
   </si>
   <si>
-    <t xml:space="preserve">29.6472396850586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.1984329223633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.3910007476807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.95676612854</t>
+    <t xml:space="preserve">29.64723777771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.1984310150146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.3910064697266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.9567642211914</t>
   </si>
   <si>
     <t xml:space="preserve">28.5597400665283</t>
   </si>
   <si>
-    <t xml:space="preserve">29.4918823242188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.0356292724609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.4067649841309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.4153938293457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.1478328704834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.1835403442383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.373420715332</t>
+    <t xml:space="preserve">29.4918842315674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.0356311798096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.406759262085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.4153995513916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.147834777832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.1835441589355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.3734245300293</t>
   </si>
   <si>
     <t xml:space="preserve">33.7728271484375</t>
   </si>
   <si>
-    <t xml:space="preserve">33.263599395752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.5386047363281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.9615173339844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.9948596954346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.4954452514648</t>
+    <t xml:space="preserve">33.2635917663574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.5385932922363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.9615211486816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.9948501586914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.4954490661621</t>
   </si>
   <si>
     <t xml:space="preserve">32.2537803649902</t>
   </si>
   <si>
-    <t xml:space="preserve">31.7100315093994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.6076431274414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.2290725708008</t>
+    <t xml:space="preserve">31.710033416748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.6076507568359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.229076385498</t>
   </si>
   <si>
     <t xml:space="preserve">33.039192199707</t>
   </si>
   <si>
-    <t xml:space="preserve">32.5817527770996</t>
+    <t xml:space="preserve">32.5817489624023</t>
   </si>
   <si>
     <t xml:space="preserve">33.4966354370117</t>
@@ -2948,67 +2948,67 @@
     <t xml:space="preserve">32.9356231689453</t>
   </si>
   <si>
-    <t xml:space="preserve">33.3240089416504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.0564575195312</t>
+    <t xml:space="preserve">33.3240203857422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.056453704834</t>
   </si>
   <si>
     <t xml:space="preserve">33.7296676635742</t>
   </si>
   <si>
-    <t xml:space="preserve">35.2573471069336</t>
+    <t xml:space="preserve">35.2573356628418</t>
   </si>
   <si>
     <t xml:space="preserve">34.2388877868652</t>
   </si>
   <si>
-    <t xml:space="preserve">34.0749053955078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.9466247558594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.4201431274414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.3091239929199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.7320442199707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.9760932922363</t>
+    <t xml:space="preserve">34.0749092102051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.9466285705566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.4201393127441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.3091278076172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.732048034668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.9760856628418</t>
   </si>
   <si>
     <t xml:space="preserve">37.2165603637695</t>
   </si>
   <si>
-    <t xml:space="preserve">37.7085304260254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36.5088272094727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.7183456420898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.8231239318848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.688289642334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36.2908020019531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.958984375</t>
+    <t xml:space="preserve">37.7085266113281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.5088233947754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.7183494567871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.8231315612793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.6882858276367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.2908058166504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.9589920043945</t>
   </si>
   <si>
     <t xml:space="preserve">36.8147392272949</t>
   </si>
   <si>
-    <t xml:space="preserve">36.7623443603516</t>
+    <t xml:space="preserve">36.762336730957</t>
   </si>
   <si>
     <t xml:space="preserve">36.9719161987305</t>
@@ -3017,13 +3017,13 @@
     <t xml:space="preserve">36.0899696350098</t>
   </si>
   <si>
-    <t xml:space="preserve">36.48291015625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.7319488525391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.4961814880371</t>
+    <t xml:space="preserve">36.4829177856445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.7319450378418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.4961853027344</t>
   </si>
   <si>
     <t xml:space="preserve">35.9065933227539</t>
@@ -3032,7 +3032,7 @@
     <t xml:space="preserve">35.8280029296875</t>
   </si>
   <si>
-    <t xml:space="preserve">36.3955993652344</t>
+    <t xml:space="preserve">36.3955917358398</t>
   </si>
   <si>
     <t xml:space="preserve">36.1074295043945</t>
@@ -3041,25 +3041,25 @@
     <t xml:space="preserve">35.9939155578613</t>
   </si>
   <si>
-    <t xml:space="preserve">36.2209548950195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36.578971862793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.4001350402832</t>
+    <t xml:space="preserve">36.2209434509277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.5789680480957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.4001312255859</t>
   </si>
   <si>
     <t xml:space="preserve">35.417594909668</t>
   </si>
   <si>
-    <t xml:space="preserve">36.2820777893066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.1814880371094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.5129661560059</t>
+    <t xml:space="preserve">36.2820739746094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.1814918518066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.5129699707031</t>
   </si>
   <si>
     <t xml:space="preserve">38.6222915649414</t>
@@ -3068,58 +3068,58 @@
     <t xml:space="preserve">39.6352157592773</t>
   </si>
   <si>
-    <t xml:space="preserve">39.6526794433594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40.2901268005371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.2946662902832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.4605751037598</t>
+    <t xml:space="preserve">39.6526832580566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40.2901306152344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.2946624755859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.460578918457</t>
   </si>
   <si>
     <t xml:space="preserve">39.2160720825195</t>
   </si>
   <si>
-    <t xml:space="preserve">38.814395904541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.6614151000977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.9321174621582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40.0281677246094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40.726734161377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40.1591529846191</t>
+    <t xml:space="preserve">38.8144035339355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.6614189147949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.9321098327637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40.0281715393066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40.7267417907715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40.1591491699219</t>
   </si>
   <si>
     <t xml:space="preserve">40.1678848266602</t>
   </si>
   <si>
-    <t xml:space="preserve">40.2988700866699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.8185920715332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40.7616691589355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.0585556030273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.390380859375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.5737609863281</t>
+    <t xml:space="preserve">40.2988624572754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.8185958862305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40.7616653442383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.0585632324219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.3903846740723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.5737571716309</t>
   </si>
   <si>
     <t xml:space="preserve">42.1937408447266</t>
@@ -3128,28 +3128,28 @@
     <t xml:space="preserve">42.5779495239258</t>
   </si>
   <si>
-    <t xml:space="preserve">42.2024765014648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.6174163818359</t>
+    <t xml:space="preserve">42.2024726867676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.6174125671387</t>
   </si>
   <si>
     <t xml:space="preserve">42.0365600585938</t>
   </si>
   <si>
-    <t xml:space="preserve">41.0061721801758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.3205223083496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.3292617797852</t>
+    <t xml:space="preserve">41.0061645507812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.3205184936523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.3292579650879</t>
   </si>
   <si>
     <t xml:space="preserve">41.137149810791</t>
   </si>
   <si>
-    <t xml:space="preserve">39.8884468078613</t>
+    <t xml:space="preserve">39.8884582519531</t>
   </si>
   <si>
     <t xml:space="preserve">39.5042419433594</t>
@@ -3158,85 +3158,85 @@
     <t xml:space="preserve">40.0019721984863</t>
   </si>
   <si>
-    <t xml:space="preserve">39.050163269043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.9977684020996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.9628410339355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.1374893188477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.8929862976074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40.3425216674805</t>
+    <t xml:space="preserve">39.0501670837402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.9977722167969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.9628486633301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.1374855041504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.8929901123047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40.342529296875</t>
   </si>
   <si>
     <t xml:space="preserve">39.3557929992676</t>
   </si>
   <si>
-    <t xml:space="preserve">40.0718269348145</t>
+    <t xml:space="preserve">40.0718193054199</t>
   </si>
   <si>
     <t xml:space="preserve">39.8360595703125</t>
   </si>
   <si>
-    <t xml:space="preserve">39.5566329956055</t>
+    <t xml:space="preserve">39.5566291809082</t>
   </si>
   <si>
     <t xml:space="preserve">40.255199432373</t>
   </si>
   <si>
-    <t xml:space="preserve">40.6044960021973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.6439552307129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.8797187805176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.5915679931641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.984504699707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.2422714233398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.7532768249512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.4693069458008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.3690567016602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.4518432617188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.1636848449707</t>
+    <t xml:space="preserve">40.6044883728027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.6439514160156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.8797225952148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.5915603637695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.9845123291016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.2422752380371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.7532730102539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.469310760498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.3690605163574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.451847076416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.1636810302734</t>
   </si>
   <si>
     <t xml:space="preserve">39.416919708252</t>
   </si>
   <si>
-    <t xml:space="preserve">39.4955024719238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.058895111084</t>
+    <t xml:space="preserve">39.4955062866211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.0589027404785</t>
   </si>
   <si>
     <t xml:space="preserve">38.7358093261719</t>
   </si>
   <si>
-    <t xml:space="preserve">39.198616027832</t>
+    <t xml:space="preserve">39.1986083984375</t>
   </si>
   <si>
     <t xml:space="preserve">39.1549530029297</t>
@@ -3245,127 +3245,127 @@
     <t xml:space="preserve">39.0938262939453</t>
   </si>
   <si>
-    <t xml:space="preserve">39.2859306335449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.9715843200684</t>
+    <t xml:space="preserve">39.2859382629395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.9715728759766</t>
   </si>
   <si>
     <t xml:space="preserve">38.1944198608398</t>
   </si>
   <si>
-    <t xml:space="preserve">38.3253936767578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.5087699890137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.8535232543945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40.0106964111328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40.7878646850586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40.4822387695312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40.5346336364746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40.2639350891113</t>
+    <t xml:space="preserve">38.3253974914551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.5087661743164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.8535194396973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40.0107040405273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40.7878608703613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40.4822425842285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40.5346298217773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40.2639312744141</t>
   </si>
   <si>
     <t xml:space="preserve">41.2593994140625</t>
   </si>
   <si>
-    <t xml:space="preserve">40.7005386352539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.3030548095703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40.9799766540527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.6959991455078</t>
+    <t xml:space="preserve">40.7005424499512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.3030624389648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40.9799690246582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.6960105895996</t>
   </si>
   <si>
     <t xml:space="preserve">41.6785469055176</t>
   </si>
   <si>
-    <t xml:space="preserve">41.6698112487793</t>
+    <t xml:space="preserve">41.6698150634766</t>
   </si>
   <si>
     <t xml:space="preserve">40.9537734985352</t>
   </si>
   <si>
-    <t xml:space="preserve">40.4560394287109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.8493270874023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.3561325073242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.3383293151855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40.3687171936035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40.4385757446289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40.0980186462402</t>
+    <t xml:space="preserve">40.4560470581055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.8493309020996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.3561248779297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.3383255004883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40.3687210083008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40.4385795593262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40.0980224609375</t>
   </si>
   <si>
     <t xml:space="preserve">38.8405914306641</t>
   </si>
   <si>
-    <t xml:space="preserve">39.827335357666</t>
+    <t xml:space="preserve">39.8273315429688</t>
   </si>
   <si>
     <t xml:space="preserve">40.0892906188965</t>
   </si>
   <si>
-    <t xml:space="preserve">41.2943305969238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40.7966041564941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40.3250617980957</t>
+    <t xml:space="preserve">41.2943344116211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40.7965965270996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40.3250579833984</t>
   </si>
   <si>
     <t xml:space="preserve">40.3949127197266</t>
   </si>
   <si>
-    <t xml:space="preserve">39.7151947021484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.6912002563477</t>
+    <t xml:space="preserve">39.7151908874512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.6911964416504</t>
   </si>
   <si>
     <t xml:space="preserve">39.2120208740234</t>
   </si>
   <si>
-    <t xml:space="preserve">39.6004333496094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.9976768493652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.3973999023438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.6558876037598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.993824005127</t>
+    <t xml:space="preserve">39.6004409790039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.997673034668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.3974075317383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.655891418457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.9938163757324</t>
   </si>
   <si>
     <t xml:space="preserve">37.9055442810059</t>
@@ -3377,31 +3377,31 @@
     <t xml:space="preserve">38.541130065918</t>
   </si>
   <si>
-    <t xml:space="preserve">38.947193145752</t>
+    <t xml:space="preserve">38.9471893310547</t>
   </si>
   <si>
     <t xml:space="preserve">38.8147811889648</t>
   </si>
   <si>
-    <t xml:space="preserve">38.8589172363281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.5209846496582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.3469161987305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.1855430603027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.85009765625</t>
+    <t xml:space="preserve">38.8589210510254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.5209922790527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.3469200134277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.1855392456055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.8500938415527</t>
   </si>
   <si>
     <t xml:space="preserve">39.2561645507812</t>
   </si>
   <si>
-    <t xml:space="preserve">39.0972633361816</t>
+    <t xml:space="preserve">39.0972595214844</t>
   </si>
   <si>
     <t xml:space="preserve">39.4768524169922</t>
@@ -3416,52 +3416,52 @@
     <t xml:space="preserve">39.8652610778809</t>
   </si>
   <si>
-    <t xml:space="preserve">38.4528579711914</t>
+    <t xml:space="preserve">38.4528541564941</t>
   </si>
   <si>
     <t xml:space="preserve">37.0051345825195</t>
   </si>
   <si>
-    <t xml:space="preserve">37.773136138916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.8172721862793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.8349266052246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.5058174133301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.6823692321777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.5499534606934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.5852699279785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.4175415039062</t>
+    <t xml:space="preserve">37.7731323242188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.817268371582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.8349227905273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.5058097839355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.682373046875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.5499610900879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.585262298584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.4175453186035</t>
   </si>
   <si>
     <t xml:space="preserve">37.5612678527832</t>
   </si>
   <si>
-    <t xml:space="preserve">37.649543762207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.8967170715332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.4465103149414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.5259552001953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.5171318054199</t>
+    <t xml:space="preserve">37.6495513916016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.8967208862305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.4465141296387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.5259628295898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.5171279907227</t>
   </si>
   <si>
     <t xml:space="preserve">37.1905174255371</t>
@@ -3473,13 +3473,13 @@
     <t xml:space="preserve">38.3822326660156</t>
   </si>
   <si>
-    <t xml:space="preserve">38.9030570983887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.7882957458496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.3557548522949</t>
+    <t xml:space="preserve">38.9030609130859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.7882995605469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.3557510375977</t>
   </si>
   <si>
     <t xml:space="preserve">39.618091583252</t>
@@ -3488,40 +3488,40 @@
     <t xml:space="preserve">40.0771217346191</t>
   </si>
   <si>
-    <t xml:space="preserve">40.2360191345215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.944709777832</t>
+    <t xml:space="preserve">40.2360229492188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.9447059631348</t>
   </si>
   <si>
     <t xml:space="preserve">39.9800224304199</t>
   </si>
   <si>
-    <t xml:space="preserve">39.5827827453613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.061954498291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.8412704467773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.6117477416992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.6647109985352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.3582382202148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.4729957580566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.84375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.7819519042969</t>
+    <t xml:space="preserve">39.5827789306641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.0619583129883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.8412666320801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.6117515563965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.6647148132324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.3582344055176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.4729995727539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.8437538146973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.7819595336914</t>
   </si>
   <si>
     <t xml:space="preserve">37.1993370056152</t>
@@ -3530,25 +3530,25 @@
     <t xml:space="preserve">37.4641609191895</t>
   </si>
   <si>
-    <t xml:space="preserve">37.6672019958496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.9673385620117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.5764427185059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.2674751281738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.5298194885254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.8564376831055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.1325759887695</t>
+    <t xml:space="preserve">37.6671981811523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.9673347473145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.5764389038086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.2674789428711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.5298156738281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.8564338684082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.1325798034668</t>
   </si>
   <si>
     <t xml:space="preserve">39.8387794494629</t>
@@ -3557,10 +3557,10 @@
     <t xml:space="preserve">39.3091278076172</t>
   </si>
   <si>
-    <t xml:space="preserve">39.9182281494141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.6710624694824</t>
+    <t xml:space="preserve">39.9182319641113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.6710586547852</t>
   </si>
   <si>
     <t xml:space="preserve">39.6622314453125</t>
@@ -3572,10 +3572,10 @@
     <t xml:space="preserve">39.9093971252441</t>
   </si>
   <si>
-    <t xml:space="preserve">40.1477470397949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.8917465209961</t>
+    <t xml:space="preserve">40.1477432250977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.8917427062988</t>
   </si>
   <si>
     <t xml:space="preserve">39.8740882873535</t>
@@ -3584,22 +3584,22 @@
     <t xml:space="preserve">40.2889823913574</t>
   </si>
   <si>
-    <t xml:space="preserve">40.4920234680176</t>
+    <t xml:space="preserve">40.4920120239258</t>
   </si>
   <si>
     <t xml:space="preserve">41.3836059570312</t>
   </si>
   <si>
-    <t xml:space="preserve">40.7480239868164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40.5361518859863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40.1300888061523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40.0506439208984</t>
+    <t xml:space="preserve">40.7480201721191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40.5361557006836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40.1300849914551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40.0506401062012</t>
   </si>
   <si>
     <t xml:space="preserve">40.2183647155762</t>
@@ -3608,19 +3608,19 @@
     <t xml:space="preserve">40.2007102966309</t>
   </si>
   <si>
-    <t xml:space="preserve">40.3596076965332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40.5096778869629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40.5626373291016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.6042900085449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.5071907043457</t>
+    <t xml:space="preserve">40.3596000671387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40.5096702575684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40.5626411437988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.6042938232422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.507194519043</t>
   </si>
   <si>
     <t xml:space="preserve">41.0834693908691</t>
@@ -3629,19 +3629,19 @@
     <t xml:space="preserve">41.0128479003906</t>
   </si>
   <si>
-    <t xml:space="preserve">40.7568473815918</t>
+    <t xml:space="preserve">40.7568435668945</t>
   </si>
   <si>
     <t xml:space="preserve">40.6509132385254</t>
   </si>
   <si>
-    <t xml:space="preserve">40.3684310913086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40.4655380249023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40.4302253723145</t>
+    <t xml:space="preserve">40.3684272766113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40.4655418395996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40.4302291870117</t>
   </si>
   <si>
     <t xml:space="preserve">40.4831924438477</t>
@@ -3650,22 +3650,22 @@
     <t xml:space="preserve">39.7416801452637</t>
   </si>
   <si>
-    <t xml:space="preserve">39.5474739074707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.6470565795898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.5676116943359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.8942375183105</t>
+    <t xml:space="preserve">39.5474662780762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.6470527648926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.5676193237305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.8942337036133</t>
   </si>
   <si>
     <t xml:space="preserve">39.0178184509277</t>
   </si>
   <si>
-    <t xml:space="preserve">39.6975364685059</t>
+    <t xml:space="preserve">39.6975402832031</t>
   </si>
   <si>
     <t xml:space="preserve">40.0065040588379</t>
@@ -3680,49 +3680,49 @@
     <t xml:space="preserve">41.128662109375</t>
   </si>
   <si>
-    <t xml:space="preserve">41.378791809082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.0393218994141</t>
+    <t xml:space="preserve">41.3787879943848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.0393257141113</t>
   </si>
   <si>
     <t xml:space="preserve">40.485466003418</t>
   </si>
   <si>
-    <t xml:space="preserve">40.905330657959</t>
+    <t xml:space="preserve">40.9053344726562</t>
   </si>
   <si>
     <t xml:space="preserve">40.6373329162598</t>
   </si>
   <si>
-    <t xml:space="preserve">40.6016006469727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40.4050674438477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40.860668182373</t>
+    <t xml:space="preserve">40.6016044616699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40.4050750732422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40.8606605529785</t>
   </si>
   <si>
     <t xml:space="preserve">41.2001266479492</t>
   </si>
   <si>
-    <t xml:space="preserve">41.9505195617676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.289981842041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.7009086608887</t>
+    <t xml:space="preserve">41.9505233764648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.2899856567383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.7009162902832</t>
   </si>
   <si>
     <t xml:space="preserve">42.3167839050293</t>
   </si>
   <si>
-    <t xml:space="preserve">42.531177520752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.6205101013184</t>
+    <t xml:space="preserve">42.5311851501465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.6205139160156</t>
   </si>
   <si>
     <t xml:space="preserve">42.852783203125</t>
@@ -3734,16 +3734,16 @@
     <t xml:space="preserve">43.3262405395508</t>
   </si>
   <si>
-    <t xml:space="preserve">43.0314407348633</t>
+    <t xml:space="preserve">43.0314445495605</t>
   </si>
   <si>
     <t xml:space="preserve">42.951042175293</t>
   </si>
   <si>
-    <t xml:space="preserve">42.4865226745605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43.102912902832</t>
+    <t xml:space="preserve">42.486515045166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43.1029052734375</t>
   </si>
   <si>
     <t xml:space="preserve">43.120777130127</t>
@@ -3752,28 +3752,28 @@
     <t xml:space="preserve">43.2637023925781</t>
   </si>
   <si>
-    <t xml:space="preserve">43.254768371582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43.0582389831543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43.5406379699707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43.4780960083008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43.4602432250977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">44.755558013916</t>
+    <t xml:space="preserve">43.2547721862793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43.0582427978516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43.540641784668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43.478099822998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43.4602394104004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44.7555541992188</t>
   </si>
   <si>
     <t xml:space="preserve">46.2206153869629</t>
   </si>
   <si>
-    <t xml:space="preserve">44.8448905944824</t>
+    <t xml:space="preserve">44.8448944091797</t>
   </si>
   <si>
     <t xml:space="preserve">46.9888725280762</t>
@@ -3782,16 +3782,16 @@
     <t xml:space="preserve">46.2563438415527</t>
   </si>
   <si>
-    <t xml:space="preserve">45.8811454772949</t>
+    <t xml:space="preserve">45.8811492919922</t>
   </si>
   <si>
     <t xml:space="preserve">45.1307525634766</t>
   </si>
   <si>
-    <t xml:space="preserve">45.148624420166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">44.6304893493652</t>
+    <t xml:space="preserve">45.1486206054688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44.6304931640625</t>
   </si>
   <si>
     <t xml:space="preserve">44.478630065918</t>
@@ -3800,10 +3800,10 @@
     <t xml:space="preserve">45.2200889587402</t>
   </si>
   <si>
-    <t xml:space="preserve">45.3272819519043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.7739524841309</t>
+    <t xml:space="preserve">45.3272895812988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.7739486694336</t>
   </si>
   <si>
     <t xml:space="preserve">45.2915534973145</t>
@@ -3815,37 +3815,37 @@
     <t xml:space="preserve">46.4528732299805</t>
   </si>
   <si>
-    <t xml:space="preserve">45.9883499145508</t>
+    <t xml:space="preserve">45.9883460998535</t>
   </si>
   <si>
     <t xml:space="preserve">46.6136703491211</t>
   </si>
   <si>
-    <t xml:space="preserve">47.0424728393555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">47.614200592041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">48.1501884460449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">48.060863494873</t>
+    <t xml:space="preserve">47.0424690246582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">47.6141967773438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">48.1501922607422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">48.0608596801758</t>
   </si>
   <si>
     <t xml:space="preserve">49.0792503356934</t>
   </si>
   <si>
-    <t xml:space="preserve">49.0435218811035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50.1869735717773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50.4192314147949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50.7765693664551</t>
+    <t xml:space="preserve">49.0435256958008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50.1869697570801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50.4192352294922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50.7765655517578</t>
   </si>
   <si>
     <t xml:space="preserve">51.0624313354492</t>
@@ -3854,10 +3854,10 @@
     <t xml:space="preserve">50.5085678100586</t>
   </si>
   <si>
-    <t xml:space="preserve">50.7944374084473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50.9730949401855</t>
+    <t xml:space="preserve">50.7944297790527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50.9731025695801</t>
   </si>
   <si>
     <t xml:space="preserve">51.3125610351562</t>
@@ -3866,13 +3866,13 @@
     <t xml:space="preserve">50.6693687438965</t>
   </si>
   <si>
-    <t xml:space="preserve">49.9904441833496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">49.5795135498047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50.1512451171875</t>
+    <t xml:space="preserve">49.9904403686523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">49.5795097351074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50.1512413024902</t>
   </si>
   <si>
     <t xml:space="preserve">49.9011077880859</t>
@@ -3887,22 +3887,22 @@
     <t xml:space="preserve">49.5437774658203</t>
   </si>
   <si>
-    <t xml:space="preserve">49.9547080993652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">48.8291168212891</t>
+    <t xml:space="preserve">49.9547004699707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">48.8291130065918</t>
   </si>
   <si>
     <t xml:space="preserve">48.1144599914551</t>
   </si>
   <si>
-    <t xml:space="preserve">47.2568702697754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.9531364440918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.8816719055176</t>
+    <t xml:space="preserve">47.2568740844727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.9531402587891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.8816680908203</t>
   </si>
   <si>
     <t xml:space="preserve">45.6488838195801</t>
@@ -3911,7 +3911,7 @@
     <t xml:space="preserve">46.3278121948242</t>
   </si>
   <si>
-    <t xml:space="preserve">45.202220916748</t>
+    <t xml:space="preserve">45.2022285461426</t>
   </si>
   <si>
     <t xml:space="preserve">44.6840934753418</t>
@@ -3920,19 +3920,19 @@
     <t xml:space="preserve">45.613151550293</t>
   </si>
   <si>
-    <t xml:space="preserve">45.1843566894531</t>
+    <t xml:space="preserve">45.1843528747559</t>
   </si>
   <si>
     <t xml:space="preserve">45.7203483581543</t>
   </si>
   <si>
-    <t xml:space="preserve">45.4344902038574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43.7014350891113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43.7639694213867</t>
+    <t xml:space="preserve">45.4344825744629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43.7014312744141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43.7639770507812</t>
   </si>
   <si>
     <t xml:space="preserve">44.9163589477539</t>
@@ -3944,49 +3944,49 @@
     <t xml:space="preserve">43.6925010681152</t>
   </si>
   <si>
-    <t xml:space="preserve">43.9426345825195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43.7461013793945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43.6746368408203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">44.1391677856445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">44.2731666564941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.4166221618652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.6846160888672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.6310157775879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.9168815612793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.1848793029785</t>
+    <t xml:space="preserve">43.9426307678223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43.7461051940918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43.674633026123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44.1391639709473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44.2731628417969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.416618347168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.6846199035645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.6310195922852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.916877746582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.1848754882812</t>
   </si>
   <si>
     <t xml:space="preserve">46.4886093139648</t>
   </si>
   <si>
-    <t xml:space="preserve">47.0960731506348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.828067779541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">47.221134185791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">48.3467216491699</t>
+    <t xml:space="preserve">47.0960693359375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.8280715942383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">47.2211265563965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">48.3467178344727</t>
   </si>
   <si>
     <t xml:space="preserve">49.2043190002441</t>
@@ -4001,70 +4001,70 @@
     <t xml:space="preserve">50.329906463623</t>
   </si>
   <si>
-    <t xml:space="preserve">50.0261764526367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50.2227096557617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50.4371070861816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">51.0802993774414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50.6515083312988</t>
+    <t xml:space="preserve">50.0261726379395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50.2227058410645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50.4371032714844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">51.0802917480469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50.6515007019043</t>
   </si>
   <si>
     <t xml:space="preserve">50.1155014038086</t>
   </si>
   <si>
-    <t xml:space="preserve">49.1685829162598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50.4907035827637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50.7522125244141</t>
+    <t xml:space="preserve">49.1685752868652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50.4907073974609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50.7522163391113</t>
   </si>
   <si>
     <t xml:space="preserve">49.9586563110352</t>
   </si>
   <si>
-    <t xml:space="preserve">50.1209754943848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50.4997253417969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">49.3815116882324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">49.5618667602539</t>
+    <t xml:space="preserve">50.120979309082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50.4997215270996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">49.3815155029297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">49.5618705749512</t>
   </si>
   <si>
     <t xml:space="preserve">49.9947242736816</t>
   </si>
   <si>
-    <t xml:space="preserve">49.6159782409668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">48.443660736084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">48.191162109375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">48.5338401794434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">49.832405090332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">48.6420440673828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">48.6240158081055</t>
+    <t xml:space="preserve">49.6159744262695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">48.4436645507812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">48.1911582946777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">48.5338363647461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">49.8323974609375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">48.6420516967773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">48.6240119934082</t>
   </si>
   <si>
     <t xml:space="preserve">48.2993774414062</t>
@@ -4073,55 +4073,55 @@
     <t xml:space="preserve">49.0027656555176</t>
   </si>
   <si>
-    <t xml:space="preserve">48.2092018127441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">49.4716949462891</t>
+    <t xml:space="preserve">48.2091979980469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">49.4716911315918</t>
   </si>
   <si>
     <t xml:space="preserve">49.7602615356445</t>
   </si>
   <si>
-    <t xml:space="preserve">50.0668716430664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50.1029357910156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50.9686470031738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50.2832984924316</t>
+    <t xml:space="preserve">50.0668678283691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50.1029396057129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50.9686508178711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50.2832946777344</t>
   </si>
   <si>
     <t xml:space="preserve">50.4456176757812</t>
   </si>
   <si>
-    <t xml:space="preserve">50.8243675231934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50.9866828918457</t>
+    <t xml:space="preserve">50.8243637084961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50.986686706543</t>
   </si>
   <si>
     <t xml:space="preserve">50.9506149291992</t>
   </si>
   <si>
-    <t xml:space="preserve">50.084903717041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">49.2552604675293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">49.291332244873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">49.020809173584</t>
+    <t xml:space="preserve">50.0849075317383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">49.2552642822266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">49.2913360595703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">49.0208015441895</t>
   </si>
   <si>
     <t xml:space="preserve">48.7683029174805</t>
   </si>
   <si>
-    <t xml:space="preserve">49.1290168762207</t>
+    <t xml:space="preserve">49.1290130615234</t>
   </si>
   <si>
     <t xml:space="preserve">49.5257987976074</t>
@@ -4130,28 +4130,28 @@
     <t xml:space="preserve">48.3174133300781</t>
   </si>
   <si>
-    <t xml:space="preserve">47.0909957885742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.1711730957031</t>
+    <t xml:space="preserve">47.090991973877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.1711692810059</t>
   </si>
   <si>
     <t xml:space="preserve">46.8925971984863</t>
   </si>
   <si>
-    <t xml:space="preserve">46.4417152404785</t>
+    <t xml:space="preserve">46.441707611084</t>
   </si>
   <si>
     <t xml:space="preserve">45.5579605102539</t>
   </si>
   <si>
-    <t xml:space="preserve">45.0439453125</t>
+    <t xml:space="preserve">45.0439414978027</t>
   </si>
   <si>
     <t xml:space="preserve">44.6201095581055</t>
   </si>
   <si>
-    <t xml:space="preserve">44.647159576416</t>
+    <t xml:space="preserve">44.6471633911133</t>
   </si>
   <si>
     <t xml:space="preserve">44.6742210388184</t>
@@ -4160,22 +4160,22 @@
     <t xml:space="preserve">44.8726081848145</t>
   </si>
   <si>
-    <t xml:space="preserve">45.0529594421387</t>
+    <t xml:space="preserve">45.0529632568359</t>
   </si>
   <si>
     <t xml:space="preserve">43.7724380493164</t>
   </si>
   <si>
-    <t xml:space="preserve">42.6993141174316</t>
+    <t xml:space="preserve">42.6993179321289</t>
   </si>
   <si>
     <t xml:space="preserve">42.3025321960449</t>
   </si>
   <si>
-    <t xml:space="preserve">41.5630760192871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.9778938293457</t>
+    <t xml:space="preserve">41.5630722045898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.977897644043</t>
   </si>
   <si>
     <t xml:space="preserve">41.3015594482422</t>
@@ -4184,67 +4184,67 @@
     <t xml:space="preserve">40.940845489502</t>
   </si>
   <si>
-    <t xml:space="preserve">40.3817443847656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.2564659118652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.0400314331055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.3105773925781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.6622657775879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.5811157226562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.7434310913086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.5720901489258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.0921897888184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40.2645149230957</t>
+    <t xml:space="preserve">40.3817405700684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.2564697265625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.0400428771973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.3105812072754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.6622734069824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.5811080932617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.7434349060059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.572093963623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.0921974182129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40.2645111083984</t>
   </si>
   <si>
     <t xml:space="preserve">39.4619255065918</t>
   </si>
   <si>
-    <t xml:space="preserve">38.2715759277344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.929874420166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.6232681274414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.9198837280273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.7395286560059</t>
+    <t xml:space="preserve">38.2715797424316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.9298782348633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.6232757568359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.9198760986328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.7395210266113</t>
   </si>
   <si>
     <t xml:space="preserve">36.3868522644043</t>
   </si>
   <si>
-    <t xml:space="preserve">39.8947830200195</t>
+    <t xml:space="preserve">39.8947792053223</t>
   </si>
   <si>
     <t xml:space="preserve">38.7946090698242</t>
   </si>
   <si>
-    <t xml:space="preserve">39.2545166015625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40.3997802734375</t>
+    <t xml:space="preserve">39.2545127868652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40.399772644043</t>
   </si>
   <si>
     <t xml:space="preserve">39.8496932983398</t>
@@ -4253,22 +4253,22 @@
     <t xml:space="preserve">40.967903137207</t>
   </si>
   <si>
-    <t xml:space="preserve">41.1753082275391</t>
+    <t xml:space="preserve">41.1753120422363</t>
   </si>
   <si>
     <t xml:space="preserve">41.1662940979004</t>
   </si>
   <si>
-    <t xml:space="preserve">41.2294158935547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.6261978149414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.3646850585938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40.9588813781738</t>
+    <t xml:space="preserve">41.229419708252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.6262016296387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.3646812438965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40.9588851928711</t>
   </si>
   <si>
     <t xml:space="preserve">40.5891494750977</t>
@@ -4277,58 +4277,58 @@
     <t xml:space="preserve">42.3566398620605</t>
   </si>
   <si>
-    <t xml:space="preserve">42.2754821777344</t>
+    <t xml:space="preserve">42.2754859924316</t>
   </si>
   <si>
     <t xml:space="preserve">41.1572723388672</t>
   </si>
   <si>
-    <t xml:space="preserve">42.5911064147949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">44.079044342041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43.087085723877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">44.2954711914062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">44.376636505127</t>
+    <t xml:space="preserve">42.5911102294922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44.0790481567383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43.0870819091797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44.295467376709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44.3766326904297</t>
   </si>
   <si>
     <t xml:space="preserve">43.8445816040039</t>
   </si>
   <si>
-    <t xml:space="preserve">42.9969100952148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43.3846702575684</t>
+    <t xml:space="preserve">42.9969062805176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43.3846740722656</t>
   </si>
   <si>
     <t xml:space="preserve">43.4568138122559</t>
   </si>
   <si>
-    <t xml:space="preserve">43.4117279052734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43.9167213439941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43.1772613525391</t>
+    <t xml:space="preserve">43.4117240905762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43.9167289733887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43.1772651672363</t>
   </si>
   <si>
     <t xml:space="preserve">41.7163772583008</t>
   </si>
   <si>
-    <t xml:space="preserve">41.1843299865723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40.5350456237793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40.3366508483887</t>
+    <t xml:space="preserve">41.184326171875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40.5350494384766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40.3366470336914</t>
   </si>
   <si>
     <t xml:space="preserve">41.472900390625</t>
@@ -4340,64 +4340,64 @@
     <t xml:space="preserve">39.1282653808594</t>
   </si>
   <si>
-    <t xml:space="preserve">38.6322822570801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.973991394043</t>
+    <t xml:space="preserve">38.6322937011719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.9739837646484</t>
   </si>
   <si>
     <t xml:space="preserve">37.3697929382324</t>
   </si>
   <si>
-    <t xml:space="preserve">38.2445182800293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.8838081359863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.9810523986816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.2796173095703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.7214851379395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.7575607299805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.2976531982422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.4329147338867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.3797950744629</t>
+    <t xml:space="preserve">38.2445259094238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.8838005065918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.9810600280762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.279613494873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.7214889526367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.7575569152832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.2976493835449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.4329109191895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.3797874450684</t>
   </si>
   <si>
     <t xml:space="preserve">38.690559387207</t>
   </si>
   <si>
-    <t xml:space="preserve">37.9319229125977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.8222351074219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.2152633666992</t>
+    <t xml:space="preserve">37.9319190979004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.8222389221191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.215259552002</t>
   </si>
   <si>
     <t xml:space="preserve">38.4711952209473</t>
   </si>
   <si>
-    <t xml:space="preserve">39.111011505127</t>
+    <t xml:space="preserve">39.1110076904297</t>
   </si>
   <si>
     <t xml:space="preserve">38.0964431762695</t>
   </si>
   <si>
-    <t xml:space="preserve">37.255542755127</t>
+    <t xml:space="preserve">37.2555351257324</t>
   </si>
   <si>
     <t xml:space="preserve">37.2189826965332</t>
@@ -4412,31 +4412,31 @@
     <t xml:space="preserve">35.8662300109863</t>
   </si>
   <si>
-    <t xml:space="preserve">36.0673065185547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.4092178344727</t>
+    <t xml:space="preserve">36.0673141479492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.4092140197754</t>
   </si>
   <si>
     <t xml:space="preserve">33.8462409973145</t>
   </si>
   <si>
-    <t xml:space="preserve">34.3398094177246</t>
+    <t xml:space="preserve">34.3398132324219</t>
   </si>
   <si>
     <t xml:space="preserve">34.3489532470703</t>
   </si>
   <si>
-    <t xml:space="preserve">34.5683135986328</t>
+    <t xml:space="preserve">34.5683212280273</t>
   </si>
   <si>
     <t xml:space="preserve">34.4769134521484</t>
   </si>
   <si>
-    <t xml:space="preserve">35.6651420593262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36.0490303039551</t>
+    <t xml:space="preserve">35.6651458740234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.0490341186523</t>
   </si>
   <si>
     <t xml:space="preserve">34.8242454528809</t>
@@ -4445,10 +4445,10 @@
     <t xml:space="preserve">34.284969329834</t>
   </si>
   <si>
-    <t xml:space="preserve">35.5463218688965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.2609672546387</t>
+    <t xml:space="preserve">35.5463180541992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.2609634399414</t>
   </si>
   <si>
     <t xml:space="preserve">37.5754470825195</t>
@@ -4460,16 +4460,16 @@
     <t xml:space="preserve">37.9044952392578</t>
   </si>
   <si>
-    <t xml:space="preserve">37.9410552978516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.3395118713379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.321231842041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.2206878662109</t>
+    <t xml:space="preserve">37.9410514831543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.3395080566406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.3212356567383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.2206916809082</t>
   </si>
   <si>
     <t xml:space="preserve">39.5223159790039</t>
@@ -4481,43 +4481,43 @@
     <t xml:space="preserve">39.7782440185547</t>
   </si>
   <si>
-    <t xml:space="preserve">40.0433158874512</t>
+    <t xml:space="preserve">40.0433082580566</t>
   </si>
   <si>
     <t xml:space="preserve">39.4766120910645</t>
   </si>
   <si>
-    <t xml:space="preserve">39.3029479980469</t>
+    <t xml:space="preserve">39.3029518127441</t>
   </si>
   <si>
     <t xml:space="preserve">38.5351753234863</t>
   </si>
   <si>
-    <t xml:space="preserve">39.2846755981445</t>
+    <t xml:space="preserve">39.2846717834473</t>
   </si>
   <si>
     <t xml:space="preserve">39.440055847168</t>
   </si>
   <si>
-    <t xml:space="preserve">39.6776962280273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.8605041503906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.2115478515625</t>
+    <t xml:space="preserve">39.6777000427246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.8605003356934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.2115516662598</t>
   </si>
   <si>
     <t xml:space="preserve">39.1658477783203</t>
   </si>
   <si>
-    <t xml:space="preserve">38.8185234069824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.5625877380371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.1147270202637</t>
+    <t xml:space="preserve">38.8185195922852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.5625915527344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.1147193908691</t>
   </si>
   <si>
     <t xml:space="preserve">39.5131759643555</t>
@@ -4526,52 +4526,52 @@
     <t xml:space="preserve">39.0104637145996</t>
   </si>
   <si>
-    <t xml:space="preserve">39.6137199401855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.7965240478516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.727108001709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.6174354553223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.0872993469238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.0835838317871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.1567039489746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.6357154846191</t>
+    <t xml:space="preserve">39.6137161254883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.7965202331543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.7271156311035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.6174392700195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.0873031616211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.0835876464844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.1567115783691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.6357116699219</t>
   </si>
   <si>
     <t xml:space="preserve">38.6631355285645</t>
   </si>
   <si>
-    <t xml:space="preserve">38.4437675476074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.7636756896973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.5680236816406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40.2261161804199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.8787841796875</t>
+    <t xml:space="preserve">38.4437713623047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.7636795043945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.5680198669434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40.2261123657227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.8787879943848</t>
   </si>
   <si>
     <t xml:space="preserve">40.4454803466797</t>
   </si>
   <si>
-    <t xml:space="preserve">39.8330841064453</t>
+    <t xml:space="preserve">39.8330879211426</t>
   </si>
   <si>
     <t xml:space="preserve">38.4986114501953</t>
@@ -4580,16 +4580,16 @@
     <t xml:space="preserve">37.5480308532715</t>
   </si>
   <si>
-    <t xml:space="preserve">37.0361785888672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.2372589111328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.1915550231934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.8313789367676</t>
+    <t xml:space="preserve">37.0361747741699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.2372627258301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.1915588378906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.8313751220703</t>
   </si>
   <si>
     <t xml:space="preserve">36.7619705200195</t>
@@ -4598,13 +4598,13 @@
     <t xml:space="preserve">37.3743667602539</t>
   </si>
   <si>
-    <t xml:space="preserve">37.0087547302246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.4657669067383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.1367263793945</t>
+    <t xml:space="preserve">37.0087623596191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.4657707214355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.1367225646973</t>
   </si>
   <si>
     <t xml:space="preserve">37.5937309265137</t>
@@ -4613,19 +4613,19 @@
     <t xml:space="preserve">37.0453147888184</t>
   </si>
   <si>
-    <t xml:space="preserve">36.652286529541</t>
+    <t xml:space="preserve">36.6522903442383</t>
   </si>
   <si>
     <t xml:space="preserve">36.7071266174316</t>
   </si>
   <si>
-    <t xml:space="preserve">36.3415184020996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36.1769981384277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.6468696594238</t>
+    <t xml:space="preserve">36.3415222167969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.1769943237305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.6468620300293</t>
   </si>
   <si>
     <t xml:space="preserve">35.6011619567871</t>
@@ -4640,19 +4640,19 @@
     <t xml:space="preserve">34.0930213928223</t>
   </si>
   <si>
-    <t xml:space="preserve">33.5811767578125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.4494895935059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.1532897949219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.9961929321289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.2649841308594</t>
+    <t xml:space="preserve">33.5811729431152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.4494934082031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.1532936096191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.9962005615234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.2649803161621</t>
   </si>
   <si>
     <t xml:space="preserve">32.3198204040527</t>
@@ -4664,10 +4664,10 @@
     <t xml:space="preserve">32.4752044677734</t>
   </si>
   <si>
-    <t xml:space="preserve">32.3929481506348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.4257888793945</t>
+    <t xml:space="preserve">32.3929405212402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.4257926940918</t>
   </si>
   <si>
     <t xml:space="preserve">33.6360092163086</t>
@@ -4676,16 +4676,16 @@
     <t xml:space="preserve">33.654296875</t>
   </si>
   <si>
-    <t xml:space="preserve">32.8590965270996</t>
+    <t xml:space="preserve">32.8590927124023</t>
   </si>
   <si>
     <t xml:space="preserve">32.9596405029297</t>
   </si>
   <si>
-    <t xml:space="preserve">32.4020881652832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.5171890258789</t>
+    <t xml:space="preserve">32.4020843505859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.5171928405762</t>
   </si>
   <si>
     <t xml:space="preserve">34.6688613891602</t>
@@ -4694,25 +4694,25 @@
     <t xml:space="preserve">34.732837677002</t>
   </si>
   <si>
-    <t xml:space="preserve">34.4586334228516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.0710296630859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.7602653503418</t>
+    <t xml:space="preserve">34.4586372375488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.0710258483887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.7602615356445</t>
   </si>
   <si>
     <t xml:space="preserve">34.8059577941895</t>
   </si>
   <si>
-    <t xml:space="preserve">35.1624374389648</t>
+    <t xml:space="preserve">35.162425994873</t>
   </si>
   <si>
     <t xml:space="preserve">34.6048774719238</t>
   </si>
   <si>
-    <t xml:space="preserve">35.1715698242188</t>
+    <t xml:space="preserve">35.1715660095215</t>
   </si>
   <si>
     <t xml:space="preserve">34.6140174865723</t>
@@ -4730,13 +4730,13 @@
     <t xml:space="preserve">37.2463989257812</t>
   </si>
   <si>
-    <t xml:space="preserve">36.8168106079102</t>
+    <t xml:space="preserve">36.8168067932129</t>
   </si>
   <si>
     <t xml:space="preserve">36.4055023193359</t>
   </si>
   <si>
-    <t xml:space="preserve">35.9393501281738</t>
+    <t xml:space="preserve">35.9393463134766</t>
   </si>
   <si>
     <t xml:space="preserve">35.8296699523926</t>
@@ -4748,46 +4748,46 @@
     <t xml:space="preserve">36.2152328491211</t>
   </si>
   <si>
-    <t xml:space="preserve">35.7981109619141</t>
+    <t xml:space="preserve">35.7981147766113</t>
   </si>
   <si>
     <t xml:space="preserve">36.2893905639648</t>
   </si>
   <si>
-    <t xml:space="preserve">37.2626686096191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.2904739379883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.2533988952637</t>
+    <t xml:space="preserve">37.2626647949219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.2904777526855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.2533950805664</t>
   </si>
   <si>
     <t xml:space="preserve">37.0865478515625</t>
   </si>
   <si>
-    <t xml:space="preserve">37.6705207824707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.5603713989258</t>
+    <t xml:space="preserve">37.6705169677734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.5603675842285</t>
   </si>
   <si>
     <t xml:space="preserve">38.4584159851074</t>
   </si>
   <si>
-    <t xml:space="preserve">38.3749847412109</t>
+    <t xml:space="preserve">38.3749923706055</t>
   </si>
   <si>
     <t xml:space="preserve">37.4665908813477</t>
   </si>
   <si>
-    <t xml:space="preserve">37.5407485961914</t>
+    <t xml:space="preserve">37.5407447814941</t>
   </si>
   <si>
     <t xml:space="preserve">37.8559036254883</t>
   </si>
   <si>
-    <t xml:space="preserve">38.8291854858398</t>
+    <t xml:space="preserve">38.8291816711426</t>
   </si>
   <si>
     <t xml:space="preserve">38.8199195861816</t>
@@ -4805,28 +4805,28 @@
     <t xml:space="preserve">36.3542747497559</t>
   </si>
   <si>
-    <t xml:space="preserve">35.6590805053711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36.317195892334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.9000816345215</t>
+    <t xml:space="preserve">35.6590728759766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.3171997070312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.900074005127</t>
   </si>
   <si>
     <t xml:space="preserve">36.2615814208984</t>
   </si>
   <si>
-    <t xml:space="preserve">35.8073844909668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36.1966896057129</t>
+    <t xml:space="preserve">35.8073883056641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.1967010498047</t>
   </si>
   <si>
     <t xml:space="preserve">36.7713928222656</t>
   </si>
   <si>
-    <t xml:space="preserve">35.9186210632324</t>
+    <t xml:space="preserve">35.9186172485352</t>
   </si>
   <si>
     <t xml:space="preserve">35.9835014343262</t>
@@ -4835,13 +4835,13 @@
     <t xml:space="preserve">36.0761909484863</t>
   </si>
   <si>
-    <t xml:space="preserve">35.5941925048828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.8537292480469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36.4655075073242</t>
+    <t xml:space="preserve">35.5941886901855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.8537330627441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.465503692627</t>
   </si>
   <si>
     <t xml:space="preserve">36.187427520752</t>
@@ -4850,34 +4850,34 @@
     <t xml:space="preserve">35.9649620056152</t>
   </si>
   <si>
-    <t xml:space="preserve">36.5118560791016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.2348594665527</t>
+    <t xml:space="preserve">36.5118522644043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.2348556518555</t>
   </si>
   <si>
     <t xml:space="preserve">37.151439666748</t>
   </si>
   <si>
-    <t xml:space="preserve">38.7921104431152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.1536102294922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.4027938842773</t>
+    <t xml:space="preserve">38.792106628418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.1536140441895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.4027900695801</t>
   </si>
   <si>
     <t xml:space="preserve">38.2915649414062</t>
   </si>
   <si>
-    <t xml:space="preserve">38.0227546691895</t>
+    <t xml:space="preserve">38.0227508544922</t>
   </si>
   <si>
     <t xml:space="preserve">37.6056327819824</t>
   </si>
   <si>
-    <t xml:space="preserve">37.7817497253418</t>
+    <t xml:space="preserve">37.7817459106445</t>
   </si>
   <si>
     <t xml:space="preserve">38.2359428405762</t>
@@ -4889,28 +4889,28 @@
     <t xml:space="preserve">36.252311706543</t>
   </si>
   <si>
-    <t xml:space="preserve">37.0587463378906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.318286895752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.6519775390625</t>
+    <t xml:space="preserve">37.0587387084961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.3182792663574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.6519813537598</t>
   </si>
   <si>
     <t xml:space="preserve">37.9300575256348</t>
   </si>
   <si>
-    <t xml:space="preserve">38.2452163696289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.0876388549805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.3090209960938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.7724800109863</t>
+    <t xml:space="preserve">38.2452125549316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.0876350402832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.3090171813965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.7724761962891</t>
   </si>
   <si>
     <t xml:space="preserve">38.0505599975586</t>
@@ -4934,13 +4934,13 @@
     <t xml:space="preserve">37.1050872802734</t>
   </si>
   <si>
-    <t xml:space="preserve">36.5674667358398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.1885108947754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.2070503234863</t>
+    <t xml:space="preserve">36.5674705505371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.1885147094727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.2070541381836</t>
   </si>
   <si>
     <t xml:space="preserve">36.4284286499023</t>
@@ -4949,16 +4949,16 @@
     <t xml:space="preserve">36.7250442504883</t>
   </si>
   <si>
-    <t xml:space="preserve">36.4098930358887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.8815383911133</t>
+    <t xml:space="preserve">36.4098892211914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.8815422058105</t>
   </si>
   <si>
     <t xml:space="preserve">35.8166542053223</t>
   </si>
   <si>
-    <t xml:space="preserve">35.2234153747559</t>
+    <t xml:space="preserve">35.2234191894531</t>
   </si>
   <si>
     <t xml:space="preserve">36.020580291748</t>
@@ -4973,7 +4973,7 @@
     <t xml:space="preserve">35.8630027770996</t>
   </si>
   <si>
-    <t xml:space="preserve">37.0402030944824</t>
+    <t xml:space="preserve">37.0402069091797</t>
   </si>
   <si>
     <t xml:space="preserve">36.3728141784668</t>
@@ -4982,10 +4982,10 @@
     <t xml:space="preserve">36.3913497924805</t>
   </si>
   <si>
-    <t xml:space="preserve">36.1132698059082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36.2059669494629</t>
+    <t xml:space="preserve">36.1132736206055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.2059631347656</t>
   </si>
   <si>
     <t xml:space="preserve">36.4840469360352</t>
@@ -4997,28 +4997,28 @@
     <t xml:space="preserve">36.9938583374023</t>
   </si>
   <si>
-    <t xml:space="preserve">37.3646278381348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.7539367675781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.8466377258301</t>
+    <t xml:space="preserve">37.364631652832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.7539443969727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.8466339111328</t>
   </si>
   <si>
     <t xml:space="preserve">37.4758644104004</t>
   </si>
   <si>
-    <t xml:space="preserve">37.2997512817383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36.9475059509277</t>
+    <t xml:space="preserve">37.299747467041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.9475135803223</t>
   </si>
   <si>
     <t xml:space="preserve">38.9589538574219</t>
   </si>
   <si>
-    <t xml:space="preserve">37.726131439209</t>
+    <t xml:space="preserve">37.7261352539062</t>
   </si>
   <si>
     <t xml:space="preserve">37.0958213806152</t>
@@ -5027,7 +5027,7 @@
     <t xml:space="preserve">38.6808738708496</t>
   </si>
   <si>
-    <t xml:space="preserve">37.939323425293</t>
+    <t xml:space="preserve">37.9393272399902</t>
   </si>
   <si>
     <t xml:space="preserve">38.1061744689941</t>
@@ -5036,22 +5036,22 @@
     <t xml:space="preserve">39.3760719299316</t>
   </si>
   <si>
-    <t xml:space="preserve">39.0053024291992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.9311408996582</t>
+    <t xml:space="preserve">39.005298614502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.9311485290527</t>
   </si>
   <si>
     <t xml:space="preserve">39.1721458435059</t>
   </si>
   <si>
-    <t xml:space="preserve">39.9878540039062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40.8684310913086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.5461845397949</t>
+    <t xml:space="preserve">39.9878463745117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40.8684349060059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.5461807250977</t>
   </si>
   <si>
     <t xml:space="preserve">42.2866401672363</t>
@@ -5066,7 +5066,7 @@
     <t xml:space="preserve">41.383129119873</t>
   </si>
   <si>
-    <t xml:space="preserve">41.6555786132812</t>
+    <t xml:space="preserve">41.655574798584</t>
   </si>
   <si>
     <t xml:space="preserve">40.5188293457031</t>
@@ -5075,43 +5075,43 @@
     <t xml:space="preserve">40.0960731506348</t>
   </si>
   <si>
-    <t xml:space="preserve">40.5564041137695</t>
+    <t xml:space="preserve">40.5564079284668</t>
   </si>
   <si>
     <t xml:space="preserve">40.0866775512695</t>
   </si>
   <si>
-    <t xml:space="preserve">39.4290542602539</t>
+    <t xml:space="preserve">39.4290580749512</t>
   </si>
   <si>
     <t xml:space="preserve">38.1607894897461</t>
   </si>
   <si>
-    <t xml:space="preserve">39.983341217041</t>
+    <t xml:space="preserve">39.9833374023438</t>
   </si>
   <si>
     <t xml:space="preserve">40.2463874816895</t>
   </si>
   <si>
-    <t xml:space="preserve">40.3966979980469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.4488945007324</t>
+    <t xml:space="preserve">40.3967018127441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.4488868713379</t>
   </si>
   <si>
     <t xml:space="preserve">41.9186210632324</t>
   </si>
   <si>
-    <t xml:space="preserve">42.134693145752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.7025489807129</t>
+    <t xml:space="preserve">42.1346969604492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.7025451660156</t>
   </si>
   <si>
     <t xml:space="preserve">42.7453460693359</t>
   </si>
   <si>
-    <t xml:space="preserve">42.2568283081055</t>
+    <t xml:space="preserve">42.2568244934082</t>
   </si>
   <si>
     <t xml:space="preserve">42.2098579406738</t>
@@ -5129,7 +5129,7 @@
     <t xml:space="preserve">40.1900177001953</t>
   </si>
   <si>
-    <t xml:space="preserve">40.330940246582</t>
+    <t xml:space="preserve">40.3309440612793</t>
   </si>
   <si>
     <t xml:space="preserve">40.1242561340332</t>
@@ -5138,7 +5138,7 @@
     <t xml:space="preserve">40.490650177002</t>
   </si>
   <si>
-    <t xml:space="preserve">40.6973266601562</t>
+    <t xml:space="preserve">40.6973304748535</t>
   </si>
   <si>
     <t xml:space="preserve">41.1012916564941</t>
@@ -5147,7 +5147,7 @@
     <t xml:space="preserve">40.7442970275879</t>
   </si>
   <si>
-    <t xml:space="preserve">40.9415855407715</t>
+    <t xml:space="preserve">40.9415893554688</t>
   </si>
   <si>
     <t xml:space="preserve">41.0449256896973</t>
@@ -5162,13 +5162,13 @@
     <t xml:space="preserve">39.757869720459</t>
   </si>
   <si>
-    <t xml:space="preserve">39.6921043395996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40.3121452331543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40.2933540344238</t>
+    <t xml:space="preserve">39.6921081542969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40.3121490478516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40.2933578491211</t>
   </si>
   <si>
     <t xml:space="preserve">40.4718589782715</t>
@@ -5177,7 +5177,7 @@
     <t xml:space="preserve">40.4060974121094</t>
   </si>
   <si>
-    <t xml:space="preserve">40.6691513061523</t>
+    <t xml:space="preserve">40.6691474914551</t>
   </si>
   <si>
     <t xml:space="preserve">40.8476409912109</t>
@@ -5189,7 +5189,7 @@
     <t xml:space="preserve">42.5856399536133</t>
   </si>
   <si>
-    <t xml:space="preserve">42.3319892883301</t>
+    <t xml:space="preserve">42.3319854736328</t>
   </si>
   <si>
     <t xml:space="preserve">41.758918762207</t>
@@ -5207,7 +5207,7 @@
     <t xml:space="preserve">44.1075592041016</t>
   </si>
   <si>
-    <t xml:space="preserve">43.1962852478027</t>
+    <t xml:space="preserve">43.1962890625</t>
   </si>
   <si>
     <t xml:space="preserve">42.8392906188965</t>
@@ -5216,10 +5216,10 @@
     <t xml:space="preserve">41.881046295166</t>
   </si>
   <si>
-    <t xml:space="preserve">40.8758239746094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.228645324707</t>
+    <t xml:space="preserve">40.8758277893066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.2286491394043</t>
   </si>
   <si>
     <t xml:space="preserve">42.7077674865723</t>
@@ -5234,7 +5234,7 @@
     <t xml:space="preserve">42.6138229370117</t>
   </si>
   <si>
-    <t xml:space="preserve">42.0971221923828</t>
+    <t xml:space="preserve">42.0971183776855</t>
   </si>
   <si>
     <t xml:space="preserve">41.9468078613281</t>
@@ -5246,25 +5246,25 @@
     <t xml:space="preserve">42.9896011352539</t>
   </si>
   <si>
-    <t xml:space="preserve">42.8017158508301</t>
+    <t xml:space="preserve">42.8017120361328</t>
   </si>
   <si>
     <t xml:space="preserve">43.0647621154785</t>
   </si>
   <si>
-    <t xml:space="preserve">43.3935661315918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">44.0511856079102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43.6566162109375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43.5720672607422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43.0177879333496</t>
+    <t xml:space="preserve">43.3935699462891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44.0511932373047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43.6566200256348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43.5720710754395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43.0177917480469</t>
   </si>
   <si>
     <t xml:space="preserve">42.8111038208008</t>
@@ -5273,16 +5273,16 @@
     <t xml:space="preserve">41.6743698120117</t>
   </si>
   <si>
-    <t xml:space="preserve">42.2850036621094</t>
+    <t xml:space="preserve">42.2850112915039</t>
   </si>
   <si>
     <t xml:space="preserve">42.8298988342285</t>
   </si>
   <si>
-    <t xml:space="preserve">42.4822998046875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.7171630859375</t>
+    <t xml:space="preserve">42.4822959899902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.7171592712402</t>
   </si>
   <si>
     <t xml:space="preserve">42.8768692016602</t>
@@ -5291,7 +5291,7 @@
     <t xml:space="preserve">43.5438842773438</t>
   </si>
   <si>
-    <t xml:space="preserve">43.9854278564453</t>
+    <t xml:space="preserve">43.985424041748</t>
   </si>
   <si>
     <t xml:space="preserve">44.0887718200684</t>
@@ -5300,13 +5300,13 @@
     <t xml:space="preserve">44.1357421875</t>
   </si>
   <si>
-    <t xml:space="preserve">44.5303230285645</t>
+    <t xml:space="preserve">44.5303192138672</t>
   </si>
   <si>
     <t xml:space="preserve">42.1816711425781</t>
   </si>
   <si>
-    <t xml:space="preserve">42.5574569702148</t>
+    <t xml:space="preserve">42.5574531555176</t>
   </si>
   <si>
     <t xml:space="preserve">42.0783309936523</t>
@@ -5315,7 +5315,7 @@
     <t xml:space="preserve">42.0689353942871</t>
   </si>
   <si>
-    <t xml:space="preserve">41.3643379211426</t>
+    <t xml:space="preserve">41.3643417358398</t>
   </si>
   <si>
     <t xml:space="preserve">41.4770774841309</t>
@@ -5324,7 +5324,7 @@
     <t xml:space="preserve">42.003173828125</t>
   </si>
   <si>
-    <t xml:space="preserve">41.4019165039062</t>
+    <t xml:space="preserve">41.4019241333008</t>
   </si>
   <si>
     <t xml:space="preserve">41.0918998718262</t>
@@ -5342,7 +5342,7 @@
     <t xml:space="preserve">42.858081817627</t>
   </si>
   <si>
-    <t xml:space="preserve">42.7829246520996</t>
+    <t xml:space="preserve">42.7829208374023</t>
   </si>
   <si>
     <t xml:space="preserve">42.735954284668</t>
@@ -5354,67 +5354,67 @@
     <t xml:space="preserve">41.3455543518066</t>
   </si>
   <si>
-    <t xml:space="preserve">41.3267669677734</t>
+    <t xml:space="preserve">41.3267707824707</t>
   </si>
   <si>
     <t xml:space="preserve">41.6837577819824</t>
   </si>
   <si>
-    <t xml:space="preserve">41.307975769043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.0637168884277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40.7912750244141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40.6127777099609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40.9603691101074</t>
+    <t xml:space="preserve">41.3079719543457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.0637130737305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40.7912712097168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40.6127738952637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40.960376739502</t>
   </si>
   <si>
     <t xml:space="preserve">41.4582824707031</t>
   </si>
   <si>
-    <t xml:space="preserve">41.6179962158203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.2891883850098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.430103302002</t>
+    <t xml:space="preserve">41.617992401123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.2891845703125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.4300994873047</t>
   </si>
   <si>
     <t xml:space="preserve">41.148265838623</t>
   </si>
   <si>
-    <t xml:space="preserve">42.0501441955566</t>
+    <t xml:space="preserve">42.0501480102539</t>
   </si>
   <si>
     <t xml:space="preserve">41.5804176330566</t>
   </si>
   <si>
-    <t xml:space="preserve">42.1910667419434</t>
+    <t xml:space="preserve">42.1910629272461</t>
   </si>
   <si>
     <t xml:space="preserve">43.0741539001465</t>
   </si>
   <si>
-    <t xml:space="preserve">41.8434638977051</t>
+    <t xml:space="preserve">41.8434677124023</t>
   </si>
   <si>
     <t xml:space="preserve">42.4447174072266</t>
   </si>
   <si>
-    <t xml:space="preserve">42.454231262207</t>
+    <t xml:space="preserve">42.4542350769043</t>
   </si>
   <si>
     <t xml:space="preserve">42.7016143798828</t>
   </si>
   <si>
-    <t xml:space="preserve">42.2354011535645</t>
+    <t xml:space="preserve">42.2353973388672</t>
   </si>
   <si>
     <t xml:space="preserve">42.3876304626465</t>
@@ -5444,7 +5444,7 @@
     <t xml:space="preserve">43.6721076965332</t>
   </si>
   <si>
-    <t xml:space="preserve">43.99560546875</t>
+    <t xml:space="preserve">43.9956016540527</t>
   </si>
   <si>
     <t xml:space="preserve">43.4437522888184</t>
@@ -5489,7 +5489,7 @@
     <t xml:space="preserve">46.0888175964355</t>
   </si>
   <si>
-    <t xml:space="preserve">46.459888458252</t>
+    <t xml:space="preserve">46.4598922729492</t>
   </si>
   <si>
     <t xml:space="preserve">46.621639251709</t>
@@ -5501,16 +5501,16 @@
     <t xml:space="preserve">46.1649360656738</t>
   </si>
   <si>
-    <t xml:space="preserve">45.4989128112793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.860466003418</t>
+    <t xml:space="preserve">45.4989166259766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.8604698181152</t>
   </si>
   <si>
     <t xml:space="preserve">46.5455169677734</t>
   </si>
   <si>
-    <t xml:space="preserve">46.7167816162109</t>
+    <t xml:space="preserve">46.7167778015137</t>
   </si>
   <si>
     <t xml:space="preserve">46.8309593200684</t>
@@ -5519,7 +5519,7 @@
     <t xml:space="preserve">48.4865036010742</t>
   </si>
   <si>
-    <t xml:space="preserve">47.5635833740234</t>
+    <t xml:space="preserve">47.5635871887207</t>
   </si>
   <si>
     <t xml:space="preserve">47.8204803466797</t>
@@ -5546,13 +5546,13 @@
     <t xml:space="preserve">47.554069519043</t>
   </si>
   <si>
-    <t xml:space="preserve">48.4294128417969</t>
+    <t xml:space="preserve">48.4294166564941</t>
   </si>
   <si>
     <t xml:space="preserve">48.1820335388184</t>
   </si>
   <si>
-    <t xml:space="preserve">48.3342666625977</t>
+    <t xml:space="preserve">48.3342704772949</t>
   </si>
   <si>
     <t xml:space="preserve">48.8099975585938</t>
@@ -5567,7 +5567,7 @@
     <t xml:space="preserve">48.6197052001953</t>
   </si>
   <si>
-    <t xml:space="preserve">47.9917449951172</t>
+    <t xml:space="preserve">47.9917411804199</t>
   </si>
   <si>
     <t xml:space="preserve">48.0107688903809</t>
@@ -5588,7 +5588,7 @@
     <t xml:space="preserve">48.7529144287109</t>
   </si>
   <si>
-    <t xml:space="preserve">49.5901947021484</t>
+    <t xml:space="preserve">49.5901985168457</t>
   </si>
   <si>
     <t xml:space="preserve">49.5521430969238</t>
@@ -5597,7 +5597,7 @@
     <t xml:space="preserve">49.171558380127</t>
   </si>
   <si>
-    <t xml:space="preserve">50.3133125305176</t>
+    <t xml:space="preserve">50.3133087158203</t>
   </si>
   <si>
     <t xml:space="preserve">49.152530670166</t>
@@ -5606,16 +5606,16 @@
     <t xml:space="preserve">48.5055351257324</t>
   </si>
   <si>
-    <t xml:space="preserve">48.2581558227539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">49.2476692199707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">49.4379653930664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">49.2096176147461</t>
+    <t xml:space="preserve">48.2581520080566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">49.247673034668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">49.4379615783691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">49.2096138000488</t>
   </si>
   <si>
     <t xml:space="preserve">50.0278739929199</t>
@@ -5630,16 +5630,16 @@
     <t xml:space="preserve">50.503604888916</t>
   </si>
   <si>
-    <t xml:space="preserve">50.2181625366211</t>
+    <t xml:space="preserve">50.2181663513184</t>
   </si>
   <si>
     <t xml:space="preserve">50.2752494812012</t>
   </si>
   <si>
-    <t xml:space="preserve">49.3428192138672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">48.73388671875</t>
+    <t xml:space="preserve">49.3428230285645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">48.7338829040527</t>
   </si>
   <si>
     <t xml:space="preserve">48.391357421875</t>
@@ -5672,25 +5672,25 @@
     <t xml:space="preserve">46.3361968994141</t>
   </si>
   <si>
-    <t xml:space="preserve">47.4969787597656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">47.1544609069824</t>
+    <t xml:space="preserve">47.4969825744629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">47.1544570922852</t>
   </si>
   <si>
     <t xml:space="preserve">47.5731010437012</t>
   </si>
   <si>
-    <t xml:space="preserve">47.0212478637695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.945140838623</t>
+    <t xml:space="preserve">47.0212516784668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.9451370239258</t>
   </si>
   <si>
     <t xml:space="preserve">46.5645484924316</t>
   </si>
   <si>
-    <t xml:space="preserve">47.3257217407227</t>
+    <t xml:space="preserve">47.3257255554199</t>
   </si>
   <si>
     <t xml:space="preserve">47.4398918151855</t>
@@ -5711,7 +5711,7 @@
     <t xml:space="preserve">47.9061088562012</t>
   </si>
   <si>
-    <t xml:space="preserve">48.7148551940918</t>
+    <t xml:space="preserve">48.7148513793945</t>
   </si>
   <si>
     <t xml:space="preserve">49.2857284545898</t>
@@ -5723,13 +5723,13 @@
     <t xml:space="preserve">47.029052734375</t>
   </si>
   <si>
-    <t xml:space="preserve">47.3565788269043</t>
+    <t xml:space="preserve">47.3565826416016</t>
   </si>
   <si>
     <t xml:space="preserve">46.7400550842285</t>
   </si>
   <si>
-    <t xml:space="preserve">46.5666618347168</t>
+    <t xml:space="preserve">46.5666580200195</t>
   </si>
   <si>
     <t xml:space="preserve">46.8941879272461</t>
@@ -5741,7 +5741,7 @@
     <t xml:space="preserve">45.950138092041</t>
   </si>
   <si>
-    <t xml:space="preserve">45.7189445495605</t>
+    <t xml:space="preserve">45.7189407348633</t>
   </si>
   <si>
     <t xml:space="preserve">46.6244621276855</t>
@@ -5750,13 +5750,13 @@
     <t xml:space="preserve">46.5859260559082</t>
   </si>
   <si>
-    <t xml:space="preserve">46.4317932128906</t>
+    <t xml:space="preserve">46.4317970275879</t>
   </si>
   <si>
     <t xml:space="preserve">46.8171195983887</t>
   </si>
   <si>
-    <t xml:space="preserve">47.4336433410645</t>
+    <t xml:space="preserve">47.4336471557617</t>
   </si>
   <si>
     <t xml:space="preserve">47.8767700195312</t>
@@ -5777,7 +5777,7 @@
     <t xml:space="preserve">45.6804084777832</t>
   </si>
   <si>
-    <t xml:space="preserve">46.0850028991699</t>
+    <t xml:space="preserve">46.0849990844727</t>
   </si>
   <si>
     <t xml:space="preserve">47.3951110839844</t>
@@ -5804,7 +5804,7 @@
     <t xml:space="preserve">47.2795143127441</t>
   </si>
   <si>
-    <t xml:space="preserve">47.3373069763184</t>
+    <t xml:space="preserve">47.3373107910156</t>
   </si>
   <si>
     <t xml:space="preserve">48.1657638549805</t>
@@ -5834,10 +5834,10 @@
     <t xml:space="preserve">49.9478988647461</t>
   </si>
   <si>
-    <t xml:space="preserve">50.3332252502441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50.0442276000977</t>
+    <t xml:space="preserve">50.3332214355469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50.0442314147949</t>
   </si>
   <si>
     <t xml:space="preserve">50.4777221679688</t>
@@ -5858,13 +5858,13 @@
     <t xml:space="preserve">47.6263046264648</t>
   </si>
   <si>
-    <t xml:space="preserve">47.1831817626953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">47.5299797058105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">47.6455688476562</t>
+    <t xml:space="preserve">47.1831855773926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">47.5299758911133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">47.6455726623535</t>
   </si>
   <si>
     <t xml:space="preserve">47.9923667907715</t>
@@ -5873,10 +5873,10 @@
     <t xml:space="preserve">48.1272277832031</t>
   </si>
   <si>
-    <t xml:space="preserve">48.7437515258789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">48.5510864257812</t>
+    <t xml:space="preserve">48.7437553405762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">48.5510902404785</t>
   </si>
   <si>
     <t xml:space="preserve">48.791919708252</t>
@@ -5888,10 +5888,10 @@
     <t xml:space="preserve">50.8148803710938</t>
   </si>
   <si>
-    <t xml:space="preserve">50.6222190856934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">51.0557060241699</t>
+    <t xml:space="preserve">50.6222152709961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">51.0557098388672</t>
   </si>
   <si>
     <t xml:space="preserve">50.7185478210449</t>
@@ -5909,7 +5909,7 @@
     <t xml:space="preserve">49.5625686645508</t>
   </si>
   <si>
-    <t xml:space="preserve">49.0327453613281</t>
+    <t xml:space="preserve">49.0327491760254</t>
   </si>
   <si>
     <t xml:space="preserve">48.9845809936523</t>
@@ -5927,7 +5927,7 @@
     <t xml:space="preserve">48.8400840759277</t>
   </si>
   <si>
-    <t xml:space="preserve">48.9364128112793</t>
+    <t xml:space="preserve">48.9364166259766</t>
   </si>
   <si>
     <t xml:space="preserve">47.6841049194336</t>
@@ -5936,13 +5936,13 @@
     <t xml:space="preserve">50.1887245178223</t>
   </si>
   <si>
-    <t xml:space="preserve">52.1153564453125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">51.4410362243652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">51.5855293273926</t>
+    <t xml:space="preserve">52.1153526306152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">51.441032409668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">51.5855331420898</t>
   </si>
   <si>
     <t xml:space="preserve">52.5006790161133</t>
@@ -5972,82 +5972,82 @@
     <t xml:space="preserve">49.9960632324219</t>
   </si>
   <si>
-    <t xml:space="preserve">49.6107406616211</t>
+    <t xml:space="preserve">49.6107368469238</t>
   </si>
   <si>
     <t xml:space="preserve">50.4295501708984</t>
   </si>
   <si>
+    <t xml:space="preserve">49.3217391967773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">48.7369003295898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">48.6394271850586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">49.1755294799805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">49.3704795837402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50.7838478088379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50.9300575256348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50.4426918029785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50.3939514160156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50.0527954101562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50.2477416992188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">49.8578491210938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50.1015319824219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50.6376419067383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">49.7603721618652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">49.8091087341309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">49.9065818786621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">49.5654258728027</t>
+  </si>
+  <si>
     <t xml:space="preserve">49.3217430114746</t>
   </si>
   <si>
-    <t xml:space="preserve">48.7369003295898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">48.6394271850586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">49.1755294799805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">49.3704795837402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50.7838478088379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50.930061340332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50.4426918029785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50.3939552307129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50.0527954101562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50.2477416992188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">49.8578491210938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50.1015319824219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50.637638092041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">49.7603721618652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">49.8091087341309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">49.9065856933594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">49.5654258728027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">49.3217391967773</t>
-  </si>
-  <si>
     <t xml:space="preserve">49.4679527282715</t>
   </si>
   <si>
     <t xml:space="preserve">49.0780563354492</t>
   </si>
   <si>
-    <t xml:space="preserve">49.1267929077148</t>
+    <t xml:space="preserve">49.1267967224121</t>
   </si>
   <si>
     <t xml:space="preserve">49.2242698669434</t>
   </si>
   <si>
-    <t xml:space="preserve">49.6141624450684</t>
+    <t xml:space="preserve">49.6141662597656</t>
   </si>
   <si>
     <t xml:space="preserve">50.4914245605469</t>
@@ -6071,10 +6071,10 @@
     <t xml:space="preserve">53.1719551086426</t>
   </si>
   <si>
-    <t xml:space="preserve">53.5131149291992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">53.2206954956055</t>
+    <t xml:space="preserve">53.5131187438965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">53.2206916809082</t>
   </si>
   <si>
     <t xml:space="preserve">53.7568016052246</t>
@@ -6086,13 +6086,13 @@
     <t xml:space="preserve">54.3903770446777</t>
   </si>
   <si>
-    <t xml:space="preserve">54.5853271484375</t>
+    <t xml:space="preserve">54.5853233337402</t>
   </si>
   <si>
     <t xml:space="preserve">55.3651161193848</t>
   </si>
   <si>
-    <t xml:space="preserve">56.0474319458008</t>
+    <t xml:space="preserve">56.047435760498</t>
   </si>
   <si>
     <t xml:space="preserve">56.6810150146484</t>
@@ -6104,7 +6104,7 @@
     <t xml:space="preserve">57.2658576965332</t>
   </si>
   <si>
-    <t xml:space="preserve">57.7532234191895</t>
+    <t xml:space="preserve">57.7532272338867</t>
   </si>
   <si>
     <t xml:space="preserve">57.6070137023926</t>
@@ -6113,7 +6113,7 @@
     <t xml:space="preserve">57.9481735229492</t>
   </si>
   <si>
-    <t xml:space="preserve">58.143123626709</t>
+    <t xml:space="preserve">58.1431198120117</t>
   </si>
   <si>
     <t xml:space="preserve">57.1196441650391</t>
@@ -6128,10 +6128,10 @@
     <t xml:space="preserve">57.558277130127</t>
   </si>
   <si>
-    <t xml:space="preserve">59.4102783203125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">58.0943794250488</t>
+    <t xml:space="preserve">59.4102821350098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">58.0943832397461</t>
   </si>
   <si>
     <t xml:space="preserve">58.240592956543</t>
@@ -6143,10 +6143,10 @@
     <t xml:space="preserve">54.4391136169434</t>
   </si>
   <si>
-    <t xml:space="preserve">53.4643783569336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">52.733325958252</t>
+    <t xml:space="preserve">53.4643745422363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">52.7333221435547</t>
   </si>
   <si>
     <t xml:space="preserve">52.3434295654297</t>
@@ -6161,28 +6161,28 @@
     <t xml:space="preserve">52.9282722473145</t>
   </si>
   <si>
-    <t xml:space="preserve">53.5618553161621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">52.8795318603516</t>
+    <t xml:space="preserve">53.5618515014648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">52.8795356750488</t>
   </si>
   <si>
     <t xml:space="preserve">52.4896392822266</t>
   </si>
   <si>
-    <t xml:space="preserve">52.1972160339355</t>
+    <t xml:space="preserve">52.1972198486328</t>
   </si>
   <si>
     <t xml:space="preserve">50.9787940979004</t>
   </si>
   <si>
-    <t xml:space="preserve">51.6611099243164</t>
+    <t xml:space="preserve">51.6611137390137</t>
   </si>
   <si>
     <t xml:space="preserve">51.612377166748</t>
   </si>
   <si>
-    <t xml:space="preserve">51.3686904907227</t>
+    <t xml:space="preserve">51.3686943054199</t>
   </si>
   <si>
     <t xml:space="preserve">52.0997467041016</t>
@@ -6215,10 +6215,10 @@
     <t xml:space="preserve">44.7014846801758</t>
   </si>
   <si>
-    <t xml:space="preserve">45.4617767333984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.4365158081055</t>
+    <t xml:space="preserve">45.4617805480957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.4365196228027</t>
   </si>
   <si>
     <t xml:space="preserve">47.1383285522461</t>
@@ -6227,16 +6227,16 @@
     <t xml:space="preserve">47.2747917175293</t>
   </si>
   <si>
-    <t xml:space="preserve">47.0798416137695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">47.7426643371582</t>
+    <t xml:space="preserve">47.0798454284668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">47.7426681518555</t>
   </si>
   <si>
     <t xml:space="preserve">47.9766044616699</t>
   </si>
   <si>
-    <t xml:space="preserve">48.2105369567871</t>
+    <t xml:space="preserve">48.2105407714844</t>
   </si>
   <si>
     <t xml:space="preserve">47.8011512756348</t>
@@ -6248,7 +6248,7 @@
     <t xml:space="preserve">50.5401649475098</t>
   </si>
   <si>
-    <t xml:space="preserve">51.8560600280762</t>
+    <t xml:space="preserve">51.8560638427734</t>
   </si>
   <si>
     <t xml:space="preserve">51.1737442016602</t>
@@ -6257,10 +6257,10 @@
     <t xml:space="preserve">50.8325843811035</t>
   </si>
   <si>
-    <t xml:space="preserve">50.34521484375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50.1990089416504</t>
+    <t xml:space="preserve">50.3452186584473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50.1990051269531</t>
   </si>
   <si>
     <t xml:space="preserve">50.8113098144531</t>
@@ -6534,6 +6534,9 @@
   </si>
   <si>
     <t xml:space="preserve">47.939998626709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">48.4599990844727</t>
   </si>
 </sst>
 </file>
@@ -72730,7 +72733,7 @@
     </row>
     <row r="2534">
       <c r="A2534" s="1" t="n">
-        <v>46007.6911342593</v>
+        <v>46007.3333333333</v>
       </c>
       <c r="B2534" t="n">
         <v>277182</v>
@@ -72751,6 +72754,32 @@
         <v>2173</v>
       </c>
       <c r="H2534" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2535">
+      <c r="A2535" s="1" t="n">
+        <v>46008.6910185185</v>
+      </c>
+      <c r="B2535" t="n">
+        <v>386801</v>
+      </c>
+      <c r="C2535" t="n">
+        <v>49.1399993896484</v>
+      </c>
+      <c r="D2535" t="n">
+        <v>47.7400016784668</v>
+      </c>
+      <c r="E2535" t="n">
+        <v>48.1599998474121</v>
+      </c>
+      <c r="F2535" t="n">
+        <v>48.4599990844727</v>
+      </c>
+      <c r="G2535" t="s">
+        <v>2174</v>
+      </c>
+      <c r="H2535" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/REC.MI.xlsx
+++ b/data/REC.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2216" uniqueCount="2216">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2217" uniqueCount="2217">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,13 +38,13 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">18.3691101074219</t>
+    <t xml:space="preserve">18.3691082000732</t>
   </si>
   <si>
     <t xml:space="preserve">REC.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">18.9363460540771</t>
+    <t xml:space="preserve">18.9363479614258</t>
   </si>
   <si>
     <t xml:space="preserve">18.6177616119385</t>
@@ -56,37 +56,37 @@
     <t xml:space="preserve">18.1204605102539</t>
   </si>
   <si>
-    <t xml:space="preserve">17.9728240966797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0116710662842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4444427490234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.5609970092773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9626789093018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9005184173584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8849754333496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.623161315918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.8485012054443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.817419052124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.1360034942627</t>
+    <t xml:space="preserve">17.9728260040283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0116767883301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4444408416748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.5609951019287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.962682723999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9005165100098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.884973526001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6231594085693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.8484935760498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.8174133300781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.1359996795654</t>
   </si>
   <si>
     <t xml:space="preserve">17.3667373657227</t>
@@ -98,94 +98,94 @@
     <t xml:space="preserve">18.066068649292</t>
   </si>
   <si>
-    <t xml:space="preserve">17.4677467346191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2424125671387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6440963745117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5407028198242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0977964401245</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2143478393555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7815885543823</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9136810302734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5042266845703</t>
+    <t xml:space="preserve">17.4677505493164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.24241065979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6440925598145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5407056808472</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0977916717529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2143449783325</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7815780639648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9136800765991</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5042285919189</t>
   </si>
   <si>
     <t xml:space="preserve">17.1647052764893</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0326156616211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.3511905670166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.7474822998047</t>
+    <t xml:space="preserve">17.0326080322266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3511981964111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.7474842071533</t>
   </si>
   <si>
     <t xml:space="preserve">17.7707939147949</t>
   </si>
   <si>
-    <t xml:space="preserve">18.034984588623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4342956542969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3798999786377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8772048950195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0403804779053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2579517364502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4055862426758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0248413085938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7994995117188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7295703887939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5508518218994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8616638183594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5353126525879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8072681427002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9082832336426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9937591552734</t>
+    <t xml:space="preserve">18.0349903106689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4342937469482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3799018859863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8772068023682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0403823852539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2579460144043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4055919647217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0248432159424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7995014190674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7295665740967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5508480072021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.861665725708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5353107452393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8072700500488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9082851409912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9937572479248</t>
   </si>
   <si>
     <t xml:space="preserve">16.9315986633301</t>
@@ -194,79 +194,79 @@
     <t xml:space="preserve">16.7217960357666</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7684230804443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8694362640381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6829471588135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9782199859619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0947704315186</t>
+    <t xml:space="preserve">16.7684173583984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8694343566895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6829452514648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9782218933105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0947742462158</t>
   </si>
   <si>
     <t xml:space="preserve">17.1025447845459</t>
   </si>
   <si>
-    <t xml:space="preserve">17.2190971374512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1336231231689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4832897186279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.5454578399658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4599781036377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4366703033447</t>
+    <t xml:space="preserve">17.2191009521484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1336269378662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4832878112793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.5454540252686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4599800109863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4366760253906</t>
   </si>
   <si>
     <t xml:space="preserve">17.4522113800049</t>
   </si>
   <si>
-    <t xml:space="preserve">17.3822765350342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4133567810059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.7677669525146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6968841552734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.531494140625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6102561950684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.3818550109863</t>
+    <t xml:space="preserve">17.3822803497314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4133548736572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.7677707672119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6968860626221</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.5314979553223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6102523803711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.381856918335</t>
   </si>
   <si>
     <t xml:space="preserve">17.444860458374</t>
   </si>
   <si>
-    <t xml:space="preserve">17.5078678131104</t>
+    <t xml:space="preserve">17.5078659057617</t>
   </si>
   <si>
     <t xml:space="preserve">17.6811351776123</t>
   </si>
   <si>
-    <t xml:space="preserve">17.4133605957031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4763698577881</t>
+    <t xml:space="preserve">17.4133586883545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4763660430908</t>
   </si>
   <si>
     <t xml:space="preserve">17.4291095733643</t>
@@ -278,43 +278,43 @@
     <t xml:space="preserve">17.8937816619873</t>
   </si>
   <si>
-    <t xml:space="preserve">17.980411529541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.6734809875488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.9648857116699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.9018802642822</t>
+    <t xml:space="preserve">17.9804153442383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6734828948975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.9648876190186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.9018783569336</t>
   </si>
   <si>
     <t xml:space="preserve">18.7286148071289</t>
   </si>
   <si>
-    <t xml:space="preserve">19.0436458587646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.0200214385986</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.0672740936279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.216911315918</t>
+    <t xml:space="preserve">19.0436477661133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.0200176239014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.0672702789307</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.2169132232666</t>
   </si>
   <si>
     <t xml:space="preserve">19.2720432281494</t>
   </si>
   <si>
-    <t xml:space="preserve">20.0911235809326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.232889175415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.4219055175781</t>
+    <t xml:space="preserve">20.091121673584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.2328910827637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.421911239624</t>
   </si>
   <si>
     <t xml:space="preserve">20.3274002075195</t>
@@ -326,40 +326,40 @@
     <t xml:space="preserve">20.760570526123</t>
   </si>
   <si>
-    <t xml:space="preserve">20.8944549560547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.9023323059082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.2488670349121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.4142551422119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.0677223205566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.9968414306641</t>
+    <t xml:space="preserve">20.894458770752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.9023342132568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.2488651275635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.4142570495605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.067720413208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.9968395233154</t>
   </si>
   <si>
     <t xml:space="preserve">21.4930152893066</t>
   </si>
   <si>
-    <t xml:space="preserve">21.4536323547363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.1464824676514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.4770393371582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.4297828674316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.6266822814941</t>
+    <t xml:space="preserve">21.4536380767822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.1464786529541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.4770374298096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.4297847747803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.6266784667969</t>
   </si>
   <si>
     <t xml:space="preserve">20.3667774200439</t>
@@ -368,154 +368,154 @@
     <t xml:space="preserve">19.9729881286621</t>
   </si>
   <si>
-    <t xml:space="preserve">20.6424255371094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.9102039337158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.8156967163086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.1386032104492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.0438690185547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.87082862854</t>
+    <t xml:space="preserve">20.642427444458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.9102096557617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.8157005310059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.1386070251465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.0438709259033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.8708305358887</t>
   </si>
   <si>
     <t xml:space="preserve">21.1543579101562</t>
   </si>
   <si>
-    <t xml:space="preserve">21.2646179199219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.2882480621338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.2803649902344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.1858577728271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.0519733428955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.3748779296875</t>
+    <t xml:space="preserve">21.2646160125732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.2882442474365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.280366897583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.1858596801758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.0519695281982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.3748817443848</t>
   </si>
   <si>
     <t xml:space="preserve">22.0758247375488</t>
   </si>
   <si>
-    <t xml:space="preserve">22.2884674072266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.1545810699463</t>
+    <t xml:space="preserve">22.2884693145752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.1545791625977</t>
   </si>
   <si>
     <t xml:space="preserve">21.918306350708</t>
   </si>
   <si>
-    <t xml:space="preserve">21.7292881011963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.9104290008545</t>
+    <t xml:space="preserve">21.7292900085449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.910436630249</t>
   </si>
   <si>
     <t xml:space="preserve">21.8001689910889</t>
   </si>
   <si>
-    <t xml:space="preserve">22.2175846099854</t>
+    <t xml:space="preserve">22.217586517334</t>
   </si>
   <si>
     <t xml:space="preserve">22.6507549285889</t>
   </si>
   <si>
-    <t xml:space="preserve">22.619255065918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.6586265563965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.3751010894775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.8161506652832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.7925224304199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.6665134429932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.8476524353027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.1233005523682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.7216377258301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.1230792999268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.4932403564453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.2412128448486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.1782073974609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.4066047668457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.3672294616699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.51686668396</t>
+    <t xml:space="preserve">22.6192512512207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.6586322784424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.3751029968262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.8161449432373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.792516708374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.6665096282959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.8476486206055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.1233043670654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.7216358184814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.1230773925781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.4932441711426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.2412109375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.1782112121582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.4066066741943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.3672275543213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.5168647766113</t>
   </si>
   <si>
     <t xml:space="preserve">21.9025573730469</t>
   </si>
   <si>
-    <t xml:space="preserve">21.894681930542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.4772644042969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.611156463623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.3355026245117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.4851398468018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.6032772064209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.6977863311768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.2094841003418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.2331123352051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.5402679443359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.3591289520264</t>
+    <t xml:space="preserve">21.8946762084961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.4772663116455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.6111488342285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.3354988098145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.485143661499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.6032752990723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.6977882385254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.2094860076904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.2331142425537</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.5402736663818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.3591251373291</t>
   </si>
   <si>
     <t xml:space="preserve">21.1228542327881</t>
@@ -524,37 +524,37 @@
     <t xml:space="preserve">21.3827514648438</t>
   </si>
   <si>
-    <t xml:space="preserve">21.2724933624268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.9655609130859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.6899070739746</t>
+    <t xml:space="preserve">21.2724914550781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.9655647277832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.6899108886719</t>
   </si>
   <si>
     <t xml:space="preserve">21.0834712982178</t>
   </si>
   <si>
-    <t xml:space="preserve">21.0047149658203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.9495868682861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.398509979248</t>
+    <t xml:space="preserve">21.0047130584717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.9495849609375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.3985061645508</t>
   </si>
   <si>
     <t xml:space="preserve">21.5481452941895</t>
   </si>
   <si>
-    <t xml:space="preserve">21.1779823303223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.3906307220459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.4063816070557</t>
+    <t xml:space="preserve">21.1779861450195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.3906288146973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.4063873291016</t>
   </si>
   <si>
     <t xml:space="preserve">21.6190299987793</t>
@@ -563,70 +563,70 @@
     <t xml:space="preserve">21.6584053039551</t>
   </si>
   <si>
-    <t xml:space="preserve">22.3908576965332</t>
+    <t xml:space="preserve">22.3908557891846</t>
   </si>
   <si>
     <t xml:space="preserve">22.5956249237061</t>
   </si>
   <si>
-    <t xml:space="preserve">22.5326232910156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.4223575592041</t>
+    <t xml:space="preserve">22.5326175689697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.4223613739014</t>
   </si>
   <si>
     <t xml:space="preserve">22.3514766693115</t>
   </si>
   <si>
-    <t xml:space="preserve">22.304220199585</t>
+    <t xml:space="preserve">22.3042163848877</t>
   </si>
   <si>
     <t xml:space="preserve">22.1860828399658</t>
   </si>
   <si>
-    <t xml:space="preserve">22.0837001800537</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.2648448944092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.5166435241699</t>
+    <t xml:space="preserve">22.0836982727051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.2648429870605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.5166454315186</t>
   </si>
   <si>
     <t xml:space="preserve">21.6820373535156</t>
   </si>
   <si>
-    <t xml:space="preserve">21.2252445220947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.3512535095215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.2567386627197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.1070995330811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.0913505554199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3037738800049</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.8627223968506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.1620082855225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.2565174102783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.8154735565186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3116493225098</t>
+    <t xml:space="preserve">21.2252349853516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.3512516021729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.256742477417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.107105255127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.0913524627686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.303768157959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.8627319335938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.1620063781738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.2565155029297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.8154716491699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3116550445557</t>
   </si>
   <si>
     <t xml:space="preserve">21.1937351226807</t>
@@ -635,28 +635,28 @@
     <t xml:space="preserve">20.5164165496826</t>
   </si>
   <si>
-    <t xml:space="preserve">20.5557956695557</t>
+    <t xml:space="preserve">20.5557975769043</t>
   </si>
   <si>
     <t xml:space="preserve">20.1383781433105</t>
   </si>
   <si>
-    <t xml:space="preserve">20.0202445983887</t>
+    <t xml:space="preserve">20.0202465057373</t>
   </si>
   <si>
     <t xml:space="preserve">20.2643928527832</t>
   </si>
   <si>
-    <t xml:space="preserve">20.2164859771729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.713472366333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.0168762207031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.2564067840576</t>
+    <t xml:space="preserve">20.2164840698242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.7134685516357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.0168743133545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.2564125061035</t>
   </si>
   <si>
     <t xml:space="preserve">20.3282661437988</t>
@@ -665,7 +665,7 @@
     <t xml:space="preserve">20.0887355804443</t>
   </si>
   <si>
-    <t xml:space="preserve">20.3602085113525</t>
+    <t xml:space="preserve">20.3602027893066</t>
   </si>
   <si>
     <t xml:space="preserve">20.5119094848633</t>
@@ -674,79 +674,79 @@
     <t xml:space="preserve">19.8092823028564</t>
   </si>
   <si>
-    <t xml:space="preserve">20.1286582946777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.34423828125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.5598182678223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.5039253234863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3841590881348</t>
+    <t xml:space="preserve">20.1286563873291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3442344665527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.5598163604736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.503927230835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3841571807861</t>
   </si>
   <si>
     <t xml:space="preserve">20.7594242095947</t>
   </si>
   <si>
-    <t xml:space="preserve">20.4719886779785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.7354755401611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.4240837097168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.1107387542725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.3582515716553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.5179424285889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.2943820953369</t>
+    <t xml:space="preserve">20.4719848632812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.7354698181152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.4240779876709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.1107425689697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.3582553863525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.517936706543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.2943782806396</t>
   </si>
   <si>
     <t xml:space="preserve">21.1027565002441</t>
   </si>
   <si>
-    <t xml:space="preserve">20.9270973205566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.5019702911377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.6057720184326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.3502674102783</t>
+    <t xml:space="preserve">20.927095413208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.5019760131836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.605770111084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.350269317627</t>
   </si>
   <si>
     <t xml:space="preserve">21.4939880371094</t>
   </si>
   <si>
-    <t xml:space="preserve">21.8053817749023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.7335186004639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.8453025817871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.1966190338135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.1806507110596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.7095642089844</t>
+    <t xml:space="preserve">21.8053779602051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.7335205078125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.8452987670898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.1966114044189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.1806449890137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.7095699310303</t>
   </si>
   <si>
     <t xml:space="preserve">22.2205677032471</t>
@@ -755,25 +755,25 @@
     <t xml:space="preserve">21.7894115447998</t>
   </si>
   <si>
-    <t xml:space="preserve">22.1087913513184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.9570865631104</t>
+    <t xml:space="preserve">22.1087875366211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.9570808410645</t>
   </si>
   <si>
     <t xml:space="preserve">21.9890213012695</t>
   </si>
   <si>
-    <t xml:space="preserve">21.7734394073486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.7814273834229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.7494888305664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.4620513916016</t>
+    <t xml:space="preserve">21.7734451293945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.7814292907715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.749490737915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.4620494842529</t>
   </si>
   <si>
     <t xml:space="preserve">21.6377086639404</t>
@@ -782,34 +782,34 @@
     <t xml:space="preserve">21.6137561798096</t>
   </si>
   <si>
-    <t xml:space="preserve">21.0069446563721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.086784362793</t>
+    <t xml:space="preserve">21.0069408416748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.0867805480957</t>
   </si>
   <si>
     <t xml:space="preserve">21.2544555664062</t>
   </si>
   <si>
-    <t xml:space="preserve">21.438102722168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.0708160400391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.4540691375732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.5578651428223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.4281673431396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.5399398803711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.595832824707</t>
+    <t xml:space="preserve">21.4380970001221</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.0708198547363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.4540672302246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.5578670501709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.428165435791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.5399417877197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.5958347320557</t>
   </si>
   <si>
     <t xml:space="preserve">22.8194007873535</t>
@@ -818,37 +818,37 @@
     <t xml:space="preserve">22.5638980865479</t>
   </si>
   <si>
-    <t xml:space="preserve">23.0509490966797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.1467590332031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.5539646148682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.5220222473145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.4501667022705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.8733406066895</t>
+    <t xml:space="preserve">23.0509452819824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.1467571258545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.5539627075195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.5220260620117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.4501686096191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.8733386993408</t>
   </si>
   <si>
     <t xml:space="preserve">23.9292297363281</t>
   </si>
   <si>
-    <t xml:space="preserve">23.8653526306152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.1687622070312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.2326354980469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.0889148712158</t>
+    <t xml:space="preserve">23.8653564453125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.1687602996826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.2326393127441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.0889186859131</t>
   </si>
   <si>
     <t xml:space="preserve">24.1847305297852</t>
@@ -857,28 +857,28 @@
     <t xml:space="preserve">24.3444194793701</t>
   </si>
   <si>
-    <t xml:space="preserve">24.6158885955811</t>
+    <t xml:space="preserve">24.6158847808838</t>
   </si>
   <si>
     <t xml:space="preserve">24.6079025268555</t>
   </si>
   <si>
-    <t xml:space="preserve">24.8554191589355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.9751853942871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.246654510498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.4382801055908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.4702186584473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.0071239471436</t>
+    <t xml:space="preserve">24.8554172515869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.9751873016357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.2466564178467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.4382839202881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.4702129364014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.0071220397949</t>
   </si>
   <si>
     <t xml:space="preserve">24.9272785186768</t>
@@ -887,139 +887,139 @@
     <t xml:space="preserve">25.1668109893799</t>
   </si>
   <si>
-    <t xml:space="preserve">25.3344841003418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.2785911560059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.6299057006836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.3983592987061</t>
+    <t xml:space="preserve">25.3344802856445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.2785930633545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.6299076080322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.3983573913574</t>
   </si>
   <si>
     <t xml:space="preserve">25.2067317962646</t>
   </si>
   <si>
-    <t xml:space="preserve">25.2865791320801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.3664226531982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.5899848937988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.9492797851562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.9652538299561</t>
+    <t xml:space="preserve">25.2865810394287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.3664207458496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.5899829864502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.9492874145508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.9652500152588</t>
   </si>
   <si>
     <t xml:space="preserve">26.2207508087158</t>
   </si>
   <si>
-    <t xml:space="preserve">26.0450916290283</t>
+    <t xml:space="preserve">26.045093536377</t>
   </si>
   <si>
     <t xml:space="preserve">26.0211429595947</t>
   </si>
   <si>
-    <t xml:space="preserve">26.4043941497803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.65989112854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.6119861602783</t>
+    <t xml:space="preserve">26.4043922424316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.6598892211914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.6119899749756</t>
   </si>
   <si>
     <t xml:space="preserve">26.3804397583008</t>
   </si>
   <si>
-    <t xml:space="preserve">26.6439208984375</t>
+    <t xml:space="preserve">26.6439266204834</t>
   </si>
   <si>
     <t xml:space="preserve">27.0351581573486</t>
   </si>
   <si>
-    <t xml:space="preserve">26.5002021789551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.6864261627197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.4685440063477</t>
+    <t xml:space="preserve">26.5002002716064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.6864242553711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.4685478210449</t>
   </si>
   <si>
     <t xml:space="preserve">27.4362697601318</t>
   </si>
   <si>
-    <t xml:space="preserve">27.7187023162842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.4443416595459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.7832489013672</t>
+    <t xml:space="preserve">27.7186965942383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.4443340301514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.7832584381104</t>
   </si>
   <si>
     <t xml:space="preserve">27.5573120117188</t>
   </si>
   <si>
-    <t xml:space="preserve">27.6218643188477</t>
+    <t xml:space="preserve">27.621862411499</t>
   </si>
   <si>
     <t xml:space="preserve">28.3481178283691</t>
   </si>
   <si>
-    <t xml:space="preserve">28.7435207366943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.7193164825439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.4455738067627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.5343379974365</t>
+    <t xml:space="preserve">28.743522644043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.7193088531494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.4455623626709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.5343341827393</t>
   </si>
   <si>
     <t xml:space="preserve">29.4536380767822</t>
   </si>
   <si>
-    <t xml:space="preserve">28.6628246307373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.8403663635254</t>
+    <t xml:space="preserve">28.6628303527832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.8403549194336</t>
   </si>
   <si>
     <t xml:space="preserve">28.9291172027588</t>
   </si>
   <si>
-    <t xml:space="preserve">28.8322887420654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.7757987976074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.9452610015869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.800012588501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.1389293670654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.3884677886963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.4852962493896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.8968410491943</t>
+    <t xml:space="preserve">28.8322830200195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.7758026123047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.9452590942383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.8000068664551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.1389312744141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.3884601593018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.4853019714355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.8968467712402</t>
   </si>
   <si>
     <t xml:space="preserve">30.5833702087402</t>
@@ -1028,148 +1028,148 @@
     <t xml:space="preserve">29.6230964660645</t>
   </si>
   <si>
-    <t xml:space="preserve">29.7441425323486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.2680435180664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.4375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.4697818756104</t>
+    <t xml:space="preserve">29.744140625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.2680416107178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.4374980926514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.4697780609131</t>
   </si>
   <si>
     <t xml:space="preserve">28.9371871948242</t>
   </si>
   <si>
-    <t xml:space="preserve">29.4052181243896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.074987411499</t>
+    <t xml:space="preserve">29.4052143096924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.0749912261963</t>
   </si>
   <si>
     <t xml:space="preserve">29.8893928527832</t>
   </si>
   <si>
-    <t xml:space="preserve">30.1072750091553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.3412799835205</t>
+    <t xml:space="preserve">30.1072692871094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.3412818908691</t>
   </si>
   <si>
     <t xml:space="preserve">30.0265731811523</t>
   </si>
   <si>
-    <t xml:space="preserve">30.1798915863037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.2519035339355</t>
+    <t xml:space="preserve">30.1798934936523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.2519016265869</t>
   </si>
   <si>
     <t xml:space="preserve">28.4610919952393</t>
   </si>
   <si>
-    <t xml:space="preserve">28.0818195343018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.5659961700439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.6386184692383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.2109336853027</t>
+    <t xml:space="preserve">28.0818252563477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.5659980773926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.6386203765869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.2109355926514</t>
   </si>
   <si>
     <t xml:space="preserve">28.1544532775879</t>
   </si>
   <si>
-    <t xml:space="preserve">28.436882019043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.2593574523926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.6063442230225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.3158397674561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.5902080535889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.6547546386719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.1147232055664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.1308574676514</t>
+    <t xml:space="preserve">28.4368858337402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.2593517303467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.6063461303711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.3158416748047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.5902004241943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.654764175415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.1147193908691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.1308631896973</t>
   </si>
   <si>
     <t xml:space="preserve">29.0663032531738</t>
   </si>
   <si>
-    <t xml:space="preserve">28.8080768585205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.6789703369141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.8565006256104</t>
+    <t xml:space="preserve">28.808084487915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.6789665222168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.8564968109131</t>
   </si>
   <si>
     <t xml:space="preserve">28.6951103210449</t>
   </si>
   <si>
-    <t xml:space="preserve">28.6305503845215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.7596607208252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.2512817382812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.9769172668457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.3561840057373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.4126758575439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.1786575317383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.2028675079346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.5337142944336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.283561706543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.5982761383057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.5014362335205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.3803958892822</t>
+    <t xml:space="preserve">28.6305484771729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.7596569061279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.2512874603271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.9769229888916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.3561916351318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.4126796722412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.1786556243896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.2028694152832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.533712387085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.2835597991943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.5982666015625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.5014381408691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.3803939819336</t>
   </si>
   <si>
     <t xml:space="preserve">28.7677307128906</t>
   </si>
   <si>
-    <t xml:space="preserve">29.0340251922607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.3325901031494</t>
+    <t xml:space="preserve">29.0340309143066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.3325996398926</t>
   </si>
   <si>
     <t xml:space="preserve">29.2115535736084</t>
@@ -1178,334 +1178,334 @@
     <t xml:space="preserve">29.1873416900635</t>
   </si>
   <si>
-    <t xml:space="preserve">29.3971519470215</t>
+    <t xml:space="preserve">29.3971481323242</t>
   </si>
   <si>
     <t xml:space="preserve">29.8409671783447</t>
   </si>
   <si>
-    <t xml:space="preserve">30.0346412658691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.9942970275879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.0992012023926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.2202396392822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.8490409851074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.0830516815186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.4058380126953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.5995044708252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.0352611541748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.5275020599365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.4387321472168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.3499717712402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.7937908172607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.471004486084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.7695846557617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.5839862823486</t>
+    <t xml:space="preserve">30.0346488952637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.9943027496338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.0991954803467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.2202453613281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.8490428924561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.0830574035645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.4058399200439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.5995025634766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.0352630615234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.5274925231934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.4387359619141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.3499641418457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.7937965393066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.4710140228271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.7695732116699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.5839786529541</t>
   </si>
   <si>
     <t xml:space="preserve">31.8018665313721</t>
   </si>
   <si>
-    <t xml:space="preserve">31.9067630767822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.9309635162354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.1649856567383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.1407852172852</t>
+    <t xml:space="preserve">31.9067707061768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.9309711456299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.1649932861328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.1407775878906</t>
   </si>
   <si>
     <t xml:space="preserve">32.3425140380859</t>
   </si>
   <si>
-    <t xml:space="preserve">32.1085052490234</t>
+    <t xml:space="preserve">32.1084976196289</t>
   </si>
   <si>
     <t xml:space="preserve">32.3586540222168</t>
   </si>
   <si>
-    <t xml:space="preserve">31.9632530212402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.011661529541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.8986949920654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.0439414978027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.2295417785645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.4232215881348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.9551773071289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.0358810424805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.1891899108887</t>
+    <t xml:space="preserve">31.9632453918457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.0116729736328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.8986930847168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.0439491271973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.229549407959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.423210144043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.9551753997803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.0358848571777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.1891937255859</t>
   </si>
   <si>
     <t xml:space="preserve">32.3667221069336</t>
   </si>
   <si>
-    <t xml:space="preserve">32.2053337097168</t>
+    <t xml:space="preserve">32.2053375244141</t>
   </si>
   <si>
     <t xml:space="preserve">32.4877700805664</t>
   </si>
   <si>
-    <t xml:space="preserve">32.1246376037598</t>
+    <t xml:space="preserve">32.1246452331543</t>
   </si>
   <si>
     <t xml:space="preserve">32.7621231079102</t>
   </si>
   <si>
-    <t xml:space="preserve">32.6491546630859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.1004295349121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.2779579162598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.4064598083496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.3176898956299</t>
+    <t xml:space="preserve">32.6491584777832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.1004257202148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.2779541015625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.4064540863037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.3176937103271</t>
   </si>
   <si>
     <t xml:space="preserve">31.1562995910645</t>
   </si>
   <si>
-    <t xml:space="preserve">31.414529800415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.8012371063232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.1805038452148</t>
+    <t xml:space="preserve">31.4145278930664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.8012409210205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.1805057525635</t>
   </si>
   <si>
     <t xml:space="preserve">30.6963424682617</t>
   </si>
   <si>
-    <t xml:space="preserve">31.2348728179932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.2756671905518</t>
+    <t xml:space="preserve">31.2348747253418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.2756748199463</t>
   </si>
   <si>
     <t xml:space="preserve">31.161434173584</t>
   </si>
   <si>
-    <t xml:space="preserve">31.2103977203369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.9982414245605</t>
+    <t xml:space="preserve">31.210391998291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.9982509613037</t>
   </si>
   <si>
     <t xml:space="preserve">30.9900817871094</t>
   </si>
   <si>
-    <t xml:space="preserve">30.6963386535645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.8432178497314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.7045001983643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.9166507720947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.6020526885986</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.2593479156494</t>
+    <t xml:space="preserve">30.6963405609131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.8432064056396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.7045021057129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.9166526794434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.6020545959473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.2593536376953</t>
   </si>
   <si>
     <t xml:space="preserve">31.0472030639648</t>
   </si>
   <si>
-    <t xml:space="preserve">31.5612545013428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.5204620361328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.5857353210449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.835054397583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.2067623138428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.8395843505859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.394437789917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.3781108856201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.8477420806885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.7416687011719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.1904392242432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.4597129821777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.5086727142334</t>
+    <t xml:space="preserve">31.5612525939941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.520450592041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.5857391357422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.8350601196289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.2067642211914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.83957862854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.3944320678711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.3781204223633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.8477458953857</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.7416667938232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.1904411315918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.4597091674805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.5086612701416</t>
   </si>
   <si>
     <t xml:space="preserve">30.2394046783447</t>
   </si>
   <si>
-    <t xml:space="preserve">30.4352283477783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.2883605957031</t>
+    <t xml:space="preserve">30.435230255127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.2883586883545</t>
   </si>
   <si>
     <t xml:space="preserve">30.7616157531738</t>
   </si>
   <si>
-    <t xml:space="preserve">31.3001499176025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.4306964874268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.5775756835938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.3491058349609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.1695995330811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.4959754943848</t>
+    <t xml:space="preserve">31.3001480102539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.4307022094727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.577579498291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.3491077423096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.1696014404297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.495979309082</t>
   </si>
   <si>
     <t xml:space="preserve">31.1043167114258</t>
   </si>
   <si>
-    <t xml:space="preserve">30.9411220550537</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.5494613647461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.7942581176758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.4633407592773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.8595333099365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.33278465271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.3128395080566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.9211730957031</t>
+    <t xml:space="preserve">30.9411239624023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.5494689941406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.7942562103271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.463342666626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.8595275878906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.3327884674072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.3128414154053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.9211807250977</t>
   </si>
   <si>
     <t xml:space="preserve">29.5539970397949</t>
   </si>
   <si>
-    <t xml:space="preserve">28.7870006561279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.1505508422852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.1550788879395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.362699508667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.0780143737793</t>
+    <t xml:space="preserve">28.7869968414307</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.1505451202393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.1550827026367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.3626956939697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.0780124664307</t>
   </si>
   <si>
     <t xml:space="preserve">25.1886234283447</t>
   </si>
   <si>
-    <t xml:space="preserve">24.6337699890137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.1686744689941</t>
+    <t xml:space="preserve">24.6337718963623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.1686820983887</t>
   </si>
   <si>
     <t xml:space="preserve">25.3518142700195</t>
   </si>
   <si>
-    <t xml:space="preserve">25.0335903167725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.4007740020752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.495059967041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.0707626342773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.9075679779053</t>
+    <t xml:space="preserve">25.0335922241211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.4007720947266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.4950580596924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.070764541626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.9075717926025</t>
   </si>
   <si>
     <t xml:space="preserve">23.7117366790771</t>
@@ -1514,109 +1514,109 @@
     <t xml:space="preserve">24.3971424102783</t>
   </si>
   <si>
-    <t xml:space="preserve">24.2339534759521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.0299663543701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.719898223877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.1405735015869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.5730266571045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.646463394165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.4216251373291</t>
+    <t xml:space="preserve">24.2339515686035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.0299625396729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.7199001312256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.1405715942383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.5730228424072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.6464614868164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.4216232299805</t>
   </si>
   <si>
     <t xml:space="preserve">24.3155479431152</t>
   </si>
   <si>
-    <t xml:space="preserve">24.552173614502</t>
+    <t xml:space="preserve">24.5521793365479</t>
   </si>
   <si>
     <t xml:space="preserve">24.2013149261475</t>
   </si>
   <si>
-    <t xml:space="preserve">23.7933349609375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.0626010894775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.9238872528076</t>
+    <t xml:space="preserve">23.7933368682861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.0626029968262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.9238891601562</t>
   </si>
   <si>
     <t xml:space="preserve">23.7035789489746</t>
   </si>
   <si>
-    <t xml:space="preserve">23.3363971710205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.2384872436523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.189525604248</t>
+    <t xml:space="preserve">23.3363952636719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.2384834289551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.1895236968994</t>
   </si>
   <si>
     <t xml:space="preserve">23.1568870544434</t>
   </si>
   <si>
-    <t xml:space="preserve">22.4551658630371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.8468246459961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.5485515594482</t>
+    <t xml:space="preserve">22.4551620483398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.8468227386475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.548547744751</t>
   </si>
   <si>
     <t xml:space="preserve">24.4624214172363</t>
   </si>
   <si>
-    <t xml:space="preserve">24.0870819091797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.3808212280273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.3563461303711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.0952415466309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.1278743743896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.9157314300537</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.2094764709473</t>
+    <t xml:space="preserve">24.0870800018311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.3808250427246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.3563442230225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.0952396392822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.1278762817383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.9157276153564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.20947265625</t>
   </si>
   <si>
     <t xml:space="preserve">24.1523551940918</t>
   </si>
   <si>
-    <t xml:space="preserve">24.3481884002686</t>
+    <t xml:space="preserve">24.3481864929199</t>
   </si>
   <si>
     <t xml:space="preserve">24.5551605224609</t>
   </si>
   <si>
-    <t xml:space="preserve">24.2902278900146</t>
+    <t xml:space="preserve">24.2902393341064</t>
   </si>
   <si>
     <t xml:space="preserve">24.5054836273193</t>
   </si>
   <si>
-    <t xml:space="preserve">24.4558143615723</t>
+    <t xml:space="preserve">24.4558124542236</t>
   </si>
   <si>
     <t xml:space="preserve">24.5468769073486</t>
@@ -1625,40 +1625,40 @@
     <t xml:space="preserve">25.5403461456299</t>
   </si>
   <si>
-    <t xml:space="preserve">25.3085384368896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.3747615814209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.5982971191406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.3333759307861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.4244422912598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.1512355804443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.2505855560303</t>
+    <t xml:space="preserve">25.3085346221924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.3747673034668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.5982990264893</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.3333740234375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.4244403839111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.1512413024902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.2505874633789</t>
   </si>
   <si>
     <t xml:space="preserve">25.5320682525635</t>
   </si>
   <si>
-    <t xml:space="preserve">25.4161643981934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.9277057647705</t>
+    <t xml:space="preserve">25.4161624908447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.9277095794678</t>
   </si>
   <si>
     <t xml:space="preserve">26.6248798370361</t>
   </si>
   <si>
-    <t xml:space="preserve">26.4261894226074</t>
+    <t xml:space="preserve">26.4261817932129</t>
   </si>
   <si>
     <t xml:space="preserve">26.6828308105469</t>
@@ -1667,40 +1667,40 @@
     <t xml:space="preserve">26.5503692626953</t>
   </si>
   <si>
-    <t xml:space="preserve">26.5089778900146</t>
+    <t xml:space="preserve">26.508975982666</t>
   </si>
   <si>
     <t xml:space="preserve">26.5669288635254</t>
   </si>
   <si>
-    <t xml:space="preserve">26.6000423431396</t>
+    <t xml:space="preserve">26.600040435791</t>
   </si>
   <si>
     <t xml:space="preserve">26.2440490722656</t>
   </si>
   <si>
-    <t xml:space="preserve">26.1115875244141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.2606067657471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.3433952331543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.2937240600586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.2540740966797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.3203067779541</t>
+    <t xml:space="preserve">26.1115837097168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.2606105804443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.3433971405029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.29372215271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.2540702819824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.3203048706055</t>
   </si>
   <si>
     <t xml:space="preserve">27.2789096832275</t>
   </si>
   <si>
-    <t xml:space="preserve">26.94775390625</t>
+    <t xml:space="preserve">26.9477577209473</t>
   </si>
   <si>
     <t xml:space="preserve">27.1298904418945</t>
@@ -1709,73 +1709,73 @@
     <t xml:space="preserve">27.187837600708</t>
   </si>
   <si>
-    <t xml:space="preserve">27.5686740875244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.1961212158203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.0636577606201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.7839202880859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.5455741882324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.2806510925293</t>
+    <t xml:space="preserve">27.5686721801758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.1961193084717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.0636558532715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.7839241027832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.5455760955811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.2806568145752</t>
   </si>
   <si>
     <t xml:space="preserve">28.3468894958496</t>
   </si>
   <si>
-    <t xml:space="preserve">27.50244140625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.4527702331543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.800479888916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.7673625946045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.1978702545166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.6876201629639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.7024345397949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.0418682098389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.3399124145508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.8035221099854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.0436115264893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.6645259857178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.6728096008301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.3582096099854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.449275970459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.8780345916748</t>
+    <t xml:space="preserve">27.5024452209473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.452766418457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.8004856109619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.7673645019531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.1978645324707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.6876163482666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.702428817749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.0418701171875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.3399066925049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.8035259246826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.0436134338379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.664529800415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.6728076934814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.3582057952881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.4492740631104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.8780307769775</t>
   </si>
   <si>
     <t xml:space="preserve">24.7538509368896</t>
@@ -1784,58 +1784,58 @@
     <t xml:space="preserve">24.8614768981934</t>
   </si>
   <si>
-    <t xml:space="preserve">25.8301067352295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.6893653869629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.9046154022217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.0619144439697</t>
+    <t xml:space="preserve">25.8301029205322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.6893615722656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.9046173095703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.061918258667</t>
   </si>
   <si>
     <t xml:space="preserve">26.0453567504883</t>
   </si>
   <si>
-    <t xml:space="preserve">25.7555999755859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.9128952026367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.4758625030518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.5006923675537</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.2357711791992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.5752010345459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.6993923187256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.9725933074951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.9891471862793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.8732452392578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.4924182891846</t>
+    <t xml:space="preserve">25.7555980682373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.912899017334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.4758586883545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.500696182251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.2357730865479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.5752067565918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.6993846893311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.9725914001465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.9891510009766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.8732433319092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.4924144744873</t>
   </si>
   <si>
     <t xml:space="preserve">26.2274932861328</t>
   </si>
   <si>
-    <t xml:space="preserve">25.6396884918213</t>
+    <t xml:space="preserve">25.6396942138672</t>
   </si>
   <si>
     <t xml:space="preserve">25.2754211425781</t>
@@ -1844,19 +1844,19 @@
     <t xml:space="preserve">25.5900173187256</t>
   </si>
   <si>
-    <t xml:space="preserve">25.4327163696289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.1926326751709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.9773826599121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.0022201538086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.1098442077637</t>
+    <t xml:space="preserve">25.4327201843262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.1926345825195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.9773807525635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.0022163391113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.109842300415</t>
   </si>
   <si>
     <t xml:space="preserve">24.9691028594971</t>
@@ -1868,34 +1868,34 @@
     <t xml:space="preserve">25.159517288208</t>
   </si>
   <si>
-    <t xml:space="preserve">25.2919769287109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.8863143920898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.2588634490967</t>
+    <t xml:space="preserve">25.2919807434082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.8863124847412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.2588653564453</t>
   </si>
   <si>
     <t xml:space="preserve">24.811803817749</t>
   </si>
   <si>
-    <t xml:space="preserve">24.6296691894531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.6710624694824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.563440322876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.3895816802979</t>
+    <t xml:space="preserve">24.6296653747559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.6710643768311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.5634384155273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.3895778656006</t>
   </si>
   <si>
     <t xml:space="preserve">24.2985134124756</t>
   </si>
   <si>
-    <t xml:space="preserve">24.1080989837646</t>
+    <t xml:space="preserve">24.1081008911133</t>
   </si>
   <si>
     <t xml:space="preserve">24.306791305542</t>
@@ -1904,79 +1904,79 @@
     <t xml:space="preserve">24.4475345611572</t>
   </si>
   <si>
-    <t xml:space="preserve">24.6131134033203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.1412143707275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.3564682006836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.4889240264893</t>
+    <t xml:space="preserve">24.6131076812744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.1412162780762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.356466293335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.4889297485352</t>
   </si>
   <si>
     <t xml:space="preserve">25.3830451965332</t>
   </si>
   <si>
-    <t xml:space="preserve">25.1181201934814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.7207355499268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.853199005127</t>
+    <t xml:space="preserve">25.1181240081787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.7207336425781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.8531970977783</t>
   </si>
   <si>
     <t xml:space="preserve">25.0187759399414</t>
   </si>
   <si>
-    <t xml:space="preserve">24.0915431976318</t>
+    <t xml:space="preserve">24.0915412902832</t>
   </si>
   <si>
     <t xml:space="preserve">23.9508037567139</t>
   </si>
   <si>
-    <t xml:space="preserve">23.8183422088623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.0004730224609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.1494960784912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.5220413208008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.8283634185791</t>
+    <t xml:space="preserve">23.8183403015137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.0004711151123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.1494922637939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.5220489501953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.8283596038818</t>
   </si>
   <si>
     <t xml:space="preserve">24.5882759094238</t>
   </si>
   <si>
-    <t xml:space="preserve">24.6627864837646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.2488384246826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.0850048065186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.606575012207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.7704086303711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.9111480712891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.9608249664307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.7952480316162</t>
+    <t xml:space="preserve">24.662784576416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.2488403320312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.0850067138672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.6065769195557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.7704124450684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.9111557006836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.9608192443848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.7952461242676</t>
   </si>
   <si>
     <t xml:space="preserve">24.9194297790527</t>
@@ -1985,106 +1985,106 @@
     <t xml:space="preserve">24.6959018707275</t>
   </si>
   <si>
-    <t xml:space="preserve">25.0270538330078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.7124576568604</t>
+    <t xml:space="preserve">25.0270519256592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.7124538421631</t>
   </si>
   <si>
     <t xml:space="preserve">24.5303230285645</t>
   </si>
   <si>
-    <t xml:space="preserve">23.9425182342529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.0087547302246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.1246566772461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.2087440490723</t>
+    <t xml:space="preserve">23.9425201416016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.0087566375732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.1246528625488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.2087459564209</t>
   </si>
   <si>
     <t xml:space="preserve">23.8639850616455</t>
   </si>
   <si>
-    <t xml:space="preserve">23.8555774688721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.4855937957764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.4771842956543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.5360431671143</t>
+    <t xml:space="preserve">23.855583190918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.4855899810791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.4771823883057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.5360469818115</t>
   </si>
   <si>
     <t xml:space="preserve">23.3426456451416</t>
   </si>
   <si>
-    <t xml:space="preserve">23.8892116546631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.2171535491943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.1919269561768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.0489768981934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.544454574585</t>
+    <t xml:space="preserve">23.8892097473145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.217155456543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.1919288635254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.0489749908447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.5444526672363</t>
   </si>
   <si>
     <t xml:space="preserve">23.6285419464111</t>
   </si>
   <si>
-    <t xml:space="preserve">23.4940052032471</t>
+    <t xml:space="preserve">23.4940032958984</t>
   </si>
   <si>
     <t xml:space="preserve">23.4603672027588</t>
   </si>
   <si>
-    <t xml:space="preserve">23.9060306549072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.880802154541</t>
+    <t xml:space="preserve">23.90602684021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.8808040618896</t>
   </si>
   <si>
     <t xml:space="preserve">24.1330661773682</t>
   </si>
   <si>
-    <t xml:space="preserve">24.3853321075439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.553503036499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.9318904876709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.4784622192383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.0754814147949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.4700527191162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.2430191040039</t>
+    <t xml:space="preserve">24.3853302001953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.5535049438477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.9318923950195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.4784641265869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.0754833221436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.4700565338135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.2430152893066</t>
   </si>
   <si>
     <t xml:space="preserve">25.0580253601074</t>
   </si>
   <si>
-    <t xml:space="preserve">25.3271007537842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.015983581543</t>
+    <t xml:space="preserve">25.3271102905273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.0159797668457</t>
   </si>
   <si>
     <t xml:space="preserve">24.8898506164551</t>
@@ -2093,10 +2093,10 @@
     <t xml:space="preserve">25.1589317321777</t>
   </si>
   <si>
-    <t xml:space="preserve">24.9150772094727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.7979927062988</t>
+    <t xml:space="preserve">24.9150791168213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.7979965209961</t>
   </si>
   <si>
     <t xml:space="preserve">25.8568553924561</t>
@@ -2105,19 +2105,19 @@
     <t xml:space="preserve">25.9913940429688</t>
   </si>
   <si>
-    <t xml:space="preserve">26.588415145874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.2352504730225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.8148136138916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.3691520690918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.1757469177246</t>
+    <t xml:space="preserve">26.5884170532227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.2352466583252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.814811706543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.3691482543945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.1757488250732</t>
   </si>
   <si>
     <t xml:space="preserve">25.2009754180908</t>
@@ -2132,61 +2132,61 @@
     <t xml:space="preserve">26.6052341461182</t>
   </si>
   <si>
-    <t xml:space="preserve">26.3866062164307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.0004444122314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.8749561309814</t>
+    <t xml:space="preserve">26.386604309082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.0004425048828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.8749504089355</t>
   </si>
   <si>
     <t xml:space="preserve">27.8329086303711</t>
   </si>
   <si>
-    <t xml:space="preserve">27.1433944702148</t>
+    <t xml:space="preserve">27.1433925628662</t>
   </si>
   <si>
     <t xml:space="preserve">26.6556835174561</t>
   </si>
   <si>
-    <t xml:space="preserve">26.9415836334229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.3115634918213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.1188068389893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.1860752105713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.4467430114746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.5560569763184</t>
+    <t xml:space="preserve">26.9415817260742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.3115673065186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.118803024292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.1860694885254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.4467468261719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.556058883667</t>
   </si>
   <si>
     <t xml:space="preserve">28.0431251525879</t>
   </si>
   <si>
-    <t xml:space="preserve">28.1944789886475</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.7992744445801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.6058731079102</t>
+    <t xml:space="preserve">28.1944808959961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.7992763519287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.6058712005615</t>
   </si>
   <si>
     <t xml:space="preserve">27.5806465148926</t>
   </si>
   <si>
-    <t xml:space="preserve">27.8160934448242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.6815509796143</t>
+    <t xml:space="preserve">27.8160915374756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.6815490722656</t>
   </si>
   <si>
     <t xml:space="preserve">27.8076820373535</t>
@@ -2195,67 +2195,67 @@
     <t xml:space="preserve">28.0094909667969</t>
   </si>
   <si>
-    <t xml:space="preserve">28.4635639190674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.589693069458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.5308303833008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.3962936401367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.3626556396484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.9008178710938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.0269412994385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.3801116943359</t>
+    <t xml:space="preserve">28.4635601043701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.5896987915039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.5308284759521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.3962955474854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.3626613616943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.9008140563965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.0269470214844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.3801155090332</t>
   </si>
   <si>
     <t xml:space="preserve">30.2966651916504</t>
   </si>
   <si>
-    <t xml:space="preserve">30.4143829345703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.8348274230957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.9020900726318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.7423324584961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.9687252044678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.0612201690674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.1789417266846</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.9014549255371</t>
+    <t xml:space="preserve">30.4143848419189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.8348255157471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.9020919799805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.7423362731934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.9687194824219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.0612182617188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.1789455413818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.901460647583</t>
   </si>
   <si>
     <t xml:space="preserve">28.8671855926514</t>
   </si>
   <si>
-    <t xml:space="preserve">29.1867141723633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.3885231018066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.9266815185547</t>
+    <t xml:space="preserve">29.186710357666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.3885250091553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.9266757965088</t>
   </si>
   <si>
     <t xml:space="preserve">30.1368999481201</t>
@@ -2264,61 +2264,61 @@
     <t xml:space="preserve">29.8341846466064</t>
   </si>
   <si>
-    <t xml:space="preserve">30.3471164703369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.38916015625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.1200923919678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.3218898773193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.4059791564941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.5152912139893</t>
+    <t xml:space="preserve">30.3471240997314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.3891620635986</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.1200847625732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.3218955993652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.4059753417969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.5152950286865</t>
   </si>
   <si>
     <t xml:space="preserve">30.3555297851562</t>
   </si>
   <si>
-    <t xml:space="preserve">29.8510036468506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.6181774139404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.2602672576904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.285831451416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.8567886352539</t>
+    <t xml:space="preserve">29.8510074615479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.6181755065918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.2602691650391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.2858276367188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.856782913208</t>
   </si>
   <si>
     <t xml:space="preserve">30.6522636413574</t>
   </si>
   <si>
-    <t xml:space="preserve">30.6693134307861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.8226947784424</t>
+    <t xml:space="preserve">30.6693058013916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.8226928710938</t>
   </si>
   <si>
     <t xml:space="preserve">30.8397369384766</t>
   </si>
   <si>
-    <t xml:space="preserve">30.2091388702393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.3880882263184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.0783405303955</t>
+    <t xml:space="preserve">30.2091426849365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.3880920410156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.0783443450928</t>
   </si>
   <si>
     <t xml:space="preserve">30.1409645080566</t>
@@ -2330,148 +2330,148 @@
     <t xml:space="preserve">28.8627223968506</t>
   </si>
   <si>
-    <t xml:space="preserve">29.4081020355225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.1068801879883</t>
+    <t xml:space="preserve">29.4081039428711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.1068725585938</t>
   </si>
   <si>
     <t xml:space="preserve">31.1720790863037</t>
   </si>
   <si>
-    <t xml:space="preserve">31.137996673584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.1465148925781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.5981693267822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.2572937011719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.8312149047852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.2658176422119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.9760818481445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.2061634063721</t>
+    <t xml:space="preserve">31.1379947662354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.1465129852295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.5981597900391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.2572956085205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.8312129974365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.2658100128174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.9760837554932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.2061672210693</t>
   </si>
   <si>
     <t xml:space="preserve">31.4021625518799</t>
   </si>
   <si>
-    <t xml:space="preserve">31.4958972930908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.5299949645996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.9731159210205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.9645900726318</t>
+    <t xml:space="preserve">31.4958992004395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.5299835205078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.9731101989746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.9645862579346</t>
   </si>
   <si>
     <t xml:space="preserve">32.382152557373</t>
   </si>
   <si>
-    <t xml:space="preserve">32.3480529785156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.4673652648926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.4503211975098</t>
+    <t xml:space="preserve">32.3480606079102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.4673690795898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.450325012207</t>
   </si>
   <si>
     <t xml:space="preserve">32.0668525695801</t>
   </si>
   <si>
-    <t xml:space="preserve">32.0498046875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.8708457946777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.5725975036621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.0527801513672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.5129489898682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.7856388092041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.862325668335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.9419975280762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.7630462646484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.2402572631836</t>
+    <t xml:space="preserve">32.0498085021973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.870849609375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.5725994110107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.0527763366699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.512939453125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.7856349945068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.8623275756836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.9420051574707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.7630443572998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.2402591705322</t>
   </si>
   <si>
     <t xml:space="preserve">31.3510360717773</t>
   </si>
   <si>
-    <t xml:space="preserve">31.6919021606445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.0327606201172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.1520652770996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.5951919555664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.1435356140137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.8252716064453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.8082275390625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.4899635314941</t>
+    <t xml:space="preserve">31.6919002532959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.0327644348145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.1520729064941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.5951843261719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.1435394287109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.8252754211426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.8082313537598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.4899597167969</t>
   </si>
   <si>
     <t xml:space="preserve">33.5155258178711</t>
   </si>
   <si>
-    <t xml:space="preserve">33.4132652282715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.788215637207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.7626533508301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.8904800415039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.0268173217773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.418815612793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.1716957092285</t>
+    <t xml:space="preserve">33.413257598877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.7882232666016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.7626457214355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.8904724121094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.0268249511719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.4188117980957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.171688079834</t>
   </si>
   <si>
     <t xml:space="preserve">34.2483825683594</t>
@@ -2480,76 +2480,76 @@
     <t xml:space="preserve">34.2057762145996</t>
   </si>
   <si>
-    <t xml:space="preserve">33.9075202941895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.5381202697754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.5551528930664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.7541275024414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.0894470214844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.1746559143066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.8308258056641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.9927406311035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.3876991271973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.1150169372559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.5525817871094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.0638732910156</t>
+    <t xml:space="preserve">33.9075126647949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.5381164550781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.5551605224609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.7541351318359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.0894546508789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.1746635437012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.8308296203613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.992733001709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.3876953125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.1150131225586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.5525856018066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.0638771057129</t>
   </si>
   <si>
     <t xml:space="preserve">33.2854423522949</t>
   </si>
   <si>
-    <t xml:space="preserve">32.9275321960449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.9586448669434</t>
+    <t xml:space="preserve">32.9275283813477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.9586524963379</t>
   </si>
   <si>
     <t xml:space="preserve">33.6689147949219</t>
   </si>
   <si>
-    <t xml:space="preserve">34.0694313049316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.0012626647949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.9130630493164</t>
+    <t xml:space="preserve">34.0694274902344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.0012550354004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.9130706787109</t>
   </si>
   <si>
     <t xml:space="preserve">34.2995147705078</t>
   </si>
   <si>
-    <t xml:space="preserve">33.967170715332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.5977668762207</t>
+    <t xml:space="preserve">33.9671745300293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.5977630615234</t>
   </si>
   <si>
     <t xml:space="preserve">34.4784660339355</t>
   </si>
   <si>
-    <t xml:space="preserve">34.5295944213867</t>
+    <t xml:space="preserve">34.5296020507812</t>
   </si>
   <si>
     <t xml:space="preserve">34.0353469848633</t>
@@ -2558,46 +2558,46 @@
     <t xml:space="preserve">34.0523910522461</t>
   </si>
   <si>
-    <t xml:space="preserve">32.5696258544922</t>
+    <t xml:space="preserve">32.5696220397949</t>
   </si>
   <si>
     <t xml:space="preserve">33.6263084411621</t>
   </si>
   <si>
-    <t xml:space="preserve">32.5440635681152</t>
+    <t xml:space="preserve">32.544059753418</t>
   </si>
   <si>
     <t xml:space="preserve">33.1064834594727</t>
   </si>
   <si>
-    <t xml:space="preserve">33.617790222168</t>
+    <t xml:space="preserve">33.6177825927734</t>
   </si>
   <si>
     <t xml:space="preserve">33.8393440246582</t>
   </si>
   <si>
-    <t xml:space="preserve">33.9160423278809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.3024940490723</t>
+    <t xml:space="preserve">33.9160499572754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.3024787902832</t>
   </si>
   <si>
     <t xml:space="preserve">33.6433448791504</t>
   </si>
   <si>
-    <t xml:space="preserve">33.5325736999512</t>
+    <t xml:space="preserve">33.5325584411621</t>
   </si>
   <si>
     <t xml:space="preserve">33.5410919189453</t>
   </si>
   <si>
-    <t xml:space="preserve">32.9360542297363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.6578197479248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.8282375335693</t>
+    <t xml:space="preserve">32.9360580444336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.6578121185303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.8282413482666</t>
   </si>
   <si>
     <t xml:space="preserve">31.3766002655029</t>
@@ -2606,154 +2606,154 @@
     <t xml:space="preserve">31.8112030029297</t>
   </si>
   <si>
-    <t xml:space="preserve">31.2743396759033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.5811252593994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.9305057525635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.5270195007324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.9219779968262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.1264991760254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.3425102233887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.1294784545898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.1550331115723</t>
+    <t xml:space="preserve">31.2743358612061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.5811195373535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.9305076599121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.5270156860352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.9219856262207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.1265029907227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.3425159454346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.1294746398926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.1550350189209</t>
   </si>
   <si>
     <t xml:space="preserve">31.4106864929199</t>
   </si>
   <si>
-    <t xml:space="preserve">31.6066913604736</t>
+    <t xml:space="preserve">31.6066837310791</t>
   </si>
   <si>
     <t xml:space="preserve">32.3991889953613</t>
   </si>
   <si>
-    <t xml:space="preserve">32.1009330749512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.1891231536865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.7174701690674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.4618129730225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.939022064209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.8964195251465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.2372817993164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.2969360351562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.0725326538086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.9344367980957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.8752021789551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.7112197875977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.2969245910645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.0897903442383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.3055610656738</t>
+    <t xml:space="preserve">32.1009368896484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.1891250610352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.7174663543701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.4618148803711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.9390316009521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.8964214324951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.2372856140137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.2969398498535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.0725288391113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.9344291687012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.8752098083496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.7112236022949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.296932220459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.0897941589355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.3055648803711</t>
   </si>
   <si>
     <t xml:space="preserve">32.6162796020508</t>
   </si>
   <si>
-    <t xml:space="preserve">32.2106246948242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.8579406738281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.209436416626</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.684139251709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.7445526123047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.5891933441162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.5287818908691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.5793838500977</t>
+    <t xml:space="preserve">32.2106285095215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.8579444885254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.2094326019287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.6841354370117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.7445545196533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.5892009735107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.5287837982178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.5793781280518</t>
   </si>
   <si>
     <t xml:space="preserve">31.0972347259521</t>
   </si>
   <si>
-    <t xml:space="preserve">31.2871189117432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.4597358703613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.4079513549805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.9862289428711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.5731239318848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.7543754577637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.4350280761719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.970142364502</t>
+    <t xml:space="preserve">31.2871170043945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.4597320556641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.4079475402832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.9862232208252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.573127746582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.7543716430664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.4350357055664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.9701499938965</t>
   </si>
   <si>
     <t xml:space="preserve">32.762996673584</t>
   </si>
   <si>
-    <t xml:space="preserve">32.426399230957</t>
+    <t xml:space="preserve">32.4264030456543</t>
   </si>
   <si>
     <t xml:space="preserve">33.0823516845703</t>
   </si>
   <si>
-    <t xml:space="preserve">32.5903816223145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.7025833129883</t>
+    <t xml:space="preserve">32.5903854370117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.7025909423828</t>
   </si>
   <si>
     <t xml:space="preserve">33.4793701171875</t>
@@ -2762,43 +2762,43 @@
     <t xml:space="preserve">33.4621047973633</t>
   </si>
   <si>
-    <t xml:space="preserve">33.4534759521484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.8504981994629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.3856239318848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.6778755187988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.0835380554199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.1612129211426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.5237121582031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.7999000549316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.7740135192871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.4632987976074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.2832412719727</t>
+    <t xml:space="preserve">33.4534797668457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.8505020141602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.3856201171875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.6778831481934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.0835342407227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.1612091064453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.5237083435059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.7999076843262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.7740097045898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.4633026123047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.2832374572754</t>
   </si>
   <si>
     <t xml:space="preserve">34.2561531066895</t>
   </si>
   <si>
-    <t xml:space="preserve">33.3412742614746</t>
+    <t xml:space="preserve">33.3412704467773</t>
   </si>
   <si>
     <t xml:space="preserve">33.9540748596191</t>
@@ -2810,49 +2810,49 @@
     <t xml:space="preserve">34.5409774780273</t>
   </si>
   <si>
-    <t xml:space="preserve">34.9552574157715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.6877021789551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.0329437255859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.317756652832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.654369354248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.3868064880371</t>
+    <t xml:space="preserve">34.9552536010742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.6876983642578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.0329360961914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.3177604675293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.6543617248535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.3867988586426</t>
   </si>
   <si>
     <t xml:space="preserve">34.8257942199707</t>
   </si>
   <si>
-    <t xml:space="preserve">35.4731101989746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.8442459106445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36.387996673584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.0674591064453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.2204437255859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.3499069213867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.342472076416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.3597297668457</t>
+    <t xml:space="preserve">35.4731178283691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.8442420959473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.3879928588867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.0674667358398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.2204475402832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.3499031066895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.3424644470215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.3597373962402</t>
   </si>
   <si>
     <t xml:space="preserve">33.3844299316406</t>
@@ -2864,34 +2864,34 @@
     <t xml:space="preserve">33.8677673339844</t>
   </si>
   <si>
-    <t xml:space="preserve">33.9713401794434</t>
+    <t xml:space="preserve">33.9713363647461</t>
   </si>
   <si>
     <t xml:space="preserve">33.306755065918</t>
   </si>
   <si>
-    <t xml:space="preserve">31.7790794372559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.64723777771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.1984310150146</t>
+    <t xml:space="preserve">31.7790775299072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.6472339630127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.1984329223633</t>
   </si>
   <si>
     <t xml:space="preserve">24.3910045623779</t>
   </si>
   <si>
-    <t xml:space="preserve">28.9567642211914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.5597438812256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.4918842315674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.0356311798096</t>
+    <t xml:space="preserve">28.95676612854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.559741973877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.4918823242188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.0356330871582</t>
   </si>
   <si>
     <t xml:space="preserve">30.4067611694336</t>
@@ -2900,40 +2900,40 @@
     <t xml:space="preserve">30.4153938293457</t>
   </si>
   <si>
-    <t xml:space="preserve">30.147834777832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.1835441589355</t>
+    <t xml:space="preserve">30.1478290557861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.1835460662842</t>
   </si>
   <si>
     <t xml:space="preserve">31.3734264373779</t>
   </si>
   <si>
-    <t xml:space="preserve">33.7728309631348</t>
+    <t xml:space="preserve">33.7728233337402</t>
   </si>
   <si>
     <t xml:space="preserve">33.2636032104492</t>
   </si>
   <si>
-    <t xml:space="preserve">32.5385971069336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.9615173339844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.9948501586914</t>
+    <t xml:space="preserve">32.5386009216309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.9615135192871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.9948616027832</t>
   </si>
   <si>
     <t xml:space="preserve">32.4954452514648</t>
   </si>
   <si>
-    <t xml:space="preserve">32.2537727355957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.710033416748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.6076469421387</t>
+    <t xml:space="preserve">32.2537803649902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.7100372314453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.6076545715332</t>
   </si>
   <si>
     <t xml:space="preserve">33.2290725708008</t>
@@ -2945,31 +2945,31 @@
     <t xml:space="preserve">32.5817565917969</t>
   </si>
   <si>
-    <t xml:space="preserve">33.4966316223145</t>
+    <t xml:space="preserve">33.4966354370117</t>
   </si>
   <si>
     <t xml:space="preserve">32.935619354248</t>
   </si>
   <si>
-    <t xml:space="preserve">33.3240089416504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.0564651489258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.7296752929688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.2573394775391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.2388916015625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.0749015808105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.9466285705566</t>
+    <t xml:space="preserve">33.3240127563477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.056453704834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.7296600341797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.2573356628418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.238899230957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.0748977661133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.9466323852539</t>
   </si>
   <si>
     <t xml:space="preserve">34.4201431274414</t>
@@ -2978,25 +2978,25 @@
     <t xml:space="preserve">35.3091278076172</t>
   </si>
   <si>
-    <t xml:space="preserve">35.7320442199707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.9760856628418</t>
+    <t xml:space="preserve">35.732048034668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.9760780334473</t>
   </si>
   <si>
     <t xml:space="preserve">37.2165603637695</t>
   </si>
   <si>
-    <t xml:space="preserve">37.7085227966309</t>
+    <t xml:space="preserve">37.7085266113281</t>
   </si>
   <si>
     <t xml:space="preserve">36.5088310241699</t>
   </si>
   <si>
-    <t xml:space="preserve">38.7183494567871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.8231353759766</t>
+    <t xml:space="preserve">38.7183418273926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.8231315612793</t>
   </si>
   <si>
     <t xml:space="preserve">35.6882858276367</t>
@@ -3005,7 +3005,7 @@
     <t xml:space="preserve">36.2908096313477</t>
   </si>
   <si>
-    <t xml:space="preserve">35.9589805603027</t>
+    <t xml:space="preserve">35.9589881896973</t>
   </si>
   <si>
     <t xml:space="preserve">36.8147354125977</t>
@@ -3014,64 +3014,64 @@
     <t xml:space="preserve">36.7623405456543</t>
   </si>
   <si>
-    <t xml:space="preserve">36.9719123840332</t>
+    <t xml:space="preserve">36.9719161987305</t>
   </si>
   <si>
     <t xml:space="preserve">36.0899696350098</t>
   </si>
   <si>
-    <t xml:space="preserve">36.48291015625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.7319526672363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.4961814880371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.9065895080566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.8280029296875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36.3955917358398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36.1074256896973</t>
+    <t xml:space="preserve">36.4829139709473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.7319488525391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.4961891174316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.9065933227539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.8279991149902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.3955955505371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.1074371337891</t>
   </si>
   <si>
     <t xml:space="preserve">35.9939155578613</t>
   </si>
   <si>
-    <t xml:space="preserve">36.2209510803223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36.578971862793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.4001312255859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.417594909668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36.2820777893066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.1814880371094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.5129699707031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.6222953796387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.6352233886719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.6526832580566</t>
+    <t xml:space="preserve">36.2209548950195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.5789680480957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.4001274108887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.4175987243652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.2820701599121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.1814918518066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.5129623413086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.6222915649414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.6352195739746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.6526870727539</t>
   </si>
   <si>
     <t xml:space="preserve">40.2901344299316</t>
@@ -3083,40 +3083,40 @@
     <t xml:space="preserve">39.4605751037598</t>
   </si>
   <si>
-    <t xml:space="preserve">39.2160797119141</t>
+    <t xml:space="preserve">39.2160758972168</t>
   </si>
   <si>
     <t xml:space="preserve">38.8143997192383</t>
   </si>
   <si>
-    <t xml:space="preserve">39.6614074707031</t>
+    <t xml:space="preserve">39.6614151000977</t>
   </si>
   <si>
     <t xml:space="preserve">39.9321136474609</t>
   </si>
   <si>
-    <t xml:space="preserve">40.0281677246094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40.7267417907715</t>
+    <t xml:space="preserve">40.0281715393066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40.726734161377</t>
   </si>
   <si>
     <t xml:space="preserve">40.1591529846191</t>
   </si>
   <si>
-    <t xml:space="preserve">40.1678848266602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40.2988624572754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.8185882568359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40.7616729736328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.0585594177246</t>
+    <t xml:space="preserve">40.1678810119629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40.2988662719727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.8185958862305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40.7616691589355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.0585632324219</t>
   </si>
   <si>
     <t xml:space="preserve">41.3903846740723</t>
@@ -3125,31 +3125,31 @@
     <t xml:space="preserve">41.5737609863281</t>
   </si>
   <si>
-    <t xml:space="preserve">42.1937408447266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.5779571533203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.2024765014648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.6174240112305</t>
+    <t xml:space="preserve">42.1937370300293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.5779495239258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.2024726867676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.6174125671387</t>
   </si>
   <si>
     <t xml:space="preserve">42.0365562438965</t>
   </si>
   <si>
-    <t xml:space="preserve">41.0061798095703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.3205261230469</t>
+    <t xml:space="preserve">41.0061721801758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.3205223083496</t>
   </si>
   <si>
     <t xml:space="preserve">41.3292579650879</t>
   </si>
   <si>
-    <t xml:space="preserve">41.137149810791</t>
+    <t xml:space="preserve">41.1371459960938</t>
   </si>
   <si>
     <t xml:space="preserve">39.8884544372559</t>
@@ -3167,70 +3167,70 @@
     <t xml:space="preserve">38.9977722167969</t>
   </si>
   <si>
-    <t xml:space="preserve">38.9628410339355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.1374855041504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.8929862976074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40.342529296875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.3557929992676</t>
+    <t xml:space="preserve">38.9628448486328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.1374893188477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.8929901123047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40.3425254821777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.3557968139648</t>
   </si>
   <si>
     <t xml:space="preserve">40.0718269348145</t>
   </si>
   <si>
-    <t xml:space="preserve">39.8360633850098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.5566329956055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40.2552032470703</t>
+    <t xml:space="preserve">39.8360595703125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.5566291809082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40.255199432373</t>
   </si>
   <si>
     <t xml:space="preserve">40.6044883728027</t>
   </si>
   <si>
-    <t xml:space="preserve">39.6439476013184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.8797225952148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.5915641784668</t>
+    <t xml:space="preserve">39.6439552307129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.8797149658203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.5915603637695</t>
   </si>
   <si>
     <t xml:space="preserve">39.9845085144043</t>
   </si>
   <si>
-    <t xml:space="preserve">39.2422676086426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.7532806396484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.4693145751953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.3690567016602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.4518432617188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.1636810302734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.416919708252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.4955062866211</t>
+    <t xml:space="preserve">39.2422714233398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.7532768249512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.4693183898926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.3690605163574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.451847076416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.1636772155762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.4169158935547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.4955101013184</t>
   </si>
   <si>
     <t xml:space="preserve">39.0588989257812</t>
@@ -3239,22 +3239,22 @@
     <t xml:space="preserve">38.7358093261719</t>
   </si>
   <si>
-    <t xml:space="preserve">39.198616027832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.1549491882324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.093822479248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.2859306335449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.9715728759766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.1944122314453</t>
+    <t xml:space="preserve">39.1986122131348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.1549530029297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.0938262939453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.2859420776367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.9715766906738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.1944198608398</t>
   </si>
   <si>
     <t xml:space="preserve">38.3253936767578</t>
@@ -3263,55 +3263,55 @@
     <t xml:space="preserve">38.5087738037109</t>
   </si>
   <si>
-    <t xml:space="preserve">39.8535232543945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40.0107078552246</t>
+    <t xml:space="preserve">39.8535194396973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40.0107002258301</t>
   </si>
   <si>
     <t xml:space="preserve">40.7878646850586</t>
   </si>
   <si>
-    <t xml:space="preserve">40.4822387695312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40.5346298217773</t>
+    <t xml:space="preserve">40.4822425842285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40.5346221923828</t>
   </si>
   <si>
     <t xml:space="preserve">40.2639350891113</t>
   </si>
   <si>
-    <t xml:space="preserve">41.2593994140625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40.7005386352539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.3030586242676</t>
+    <t xml:space="preserve">41.2594032287598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40.7005424499512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.3030548095703</t>
   </si>
   <si>
     <t xml:space="preserve">40.9799728393555</t>
   </si>
   <si>
-    <t xml:space="preserve">41.6960067749023</t>
+    <t xml:space="preserve">41.6960029602051</t>
   </si>
   <si>
     <t xml:space="preserve">41.6785430908203</t>
   </si>
   <si>
-    <t xml:space="preserve">41.669807434082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40.9537734985352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40.4560394287109</t>
+    <t xml:space="preserve">41.6698112487793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40.9537773132324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40.4560432434082</t>
   </si>
   <si>
     <t xml:space="preserve">38.8493270874023</t>
   </si>
   <si>
-    <t xml:space="preserve">37.356128692627</t>
+    <t xml:space="preserve">37.3561248779297</t>
   </si>
   <si>
     <t xml:space="preserve">39.3383255004883</t>
@@ -3323,22 +3323,22 @@
     <t xml:space="preserve">40.4385757446289</t>
   </si>
   <si>
-    <t xml:space="preserve">40.0980186462402</t>
+    <t xml:space="preserve">40.0980224609375</t>
   </si>
   <si>
     <t xml:space="preserve">38.8405990600586</t>
   </si>
   <si>
-    <t xml:space="preserve">39.8273277282715</t>
+    <t xml:space="preserve">39.8273239135742</t>
   </si>
   <si>
     <t xml:space="preserve">40.0892944335938</t>
   </si>
   <si>
-    <t xml:space="preserve">41.2943229675293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40.7965965270996</t>
+    <t xml:space="preserve">41.2943267822266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40.7966003417969</t>
   </si>
   <si>
     <t xml:space="preserve">40.3250579833984</t>
@@ -3347,31 +3347,31 @@
     <t xml:space="preserve">40.3949165344238</t>
   </si>
   <si>
-    <t xml:space="preserve">39.7151908874512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.6912002563477</t>
+    <t xml:space="preserve">39.7151985168457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.6911964416504</t>
   </si>
   <si>
     <t xml:space="preserve">39.2120208740234</t>
   </si>
   <si>
-    <t xml:space="preserve">39.6004371643066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.9976806640625</t>
+    <t xml:space="preserve">39.6004333496094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.9976768493652</t>
   </si>
   <si>
     <t xml:space="preserve">39.3973999023438</t>
   </si>
   <si>
-    <t xml:space="preserve">38.655891418457</t>
+    <t xml:space="preserve">38.6558876037598</t>
   </si>
   <si>
     <t xml:space="preserve">37.9938201904297</t>
   </si>
   <si>
-    <t xml:space="preserve">37.9055480957031</t>
+    <t xml:space="preserve">37.9055442810059</t>
   </si>
   <si>
     <t xml:space="preserve">38.1262283325195</t>
@@ -3380,31 +3380,31 @@
     <t xml:space="preserve">38.5411338806152</t>
   </si>
   <si>
-    <t xml:space="preserve">38.9471893310547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.8147850036621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.8589248657227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.5209846496582</t>
+    <t xml:space="preserve">38.947193145752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.8147888183594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.8589210510254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.5209884643555</t>
   </si>
   <si>
     <t xml:space="preserve">38.3469200134277</t>
   </si>
   <si>
-    <t xml:space="preserve">39.1855430603027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.8500862121582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.2561683654785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.0972595214844</t>
+    <t xml:space="preserve">39.1855392456055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.8500938415527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.2561645507812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.0972671508789</t>
   </si>
   <si>
     <t xml:space="preserve">39.4768486022949</t>
@@ -3413,64 +3413,64 @@
     <t xml:space="preserve">39.7240219116211</t>
   </si>
   <si>
-    <t xml:space="preserve">40.0153312683105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.8652648925781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.4528541564941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.0051307678223</t>
+    <t xml:space="preserve">40.0153350830078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.8652610778809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.4528579711914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.005126953125</t>
   </si>
   <si>
     <t xml:space="preserve">37.773136138916</t>
   </si>
   <si>
-    <t xml:space="preserve">37.817268371582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.8349227905273</t>
+    <t xml:space="preserve">37.8172760009766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.8349266052246</t>
   </si>
   <si>
     <t xml:space="preserve">38.5058174133301</t>
   </si>
   <si>
-    <t xml:space="preserve">38.6823692321777</t>
+    <t xml:space="preserve">38.682373046875</t>
   </si>
   <si>
     <t xml:space="preserve">38.5499534606934</t>
   </si>
   <si>
-    <t xml:space="preserve">38.585262298584</t>
+    <t xml:space="preserve">38.5852661132812</t>
   </si>
   <si>
     <t xml:space="preserve">38.4175453186035</t>
   </si>
   <si>
-    <t xml:space="preserve">37.5612754821777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.6495475769043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.8967132568359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.4465065002441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.5259590148926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.5171318054199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.1905097961426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.7113418579102</t>
+    <t xml:space="preserve">37.5612678527832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.6495399475098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.8967170715332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.4465103149414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.5259552001953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.5171356201172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.1905136108398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.7113456726074</t>
   </si>
   <si>
     <t xml:space="preserve">38.3822288513184</t>
@@ -3479,112 +3479,112 @@
     <t xml:space="preserve">38.9030609130859</t>
   </si>
   <si>
-    <t xml:space="preserve">38.7882995605469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.3557510375977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.618091583252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40.0771217346191</t>
+    <t xml:space="preserve">38.7883033752441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.3557548522949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.6180877685547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40.0771255493164</t>
   </si>
   <si>
     <t xml:space="preserve">40.2360229492188</t>
   </si>
   <si>
-    <t xml:space="preserve">39.944709777832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.9800224304199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.5827789306641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.061954498291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.8412666320801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.6117477416992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.6647186279297</t>
+    <t xml:space="preserve">39.9447059631348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.9800186157227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.5827827453613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.0619468688965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.8412590026855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.6117553710938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.6647109985352</t>
   </si>
   <si>
     <t xml:space="preserve">37.3582382202148</t>
   </si>
   <si>
-    <t xml:space="preserve">37.4729919433594</t>
+    <t xml:space="preserve">37.4730033874512</t>
   </si>
   <si>
     <t xml:space="preserve">37.84375</t>
   </si>
   <si>
-    <t xml:space="preserve">37.7819633483887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.1993446350098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.464168548584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.6671981811523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.9673347473145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.5764350891113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.2674751281738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.5298156738281</t>
+    <t xml:space="preserve">37.7819595336914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.199333190918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.4641647338867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.6671943664551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.967342376709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.5764389038086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.2674789428711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.5298118591309</t>
   </si>
   <si>
     <t xml:space="preserve">39.8564376831055</t>
   </si>
   <si>
-    <t xml:space="preserve">39.1325798034668</t>
+    <t xml:space="preserve">39.1325721740723</t>
   </si>
   <si>
     <t xml:space="preserve">39.8387794494629</t>
   </si>
   <si>
-    <t xml:space="preserve">39.3091201782227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.9182243347168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.6710510253906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.6622352600098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.4945106506348</t>
+    <t xml:space="preserve">39.3091239929199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.9182319641113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.6710548400879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.6622314453125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.4945030212402</t>
   </si>
   <si>
     <t xml:space="preserve">39.9094047546387</t>
   </si>
   <si>
-    <t xml:space="preserve">40.1477470397949</t>
+    <t xml:space="preserve">40.1477508544922</t>
   </si>
   <si>
     <t xml:space="preserve">39.8917427062988</t>
   </si>
   <si>
-    <t xml:space="preserve">39.8740921020508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40.2889862060547</t>
+    <t xml:space="preserve">39.8740844726562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40.2889823913574</t>
   </si>
   <si>
     <t xml:space="preserve">40.4920196533203</t>
@@ -3596,40 +3596,40 @@
     <t xml:space="preserve">40.7480201721191</t>
   </si>
   <si>
-    <t xml:space="preserve">40.5361518859863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40.1300888061523</t>
+    <t xml:space="preserve">40.5361557006836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40.1300849914551</t>
   </si>
   <si>
     <t xml:space="preserve">40.0506401062012</t>
   </si>
   <si>
-    <t xml:space="preserve">40.2183647155762</t>
+    <t xml:space="preserve">40.2183609008789</t>
   </si>
   <si>
     <t xml:space="preserve">40.2007102966309</t>
   </si>
   <si>
-    <t xml:space="preserve">40.3596076965332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40.5096740722656</t>
+    <t xml:space="preserve">40.3596038818359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40.5096778869629</t>
   </si>
   <si>
     <t xml:space="preserve">40.5626411437988</t>
   </si>
   <si>
-    <t xml:space="preserve">41.6042900085449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.5071868896484</t>
+    <t xml:space="preserve">41.6042938232422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.507194519043</t>
   </si>
   <si>
     <t xml:space="preserve">41.0834693908691</t>
   </si>
   <si>
-    <t xml:space="preserve">41.0128440856934</t>
+    <t xml:space="preserve">41.0128479003906</t>
   </si>
   <si>
     <t xml:space="preserve">40.7568435668945</t>
@@ -3641,34 +3641,34 @@
     <t xml:space="preserve">40.3684349060059</t>
   </si>
   <si>
-    <t xml:space="preserve">40.4655380249023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40.4302291870117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40.4832000732422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.7416877746582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.5474739074707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.6470603942871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.5676078796387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.8942375183105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.017822265625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.6975440979004</t>
+    <t xml:space="preserve">40.4655418395996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40.4302253723145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40.4831924438477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.7416763305664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.5474700927734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.6470565795898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.5676116943359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.8942337036133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.0178146362305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.6975402832031</t>
   </si>
   <si>
     <t xml:space="preserve">40.0065040588379</t>
@@ -3680,16 +3680,16 @@
     <t xml:space="preserve">41.0393333435059</t>
   </si>
   <si>
-    <t xml:space="preserve">41.128662109375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.3787879943848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.0393257141113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40.4854698181152</t>
+    <t xml:space="preserve">41.1286659240723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.3787956237793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.0393295288086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40.485466003418</t>
   </si>
   <si>
     <t xml:space="preserve">40.9053344726562</t>
@@ -3701,31 +3701,31 @@
     <t xml:space="preserve">40.6016044616699</t>
   </si>
   <si>
-    <t xml:space="preserve">40.4050674438477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40.860668182373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.2001266479492</t>
+    <t xml:space="preserve">40.4050750732422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40.8606643676758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.2001304626465</t>
   </si>
   <si>
     <t xml:space="preserve">41.9505233764648</t>
   </si>
   <si>
-    <t xml:space="preserve">42.2899856567383</t>
+    <t xml:space="preserve">42.289981842041</t>
   </si>
   <si>
     <t xml:space="preserve">42.7009124755859</t>
   </si>
   <si>
-    <t xml:space="preserve">42.316780090332</t>
+    <t xml:space="preserve">42.3167877197266</t>
   </si>
   <si>
     <t xml:space="preserve">42.5311851501465</t>
   </si>
   <si>
-    <t xml:space="preserve">42.6205062866211</t>
+    <t xml:space="preserve">42.6205101013184</t>
   </si>
   <si>
     <t xml:space="preserve">42.8527755737305</t>
@@ -3734,7 +3734,7 @@
     <t xml:space="preserve">43.2458381652832</t>
   </si>
   <si>
-    <t xml:space="preserve">43.326244354248</t>
+    <t xml:space="preserve">43.3262367248535</t>
   </si>
   <si>
     <t xml:space="preserve">43.0314407348633</t>
@@ -3743,64 +3743,64 @@
     <t xml:space="preserve">42.9510459899902</t>
   </si>
   <si>
-    <t xml:space="preserve">42.486515045166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43.1029090881348</t>
+    <t xml:space="preserve">42.4865112304688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43.1029014587402</t>
   </si>
   <si>
     <t xml:space="preserve">43.120777130127</t>
   </si>
   <si>
-    <t xml:space="preserve">43.2637023925781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43.2547760009766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43.0582466125488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43.5406455993652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43.4781036376953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43.4602432250977</t>
+    <t xml:space="preserve">43.2637100219727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43.2547721862793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43.0582389831543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43.540641784668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43.478099822998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43.4602355957031</t>
   </si>
   <si>
     <t xml:space="preserve">44.7555618286133</t>
   </si>
   <si>
-    <t xml:space="preserve">46.2206153869629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">44.8448905944824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.9888687133789</t>
+    <t xml:space="preserve">46.2206115722656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44.8448867797852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.9888725280762</t>
   </si>
   <si>
     <t xml:space="preserve">46.2563438415527</t>
   </si>
   <si>
-    <t xml:space="preserve">45.8811492919922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.1307525634766</t>
+    <t xml:space="preserve">45.8811531066895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.1307601928711</t>
   </si>
   <si>
     <t xml:space="preserve">45.1486282348633</t>
   </si>
   <si>
-    <t xml:space="preserve">44.6304893493652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">44.4786262512207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.2200889587402</t>
+    <t xml:space="preserve">44.6304931640625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44.478630065918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.220085144043</t>
   </si>
   <si>
     <t xml:space="preserve">45.3272819519043</t>
@@ -3815,37 +3815,37 @@
     <t xml:space="preserve">45.5595474243164</t>
   </si>
   <si>
-    <t xml:space="preserve">46.4528770446777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.9883422851562</t>
+    <t xml:space="preserve">46.4528694152832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.9883460998535</t>
   </si>
   <si>
     <t xml:space="preserve">46.6136741638184</t>
   </si>
   <si>
-    <t xml:space="preserve">47.0424652099609</t>
+    <t xml:space="preserve">47.0424690246582</t>
   </si>
   <si>
     <t xml:space="preserve">47.614200592041</t>
   </si>
   <si>
-    <t xml:space="preserve">48.1501884460449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">48.0608596801758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">49.0792465209961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">49.043514251709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50.1869735717773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50.4192352294922</t>
+    <t xml:space="preserve">48.1501922607422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">48.0608558654785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">49.0792503356934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">49.0435218811035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50.1869773864746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50.4192390441895</t>
   </si>
   <si>
     <t xml:space="preserve">50.7765617370605</t>
@@ -3854,13 +3854,13 @@
     <t xml:space="preserve">51.0624351501465</t>
   </si>
   <si>
-    <t xml:space="preserve">50.5085678100586</t>
+    <t xml:space="preserve">50.5085716247559</t>
   </si>
   <si>
     <t xml:space="preserve">50.79443359375</t>
   </si>
   <si>
-    <t xml:space="preserve">50.9730911254883</t>
+    <t xml:space="preserve">50.9730949401855</t>
   </si>
   <si>
     <t xml:space="preserve">51.3125648498535</t>
@@ -3869,7 +3869,7 @@
     <t xml:space="preserve">50.6693687438965</t>
   </si>
   <si>
-    <t xml:space="preserve">49.9904327392578</t>
+    <t xml:space="preserve">49.9904441833496</t>
   </si>
   <si>
     <t xml:space="preserve">49.5795135498047</t>
@@ -3881,28 +3881,28 @@
     <t xml:space="preserve">49.9011116027832</t>
   </si>
   <si>
-    <t xml:space="preserve">49.633113861084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">49.7581748962402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">49.5437812805176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">49.954704284668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">48.8291206359863</t>
+    <t xml:space="preserve">49.6331100463867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">49.758171081543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">49.5437774658203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">49.9547119140625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">48.8291244506836</t>
   </si>
   <si>
     <t xml:space="preserve">48.1144638061523</t>
   </si>
   <si>
-    <t xml:space="preserve">47.2568626403809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.9531440734863</t>
+    <t xml:space="preserve">47.2568702697754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.9531364440918</t>
   </si>
   <si>
     <t xml:space="preserve">46.8816719055176</t>
@@ -3911,82 +3911,82 @@
     <t xml:space="preserve">45.6488838195801</t>
   </si>
   <si>
-    <t xml:space="preserve">46.3278121948242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.2022171020508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">44.6840972900391</t>
+    <t xml:space="preserve">46.327808380127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.202220916748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44.6840896606445</t>
   </si>
   <si>
     <t xml:space="preserve">45.613151550293</t>
   </si>
   <si>
-    <t xml:space="preserve">45.1843566894531</t>
+    <t xml:space="preserve">45.1843528747559</t>
   </si>
   <si>
     <t xml:space="preserve">45.7203483581543</t>
   </si>
   <si>
-    <t xml:space="preserve">45.4344902038574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43.7014350891113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43.763973236084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">44.9163627624512</t>
+    <t xml:space="preserve">45.4344787597656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43.7014389038086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43.7639770507812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44.9163551330566</t>
   </si>
   <si>
     <t xml:space="preserve">44.1034317016602</t>
   </si>
   <si>
-    <t xml:space="preserve">43.6925086975098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43.9426307678223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43.7461013793945</t>
+    <t xml:space="preserve">43.6925048828125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43.9426345825195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43.7461051940918</t>
   </si>
   <si>
     <t xml:space="preserve">43.6746368408203</t>
   </si>
   <si>
-    <t xml:space="preserve">44.1391677856445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">44.2731666564941</t>
+    <t xml:space="preserve">44.1391716003418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44.2731628417969</t>
   </si>
   <si>
     <t xml:space="preserve">45.416618347168</t>
   </si>
   <si>
-    <t xml:space="preserve">45.6846160888672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.6310157775879</t>
+    <t xml:space="preserve">45.6846122741699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.6310195922852</t>
   </si>
   <si>
     <t xml:space="preserve">45.9168853759766</t>
   </si>
   <si>
-    <t xml:space="preserve">46.1848793029785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.4886093139648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">47.0960693359375</t>
+    <t xml:space="preserve">46.1848678588867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.4886131286621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">47.0960731506348</t>
   </si>
   <si>
     <t xml:space="preserve">46.8280715942383</t>
   </si>
   <si>
-    <t xml:space="preserve">47.2211418151855</t>
+    <t xml:space="preserve">47.221134185791</t>
   </si>
   <si>
     <t xml:space="preserve">48.3467254638672</t>
@@ -3995,79 +3995,79 @@
     <t xml:space="preserve">49.2043190002441</t>
   </si>
   <si>
-    <t xml:space="preserve">50.3120384216309</t>
+    <t xml:space="preserve">50.3120460510254</t>
   </si>
   <si>
     <t xml:space="preserve">50.4728355407715</t>
   </si>
   <si>
-    <t xml:space="preserve">50.329906463623</t>
+    <t xml:space="preserve">50.3299102783203</t>
   </si>
   <si>
     <t xml:space="preserve">50.0261688232422</t>
   </si>
   <si>
-    <t xml:space="preserve">50.2227058410645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50.4371032714844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">51.0802993774414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50.6515045166016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50.1155090332031</t>
+    <t xml:space="preserve">50.222713470459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50.4371070861816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">51.0803031921387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50.6515007019043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50.1155052185059</t>
   </si>
   <si>
     <t xml:space="preserve">49.1685829162598</t>
   </si>
   <si>
-    <t xml:space="preserve">50.4906997680664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50.7522163391113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">49.9586563110352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50.120979309082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50.4997253417969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">49.3815116882324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">49.5618667602539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">49.9947242736816</t>
+    <t xml:space="preserve">50.4907035827637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50.7522201538086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">49.9586524963379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50.1209716796875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50.4997177124023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">49.3815155029297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">49.5618743896484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">49.9947204589844</t>
   </si>
   <si>
     <t xml:space="preserve">49.6159782409668</t>
   </si>
   <si>
-    <t xml:space="preserve">48.4436683654785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">48.191162109375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">48.5338401794434</t>
+    <t xml:space="preserve">48.4436645507812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">48.1911659240723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">48.5338439941406</t>
   </si>
   <si>
     <t xml:space="preserve">49.832405090332</t>
   </si>
   <si>
-    <t xml:space="preserve">48.6420555114746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">48.6240119934082</t>
+    <t xml:space="preserve">48.6420516967773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">48.6240158081055</t>
   </si>
   <si>
     <t xml:space="preserve">48.2993774414062</t>
@@ -4085,13 +4085,13 @@
     <t xml:space="preserve">49.7602615356445</t>
   </si>
   <si>
-    <t xml:space="preserve">50.0668716430664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50.1029396057129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50.9686470031738</t>
+    <t xml:space="preserve">50.0668678283691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50.1029357910156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50.9686508178711</t>
   </si>
   <si>
     <t xml:space="preserve">50.2832946777344</t>
@@ -4106,16 +4106,16 @@
     <t xml:space="preserve">50.986686706543</t>
   </si>
   <si>
-    <t xml:space="preserve">50.9506072998047</t>
+    <t xml:space="preserve">50.950611114502</t>
   </si>
   <si>
     <t xml:space="preserve">50.084903717041</t>
   </si>
   <si>
-    <t xml:space="preserve">49.2552642822266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">49.2913360595703</t>
+    <t xml:space="preserve">49.2552604675293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">49.2913398742676</t>
   </si>
   <si>
     <t xml:space="preserve">49.0207977294922</t>
@@ -4124,40 +4124,40 @@
     <t xml:space="preserve">48.7683029174805</t>
   </si>
   <si>
-    <t xml:space="preserve">49.1290168762207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">49.5257987976074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">48.3174209594727</t>
+    <t xml:space="preserve">49.1290092468262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">49.5257949829102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">48.3174171447754</t>
   </si>
   <si>
     <t xml:space="preserve">47.090991973877</t>
   </si>
   <si>
-    <t xml:space="preserve">46.1711730957031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.8926010131836</t>
+    <t xml:space="preserve">46.1711769104004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.8925933837891</t>
   </si>
   <si>
     <t xml:space="preserve">46.4417114257812</t>
   </si>
   <si>
-    <t xml:space="preserve">45.5579605102539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.0439529418945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">44.6201095581055</t>
+    <t xml:space="preserve">45.5579681396484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.0439491271973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44.6201133728027</t>
   </si>
   <si>
     <t xml:space="preserve">44.6471633911133</t>
   </si>
   <si>
-    <t xml:space="preserve">44.6742210388184</t>
+    <t xml:space="preserve">44.6742248535156</t>
   </si>
   <si>
     <t xml:space="preserve">44.8726081848145</t>
@@ -4169,10 +4169,10 @@
     <t xml:space="preserve">43.7724380493164</t>
   </si>
   <si>
-    <t xml:space="preserve">42.6993141174316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.3025321960449</t>
+    <t xml:space="preserve">42.6993179321289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.3025360107422</t>
   </si>
   <si>
     <t xml:space="preserve">41.5630760192871</t>
@@ -4181,19 +4181,19 @@
     <t xml:space="preserve">41.9778938293457</t>
   </si>
   <si>
-    <t xml:space="preserve">41.3015556335449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40.940845489502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40.3817405700684</t>
+    <t xml:space="preserve">41.3015594482422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40.9408493041992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40.3817367553711</t>
   </si>
   <si>
     <t xml:space="preserve">41.2564697265625</t>
   </si>
   <si>
-    <t xml:space="preserve">41.0400390625</t>
+    <t xml:space="preserve">41.0400428771973</t>
   </si>
   <si>
     <t xml:space="preserve">41.3105773925781</t>
@@ -4205,7 +4205,7 @@
     <t xml:space="preserve">41.581111907959</t>
   </si>
   <si>
-    <t xml:space="preserve">41.7434310913086</t>
+    <t xml:space="preserve">41.7434349060059</t>
   </si>
   <si>
     <t xml:space="preserve">41.5720901489258</t>
@@ -4214,70 +4214,70 @@
     <t xml:space="preserve">39.0921974182129</t>
   </si>
   <si>
-    <t xml:space="preserve">40.2645149230957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.4619216918945</t>
+    <t xml:space="preserve">40.2645111083984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.4619293212891</t>
   </si>
   <si>
     <t xml:space="preserve">38.2715759277344</t>
   </si>
   <si>
-    <t xml:space="preserve">38.9298667907715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.6232719421387</t>
+    <t xml:space="preserve">38.9298706054688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.6232681274414</t>
   </si>
   <si>
     <t xml:space="preserve">37.9198799133301</t>
   </si>
   <si>
-    <t xml:space="preserve">37.7395248413086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36.3868560791016</t>
+    <t xml:space="preserve">37.7395210266113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.3868522644043</t>
   </si>
   <si>
     <t xml:space="preserve">39.8947830200195</t>
   </si>
   <si>
-    <t xml:space="preserve">38.7946014404297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.2545166015625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40.3997802734375</t>
+    <t xml:space="preserve">38.7946090698242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.254508972168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40.3997764587402</t>
   </si>
   <si>
     <t xml:space="preserve">39.8496894836426</t>
   </si>
   <si>
-    <t xml:space="preserve">40.9678993225098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.1753158569336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.1662940979004</t>
+    <t xml:space="preserve">40.967903137207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.1753082275391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.1662979125977</t>
   </si>
   <si>
     <t xml:space="preserve">41.2294158935547</t>
   </si>
   <si>
-    <t xml:space="preserve">41.6261978149414</t>
+    <t xml:space="preserve">41.6262016296387</t>
   </si>
   <si>
     <t xml:space="preserve">41.3646850585938</t>
   </si>
   <si>
-    <t xml:space="preserve">40.9588813781738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40.5891532897949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.3566436767578</t>
+    <t xml:space="preserve">40.9588775634766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40.5891494750977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.3566398620605</t>
   </si>
   <si>
     <t xml:space="preserve">42.2754821777344</t>
@@ -4286,148 +4286,148 @@
     <t xml:space="preserve">41.1572723388672</t>
   </si>
   <si>
-    <t xml:space="preserve">42.5911026000977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">44.079044342041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43.087085723877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">44.2954711914062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">44.3766250610352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43.8445777893066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.9969062805176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43.3846664428711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43.4568138122559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43.4117279052734</t>
+    <t xml:space="preserve">42.5911064147949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44.0790481567383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43.0870780944824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44.2954750061035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44.3766288757324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43.8445816040039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.9969100952148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43.3846702575684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43.4568099975586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43.4117202758789</t>
   </si>
   <si>
     <t xml:space="preserve">43.9167213439941</t>
   </si>
   <si>
-    <t xml:space="preserve">43.1772651672363</t>
+    <t xml:space="preserve">43.1772613525391</t>
   </si>
   <si>
     <t xml:space="preserve">41.7163772583008</t>
   </si>
   <si>
-    <t xml:space="preserve">41.184326171875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40.535041809082</t>
+    <t xml:space="preserve">41.1843223571777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40.5350456237793</t>
   </si>
   <si>
     <t xml:space="preserve">40.3366508483887</t>
   </si>
   <si>
-    <t xml:space="preserve">41.472900390625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40.1021842956543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.1282691955566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.6322860717773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.9739837646484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.3697929382324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.2445259094238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.8838119506836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.9810485839844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.279613494873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.7214889526367</t>
+    <t xml:space="preserve">41.4728965759277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40.1021881103516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.1282615661621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.6322898864746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.9739875793457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.3697891235352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.2445220947266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.8838081359863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.9810562133789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.2796173095703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.721492767334</t>
   </si>
   <si>
     <t xml:space="preserve">37.7575607299805</t>
   </si>
   <si>
-    <t xml:space="preserve">37.2976493835449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.4329147338867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.3797874450684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.6905555725098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.9319114685059</t>
+    <t xml:space="preserve">37.2976455688477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.432918548584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.3797912597656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.690559387207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.9319152832031</t>
   </si>
   <si>
     <t xml:space="preserve">37.8222351074219</t>
   </si>
   <si>
-    <t xml:space="preserve">38.2152671813965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.47119140625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.1110000610352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.0964431762695</t>
+    <t xml:space="preserve">38.2152709960938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.4711875915527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.1110038757324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.0964393615723</t>
   </si>
   <si>
     <t xml:space="preserve">37.2555389404297</t>
   </si>
   <si>
-    <t xml:space="preserve">37.2189865112305</t>
+    <t xml:space="preserve">37.2189826965332</t>
   </si>
   <si>
     <t xml:space="preserve">36.1404342651367</t>
   </si>
   <si>
-    <t xml:space="preserve">36.4146423339844</t>
+    <t xml:space="preserve">36.4146461486816</t>
   </si>
   <si>
     <t xml:space="preserve">35.8662300109863</t>
   </si>
   <si>
-    <t xml:space="preserve">36.067310333252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.4092178344727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.8462333679199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.3398094177246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.3489570617676</t>
+    <t xml:space="preserve">36.0673141479492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.4092216491699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.8462409973145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.3398132324219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.3489532470703</t>
   </si>
   <si>
     <t xml:space="preserve">34.5683174133301</t>
@@ -4436,10 +4436,10 @@
     <t xml:space="preserve">34.4769134521484</t>
   </si>
   <si>
-    <t xml:space="preserve">35.6651458740234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36.0490226745605</t>
+    <t xml:space="preserve">35.6651420593262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.0490341186523</t>
   </si>
   <si>
     <t xml:space="preserve">34.8242378234863</t>
@@ -4451,40 +4451,40 @@
     <t xml:space="preserve">35.5463218688965</t>
   </si>
   <si>
-    <t xml:space="preserve">38.2609710693359</t>
+    <t xml:space="preserve">38.2609634399414</t>
   </si>
   <si>
     <t xml:space="preserve">37.5754470825195</t>
   </si>
   <si>
-    <t xml:space="preserve">37.6394386291504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.9044990539551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.9410552978516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.3395080566406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.321231842041</t>
+    <t xml:space="preserve">37.6394309997559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.9045028686523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.9410591125488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.3395118713379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.3212280273438</t>
   </si>
   <si>
     <t xml:space="preserve">39.2206878662109</t>
   </si>
   <si>
-    <t xml:space="preserve">39.5223197937012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.7691040039062</t>
+    <t xml:space="preserve">39.5223159790039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.769100189209</t>
   </si>
   <si>
     <t xml:space="preserve">39.7782440185547</t>
   </si>
   <si>
-    <t xml:space="preserve">40.0433120727539</t>
+    <t xml:space="preserve">40.0433082580566</t>
   </si>
   <si>
     <t xml:space="preserve">39.4766159057617</t>
@@ -4493,28 +4493,28 @@
     <t xml:space="preserve">39.3029556274414</t>
   </si>
   <si>
-    <t xml:space="preserve">38.5351753234863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.2846717834473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.4400520324707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.6777000427246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.8605079650879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.2115478515625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.1658477783203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.8185157775879</t>
+    <t xml:space="preserve">38.5351715087891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.28466796875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.4400596618652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.6777038574219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.8605003356934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.2115516662598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.1658515930176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.8185234069824</t>
   </si>
   <si>
     <t xml:space="preserve">38.5625877380371</t>
@@ -4523,28 +4523,28 @@
     <t xml:space="preserve">38.1147232055664</t>
   </si>
   <si>
-    <t xml:space="preserve">39.5131759643555</t>
+    <t xml:space="preserve">39.5131797790527</t>
   </si>
   <si>
     <t xml:space="preserve">39.0104637145996</t>
   </si>
   <si>
-    <t xml:space="preserve">39.6137199401855</t>
+    <t xml:space="preserve">39.6137237548828</t>
   </si>
   <si>
     <t xml:space="preserve">39.7965240478516</t>
   </si>
   <si>
-    <t xml:space="preserve">38.7271194458008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.6174392700195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.0872993469238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.0835876464844</t>
+    <t xml:space="preserve">38.7271156311035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.6174354553223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.0872955322266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.0835838317871</t>
   </si>
   <si>
     <t xml:space="preserve">39.1567077636719</t>
@@ -4553,10 +4553,10 @@
     <t xml:space="preserve">38.6357154846191</t>
   </si>
   <si>
-    <t xml:space="preserve">38.6631317138672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.4437675476074</t>
+    <t xml:space="preserve">38.6631355285645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.4437713623047</t>
   </si>
   <si>
     <t xml:space="preserve">38.7636795043945</t>
@@ -4565,7 +4565,7 @@
     <t xml:space="preserve">39.5680198669434</t>
   </si>
   <si>
-    <t xml:space="preserve">40.2261085510254</t>
+    <t xml:space="preserve">40.2261161804199</t>
   </si>
   <si>
     <t xml:space="preserve">39.8787841796875</t>
@@ -4574,10 +4574,10 @@
     <t xml:space="preserve">40.4454765319824</t>
   </si>
   <si>
-    <t xml:space="preserve">39.8330841064453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.4986114501953</t>
+    <t xml:space="preserve">39.8330879211426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.498607635498</t>
   </si>
   <si>
     <t xml:space="preserve">37.5480346679688</t>
@@ -4586,25 +4586,25 @@
     <t xml:space="preserve">37.0361785888672</t>
   </si>
   <si>
-    <t xml:space="preserve">37.2372589111328</t>
+    <t xml:space="preserve">37.2372627258301</t>
   </si>
   <si>
     <t xml:space="preserve">37.1915626525879</t>
   </si>
   <si>
-    <t xml:space="preserve">37.8313751220703</t>
+    <t xml:space="preserve">37.8313789367676</t>
   </si>
   <si>
     <t xml:space="preserve">36.7619705200195</t>
   </si>
   <si>
-    <t xml:space="preserve">37.3743667602539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.0087585449219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.465763092041</t>
+    <t xml:space="preserve">37.3743591308594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.0087623596191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.4657669067383</t>
   </si>
   <si>
     <t xml:space="preserve">37.13671875</t>
@@ -4613,40 +4613,40 @@
     <t xml:space="preserve">37.5937309265137</t>
   </si>
   <si>
-    <t xml:space="preserve">37.0453186035156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36.6522903442383</t>
+    <t xml:space="preserve">37.0453224182129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.652286529541</t>
   </si>
   <si>
     <t xml:space="preserve">36.7071304321289</t>
   </si>
   <si>
-    <t xml:space="preserve">36.3415145874023</t>
+    <t xml:space="preserve">36.3415184020996</t>
   </si>
   <si>
     <t xml:space="preserve">36.1769943237305</t>
   </si>
   <si>
-    <t xml:space="preserve">35.6468620300293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.6011581420898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.9102210998535</t>
+    <t xml:space="preserve">35.6468658447266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.6011619567871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.9102172851562</t>
   </si>
   <si>
     <t xml:space="preserve">33.316104888916</t>
   </si>
   <si>
-    <t xml:space="preserve">34.0930213928223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.5811767578125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.4494934082031</t>
+    <t xml:space="preserve">34.0930252075195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.5811729431152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.4494895935059</t>
   </si>
   <si>
     <t xml:space="preserve">35.1532897949219</t>
@@ -4655,7 +4655,7 @@
     <t xml:space="preserve">32.9962005615234</t>
   </si>
   <si>
-    <t xml:space="preserve">32.2649841308594</t>
+    <t xml:space="preserve">32.2649803161621</t>
   </si>
   <si>
     <t xml:space="preserve">32.31982421875</t>
@@ -4664,37 +4664,37 @@
     <t xml:space="preserve">32.7494163513184</t>
   </si>
   <si>
-    <t xml:space="preserve">32.4752082824707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.3929443359375</t>
+    <t xml:space="preserve">32.475212097168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.3929405212402</t>
   </si>
   <si>
     <t xml:space="preserve">33.4257850646973</t>
   </si>
   <si>
-    <t xml:space="preserve">33.6360168457031</t>
+    <t xml:space="preserve">33.6360206604004</t>
   </si>
   <si>
     <t xml:space="preserve">33.6542930603027</t>
   </si>
   <si>
-    <t xml:space="preserve">32.8590927124023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.9596366882324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.4020805358887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.5171890258789</t>
+    <t xml:space="preserve">32.8590965270996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.9596405029297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.4020843505859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.5171852111816</t>
   </si>
   <si>
     <t xml:space="preserve">34.6688575744629</t>
   </si>
   <si>
-    <t xml:space="preserve">34.732837677002</t>
+    <t xml:space="preserve">34.7328453063965</t>
   </si>
   <si>
     <t xml:space="preserve">34.4586372375488</t>
@@ -4703,13 +4703,13 @@
     <t xml:space="preserve">35.0710258483887</t>
   </si>
   <si>
-    <t xml:space="preserve">34.7602615356445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.8059616088867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.162425994873</t>
+    <t xml:space="preserve">34.7602653503418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.805965423584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.1624298095703</t>
   </si>
   <si>
     <t xml:space="preserve">34.6048774719238</t>
@@ -4718,13 +4718,13 @@
     <t xml:space="preserve">35.1715698242188</t>
   </si>
   <si>
-    <t xml:space="preserve">34.614013671875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.1441497802734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.0910148620605</t>
+    <t xml:space="preserve">34.6140213012695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.1441535949707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.0910186767578</t>
   </si>
   <si>
     <t xml:space="preserve">37.9593391418457</t>
@@ -4733,10 +4733,10 @@
     <t xml:space="preserve">37.2463989257812</t>
   </si>
   <si>
-    <t xml:space="preserve">36.8168067932129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36.4055061340332</t>
+    <t xml:space="preserve">36.8168144226074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.4055099487305</t>
   </si>
   <si>
     <t xml:space="preserve">35.9393463134766</t>
@@ -4745,16 +4745,16 @@
     <t xml:space="preserve">35.8296661376953</t>
   </si>
   <si>
-    <t xml:space="preserve">36.0947341918945</t>
+    <t xml:space="preserve">36.0947380065918</t>
   </si>
   <si>
     <t xml:space="preserve">36.2152328491211</t>
   </si>
   <si>
-    <t xml:space="preserve">35.7981109619141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36.2893943786621</t>
+    <t xml:space="preserve">35.7981071472168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.2893905639648</t>
   </si>
   <si>
     <t xml:space="preserve">37.2626686096191</t>
@@ -4763,40 +4763,40 @@
     <t xml:space="preserve">37.2904777526855</t>
   </si>
   <si>
-    <t xml:space="preserve">37.2533988952637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.0865440368652</t>
+    <t xml:space="preserve">37.2533950805664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.0865478515625</t>
   </si>
   <si>
     <t xml:space="preserve">37.6705207824707</t>
   </si>
   <si>
-    <t xml:space="preserve">38.5603713989258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.4584159851074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.3749885559082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.4665946960449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.5407447814941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.8559074401855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.8291816711426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.8199119567871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.5881805419922</t>
+    <t xml:space="preserve">38.560375213623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.4584121704102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.3749847412109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.4665908813477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.5407485961914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.8559036254883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.8291854858398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.8199195861816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.5881843566895</t>
   </si>
   <si>
     <t xml:space="preserve">37.4944000244141</t>
@@ -4805,13 +4805,13 @@
     <t xml:space="preserve">36.7065048217773</t>
   </si>
   <si>
-    <t xml:space="preserve">36.3542709350586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.6590690612793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36.3171997070312</t>
+    <t xml:space="preserve">36.3542747497559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.6590728759766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.317195892334</t>
   </si>
   <si>
     <t xml:space="preserve">35.9000778198242</t>
@@ -4820,13 +4820,13 @@
     <t xml:space="preserve">36.2615852355957</t>
   </si>
   <si>
-    <t xml:space="preserve">35.8073806762695</t>
+    <t xml:space="preserve">35.8073844909668</t>
   </si>
   <si>
     <t xml:space="preserve">36.1966934204102</t>
   </si>
   <si>
-    <t xml:space="preserve">36.7713928222656</t>
+    <t xml:space="preserve">36.7713966369629</t>
   </si>
   <si>
     <t xml:space="preserve">35.9186172485352</t>
@@ -4835,22 +4835,22 @@
     <t xml:space="preserve">35.9835014343262</t>
   </si>
   <si>
-    <t xml:space="preserve">36.0761947631836</t>
+    <t xml:space="preserve">36.0761909484863</t>
   </si>
   <si>
     <t xml:space="preserve">35.5941925048828</t>
   </si>
   <si>
-    <t xml:space="preserve">35.8537292480469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36.4655113220215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36.1874313354492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.9649658203125</t>
+    <t xml:space="preserve">35.8537330627441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.465503692627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.187427520752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.964958190918</t>
   </si>
   <si>
     <t xml:space="preserve">36.5118522644043</t>
@@ -4859,13 +4859,13 @@
     <t xml:space="preserve">37.2348556518555</t>
   </si>
   <si>
-    <t xml:space="preserve">37.1514358520508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.792106628418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.1536140441895</t>
+    <t xml:space="preserve">37.151439666748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.7921028137207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.1536102294922</t>
   </si>
   <si>
     <t xml:space="preserve">38.4027976989746</t>
@@ -4877,37 +4877,37 @@
     <t xml:space="preserve">38.0227546691895</t>
   </si>
   <si>
-    <t xml:space="preserve">37.6056365966797</t>
+    <t xml:space="preserve">37.6056289672852</t>
   </si>
   <si>
     <t xml:space="preserve">37.7817459106445</t>
   </si>
   <si>
-    <t xml:space="preserve">38.2359428405762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.1977767944336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36.252311706543</t>
+    <t xml:space="preserve">38.2359466552734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.1977806091309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.2523155212402</t>
   </si>
   <si>
     <t xml:space="preserve">37.0587463378906</t>
   </si>
   <si>
-    <t xml:space="preserve">37.3182830810547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.6519813537598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.9300575256348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.2452201843262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.0876312255859</t>
+    <t xml:space="preserve">37.3182792663574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.6519775390625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.930061340332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.2452125549316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.0876388549805</t>
   </si>
   <si>
     <t xml:space="preserve">37.3090171813965</t>
@@ -4916,40 +4916,40 @@
     <t xml:space="preserve">37.7724800109863</t>
   </si>
   <si>
-    <t xml:space="preserve">38.0505638122559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.9764022827148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.3564491271973</t>
+    <t xml:space="preserve">38.0505599975586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.9764060974121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.3564453125</t>
   </si>
   <si>
     <t xml:space="preserve">38.0969085693359</t>
   </si>
   <si>
-    <t xml:space="preserve">37.6241722106934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36.6601600646973</t>
+    <t xml:space="preserve">37.6241683959961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.6601638793945</t>
   </si>
   <si>
     <t xml:space="preserve">37.1050872802734</t>
   </si>
   <si>
-    <t xml:space="preserve">36.5674705505371</t>
+    <t xml:space="preserve">36.5674667358398</t>
   </si>
   <si>
     <t xml:space="preserve">37.1885147094727</t>
   </si>
   <si>
-    <t xml:space="preserve">37.2070503234863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36.4284248352051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36.7250480651855</t>
+    <t xml:space="preserve">37.2070541381836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.4284286499023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.7250442504883</t>
   </si>
   <si>
     <t xml:space="preserve">36.4098930358887</t>
@@ -4958,13 +4958,13 @@
     <t xml:space="preserve">35.8815383911133</t>
   </si>
   <si>
-    <t xml:space="preserve">35.8166542053223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.2234153747559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36.0205841064453</t>
+    <t xml:space="preserve">35.8166465759277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.2234191894531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.020580291748</t>
   </si>
   <si>
     <t xml:space="preserve">35.4829597473145</t>
@@ -4973,7 +4973,7 @@
     <t xml:space="preserve">35.7239646911621</t>
   </si>
   <si>
-    <t xml:space="preserve">35.8629951477051</t>
+    <t xml:space="preserve">35.8630027770996</t>
   </si>
   <si>
     <t xml:space="preserve">37.0402069091797</t>
@@ -4982,19 +4982,19 @@
     <t xml:space="preserve">36.3728179931641</t>
   </si>
   <si>
-    <t xml:space="preserve">36.3913536071777</t>
+    <t xml:space="preserve">36.391357421875</t>
   </si>
   <si>
     <t xml:space="preserve">36.1132736206055</t>
   </si>
   <si>
-    <t xml:space="preserve">36.2059593200684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36.4840469360352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36.9382362365723</t>
+    <t xml:space="preserve">36.2059631347656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.4840431213379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.9382438659668</t>
   </si>
   <si>
     <t xml:space="preserve">36.9938545227051</t>
@@ -5021,25 +5021,25 @@
     <t xml:space="preserve">38.9589538574219</t>
   </si>
   <si>
-    <t xml:space="preserve">37.7261352539062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.095817565918</t>
+    <t xml:space="preserve">37.726131439209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.0958213806152</t>
   </si>
   <si>
     <t xml:space="preserve">38.6808700561523</t>
   </si>
   <si>
-    <t xml:space="preserve">37.9393272399902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.1061782836914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.3760719299316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.0053024291992</t>
+    <t xml:space="preserve">37.9393310546875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.1061744689941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.3760757446289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.005298614502</t>
   </si>
   <si>
     <t xml:space="preserve">38.9311447143555</t>
@@ -5057,19 +5057,19 @@
     <t xml:space="preserve">42.5461845397949</t>
   </si>
   <si>
-    <t xml:space="preserve">42.2866401672363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.7119407653809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.3040924072266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.3831329345703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.655574798584</t>
+    <t xml:space="preserve">42.2866363525391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.7119445800781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.3040962219238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.383129119873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.6555709838867</t>
   </si>
   <si>
     <t xml:space="preserve">40.5188293457031</t>
@@ -5078,13 +5078,13 @@
     <t xml:space="preserve">40.0960731506348</t>
   </si>
   <si>
-    <t xml:space="preserve">40.5564002990723</t>
+    <t xml:space="preserve">40.5564041137695</t>
   </si>
   <si>
     <t xml:space="preserve">40.0866775512695</t>
   </si>
   <si>
-    <t xml:space="preserve">39.4290618896484</t>
+    <t xml:space="preserve">39.4290580749512</t>
   </si>
   <si>
     <t xml:space="preserve">38.1607894897461</t>
@@ -5096,31 +5096,31 @@
     <t xml:space="preserve">40.2463912963867</t>
   </si>
   <si>
-    <t xml:space="preserve">40.3967018127441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.4488906860352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.9186210632324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.134693145752</t>
+    <t xml:space="preserve">40.3967056274414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.4488868713379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.9186248779297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.1346969604492</t>
   </si>
   <si>
     <t xml:space="preserve">41.7025451660156</t>
   </si>
   <si>
-    <t xml:space="preserve">42.7453460693359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.2568283081055</t>
+    <t xml:space="preserve">42.7453384399414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.2568244934082</t>
   </si>
   <si>
     <t xml:space="preserve">42.2098541259766</t>
   </si>
   <si>
-    <t xml:space="preserve">42.5198745727539</t>
+    <t xml:space="preserve">42.5198707580566</t>
   </si>
   <si>
     <t xml:space="preserve">41.3925247192383</t>
@@ -5129,19 +5129,19 @@
     <t xml:space="preserve">40.6597480773926</t>
   </si>
   <si>
-    <t xml:space="preserve">40.1900177001953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40.3309364318848</t>
+    <t xml:space="preserve">40.1900215148926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40.330940246582</t>
   </si>
   <si>
     <t xml:space="preserve">40.1242561340332</t>
   </si>
   <si>
-    <t xml:space="preserve">40.4906463623047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40.697322845459</t>
+    <t xml:space="preserve">40.4906425476074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40.6973266601562</t>
   </si>
   <si>
     <t xml:space="preserve">41.1012954711914</t>
@@ -5165,7 +5165,7 @@
     <t xml:space="preserve">39.7578735351562</t>
   </si>
   <si>
-    <t xml:space="preserve">39.6921081542969</t>
+    <t xml:space="preserve">39.6921043395996</t>
   </si>
   <si>
     <t xml:space="preserve">40.3121490478516</t>
@@ -5180,19 +5180,19 @@
     <t xml:space="preserve">40.4060974121094</t>
   </si>
   <si>
-    <t xml:space="preserve">40.6691436767578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40.8476371765137</t>
+    <t xml:space="preserve">40.6691398620605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40.8476409912109</t>
   </si>
   <si>
     <t xml:space="preserve">40.5470123291016</t>
   </si>
   <si>
-    <t xml:space="preserve">42.5856437683105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.3319892883301</t>
+    <t xml:space="preserve">42.5856399536133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.3319854736328</t>
   </si>
   <si>
     <t xml:space="preserve">41.7589149475098</t>
@@ -5201,25 +5201,25 @@
     <t xml:space="preserve">42.5386657714844</t>
   </si>
   <si>
-    <t xml:space="preserve">43.675407409668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43.9760398864746</t>
+    <t xml:space="preserve">43.6754112243652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43.9760360717773</t>
   </si>
   <si>
     <t xml:space="preserve">44.1075592041016</t>
   </si>
   <si>
-    <t xml:space="preserve">43.1962852478027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.8392868041992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.881046295166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40.8758201599121</t>
+    <t xml:space="preserve">43.1962814331055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.8392944335938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.8810424804688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40.8758239746094</t>
   </si>
   <si>
     <t xml:space="preserve">42.2286415100098</t>
@@ -5228,40 +5228,40 @@
     <t xml:space="preserve">42.7077674865723</t>
   </si>
   <si>
-    <t xml:space="preserve">42.2756118774414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.698371887207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.6138229370117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.0971183776855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.9468078613281</t>
+    <t xml:space="preserve">42.2756156921387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.6983757019043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.6138191223145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.0971145629883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.9468116760254</t>
   </si>
   <si>
     <t xml:space="preserve">41.9749908447266</t>
   </si>
   <si>
-    <t xml:space="preserve">42.9896049499512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.8017158508301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43.0647583007812</t>
+    <t xml:space="preserve">42.9896087646484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.8017120361328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43.0647621154785</t>
   </si>
   <si>
     <t xml:space="preserve">43.3935699462891</t>
   </si>
   <si>
-    <t xml:space="preserve">44.0511932373047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43.656623840332</t>
+    <t xml:space="preserve">44.0511894226074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43.6566200256348</t>
   </si>
   <si>
     <t xml:space="preserve">43.5720672607422</t>
@@ -5270,31 +5270,31 @@
     <t xml:space="preserve">43.0177879333496</t>
   </si>
   <si>
-    <t xml:space="preserve">42.8111114501953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.6743659973145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.2850074768066</t>
+    <t xml:space="preserve">42.811107635498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.6743621826172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.2850112915039</t>
   </si>
   <si>
     <t xml:space="preserve">42.8298950195312</t>
   </si>
   <si>
-    <t xml:space="preserve">42.4822959899902</t>
+    <t xml:space="preserve">42.4822998046875</t>
   </si>
   <si>
     <t xml:space="preserve">42.7171630859375</t>
   </si>
   <si>
-    <t xml:space="preserve">42.8768653869629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43.5438842773438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43.9854316711426</t>
+    <t xml:space="preserve">42.8768692016602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43.5438804626465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43.9854278564453</t>
   </si>
   <si>
     <t xml:space="preserve">44.0887718200684</t>
@@ -5306,13 +5306,13 @@
     <t xml:space="preserve">44.5303192138672</t>
   </si>
   <si>
-    <t xml:space="preserve">42.1816749572754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.5574531555176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.0783348083496</t>
+    <t xml:space="preserve">42.1816711425781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.5574569702148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.0783309936523</t>
   </si>
   <si>
     <t xml:space="preserve">42.0689353942871</t>
@@ -5324,34 +5324,34 @@
     <t xml:space="preserve">41.4770812988281</t>
   </si>
   <si>
-    <t xml:space="preserve">42.0031700134277</t>
+    <t xml:space="preserve">42.003173828125</t>
   </si>
   <si>
     <t xml:space="preserve">41.4019203186035</t>
   </si>
   <si>
-    <t xml:space="preserve">41.0919036865234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.3549423217773</t>
+    <t xml:space="preserve">41.0918998718262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.3549499511719</t>
   </si>
   <si>
     <t xml:space="preserve">41.9843826293945</t>
   </si>
   <si>
-    <t xml:space="preserve">41.9374160766602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.8580780029297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.7829208374023</t>
+    <t xml:space="preserve">41.9374122619629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.858081817627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.7829246520996</t>
   </si>
   <si>
     <t xml:space="preserve">42.7359504699707</t>
   </si>
   <si>
-    <t xml:space="preserve">42.1159133911133</t>
+    <t xml:space="preserve">42.115909576416</t>
   </si>
   <si>
     <t xml:space="preserve">41.3455505371094</t>
@@ -5363,10 +5363,10 @@
     <t xml:space="preserve">41.6837577819824</t>
   </si>
   <si>
-    <t xml:space="preserve">41.3079795837402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.0637092590332</t>
+    <t xml:space="preserve">41.307975769043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.0637130737305</t>
   </si>
   <si>
     <t xml:space="preserve">40.7912712097168</t>
@@ -5378,10 +5378,10 @@
     <t xml:space="preserve">40.9603729248047</t>
   </si>
   <si>
-    <t xml:space="preserve">41.4582901000977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.6179962158203</t>
+    <t xml:space="preserve">41.4582824707031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.617992401123</t>
   </si>
   <si>
     <t xml:space="preserve">41.2891883850098</t>
@@ -5393,16 +5393,16 @@
     <t xml:space="preserve">41.148265838623</t>
   </si>
   <si>
-    <t xml:space="preserve">42.0501441955566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.5804100036621</t>
+    <t xml:space="preserve">42.0501480102539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.5804138183594</t>
   </si>
   <si>
     <t xml:space="preserve">42.1910667419434</t>
   </si>
   <si>
-    <t xml:space="preserve">43.0741539001465</t>
+    <t xml:space="preserve">43.0741577148438</t>
   </si>
   <si>
     <t xml:space="preserve">41.8434638977051</t>
@@ -5411,10 +5411,10 @@
     <t xml:space="preserve">42.4447212219238</t>
   </si>
   <si>
-    <t xml:space="preserve">42.454231262207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.7016105651855</t>
+    <t xml:space="preserve">42.4542350769043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.7016181945801</t>
   </si>
   <si>
     <t xml:space="preserve">42.2353973388672</t>
@@ -5435,13 +5435,13 @@
     <t xml:space="preserve">42.0260772705078</t>
   </si>
   <si>
-    <t xml:space="preserve">42.0451049804688</t>
+    <t xml:space="preserve">42.0451011657715</t>
   </si>
   <si>
     <t xml:space="preserve">43.0251121520996</t>
   </si>
   <si>
-    <t xml:space="preserve">43.6721038818359</t>
+    <t xml:space="preserve">43.6721076965332</t>
   </si>
   <si>
     <t xml:space="preserve">43.99560546875</t>
@@ -5450,13 +5450,13 @@
     <t xml:space="preserve">43.4437522888184</t>
   </si>
   <si>
-    <t xml:space="preserve">44.4332733154297</t>
+    <t xml:space="preserve">44.433277130127</t>
   </si>
   <si>
     <t xml:space="preserve">44.3857002258301</t>
   </si>
   <si>
-    <t xml:space="preserve">44.928035736084</t>
+    <t xml:space="preserve">44.9280319213867</t>
   </si>
   <si>
     <t xml:space="preserve">44.7282257080078</t>
@@ -5468,13 +5468,13 @@
     <t xml:space="preserve">45.5559997558594</t>
   </si>
   <si>
-    <t xml:space="preserve">45.5464859008789</t>
+    <t xml:space="preserve">45.5464820861816</t>
   </si>
   <si>
     <t xml:space="preserve">45.6606636047363</t>
   </si>
   <si>
-    <t xml:space="preserve">45.2800750732422</t>
+    <t xml:space="preserve">45.2800788879395</t>
   </si>
   <si>
     <t xml:space="preserve">45.7938652038574</t>
@@ -5489,7 +5489,7 @@
     <t xml:space="preserve">46.0888137817383</t>
   </si>
   <si>
-    <t xml:space="preserve">46.459888458252</t>
+    <t xml:space="preserve">46.4598922729492</t>
   </si>
   <si>
     <t xml:space="preserve">46.621639251709</t>
@@ -5498,13 +5498,13 @@
     <t xml:space="preserve">45.6892051696777</t>
   </si>
   <si>
-    <t xml:space="preserve">46.1649360656738</t>
+    <t xml:space="preserve">46.1649398803711</t>
   </si>
   <si>
     <t xml:space="preserve">45.4989128112793</t>
   </si>
   <si>
-    <t xml:space="preserve">45.860466003418</t>
+    <t xml:space="preserve">45.8604698181152</t>
   </si>
   <si>
     <t xml:space="preserve">46.5455169677734</t>
@@ -5516,16 +5516,16 @@
     <t xml:space="preserve">46.8309593200684</t>
   </si>
   <si>
-    <t xml:space="preserve">48.486499786377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">47.5635833740234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">47.8204803466797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">48.0488357543945</t>
+    <t xml:space="preserve">48.4865036010742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">47.5635871887207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">47.8204727172852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">48.048828125</t>
   </si>
   <si>
     <t xml:space="preserve">47.3732948303223</t>
@@ -5537,13 +5537,13 @@
     <t xml:space="preserve">47.1639709472656</t>
   </si>
   <si>
-    <t xml:space="preserve">47.3066940307617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">47.5160102844238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">47.554069519043</t>
+    <t xml:space="preserve">47.3066902160645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">47.5160140991211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">47.5540657043457</t>
   </si>
   <si>
     <t xml:space="preserve">48.4294166564941</t>
@@ -5552,19 +5552,19 @@
     <t xml:space="preserve">48.1820335388184</t>
   </si>
   <si>
-    <t xml:space="preserve">48.3342628479004</t>
+    <t xml:space="preserve">48.3342666625977</t>
   </si>
   <si>
     <t xml:space="preserve">48.8099975585938</t>
   </si>
   <si>
-    <t xml:space="preserve">48.2391242980957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">48.3532943725586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">48.6197052001953</t>
+    <t xml:space="preserve">48.239128112793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">48.3532981872559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">48.6197090148926</t>
   </si>
   <si>
     <t xml:space="preserve">47.9917411804199</t>
@@ -5573,7 +5573,7 @@
     <t xml:space="preserve">48.0107688903809</t>
   </si>
   <si>
-    <t xml:space="preserve">48.1059188842773</t>
+    <t xml:space="preserve">48.1059226989746</t>
   </si>
   <si>
     <t xml:space="preserve">47.9346580505371</t>
@@ -5597,25 +5597,25 @@
     <t xml:space="preserve">49.1715545654297</t>
   </si>
   <si>
-    <t xml:space="preserve">50.3133163452148</t>
+    <t xml:space="preserve">50.3133087158203</t>
   </si>
   <si>
     <t xml:space="preserve">49.1525268554688</t>
   </si>
   <si>
-    <t xml:space="preserve">48.5055313110352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">48.2581558227539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">49.2476692199707</t>
+    <t xml:space="preserve">48.5055274963379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">48.2581520080566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">49.247673034668</t>
   </si>
   <si>
     <t xml:space="preserve">49.4379653930664</t>
   </si>
   <si>
-    <t xml:space="preserve">49.2096176147461</t>
+    <t xml:space="preserve">49.2096138000488</t>
   </si>
   <si>
     <t xml:space="preserve">50.0278739929199</t>
@@ -5633,13 +5633,13 @@
     <t xml:space="preserve">50.2181625366211</t>
   </si>
   <si>
-    <t xml:space="preserve">50.2752494812012</t>
+    <t xml:space="preserve">50.2752532958984</t>
   </si>
   <si>
     <t xml:space="preserve">49.3428192138672</t>
   </si>
   <si>
-    <t xml:space="preserve">48.73388671875</t>
+    <t xml:space="preserve">48.7338829040527</t>
   </si>
   <si>
     <t xml:space="preserve">48.391357421875</t>
@@ -5651,10 +5651,10 @@
     <t xml:space="preserve">49.8185501098633</t>
   </si>
   <si>
-    <t xml:space="preserve">49.4760208129883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">48.9051475524902</t>
+    <t xml:space="preserve">49.4760246276855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">48.905143737793</t>
   </si>
   <si>
     <t xml:space="preserve">49.228645324707</t>
@@ -5681,7 +5681,7 @@
     <t xml:space="preserve">47.5731010437012</t>
   </si>
   <si>
-    <t xml:space="preserve">47.0212478637695</t>
+    <t xml:space="preserve">47.0212516784668</t>
   </si>
   <si>
     <t xml:space="preserve">46.9451370239258</t>
@@ -5690,13 +5690,13 @@
     <t xml:space="preserve">46.5645484924316</t>
   </si>
   <si>
-    <t xml:space="preserve">47.3257179260254</t>
+    <t xml:space="preserve">47.3257217407227</t>
   </si>
   <si>
     <t xml:space="preserve">47.4398956298828</t>
   </si>
   <si>
-    <t xml:space="preserve">50.0469017028809</t>
+    <t xml:space="preserve">50.0468978881836</t>
   </si>
   <si>
     <t xml:space="preserve">46.4313468933105</t>
@@ -5708,7 +5708,7 @@
     <t xml:space="preserve">47.7633934020996</t>
   </si>
   <si>
-    <t xml:space="preserve">47.9061088562012</t>
+    <t xml:space="preserve">47.9061126708984</t>
   </si>
   <si>
     <t xml:space="preserve">48.7148551940918</t>
@@ -5717,13 +5717,13 @@
     <t xml:space="preserve">49.2857284545898</t>
   </si>
   <si>
-    <t xml:space="preserve">48.5029220581055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">47.029052734375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">47.3565788269043</t>
+    <t xml:space="preserve">48.5029258728027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">47.0290489196777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">47.356575012207</t>
   </si>
   <si>
     <t xml:space="preserve">46.7400550842285</t>
@@ -5741,22 +5741,22 @@
     <t xml:space="preserve">45.950138092041</t>
   </si>
   <si>
-    <t xml:space="preserve">45.7189445495605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.6244621276855</t>
+    <t xml:space="preserve">45.7189407348633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.6244583129883</t>
   </si>
   <si>
     <t xml:space="preserve">46.5859260559082</t>
   </si>
   <si>
-    <t xml:space="preserve">46.4317932128906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.8171195983887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">47.4336433410645</t>
+    <t xml:space="preserve">46.4317970275879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.8171234130859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">47.4336471557617</t>
   </si>
   <si>
     <t xml:space="preserve">47.8767700195312</t>
@@ -5765,7 +5765,7 @@
     <t xml:space="preserve">47.7226409912109</t>
   </si>
   <si>
-    <t xml:space="preserve">46.6437187194824</t>
+    <t xml:space="preserve">46.643726348877</t>
   </si>
   <si>
     <t xml:space="preserve">47.4529075622559</t>
@@ -5780,19 +5780,19 @@
     <t xml:space="preserve">46.0850028991699</t>
   </si>
   <si>
-    <t xml:space="preserve">47.3951110839844</t>
+    <t xml:space="preserve">47.3951148986816</t>
   </si>
   <si>
     <t xml:space="preserve">48.262092590332</t>
   </si>
   <si>
-    <t xml:space="preserve">47.587776184082</t>
+    <t xml:space="preserve">47.5877723693848</t>
   </si>
   <si>
     <t xml:space="preserve">47.7997016906738</t>
   </si>
   <si>
-    <t xml:space="preserve">46.9134521484375</t>
+    <t xml:space="preserve">46.9134559631348</t>
   </si>
   <si>
     <t xml:space="preserve">47.0097846984863</t>
@@ -5804,7 +5804,7 @@
     <t xml:space="preserve">47.2795143127441</t>
   </si>
   <si>
-    <t xml:space="preserve">47.3373069763184</t>
+    <t xml:space="preserve">47.3373107910156</t>
   </si>
   <si>
     <t xml:space="preserve">48.1657638549805</t>
@@ -5819,7 +5819,7 @@
     <t xml:space="preserve">49.1772422790527</t>
   </si>
   <si>
-    <t xml:space="preserve">49.2254066467285</t>
+    <t xml:space="preserve">49.2254104614258</t>
   </si>
   <si>
     <t xml:space="preserve">49.8515663146973</t>
@@ -5828,19 +5828,19 @@
     <t xml:space="preserve">49.3699073791504</t>
   </si>
   <si>
-    <t xml:space="preserve">49.514404296875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">49.9478988647461</t>
+    <t xml:space="preserve">49.5144081115723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">49.9478950500488</t>
   </si>
   <si>
     <t xml:space="preserve">50.3332252502441</t>
   </si>
   <si>
-    <t xml:space="preserve">50.0442276000977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50.4777221679688</t>
+    <t xml:space="preserve">50.0442314147949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50.4777183532715</t>
   </si>
   <si>
     <t xml:space="preserve">48.8882484436035</t>
@@ -5858,40 +5858,40 @@
     <t xml:space="preserve">47.6263046264648</t>
   </si>
   <si>
-    <t xml:space="preserve">47.1831817626953</t>
+    <t xml:space="preserve">47.183177947998</t>
   </si>
   <si>
     <t xml:space="preserve">47.5299797058105</t>
   </si>
   <si>
-    <t xml:space="preserve">47.6455688476562</t>
+    <t xml:space="preserve">47.6455726623535</t>
   </si>
   <si>
     <t xml:space="preserve">47.9923667907715</t>
   </si>
   <si>
-    <t xml:space="preserve">48.1272277832031</t>
+    <t xml:space="preserve">48.1272315979004</t>
   </si>
   <si>
     <t xml:space="preserve">48.7437515258789</t>
   </si>
   <si>
-    <t xml:space="preserve">48.5510864257812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">48.791919708252</t>
+    <t xml:space="preserve">48.5510902404785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">48.7919158935547</t>
   </si>
   <si>
     <t xml:space="preserve">49.7070655822754</t>
   </si>
   <si>
-    <t xml:space="preserve">50.8148803710938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50.6222190856934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">51.0557060241699</t>
+    <t xml:space="preserve">50.8148765563965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50.6222152709961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">51.0557098388672</t>
   </si>
   <si>
     <t xml:space="preserve">50.7185478210449</t>
@@ -5900,16 +5900,16 @@
     <t xml:space="preserve">50.8630447387695</t>
   </si>
   <si>
-    <t xml:space="preserve">50.1405601501465</t>
+    <t xml:space="preserve">50.1405563354492</t>
   </si>
   <si>
     <t xml:space="preserve">49.4180717468262</t>
   </si>
   <si>
-    <t xml:space="preserve">49.5625686645508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">49.0327453613281</t>
+    <t xml:space="preserve">49.562572479248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">49.0327491760254</t>
   </si>
   <si>
     <t xml:space="preserve">48.9845809936523</t>
@@ -5918,13 +5918,13 @@
     <t xml:space="preserve">48.6955833435059</t>
   </si>
   <si>
-    <t xml:space="preserve">48.1079635620117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">47.9730987548828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">48.8400840759277</t>
+    <t xml:space="preserve">48.1079597473145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">47.9730949401855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">48.840087890625</t>
   </si>
   <si>
     <t xml:space="preserve">48.9364128112793</t>
@@ -5936,7 +5936,7 @@
     <t xml:space="preserve">50.1887245178223</t>
   </si>
   <si>
-    <t xml:space="preserve">52.1153564453125</t>
+    <t xml:space="preserve">52.1153526306152</t>
   </si>
   <si>
     <t xml:space="preserve">51.4410362243652</t>
@@ -5945,7 +5945,7 @@
     <t xml:space="preserve">51.5855293273926</t>
   </si>
   <si>
-    <t xml:space="preserve">52.5006790161133</t>
+    <t xml:space="preserve">52.5006828308105</t>
   </si>
   <si>
     <t xml:space="preserve">52.2116889953613</t>
@@ -5957,10 +5957,10 @@
     <t xml:space="preserve">51.3928680419922</t>
   </si>
   <si>
-    <t xml:space="preserve">51.7300300598145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">51.8263626098633</t>
+    <t xml:space="preserve">51.7300338745117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">51.826358795166</t>
   </si>
   <si>
     <t xml:space="preserve">51.8745269775391</t>
@@ -5972,82 +5972,82 @@
     <t xml:space="preserve">49.9960632324219</t>
   </si>
   <si>
-    <t xml:space="preserve">49.6107406616211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50.4295501708984</t>
+    <t xml:space="preserve">49.6107368469238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50.4295539855957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">49.3217468261719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">48.7369003295898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">48.6394271850586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">49.1755294799805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">49.3704795837402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50.7838478088379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50.9300575256348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50.4426918029785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50.3939514160156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50.0527954101562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50.2477416992188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">49.8578491210938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50.1015319824219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50.6376419067383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">49.7603721618652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">49.8091087341309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">49.9065818786621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">49.5654258728027</t>
   </si>
   <si>
     <t xml:space="preserve">49.3217430114746</t>
   </si>
   <si>
-    <t xml:space="preserve">48.7369003295898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">48.6394271850586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">49.1755294799805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">49.3704795837402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50.7838478088379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50.930061340332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50.4426918029785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50.3939552307129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50.0527954101562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50.2477416992188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">49.8578491210938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50.1015319824219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50.637638092041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">49.7603721618652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">49.8091087341309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">49.9065856933594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">49.5654258728027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">49.3217391967773</t>
-  </si>
-  <si>
     <t xml:space="preserve">49.4679527282715</t>
   </si>
   <si>
     <t xml:space="preserve">49.0780563354492</t>
   </si>
   <si>
-    <t xml:space="preserve">49.1267929077148</t>
+    <t xml:space="preserve">49.1267967224121</t>
   </si>
   <si>
     <t xml:space="preserve">49.2242698669434</t>
   </si>
   <si>
-    <t xml:space="preserve">49.6141624450684</t>
+    <t xml:space="preserve">49.6141662597656</t>
   </si>
   <si>
     <t xml:space="preserve">50.4914245605469</t>
@@ -6071,10 +6071,10 @@
     <t xml:space="preserve">53.1719551086426</t>
   </si>
   <si>
-    <t xml:space="preserve">53.5131149291992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">53.2206954956055</t>
+    <t xml:space="preserve">53.5131187438965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">53.2206916809082</t>
   </si>
   <si>
     <t xml:space="preserve">53.7568016052246</t>
@@ -6086,13 +6086,13 @@
     <t xml:space="preserve">54.3903770446777</t>
   </si>
   <si>
-    <t xml:space="preserve">54.5853271484375</t>
+    <t xml:space="preserve">54.5853233337402</t>
   </si>
   <si>
     <t xml:space="preserve">55.3651161193848</t>
   </si>
   <si>
-    <t xml:space="preserve">56.0474319458008</t>
+    <t xml:space="preserve">56.047435760498</t>
   </si>
   <si>
     <t xml:space="preserve">56.6810150146484</t>
@@ -6104,7 +6104,7 @@
     <t xml:space="preserve">57.2658576965332</t>
   </si>
   <si>
-    <t xml:space="preserve">57.7532234191895</t>
+    <t xml:space="preserve">57.7532272338867</t>
   </si>
   <si>
     <t xml:space="preserve">57.6070137023926</t>
@@ -6113,7 +6113,7 @@
     <t xml:space="preserve">57.9481735229492</t>
   </si>
   <si>
-    <t xml:space="preserve">58.143123626709</t>
+    <t xml:space="preserve">58.1431198120117</t>
   </si>
   <si>
     <t xml:space="preserve">57.1196441650391</t>
@@ -6128,10 +6128,10 @@
     <t xml:space="preserve">57.558277130127</t>
   </si>
   <si>
-    <t xml:space="preserve">59.4102783203125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">58.0943794250488</t>
+    <t xml:space="preserve">59.4102821350098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">58.0943832397461</t>
   </si>
   <si>
     <t xml:space="preserve">58.240592956543</t>
@@ -6143,10 +6143,10 @@
     <t xml:space="preserve">54.4391136169434</t>
   </si>
   <si>
-    <t xml:space="preserve">53.4643783569336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">52.733325958252</t>
+    <t xml:space="preserve">53.4643745422363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">52.7333221435547</t>
   </si>
   <si>
     <t xml:space="preserve">52.3434295654297</t>
@@ -6161,28 +6161,28 @@
     <t xml:space="preserve">52.9282722473145</t>
   </si>
   <si>
-    <t xml:space="preserve">53.5618553161621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">52.8795318603516</t>
+    <t xml:space="preserve">53.5618515014648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">52.8795356750488</t>
   </si>
   <si>
     <t xml:space="preserve">52.4896392822266</t>
   </si>
   <si>
-    <t xml:space="preserve">52.1972160339355</t>
+    <t xml:space="preserve">52.1972198486328</t>
   </si>
   <si>
     <t xml:space="preserve">50.9787940979004</t>
   </si>
   <si>
-    <t xml:space="preserve">51.6611099243164</t>
+    <t xml:space="preserve">51.6611137390137</t>
   </si>
   <si>
     <t xml:space="preserve">51.612377166748</t>
   </si>
   <si>
-    <t xml:space="preserve">51.3686904907227</t>
+    <t xml:space="preserve">51.3686943054199</t>
   </si>
   <si>
     <t xml:space="preserve">52.0997467041016</t>
@@ -6215,10 +6215,10 @@
     <t xml:space="preserve">44.7014846801758</t>
   </si>
   <si>
-    <t xml:space="preserve">45.4617767333984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.4365158081055</t>
+    <t xml:space="preserve">45.4617805480957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.4365196228027</t>
   </si>
   <si>
     <t xml:space="preserve">47.1383285522461</t>
@@ -6227,16 +6227,16 @@
     <t xml:space="preserve">47.2747917175293</t>
   </si>
   <si>
-    <t xml:space="preserve">47.0798416137695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">47.7426643371582</t>
+    <t xml:space="preserve">47.0798454284668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">47.7426681518555</t>
   </si>
   <si>
     <t xml:space="preserve">47.9766044616699</t>
   </si>
   <si>
-    <t xml:space="preserve">48.2105369567871</t>
+    <t xml:space="preserve">48.2105407714844</t>
   </si>
   <si>
     <t xml:space="preserve">47.8011512756348</t>
@@ -6248,7 +6248,7 @@
     <t xml:space="preserve">50.5401649475098</t>
   </si>
   <si>
-    <t xml:space="preserve">51.8560600280762</t>
+    <t xml:space="preserve">51.8560638427734</t>
   </si>
   <si>
     <t xml:space="preserve">51.1737442016602</t>
@@ -6257,10 +6257,10 @@
     <t xml:space="preserve">50.8325843811035</t>
   </si>
   <si>
-    <t xml:space="preserve">50.34521484375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50.1990089416504</t>
+    <t xml:space="preserve">50.3452186584473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50.1990051269531</t>
   </si>
   <si>
     <t xml:space="preserve">50.8113098144531</t>
@@ -6660,6 +6660,9 @@
   </si>
   <si>
     <t xml:space="preserve">47.3199996948242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">47.9599990844727</t>
   </si>
 </sst>
 </file>
@@ -74130,7 +74133,7 @@
     </row>
     <row r="2583">
       <c r="A2583" s="1" t="n">
-        <v>46083.6911805556</v>
+        <v>46083.3333333333</v>
       </c>
       <c r="B2583" t="n">
         <v>342611</v>
@@ -74151,6 +74154,32 @@
         <v>2215</v>
       </c>
       <c r="H2583" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2584">
+      <c r="A2584" s="1" t="n">
+        <v>46084.6937384259</v>
+      </c>
+      <c r="B2584" t="n">
+        <v>525660</v>
+      </c>
+      <c r="C2584" t="n">
+        <v>47.9799995422363</v>
+      </c>
+      <c r="D2584" t="n">
+        <v>46.7599983215332</v>
+      </c>
+      <c r="E2584" t="n">
+        <v>47.1199989318848</v>
+      </c>
+      <c r="F2584" t="n">
+        <v>47.9599990844727</v>
+      </c>
+      <c r="G2584" t="s">
+        <v>2216</v>
+      </c>
+      <c r="H2584" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/REC.MI.xlsx
+++ b/data/REC.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2225" uniqueCount="2225">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2226" uniqueCount="2226">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,7 +38,7 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">18.3691120147705</t>
+    <t xml:space="preserve">18.3691101074219</t>
   </si>
   <si>
     <t xml:space="preserve">REC.MI</t>
@@ -47,67 +47,67 @@
     <t xml:space="preserve">18.9363460540771</t>
   </si>
   <si>
-    <t xml:space="preserve">18.6177654266357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2680988311768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.1204624176025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9728240966797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0116748809814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4444446563721</t>
+    <t xml:space="preserve">18.6177597045898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2680931091309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.1204586029053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9728202819824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0116786956787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4444408416748</t>
   </si>
   <si>
     <t xml:space="preserve">17.5609931945801</t>
   </si>
   <si>
-    <t xml:space="preserve">16.962682723999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9005165100098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8849678039551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6231594085693</t>
+    <t xml:space="preserve">16.9626808166504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9005146026611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8849716186523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6231575012207</t>
   </si>
   <si>
     <t xml:space="preserve">17.8484992980957</t>
   </si>
   <si>
-    <t xml:space="preserve">17.8174171447754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.13600730896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.3667373657227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.716402053833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0660724639893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.467752456665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.24241065979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6440944671631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5407047271729</t>
+    <t xml:space="preserve">17.8174228668213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.1360015869141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3667392730713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.7164001464844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0660667419434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4677543640137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2424125671387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6440963745117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5407056808472</t>
   </si>
   <si>
     <t xml:space="preserve">15.0977954864502</t>
@@ -119,25 +119,25 @@
     <t xml:space="preserve">15.7815856933594</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9136829376221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5042266845703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1647109985352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0326099395752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.3511962890625</t>
+    <t xml:space="preserve">15.9136791229248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5042285919189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1647033691406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0326118469238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3511924743652</t>
   </si>
   <si>
     <t xml:space="preserve">17.7474842071533</t>
   </si>
   <si>
-    <t xml:space="preserve">17.7707996368408</t>
+    <t xml:space="preserve">17.7707958221436</t>
   </si>
   <si>
     <t xml:space="preserve">18.034984588623</t>
@@ -146,34 +146,34 @@
     <t xml:space="preserve">16.4342918395996</t>
   </si>
   <si>
-    <t xml:space="preserve">16.3798980712891</t>
+    <t xml:space="preserve">16.3799057006836</t>
   </si>
   <si>
     <t xml:space="preserve">16.8772029876709</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0403842926025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2579498291016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4055881500244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0248374938965</t>
+    <t xml:space="preserve">17.0403804779053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2579517364502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4055862426758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0248413085938</t>
   </si>
   <si>
     <t xml:space="preserve">16.7995014190674</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7295722961426</t>
+    <t xml:space="preserve">16.7295703887939</t>
   </si>
   <si>
     <t xml:space="preserve">16.5508480072021</t>
   </si>
   <si>
-    <t xml:space="preserve">16.861665725708</t>
+    <t xml:space="preserve">16.8616619110107</t>
   </si>
   <si>
     <t xml:space="preserve">16.535306930542</t>
@@ -182,49 +182,49 @@
     <t xml:space="preserve">16.8072700500488</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9082870483398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9937572479248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9316005706787</t>
+    <t xml:space="preserve">16.9082889556885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9937591552734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9315967559814</t>
   </si>
   <si>
     <t xml:space="preserve">16.7217979431152</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7684211730957</t>
+    <t xml:space="preserve">16.7684192657471</t>
   </si>
   <si>
     <t xml:space="preserve">16.8694324493408</t>
   </si>
   <si>
-    <t xml:space="preserve">16.6829433441162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9782180786133</t>
+    <t xml:space="preserve">16.6829452514648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9782218933105</t>
   </si>
   <si>
     <t xml:space="preserve">17.0947780609131</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1025409698486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2190952301025</t>
+    <t xml:space="preserve">17.1025485992432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2191009521484</t>
   </si>
   <si>
     <t xml:space="preserve">17.1336250305176</t>
   </si>
   <si>
-    <t xml:space="preserve">17.4832897186279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.5454578399658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.459981918335</t>
+    <t xml:space="preserve">17.4832878112793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.5454540252686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4599781036377</t>
   </si>
   <si>
     <t xml:space="preserve">17.4366683959961</t>
@@ -233,25 +233,25 @@
     <t xml:space="preserve">17.4522075653076</t>
   </si>
   <si>
-    <t xml:space="preserve">17.3822765350342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4133586883545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.7677688598633</t>
+    <t xml:space="preserve">17.3822784423828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4133567810059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.7677707672119</t>
   </si>
   <si>
     <t xml:space="preserve">17.6968879699707</t>
   </si>
   <si>
-    <t xml:space="preserve">17.5314998626709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6102561950684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.3818550109863</t>
+    <t xml:space="preserve">17.531494140625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6102542877197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.381856918335</t>
   </si>
   <si>
     <t xml:space="preserve">17.4448623657227</t>
@@ -260,46 +260,46 @@
     <t xml:space="preserve">17.5078678131104</t>
   </si>
   <si>
-    <t xml:space="preserve">17.6811408996582</t>
+    <t xml:space="preserve">17.6811370849609</t>
   </si>
   <si>
     <t xml:space="preserve">17.4133605957031</t>
   </si>
   <si>
-    <t xml:space="preserve">17.4763641357422</t>
+    <t xml:space="preserve">17.4763679504395</t>
   </si>
   <si>
     <t xml:space="preserve">17.4291095733643</t>
   </si>
   <si>
-    <t xml:space="preserve">17.6023788452148</t>
+    <t xml:space="preserve">17.6023750305176</t>
   </si>
   <si>
     <t xml:space="preserve">17.8937816619873</t>
   </si>
   <si>
-    <t xml:space="preserve">17.9804172515869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.6734809875488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.9648876190186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.9018840789795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.7286148071289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.0436458587646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.0200176239014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.0672760009766</t>
+    <t xml:space="preserve">17.9804134368896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6734828948975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.9648895263672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.9018821716309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.7286128997803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.043643951416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.0200214385986</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.0672740936279</t>
   </si>
   <si>
     <t xml:space="preserve">19.216911315918</t>
@@ -311,19 +311,19 @@
     <t xml:space="preserve">20.0911273956299</t>
   </si>
   <si>
-    <t xml:space="preserve">20.2328929901123</t>
+    <t xml:space="preserve">20.232889175415</t>
   </si>
   <si>
     <t xml:space="preserve">20.421911239624</t>
   </si>
   <si>
-    <t xml:space="preserve">20.3274002075195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.4691619873047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.760570526123</t>
+    <t xml:space="preserve">20.3273944854736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.4691600799561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.7605686187744</t>
   </si>
   <si>
     <t xml:space="preserve">20.8944568634033</t>
@@ -335,49 +335,49 @@
     <t xml:space="preserve">21.2488670349121</t>
   </si>
   <si>
-    <t xml:space="preserve">21.4142570495605</t>
+    <t xml:space="preserve">21.4142551422119</t>
   </si>
   <si>
     <t xml:space="preserve">21.067720413208</t>
   </si>
   <si>
-    <t xml:space="preserve">20.9968414306641</t>
+    <t xml:space="preserve">20.9968357086182</t>
   </si>
   <si>
     <t xml:space="preserve">21.4930152893066</t>
   </si>
   <si>
-    <t xml:space="preserve">21.4536361694336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.146484375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.4770374298096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.4297847747803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.6266784667969</t>
+    <t xml:space="preserve">21.4536323547363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.1464805603027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.4770412445068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.4297866821289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.6266822814941</t>
   </si>
   <si>
     <t xml:space="preserve">20.3667755126953</t>
   </si>
   <si>
-    <t xml:space="preserve">19.9729900360107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.6424312591553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.9102077484131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.8156986236572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.1386051177979</t>
+    <t xml:space="preserve">19.9729919433594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.6424293518066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.9102058410645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.8156967163086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.1386032104492</t>
   </si>
   <si>
     <t xml:space="preserve">20.0438690185547</t>
@@ -389,25 +389,25 @@
     <t xml:space="preserve">21.1543579101562</t>
   </si>
   <si>
-    <t xml:space="preserve">21.2646198272705</t>
+    <t xml:space="preserve">21.2646179199219</t>
   </si>
   <si>
     <t xml:space="preserve">21.2882461547852</t>
   </si>
   <si>
-    <t xml:space="preserve">21.2803649902344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.1858577728271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.0519714355469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.3748760223389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.0758209228516</t>
+    <t xml:space="preserve">21.2803688049316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.1858596801758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.0519733428955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.3748817443848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.0758266448975</t>
   </si>
   <si>
     <t xml:space="preserve">22.2884693145752</t>
@@ -416,13 +416,13 @@
     <t xml:space="preserve">22.1545810699463</t>
   </si>
   <si>
-    <t xml:space="preserve">21.9183082580566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.7292861938477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.9104328155518</t>
+    <t xml:space="preserve">21.9183044433594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.7292900085449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.9104347229004</t>
   </si>
   <si>
     <t xml:space="preserve">21.8001689910889</t>
@@ -431,49 +431,49 @@
     <t xml:space="preserve">22.217586517334</t>
   </si>
   <si>
-    <t xml:space="preserve">22.6507549285889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.6192512512207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.6586303710938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.3750991821289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.8161487579346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.7925205230713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.6665058135986</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.8476505279541</t>
+    <t xml:space="preserve">22.6507568359375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.6192531585693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.6586322784424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.3751029968262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.8161506652832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.7925186157227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.66650390625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.8476524353027</t>
   </si>
   <si>
     <t xml:space="preserve">23.1233024597168</t>
   </si>
   <si>
-    <t xml:space="preserve">22.7216377258301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.1230773925781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.4932422637939</t>
+    <t xml:space="preserve">22.7216339111328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.1230754852295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.4932384490967</t>
   </si>
   <si>
     <t xml:space="preserve">22.2412166595459</t>
   </si>
   <si>
-    <t xml:space="preserve">22.1782073974609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.4066066741943</t>
+    <t xml:space="preserve">22.1782093048096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.4066047668457</t>
   </si>
   <si>
     <t xml:space="preserve">22.3672256469727</t>
@@ -482,7 +482,7 @@
     <t xml:space="preserve">22.5168704986572</t>
   </si>
   <si>
-    <t xml:space="preserve">21.9025573730469</t>
+    <t xml:space="preserve">21.9025535583496</t>
   </si>
   <si>
     <t xml:space="preserve">21.8946800231934</t>
@@ -491,10 +491,10 @@
     <t xml:space="preserve">21.4772644042969</t>
   </si>
   <si>
-    <t xml:space="preserve">21.6111507415771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.3355007171631</t>
+    <t xml:space="preserve">21.6111583709717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.3354988098145</t>
   </si>
   <si>
     <t xml:space="preserve">21.4851417541504</t>
@@ -506,148 +506,148 @@
     <t xml:space="preserve">21.6977825164795</t>
   </si>
   <si>
-    <t xml:space="preserve">21.2094860076904</t>
+    <t xml:space="preserve">21.2094841003418</t>
   </si>
   <si>
     <t xml:space="preserve">21.2331142425537</t>
   </si>
   <si>
-    <t xml:space="preserve">21.5402717590332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.3591270446777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.1228542327881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.3827514648438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.2724895477295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.9655628204346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.6899108886719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.0834808349609</t>
+    <t xml:space="preserve">21.5402698516846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.3591289520264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.1228561401367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.3827533721924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.2724933624268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.9655609130859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.6899147033691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.083475112915</t>
   </si>
   <si>
     <t xml:space="preserve">21.0047168731689</t>
   </si>
   <si>
-    <t xml:space="preserve">20.9495830535889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.3985023498535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.5481452941895</t>
+    <t xml:space="preserve">20.9495868682861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.3985042572021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.5481472015381</t>
   </si>
   <si>
     <t xml:space="preserve">21.1779842376709</t>
   </si>
   <si>
-    <t xml:space="preserve">21.3906269073486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.4063816070557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.6190280914307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.6584091186523</t>
+    <t xml:space="preserve">21.3906326293945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.4063835144043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.6190319061279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.6584072113037</t>
   </si>
   <si>
     <t xml:space="preserve">22.3908557891846</t>
   </si>
   <si>
-    <t xml:space="preserve">22.5956268310547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.532621383667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.4223556518555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.3514747619629</t>
+    <t xml:space="preserve">22.5956249237061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.5326194763184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.4223594665527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.3514766693115</t>
   </si>
   <si>
     <t xml:space="preserve">22.304220199585</t>
   </si>
   <si>
-    <t xml:space="preserve">22.1860847473145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.0837020874023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.2648448944092</t>
+    <t xml:space="preserve">22.1860828399658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.0837001800537</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.2648429870605</t>
   </si>
   <si>
     <t xml:space="preserve">21.5166435241699</t>
   </si>
   <si>
-    <t xml:space="preserve">21.6820411682129</t>
+    <t xml:space="preserve">21.6820335388184</t>
   </si>
   <si>
     <t xml:space="preserve">21.2252388000488</t>
   </si>
   <si>
-    <t xml:space="preserve">21.3512554168701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.256742477417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.1070995330811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.0913505554199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3037700653076</t>
+    <t xml:space="preserve">21.3512516021729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.2567405700684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.1071033477783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.0913524627686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3037757873535</t>
   </si>
   <si>
     <t xml:space="preserve">19.8627281188965</t>
   </si>
   <si>
-    <t xml:space="preserve">20.1620101928711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.2565174102783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.8154735565186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3116474151611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.1937351226807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.5164184570312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.555793762207</t>
+    <t xml:space="preserve">20.1620082855225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.2565135955811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.8154754638672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3116512298584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.1937370300293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.5164165496826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.5558013916016</t>
   </si>
   <si>
     <t xml:space="preserve">20.1383800506592</t>
   </si>
   <si>
-    <t xml:space="preserve">20.02024269104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.2643947601318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.2164840698242</t>
+    <t xml:space="preserve">20.0202407836914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.2643890380859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.2164859771729</t>
   </si>
   <si>
     <t xml:space="preserve">19.7134704589844</t>
@@ -659,73 +659,73 @@
     <t xml:space="preserve">20.2564086914062</t>
   </si>
   <si>
-    <t xml:space="preserve">20.3282661437988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.0887336730957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3602085113525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.5119094848633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.8092784881592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.1286582946777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3442344665527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.5598163604736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.5039253234863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3841590881348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.7594261169434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.4719848632812</t>
+    <t xml:space="preserve">20.3282680511475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.088737487793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3602027893066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.511905670166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.8092861175537</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.1286602020264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3442363739014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.559814453125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.503927230835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3841609954834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.7594299316406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.4719886779785</t>
   </si>
   <si>
     <t xml:space="preserve">20.7354736328125</t>
   </si>
   <si>
-    <t xml:space="preserve">20.4240818023682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.1107444763184</t>
+    <t xml:space="preserve">20.4240798950195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.1107349395752</t>
   </si>
   <si>
     <t xml:space="preserve">21.3582534790039</t>
   </si>
   <si>
-    <t xml:space="preserve">21.5179443359375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.2943801879883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.1027545928955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.9270992279053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.501974105835</t>
+    <t xml:space="preserve">21.5179424285889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.2943820953369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.1027526855469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.927095413208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.5019721984863</t>
   </si>
   <si>
     <t xml:space="preserve">21.605770111084</t>
   </si>
   <si>
-    <t xml:space="preserve">21.3502674102783</t>
+    <t xml:space="preserve">21.3502712249756</t>
   </si>
   <si>
     <t xml:space="preserve">21.4939880371094</t>
@@ -734,127 +734,127 @@
     <t xml:space="preserve">21.8053817749023</t>
   </si>
   <si>
-    <t xml:space="preserve">21.7335224151611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.8453044891357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.1966152191162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.1806507110596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.7095680236816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.2205715179443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.7894096374512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.1087913513184</t>
+    <t xml:space="preserve">21.7335243225098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.8453025817871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.1966171264648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.1806468963623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.709566116333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.2205677032471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.7894115447998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.1087894439697</t>
   </si>
   <si>
     <t xml:space="preserve">21.9570846557617</t>
   </si>
   <si>
-    <t xml:space="preserve">21.9890213012695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.7734451293945</t>
+    <t xml:space="preserve">21.9890251159668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.7734470367432</t>
   </si>
   <si>
     <t xml:space="preserve">21.7814292907715</t>
   </si>
   <si>
-    <t xml:space="preserve">21.749490737915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.4620513916016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.6377067565918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.6137561798096</t>
+    <t xml:space="preserve">21.7494869232178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.4620475769043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.6377086639404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.6137580871582</t>
   </si>
   <si>
     <t xml:space="preserve">21.0069408416748</t>
   </si>
   <si>
-    <t xml:space="preserve">21.0867805480957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.2544536590576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.438102722168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.0708122253418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.454065322876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.5578632354736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.4281635284424</t>
+    <t xml:space="preserve">21.086784362793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.2544593811035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.4380989074707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.0708160400391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.4540691375732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.5578651428223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.4281616210938</t>
   </si>
   <si>
     <t xml:space="preserve">22.539945602417</t>
   </si>
   <si>
-    <t xml:space="preserve">22.5958385467529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.8194026947021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.5638942718506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.0509452819824</t>
+    <t xml:space="preserve">22.5958347320557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.8193988800049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.5639038085938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.0509433746338</t>
   </si>
   <si>
     <t xml:space="preserve">23.1467590332031</t>
   </si>
   <si>
-    <t xml:space="preserve">23.5539684295654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.5220241546631</t>
+    <t xml:space="preserve">23.5539646148682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.5220260620117</t>
   </si>
   <si>
     <t xml:space="preserve">23.4501667022705</t>
   </si>
   <si>
-    <t xml:space="preserve">23.8733425140381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.9292297363281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.8653545379639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.1687660217285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.2326354980469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.0889186859131</t>
+    <t xml:space="preserve">23.8733348846436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.9292259216309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.8653526306152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.1687602996826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.2326335906982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.0889205932617</t>
   </si>
   <si>
     <t xml:space="preserve">24.1847305297852</t>
   </si>
   <si>
-    <t xml:space="preserve">24.3444194793701</t>
+    <t xml:space="preserve">24.3444213867188</t>
   </si>
   <si>
     <t xml:space="preserve">24.6158847808838</t>
@@ -863,16 +863,16 @@
     <t xml:space="preserve">24.6079044342041</t>
   </si>
   <si>
-    <t xml:space="preserve">24.8554191589355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.9751892089844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.2466564178467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.4382820129395</t>
+    <t xml:space="preserve">24.8554172515869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.9751853942871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.2466526031494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.4382762908936</t>
   </si>
   <si>
     <t xml:space="preserve">25.4702167510986</t>
@@ -881,34 +881,34 @@
     <t xml:space="preserve">25.0071220397949</t>
   </si>
   <si>
-    <t xml:space="preserve">24.9272804260254</t>
+    <t xml:space="preserve">24.9272842407227</t>
   </si>
   <si>
     <t xml:space="preserve">25.1668090820312</t>
   </si>
   <si>
-    <t xml:space="preserve">25.3344821929932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.2785949707031</t>
+    <t xml:space="preserve">25.3344841003418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.2785911560059</t>
   </si>
   <si>
     <t xml:space="preserve">25.629903793335</t>
   </si>
   <si>
-    <t xml:space="preserve">25.3983554840088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.2067279815674</t>
+    <t xml:space="preserve">25.3983592987061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.2067317962646</t>
   </si>
   <si>
     <t xml:space="preserve">25.2865772247314</t>
   </si>
   <si>
-    <t xml:space="preserve">25.3664226531982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.5899848937988</t>
+    <t xml:space="preserve">25.3664169311523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.5899829864502</t>
   </si>
   <si>
     <t xml:space="preserve">25.9492835998535</t>
@@ -917,19 +917,19 @@
     <t xml:space="preserve">25.9652500152588</t>
   </si>
   <si>
-    <t xml:space="preserve">26.2207527160645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.045093536377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.0211391448975</t>
+    <t xml:space="preserve">26.2207489013672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.0450916290283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.0211410522461</t>
   </si>
   <si>
     <t xml:space="preserve">26.4043922424316</t>
   </si>
   <si>
-    <t xml:space="preserve">26.6598892211914</t>
+    <t xml:space="preserve">26.65989112854</t>
   </si>
   <si>
     <t xml:space="preserve">26.6119861602783</t>
@@ -938,226 +938,226 @@
     <t xml:space="preserve">26.3804378509521</t>
   </si>
   <si>
-    <t xml:space="preserve">26.6439266204834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.0351581573486</t>
+    <t xml:space="preserve">26.643928527832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.0351619720459</t>
   </si>
   <si>
     <t xml:space="preserve">26.5002040863037</t>
   </si>
   <si>
-    <t xml:space="preserve">27.6864166259766</t>
+    <t xml:space="preserve">27.6864185333252</t>
   </si>
   <si>
     <t xml:space="preserve">27.4685459136963</t>
   </si>
   <si>
-    <t xml:space="preserve">27.4362735748291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.7186985015869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.4443321228027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.7832565307617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.5573101043701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.6218585968018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.3481197357178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.743522644043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.7193183898926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.4455738067627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.534330368042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.4536399841309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.6628246307373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.8403644561768</t>
+    <t xml:space="preserve">27.4362697601318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.7187004089355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.4443340301514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.783260345459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.5573120117188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.621862411499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.3481178283691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.7435188293457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.719310760498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.4455680847168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.5343360900879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.4536418914795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.6628265380859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.8403587341309</t>
   </si>
   <si>
     <t xml:space="preserve">28.929126739502</t>
   </si>
   <si>
-    <t xml:space="preserve">28.8322887420654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.7758007049561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.945255279541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.8000068664551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.1389293670654</t>
+    <t xml:space="preserve">28.8322849273682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.7757968902588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.9452610015869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.8000106811523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.1389312744141</t>
   </si>
   <si>
     <t xml:space="preserve">28.3884658813477</t>
   </si>
   <si>
-    <t xml:space="preserve">28.4852981567383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.8968467712402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.583366394043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.6230964660645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.7441425323486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.2680416107178</t>
+    <t xml:space="preserve">28.4853000640869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.8968448638916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.5833778381348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.6230926513672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.7441368103027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.2680397033691</t>
   </si>
   <si>
     <t xml:space="preserve">29.4375</t>
   </si>
   <si>
-    <t xml:space="preserve">29.4697704315186</t>
+    <t xml:space="preserve">29.4697761535645</t>
   </si>
   <si>
     <t xml:space="preserve">28.9371929168701</t>
   </si>
   <si>
-    <t xml:space="preserve">29.4052200317383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.0749893188477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.8893928527832</t>
+    <t xml:space="preserve">29.4052219390869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.0749931335449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.8893890380859</t>
   </si>
   <si>
     <t xml:space="preserve">30.1072654724121</t>
   </si>
   <si>
-    <t xml:space="preserve">30.3412799835205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.0265731811523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.1798973083496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.2518997192383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.4610939025879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.0818214416504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.5659923553467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.6386260986328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.2109394073486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.1544532775879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.4368801116943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.2593574523926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.6063404083252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.3158397674561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.590202331543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.6547565460205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.1147155761719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.1308574676514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.0663013458252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.8080806732178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.6789665222168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.8564987182617</t>
+    <t xml:space="preserve">30.3412780761719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.026575088501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.1798915863037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.251895904541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.4610919952393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.0818290710449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.5659942626953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.6386241912842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.2109355926514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.1544494628906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.4368877410889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.2593612670898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.6063461303711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.3158416748047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.5902004241943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.6547527313232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.1147270202637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.1308555603027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.0663032531738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.8080711364746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.6789684295654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.8564929962158</t>
   </si>
   <si>
     <t xml:space="preserve">28.6951084136963</t>
   </si>
   <si>
-    <t xml:space="preserve">28.6305522918701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.7596626281738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.2512817382812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.976921081543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.3561897277832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.4126720428467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.1786575317383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.2028713226318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.5337200164795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.2835597991943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.5982723236084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.5014381408691</t>
+    <t xml:space="preserve">28.6305503845215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.7596683502197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.2512798309326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.9769153594971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.3561878204346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.4126777648926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.1786594390869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.2028675079346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.533712387085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.283561706543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.5982704162598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.5014362335205</t>
   </si>
   <si>
     <t xml:space="preserve">28.3803958892822</t>
@@ -1166,301 +1166,301 @@
     <t xml:space="preserve">28.7677307128906</t>
   </si>
   <si>
-    <t xml:space="preserve">29.0340270996094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.332592010498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.2115592956543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.1873378753662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.3971500396729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.8409767150879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.0346488952637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.9942932128906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.0991954803467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.2202472686768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.8490428924561</t>
+    <t xml:space="preserve">29.0340251922607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.3325881958008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.211555480957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.1873455047607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.3971481323242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.8409729003906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.0346450805664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.9942989349365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.0991973876953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.2202396392822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.849048614502</t>
   </si>
   <si>
     <t xml:space="preserve">30.0830612182617</t>
   </si>
   <si>
-    <t xml:space="preserve">30.4058361053467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.5995025634766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.0352573394775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.5275039672852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.4387302398682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.3499622344971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.7937889099121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.4710140228271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.7695808410645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.5839786529541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.8018608093262</t>
+    <t xml:space="preserve">30.4058437347412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.5995063781738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.0352554321289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.5274982452393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.4387321472168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.3499698638916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.7937984466553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.4710102081299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.7695827484131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.5839824676514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.8018569946289</t>
   </si>
   <si>
     <t xml:space="preserve">31.9067668914795</t>
   </si>
   <si>
-    <t xml:space="preserve">31.9309673309326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.1649894714355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.1407737731934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.3425178527832</t>
+    <t xml:space="preserve">31.9309711456299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.1649932861328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.1407852172852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.3425216674805</t>
   </si>
   <si>
     <t xml:space="preserve">32.1085052490234</t>
   </si>
   <si>
-    <t xml:space="preserve">32.3586578369141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.9632587432861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.0116691589355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.8986892700195</t>
+    <t xml:space="preserve">32.3586540222168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.963249206543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.0116729736328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.8986930847168</t>
   </si>
   <si>
     <t xml:space="preserve">32.0439453125</t>
   </si>
   <si>
-    <t xml:space="preserve">32.2295417785645</t>
+    <t xml:space="preserve">32.2295341491699</t>
   </si>
   <si>
     <t xml:space="preserve">32.423210144043</t>
   </si>
   <si>
-    <t xml:space="preserve">31.9551792144775</t>
+    <t xml:space="preserve">31.955171585083</t>
   </si>
   <si>
     <t xml:space="preserve">32.0358772277832</t>
   </si>
   <si>
-    <t xml:space="preserve">32.1891975402832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.3667144775391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.2053413391113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.4877662658691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.1246452331543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.7621269226074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.6491546630859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.1004333496094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.277961730957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.4064502716064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.3176956176758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.1562995910645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.4145202636719</t>
+    <t xml:space="preserve">32.1892013549805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.3667221069336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.2053375244141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.4877700805664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.124641418457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.762134552002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.6491508483887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.1004257202148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.2779541015625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.4064540863037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.3176918029785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.1563014984131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.4145183563232</t>
   </si>
   <si>
     <t xml:space="preserve">30.8012466430664</t>
   </si>
   <si>
-    <t xml:space="preserve">31.1805038452148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.6963424682617</t>
+    <t xml:space="preserve">31.1805057525635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.6963367462158</t>
   </si>
   <si>
     <t xml:space="preserve">31.2348709106445</t>
   </si>
   <si>
-    <t xml:space="preserve">31.275671005249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.1614322662354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.210391998291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.9982376098633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.9900798797607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.6963386535645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.8432197570801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.7044982910156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.9166469573975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.60205078125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.2593517303467</t>
+    <t xml:space="preserve">31.2756729125977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.1614437103271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.2103958129883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.9982471466064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.9900875091553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.696346282959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.8432178497314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.7045021057129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.9166488647461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.6020545959473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.2593555450439</t>
   </si>
   <si>
     <t xml:space="preserve">31.0472049713135</t>
   </si>
   <si>
-    <t xml:space="preserve">31.5612545013428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.5204639434814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.5857315063477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.835054397583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.2067680358887</t>
+    <t xml:space="preserve">31.56125831604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.5204544067383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.5857276916504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.8350601196289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.2067623138428</t>
   </si>
   <si>
     <t xml:space="preserve">29.8395843505859</t>
   </si>
   <si>
-    <t xml:space="preserve">30.3944282531738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.3781185150146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.8477439880371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.7416706085205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.1904449462891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.4597148895264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.5086688995361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.2394027709961</t>
+    <t xml:space="preserve">30.394437789917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.3781147003174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.8477478027344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.7416667938232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.1904411315918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.4597129821777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.5086765289307</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.2394123077393</t>
   </si>
   <si>
     <t xml:space="preserve">30.4352321624756</t>
   </si>
   <si>
-    <t xml:space="preserve">30.2883567810059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.7616195678711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.3001480102539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.4307117462158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.5775737762451</t>
+    <t xml:space="preserve">30.2883605957031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.7616157531738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.300142288208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.430700302124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.5775756835938</t>
   </si>
   <si>
     <t xml:space="preserve">31.3491039276123</t>
   </si>
   <si>
-    <t xml:space="preserve">31.1695919036865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.4959831237793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.1043148040771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.9411239624023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.5494709014893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.7942581176758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.4633464813232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.8595352172852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.3327884674072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.3128490447998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.9211826324463</t>
+    <t xml:space="preserve">31.1695938110352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.4959754943848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.1043071746826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.941125869751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.5494632720947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.7942543029785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.4633388519287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.8595314025879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.33278465271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.3128356933594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.9211730957031</t>
   </si>
   <si>
     <t xml:space="preserve">29.5540027618408</t>
@@ -1469,70 +1469,70 @@
     <t xml:space="preserve">28.7869930267334</t>
   </si>
   <si>
-    <t xml:space="preserve">28.1505508422852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.155086517334</t>
+    <t xml:space="preserve">28.1505489349365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.1550807952881</t>
   </si>
   <si>
     <t xml:space="preserve">28.362699508667</t>
   </si>
   <si>
-    <t xml:space="preserve">26.0780162811279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.1886253356934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.6337738037109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.1686744689941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.3518161773682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.0335884094238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.4007682800293</t>
+    <t xml:space="preserve">26.0780181884766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.1886234283447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.6337699890137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.1686782836914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.3518123626709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.0335922241211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.4007701873779</t>
   </si>
   <si>
     <t xml:space="preserve">24.495059967041</t>
   </si>
   <si>
-    <t xml:space="preserve">24.070764541626</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.9075679779053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.711742401123</t>
+    <t xml:space="preserve">24.0707607269287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.907564163208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.7117385864258</t>
   </si>
   <si>
     <t xml:space="preserve">24.397144317627</t>
   </si>
   <si>
-    <t xml:space="preserve">24.2339534759521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.0299606323242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.7199001312256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.140567779541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.5730247497559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.6464691162109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.4216213226318</t>
+    <t xml:space="preserve">24.2339553833008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.0299644470215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.719898223877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.1405639648438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.5730266571045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.6464614868164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.4216251373291</t>
   </si>
   <si>
     <t xml:space="preserve">24.3155498504639</t>
@@ -1541,82 +1541,82 @@
     <t xml:space="preserve">24.5521755218506</t>
   </si>
   <si>
-    <t xml:space="preserve">24.2013149261475</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.7933349609375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.0626010894775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.9238872528076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.7035789489746</t>
+    <t xml:space="preserve">24.2013111114502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.7933330535889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.0626049041748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.9238891601562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.7035808563232</t>
   </si>
   <si>
     <t xml:space="preserve">23.3363990783691</t>
   </si>
   <si>
-    <t xml:space="preserve">23.2384796142578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.189525604248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.1568851470947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.4551658630371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.8468246459961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.548547744751</t>
+    <t xml:space="preserve">23.2384834289551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.1895236968994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.1568870544434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.4551620483398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.8468227386475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.5485496520996</t>
   </si>
   <si>
     <t xml:space="preserve">24.4624195098877</t>
   </si>
   <si>
-    <t xml:space="preserve">24.0870819091797</t>
+    <t xml:space="preserve">24.0870780944824</t>
   </si>
   <si>
     <t xml:space="preserve">24.380823135376</t>
   </si>
   <si>
-    <t xml:space="preserve">24.3563499450684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.0952396392822</t>
+    <t xml:space="preserve">24.3563442230225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.0952377319336</t>
   </si>
   <si>
     <t xml:space="preserve">24.1278762817383</t>
   </si>
   <si>
-    <t xml:space="preserve">23.9157257080078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.2094745635986</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.1523532867432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.3481845855713</t>
+    <t xml:space="preserve">23.9157276153564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.2094707489014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.1523590087891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.3481884002686</t>
   </si>
   <si>
     <t xml:space="preserve">24.5551605224609</t>
   </si>
   <si>
-    <t xml:space="preserve">24.2902374267578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.5054836273193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.4558124542236</t>
+    <t xml:space="preserve">24.2902355194092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.505485534668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.4558143615723</t>
   </si>
   <si>
     <t xml:space="preserve">24.5468769073486</t>
@@ -1628,22 +1628,22 @@
     <t xml:space="preserve">25.308536529541</t>
   </si>
   <si>
-    <t xml:space="preserve">25.3747634887695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.5982971191406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.3333721160889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.4244403839111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.151237487793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.2505874633789</t>
+    <t xml:space="preserve">25.3747653961182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.5983028411865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.3333740234375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.4244365692139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.1512393951416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.2505855560303</t>
   </si>
   <si>
     <t xml:space="preserve">25.5320682525635</t>
@@ -1652,79 +1652,79 @@
     <t xml:space="preserve">25.4161624908447</t>
   </si>
   <si>
-    <t xml:space="preserve">24.9277076721191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.6248779296875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.4261875152588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.6828308105469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.550365447998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.5089778900146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.566930770874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.600040435791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.2440490722656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.1115875244141</t>
+    <t xml:space="preserve">24.9277095794678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.6248760223389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.4261856079102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.6828327178955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.5503673553467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.5089721679688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.5669250488281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.6000442504883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.2440528869629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.1115894317627</t>
   </si>
   <si>
     <t xml:space="preserve">26.2606067657471</t>
   </si>
   <si>
-    <t xml:space="preserve">26.3433952331543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.2937278747559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.2540760040283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.3203067779541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.2789115905762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.94775390625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.1298942565918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.1878433227539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.5686683654785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.1961231231689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.0636615753174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.7839260101318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.5455837249756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.2806510925293</t>
+    <t xml:space="preserve">26.3433933258057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.2937240600586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.2540721893311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.3203010559082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.2789096832275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.9477500915527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.1298904418945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.1878452301025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.5686702728271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.1961193084717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.063663482666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.7839241027832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.5455741882324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.2806549072266</t>
   </si>
   <si>
     <t xml:space="preserve">28.3468837738037</t>
@@ -1733,7 +1733,7 @@
     <t xml:space="preserve">27.5024394989014</t>
   </si>
   <si>
-    <t xml:space="preserve">27.4527683258057</t>
+    <t xml:space="preserve">27.4527702331543</t>
   </si>
   <si>
     <t xml:space="preserve">27.800479888916</t>
@@ -1742,46 +1742,46 @@
     <t xml:space="preserve">27.7673645019531</t>
   </si>
   <si>
-    <t xml:space="preserve">28.197868347168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.6876163482666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.7024345397949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.0418682098389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.3399085998535</t>
+    <t xml:space="preserve">28.1978626251221</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.6876220703125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.7024326324463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.0418701171875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.3399047851562</t>
   </si>
   <si>
     <t xml:space="preserve">24.8035202026367</t>
   </si>
   <si>
-    <t xml:space="preserve">25.0436172485352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.6645278930664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.6728076934814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.358211517334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.4492740631104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.8780345916748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.7538547515869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.8614768981934</t>
+    <t xml:space="preserve">25.0436134338379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.664529800415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.6728096008301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.3582077026367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.4492721557617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.8780326843262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.7538528442383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.861478805542</t>
   </si>
   <si>
     <t xml:space="preserve">25.8301067352295</t>
@@ -1799,154 +1799,154 @@
     <t xml:space="preserve">26.0453548431396</t>
   </si>
   <si>
-    <t xml:space="preserve">25.7555923461914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.9128952026367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.4758548736572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.5006942749023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.2357692718506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.5752067565918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.6993885040283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.9725894927979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.9891490936279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.8732452392578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.4924125671387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.2274951934814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.6396903991699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.2754211425781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.5900192260742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.4327220916748</t>
+    <t xml:space="preserve">25.7555961608887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.9128932952881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.4758567810059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.5006923675537</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.2357711791992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.5752029418945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.6993865966797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.9725933074951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.9891471862793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.8732471466064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.4924144744873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.2274913787842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.6396942138672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.2754192352295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.5900173187256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.4327201843262</t>
   </si>
   <si>
     <t xml:space="preserve">25.1926345825195</t>
   </si>
   <si>
-    <t xml:space="preserve">24.9773807525635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.0022163391113</t>
+    <t xml:space="preserve">24.9773845672607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.0022201538086</t>
   </si>
   <si>
     <t xml:space="preserve">25.1098461151123</t>
   </si>
   <si>
-    <t xml:space="preserve">24.9691009521484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.2423076629639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.1595153808594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.2919769287109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.8863086700439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.2588653564453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.811803817749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.6296710968018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.6710643768311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.563440322876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.3895778656006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.2985134124756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.1080989837646</t>
+    <t xml:space="preserve">24.9691028594971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.2423038482666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.159517288208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.2919788360596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.8863124847412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.2588634490967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.8118057250977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.6296691894531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.6710605621338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.5634384155273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.3895797729492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.2985095977783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.108097076416</t>
   </si>
   <si>
     <t xml:space="preserve">24.3067893981934</t>
   </si>
   <si>
-    <t xml:space="preserve">24.4475345611572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.6131057739258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.1412162780762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.356466293335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.4889297485352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.3830471038818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.1181240081787</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.7207336425781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.8531970977783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.01877784729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.0915412902832</t>
+    <t xml:space="preserve">24.4475364685059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.6131114959717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.1412124633789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.3564682006836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.4889278411865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.3830451965332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.1181259155273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.7207355499268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.853199005127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.0187759399414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.0915393829346</t>
   </si>
   <si>
     <t xml:space="preserve">23.9508018493652</t>
   </si>
   <si>
-    <t xml:space="preserve">23.8183364868164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.0004730224609</t>
+    <t xml:space="preserve">23.8183403015137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.0004749298096</t>
   </si>
   <si>
     <t xml:space="preserve">24.1494922637939</t>
   </si>
   <si>
-    <t xml:space="preserve">24.5220432281494</t>
+    <t xml:space="preserve">24.522045135498</t>
   </si>
   <si>
     <t xml:space="preserve">24.8283596038818</t>
@@ -1961,130 +1961,130 @@
     <t xml:space="preserve">24.2488403320312</t>
   </si>
   <si>
-    <t xml:space="preserve">25.0850086212158</t>
+    <t xml:space="preserve">25.0850048065186</t>
   </si>
   <si>
     <t xml:space="preserve">25.6065769195557</t>
   </si>
   <si>
-    <t xml:space="preserve">24.7704105377197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.9111499786377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.960823059082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.7952499389648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.9194278717041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.695894241333</t>
+    <t xml:space="preserve">24.7704086303711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.9111518859863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.9608249664307</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.7952480316162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.9194297790527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.6958980560303</t>
   </si>
   <si>
     <t xml:space="preserve">25.0270538330078</t>
   </si>
   <si>
-    <t xml:space="preserve">24.712459564209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.5303192138672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.9425182342529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.0087547302246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.1246528625488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.2087478637695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.8639888763428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.8555793762207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.485595703125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.4771862030029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.5360450744629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.3426418304443</t>
+    <t xml:space="preserve">24.7124557495117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.5303211212158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.9425201416016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.0087509155273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.1246566772461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.2087440490723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.8639850616455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.8555755615234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.4855937957764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.4771823883057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.5360469818115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.3426456451416</t>
   </si>
   <si>
     <t xml:space="preserve">23.8892135620117</t>
   </si>
   <si>
-    <t xml:space="preserve">24.217155456543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.1919250488281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.048978805542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.544454574585</t>
+    <t xml:space="preserve">24.2171497344971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.1919269561768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.0489768981934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.5444526672363</t>
   </si>
   <si>
     <t xml:space="preserve">23.6285457611084</t>
   </si>
   <si>
-    <t xml:space="preserve">23.4940013885498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.4603652954102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.9060325622559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.8808002471924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.1330699920654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.3853282928467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.553503036499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.9318923950195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.4784641265869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.0754814147949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.4700584411621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.2430171966553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.0580253601074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.3271064758301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.015983581543</t>
+    <t xml:space="preserve">23.4940032958984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.4603633880615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.9060287475586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.8808040618896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.1330661773682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.385326385498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.5535011291504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.9318943023682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.4784603118896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.0754852294922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.4700508117676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.2430191040039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.0580234527588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.3271083831787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.0159816741943</t>
   </si>
   <si>
     <t xml:space="preserve">24.8898525238037</t>
@@ -2093,16 +2093,16 @@
     <t xml:space="preserve">25.1589298248291</t>
   </si>
   <si>
-    <t xml:space="preserve">24.9150733947754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.7979984283447</t>
+    <t xml:space="preserve">24.9150791168213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.7979946136475</t>
   </si>
   <si>
     <t xml:space="preserve">25.8568553924561</t>
   </si>
   <si>
-    <t xml:space="preserve">25.9913959503174</t>
+    <t xml:space="preserve">25.9913940429688</t>
   </si>
   <si>
     <t xml:space="preserve">26.588415145874</t>
@@ -2114,211 +2114,211 @@
     <t xml:space="preserve">25.814811706543</t>
   </si>
   <si>
-    <t xml:space="preserve">25.3691482543945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.1757507324219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.2009735107422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.2766494750977</t>
+    <t xml:space="preserve">25.3691501617432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.1757488250732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.2009754180908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.2766532897949</t>
   </si>
   <si>
     <t xml:space="preserve">25.5877780914307</t>
   </si>
   <si>
-    <t xml:space="preserve">26.6052341461182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.386604309082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.0004425048828</t>
+    <t xml:space="preserve">26.6052303314209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.3866024017334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.0004444122314</t>
   </si>
   <si>
     <t xml:space="preserve">27.8749542236328</t>
   </si>
   <si>
-    <t xml:space="preserve">27.8329105377197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.1433925628662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.6556835174561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.9415817260742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.3115634918213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.1188049316406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.1860771179199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.4467468261719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.5560569763184</t>
+    <t xml:space="preserve">27.8329067230225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.1433887481689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.6556854248047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.9415836334229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.3115653991699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.1188068389893</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.1860752105713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.4467487335205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.556058883667</t>
   </si>
   <si>
     <t xml:space="preserve">28.0431251525879</t>
   </si>
   <si>
-    <t xml:space="preserve">28.1944808959961</t>
+    <t xml:space="preserve">28.1944847106934</t>
   </si>
   <si>
     <t xml:space="preserve">27.7992744445801</t>
   </si>
   <si>
-    <t xml:space="preserve">27.6058731079102</t>
+    <t xml:space="preserve">27.6058750152588</t>
   </si>
   <si>
     <t xml:space="preserve">27.5806446075439</t>
   </si>
   <si>
-    <t xml:space="preserve">27.8160915374756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.6815547943115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.8076839447021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.0094909667969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.4635601043701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.5896949768066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.5308380126953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.396297454834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.3626594543457</t>
+    <t xml:space="preserve">27.8160953521729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.6815490722656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.8076801300049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.0094947814941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.4635639190674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.5896911621094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.5308322906494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.3962993621826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.3626537322998</t>
   </si>
   <si>
     <t xml:space="preserve">28.9008178710938</t>
   </si>
   <si>
-    <t xml:space="preserve">29.0269432067871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.3801155090332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.2966613769531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.4143829345703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.8348255157471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.9021034240723</t>
+    <t xml:space="preserve">29.0269508361816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.3801116943359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.2966651916504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.4143867492676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.8348293304443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.9020957946777</t>
   </si>
   <si>
     <t xml:space="preserve">30.7423324584961</t>
   </si>
   <si>
-    <t xml:space="preserve">29.9687232971191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.0612258911133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.1789398193359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.9014568328857</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.8671817779541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.1867141723633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.388521194458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.926685333252</t>
+    <t xml:space="preserve">29.9687252044678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.0612239837646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.1789436340332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.9014549255371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.8671798706055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.186710357666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.3885231018066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.9266796112061</t>
   </si>
   <si>
     <t xml:space="preserve">30.1368980407715</t>
   </si>
   <si>
-    <t xml:space="preserve">29.8341884613037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.3471126556396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.3891620635986</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.1200847625732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.3218898773193</t>
+    <t xml:space="preserve">29.8341827392578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.3471202850342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.3891582489014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.1200828552246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.3218975067139</t>
   </si>
   <si>
     <t xml:space="preserve">30.4059791564941</t>
   </si>
   <si>
-    <t xml:space="preserve">30.5152950286865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.3555221557617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.851001739502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.6181774139404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.2602710723877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.285831451416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.8567848205566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.6522617340088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.669303894043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.8226928710938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.8397369384766</t>
+    <t xml:space="preserve">30.5152931213379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.355525970459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.8509979248047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.6181697845459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.2602691650391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.2858276367188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.8567771911621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.6522636413574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.6693019866943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.8226909637451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.8397350311279</t>
   </si>
   <si>
     <t xml:space="preserve">30.209135055542</t>
   </si>
   <si>
-    <t xml:space="preserve">30.3880920410156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.0783443450928</t>
+    <t xml:space="preserve">30.388090133667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.0783405303955</t>
   </si>
   <si>
     <t xml:space="preserve">30.140962600708</t>
@@ -2327,142 +2327,142 @@
     <t xml:space="preserve">29.970531463623</t>
   </si>
   <si>
-    <t xml:space="preserve">28.8627185821533</t>
+    <t xml:space="preserve">28.8627223968506</t>
   </si>
   <si>
     <t xml:space="preserve">29.4081020355225</t>
   </si>
   <si>
-    <t xml:space="preserve">30.1068744659424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.172082901001</t>
+    <t xml:space="preserve">30.1068782806396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.1720790863037</t>
   </si>
   <si>
     <t xml:space="preserve">31.1379947662354</t>
   </si>
   <si>
-    <t xml:space="preserve">31.1465225219727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.598165512085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.2572975158691</t>
+    <t xml:space="preserve">31.1465167999268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.5981674194336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.2572956085205</t>
   </si>
   <si>
     <t xml:space="preserve">30.8312149047852</t>
   </si>
   <si>
-    <t xml:space="preserve">31.2658176422119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.9760723114014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.2061672210693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.4021606445312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.4959030151367</t>
+    <t xml:space="preserve">31.2658195495605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.9760799407959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.2061614990234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.4021625518799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.4959049224854</t>
   </si>
   <si>
     <t xml:space="preserve">31.5299873352051</t>
   </si>
   <si>
-    <t xml:space="preserve">31.9731140136719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.9645862579346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.3821487426758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.3480567932129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.4673652648926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.4503135681152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.0668487548828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.0498123168945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.8708534240723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.5725994110107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.0527801513672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.5129451751709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.7856349945068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.8623313903809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.9420032501221</t>
+    <t xml:space="preserve">31.9731101989746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.9645900726318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.382152557373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.3480644226074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.4673728942871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.4503211975098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.0668601989746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.0498046875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.8708572387695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.5725955963135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.0527763366699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.5129470825195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.7856407165527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.8623332977295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.9420070648193</t>
   </si>
   <si>
     <t xml:space="preserve">30.7630386352539</t>
   </si>
   <si>
-    <t xml:space="preserve">31.2402534484863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.3510284423828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.69189453125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.0327682495117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.1520652770996</t>
+    <t xml:space="preserve">31.2402496337891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.3510341644287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.6919002532959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.0327644348145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.1520614624023</t>
   </si>
   <si>
     <t xml:space="preserve">32.5951881408691</t>
   </si>
   <si>
-    <t xml:space="preserve">32.1435432434082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.8252792358398</t>
+    <t xml:space="preserve">32.1435394287109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.8252716064453</t>
   </si>
   <si>
     <t xml:space="preserve">32.8082313537598</t>
   </si>
   <si>
-    <t xml:space="preserve">33.4899559020996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.5155334472656</t>
+    <t xml:space="preserve">33.4899520874023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.5155296325684</t>
   </si>
   <si>
     <t xml:space="preserve">33.4132614135742</t>
   </si>
   <si>
-    <t xml:space="preserve">33.7882194519043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.7626457214355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.8904685974121</t>
+    <t xml:space="preserve">33.7882232666016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.7626571655273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.8904800415039</t>
   </si>
   <si>
     <t xml:space="preserve">34.0268211364746</t>
@@ -2471,16 +2471,16 @@
     <t xml:space="preserve">34.418815612793</t>
   </si>
   <si>
-    <t xml:space="preserve">34.1716918945312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.2483825683594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.2057762145996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.9075202941895</t>
+    <t xml:space="preserve">34.171688079834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.2483863830566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.2057800292969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.9075241088867</t>
   </si>
   <si>
     <t xml:space="preserve">34.5381164550781</t>
@@ -2492,10 +2492,10 @@
     <t xml:space="preserve">33.7541313171387</t>
   </si>
   <si>
-    <t xml:space="preserve">33.0894432067871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.1746597290039</t>
+    <t xml:space="preserve">33.0894393920898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.1746520996094</t>
   </si>
   <si>
     <t xml:space="preserve">33.8308258056641</t>
@@ -2504,130 +2504,130 @@
     <t xml:space="preserve">33.992733001709</t>
   </si>
   <si>
-    <t xml:space="preserve">33.3877067565918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.1150169372559</t>
+    <t xml:space="preserve">33.3877029418945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.1150131225586</t>
   </si>
   <si>
     <t xml:space="preserve">32.5525817871094</t>
   </si>
   <si>
-    <t xml:space="preserve">33.0638732910156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.2854499816895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.9275360107422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.9586410522461</t>
+    <t xml:space="preserve">33.0638771057129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.2854423522949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.9275398254395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.9586448669434</t>
   </si>
   <si>
     <t xml:space="preserve">33.6689147949219</t>
   </si>
   <si>
-    <t xml:space="preserve">34.0694313049316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.0012626647949</t>
+    <t xml:space="preserve">34.0694351196289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.0012588500977</t>
   </si>
   <si>
     <t xml:space="preserve">34.9130706787109</t>
   </si>
   <si>
-    <t xml:space="preserve">34.2995147705078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.9671745300293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.597770690918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.4784622192383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.5295944213867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.0353393554688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.0523834228516</t>
+    <t xml:space="preserve">34.2995109558105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.967170715332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.5977630615234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.4784698486328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.529598236084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.035343170166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.0523872375488</t>
   </si>
   <si>
     <t xml:space="preserve">32.5696296691895</t>
   </si>
   <si>
-    <t xml:space="preserve">33.6263084411621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.5440559387207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.1064834594727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.6177864074707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.8393516540527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.9160461425781</t>
+    <t xml:space="preserve">33.6263046264648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.544059753418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.1064910888672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.617790222168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.8393402099609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.9160423278809</t>
   </si>
   <si>
     <t xml:space="preserve">33.302490234375</t>
   </si>
   <si>
-    <t xml:space="preserve">33.6433486938477</t>
+    <t xml:space="preserve">33.6433410644531</t>
   </si>
   <si>
     <t xml:space="preserve">33.5325660705566</t>
   </si>
   <si>
-    <t xml:space="preserve">33.541088104248</t>
+    <t xml:space="preserve">33.5410919189453</t>
   </si>
   <si>
     <t xml:space="preserve">32.9360580444336</t>
   </si>
   <si>
-    <t xml:space="preserve">31.6578159332275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.8282413482666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.3765983581543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.8112030029297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.2743377685547</t>
+    <t xml:space="preserve">31.6578121185303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.8282432556152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.3765964508057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.8112010955811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.274341583252</t>
   </si>
   <si>
     <t xml:space="preserve">31.5811195373535</t>
   </si>
   <si>
-    <t xml:space="preserve">31.9305076599121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.5270195007324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.9219856262207</t>
+    <t xml:space="preserve">31.9305114746094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.5270156860352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.9219779968262</t>
   </si>
   <si>
     <t xml:space="preserve">32.1264991760254</t>
   </si>
   <si>
-    <t xml:space="preserve">31.3425197601318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.1294689178467</t>
+    <t xml:space="preserve">31.3425064086914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.1294708251953</t>
   </si>
   <si>
     <t xml:space="preserve">31.1550350189209</t>
@@ -2636,79 +2636,79 @@
     <t xml:space="preserve">31.4106884002686</t>
   </si>
   <si>
-    <t xml:space="preserve">31.6066856384277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.3991966247559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.1009407043457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.1891231536865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.7174701690674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.4618110656738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.9390239715576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.8964176177979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.2372894287109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.2969360351562</t>
+    <t xml:space="preserve">31.6066837310791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.3991928100586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.1009292602539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.1891212463379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.7174644470215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.4618072509766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.9390258789062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.8964214324951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.2372779846191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.296932220459</t>
   </si>
   <si>
     <t xml:space="preserve">32.0725288391113</t>
   </si>
   <si>
-    <t xml:space="preserve">31.9344329833984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.8752098083496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.7112236022949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.2969398498535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.0897903442383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.3055686950684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.6162796020508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.2106285095215</t>
+    <t xml:space="preserve">31.9344272613525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.8752021789551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.7112159729004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.2969284057617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.089786529541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.3055648803711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.6162757873535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.210620880127</t>
   </si>
   <si>
     <t xml:space="preserve">32.8579444885254</t>
   </si>
   <si>
-    <t xml:space="preserve">31.2094402313232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.6841354370117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.7445602416992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.5891990661621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.5287780761719</t>
+    <t xml:space="preserve">31.2094421386719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.6841373443604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.7445507049561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.5891952514648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.5287818908691</t>
   </si>
   <si>
     <t xml:space="preserve">30.5793781280518</t>
@@ -2717,49 +2717,49 @@
     <t xml:space="preserve">31.0972328186035</t>
   </si>
   <si>
-    <t xml:space="preserve">31.2871150970459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.4597263336182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.4079513549805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.9862232208252</t>
+    <t xml:space="preserve">31.2871112823486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.4597358703613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.4079437255859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.9862251281738</t>
   </si>
   <si>
     <t xml:space="preserve">32.5731239318848</t>
   </si>
   <si>
-    <t xml:space="preserve">32.7543754577637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.4350357055664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.9701461791992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.762996673584</t>
+    <t xml:space="preserve">32.7543678283691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.4350280761719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.9701499938965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.7630043029785</t>
   </si>
   <si>
     <t xml:space="preserve">32.426399230957</t>
   </si>
   <si>
-    <t xml:space="preserve">33.0823516845703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.5903778076172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.7025871276855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.4793701171875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.4621047973633</t>
+    <t xml:space="preserve">33.082347869873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.5903816223145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.7025909423828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.479377746582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.4621086120605</t>
   </si>
   <si>
     <t xml:space="preserve">33.4534721374512</t>
@@ -2768,301 +2768,301 @@
     <t xml:space="preserve">33.8505058288574</t>
   </si>
   <si>
-    <t xml:space="preserve">34.3856201171875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.6778793334961</t>
+    <t xml:space="preserve">34.3856239318848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.6778831481934</t>
   </si>
   <si>
     <t xml:space="preserve">34.0835380554199</t>
   </si>
   <si>
-    <t xml:space="preserve">34.1612129211426</t>
+    <t xml:space="preserve">34.1612205505371</t>
   </si>
   <si>
     <t xml:space="preserve">34.5237159729004</t>
   </si>
   <si>
-    <t xml:space="preserve">34.7999000549316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.7740058898926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.4632949829102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.2832336425781</t>
+    <t xml:space="preserve">34.7999038696289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.7740173339844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.4632987976074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.2832374572754</t>
   </si>
   <si>
     <t xml:space="preserve">34.2561569213867</t>
   </si>
   <si>
-    <t xml:space="preserve">33.3412742614746</t>
+    <t xml:space="preserve">33.3412818908691</t>
   </si>
   <si>
     <t xml:space="preserve">33.9540710449219</t>
   </si>
   <si>
-    <t xml:space="preserve">34.5496063232422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.5409736633301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.9552612304688</t>
+    <t xml:space="preserve">34.5496101379395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.5409812927246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.9552536010742</t>
   </si>
   <si>
     <t xml:space="preserve">34.6877021789551</t>
   </si>
   <si>
-    <t xml:space="preserve">35.0329360961914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.3177642822266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.6543617248535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.3867988586426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.8257904052734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.4731101989746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.8442459106445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36.3879890441895</t>
+    <t xml:space="preserve">35.0329399108887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.317756652832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.6543655395508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.3868103027344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.825798034668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.4731178283691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.8442497253418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.3879928588867</t>
   </si>
   <si>
     <t xml:space="preserve">35.0674629211426</t>
   </si>
   <si>
-    <t xml:space="preserve">33.2204437255859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.3499145507812</t>
+    <t xml:space="preserve">33.2204475402832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.349910736084</t>
   </si>
   <si>
     <t xml:space="preserve">34.3424644470215</t>
   </si>
   <si>
-    <t xml:space="preserve">34.3597297668457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.3844299316406</t>
+    <t xml:space="preserve">34.3597259521484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.3844375610352</t>
   </si>
   <si>
     <t xml:space="preserve">33.203182220459</t>
   </si>
   <si>
-    <t xml:space="preserve">33.8677635192871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.9713363647461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.306755065918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.7790775299072</t>
+    <t xml:space="preserve">33.8677711486816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.9713325500488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.3067588806152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.7790813446045</t>
   </si>
   <si>
     <t xml:space="preserve">29.64723777771</t>
   </si>
   <si>
-    <t xml:space="preserve">29.1984348297119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.3910064697266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.9567699432373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.5597476959229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.4918804168701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.0356311798096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.406759262085</t>
+    <t xml:space="preserve">29.1984405517578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.3910045623779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.9567642211914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.5597362518311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.4918842315674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.0356292724609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.4067573547363</t>
   </si>
   <si>
     <t xml:space="preserve">30.4153938293457</t>
   </si>
   <si>
-    <t xml:space="preserve">30.1478328704834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.1835479736328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.3734149932861</t>
+    <t xml:space="preserve">30.1478290557861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.1835441589355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.373420715332</t>
   </si>
   <si>
     <t xml:space="preserve">33.7728233337402</t>
   </si>
   <si>
-    <t xml:space="preserve">33.2635955810547</t>
+    <t xml:space="preserve">33.263599395752</t>
   </si>
   <si>
     <t xml:space="preserve">32.5386009216309</t>
   </si>
   <si>
-    <t xml:space="preserve">32.9615135192871</t>
+    <t xml:space="preserve">32.9615173339844</t>
   </si>
   <si>
     <t xml:space="preserve">31.9948501586914</t>
   </si>
   <si>
-    <t xml:space="preserve">32.4954452514648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.2537803649902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.7100372314453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.6076507568359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.2290725708008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.039192199707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.5817527770996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.4966354370117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.9356269836426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.3240203857422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.0564498901367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.7296714782715</t>
+    <t xml:space="preserve">32.4954490661621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.253776550293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.710033416748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.6076545715332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.229076385498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.0391960144043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.5817604064941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.4966316223145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.9356231689453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.3240127563477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.0564651489258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.7296676635742</t>
   </si>
   <si>
     <t xml:space="preserve">35.2573356628418</t>
   </si>
   <si>
-    <t xml:space="preserve">34.2388954162598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.0749092102051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.9466247558594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.4201431274414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.3091239929199</t>
+    <t xml:space="preserve">34.2388916015625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.0749053955078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.9466323852539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.4201469421387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.3091278076172</t>
   </si>
   <si>
     <t xml:space="preserve">35.7320404052734</t>
   </si>
   <si>
-    <t xml:space="preserve">37.9760856628418</t>
+    <t xml:space="preserve">37.9760894775391</t>
   </si>
   <si>
     <t xml:space="preserve">37.2165679931641</t>
   </si>
   <si>
-    <t xml:space="preserve">37.7085304260254</t>
+    <t xml:space="preserve">37.7085227966309</t>
   </si>
   <si>
     <t xml:space="preserve">36.5088233947754</t>
   </si>
   <si>
-    <t xml:space="preserve">38.7183418273926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.8231315612793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.6882858276367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36.2908134460449</t>
+    <t xml:space="preserve">38.7183456420898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.823127746582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.6882820129395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.2908058166504</t>
   </si>
   <si>
     <t xml:space="preserve">35.9589881896973</t>
   </si>
   <si>
-    <t xml:space="preserve">36.8147315979004</t>
+    <t xml:space="preserve">36.8147392272949</t>
   </si>
   <si>
     <t xml:space="preserve">36.7623405456543</t>
   </si>
   <si>
-    <t xml:space="preserve">36.9719200134277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36.0899620056152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36.48291015625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.7319564819336</t>
+    <t xml:space="preserve">36.9719161987305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.0899696350098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.4829139709473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.7319488525391</t>
   </si>
   <si>
     <t xml:space="preserve">35.4961853027344</t>
   </si>
   <si>
-    <t xml:space="preserve">35.9065856933594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.8279991149902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36.3955879211426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36.1074256896973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.9939155578613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36.2209434509277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36.5789680480957</t>
+    <t xml:space="preserve">35.9065971374512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.8280067443848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.3955993652344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.1074333190918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.9939117431641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.220947265625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.5789642333984</t>
   </si>
   <si>
     <t xml:space="preserve">35.4001274108887</t>
   </si>
   <si>
-    <t xml:space="preserve">35.4175987243652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36.2820777893066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.1814956665039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.5129661560059</t>
+    <t xml:space="preserve">35.417594909668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.2820739746094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.1814880371094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.5129699707031</t>
   </si>
   <si>
     <t xml:space="preserve">38.6222915649414</t>
@@ -3074,121 +3074,121 @@
     <t xml:space="preserve">39.6526832580566</t>
   </si>
   <si>
-    <t xml:space="preserve">40.2901306152344</t>
+    <t xml:space="preserve">40.2901268005371</t>
   </si>
   <si>
     <t xml:space="preserve">39.2946662902832</t>
   </si>
   <si>
-    <t xml:space="preserve">39.460578918457</t>
+    <t xml:space="preserve">39.4605751037598</t>
   </si>
   <si>
     <t xml:space="preserve">39.2160758972168</t>
   </si>
   <si>
-    <t xml:space="preserve">38.814395904541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.6614112854004</t>
+    <t xml:space="preserve">38.8143997192383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.6614151000977</t>
   </si>
   <si>
     <t xml:space="preserve">39.9321098327637</t>
   </si>
   <si>
-    <t xml:space="preserve">40.0281677246094</t>
+    <t xml:space="preserve">40.0281715393066</t>
   </si>
   <si>
     <t xml:space="preserve">40.7267417907715</t>
   </si>
   <si>
-    <t xml:space="preserve">40.1591529846191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40.1678771972656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40.2988662719727</t>
+    <t xml:space="preserve">40.1591491699219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40.1678924560547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40.2988624572754</t>
   </si>
   <si>
     <t xml:space="preserve">39.8185958862305</t>
   </si>
   <si>
-    <t xml:space="preserve">40.7616653442383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.0585594177246</t>
+    <t xml:space="preserve">40.761661529541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.0585632324219</t>
   </si>
   <si>
     <t xml:space="preserve">41.390380859375</t>
   </si>
   <si>
-    <t xml:space="preserve">41.5737609863281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.1937294006348</t>
+    <t xml:space="preserve">41.5737571716309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.1937370300293</t>
   </si>
   <si>
     <t xml:space="preserve">42.5779571533203</t>
   </si>
   <si>
-    <t xml:space="preserve">42.2024726867676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.6174201965332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.0365676879883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.0061683654785</t>
+    <t xml:space="preserve">42.2024765014648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.6174163818359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.0365562438965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.0061645507812</t>
   </si>
   <si>
     <t xml:space="preserve">41.3205223083496</t>
   </si>
   <si>
-    <t xml:space="preserve">41.3292579650879</t>
+    <t xml:space="preserve">41.3292617797852</t>
   </si>
   <si>
     <t xml:space="preserve">41.137149810791</t>
   </si>
   <si>
-    <t xml:space="preserve">39.8884582519531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.5042457580566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40.0019721984863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.0501670837402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.9977798461914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.9628372192383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.1374816894531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.8929901123047</t>
+    <t xml:space="preserve">39.8884544372559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.5042381286621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40.0019645690918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.0501708984375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.9977722167969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.9628448486328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.1374855041504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.8929862976074</t>
   </si>
   <si>
     <t xml:space="preserve">40.342529296875</t>
   </si>
   <si>
-    <t xml:space="preserve">39.3557891845703</t>
+    <t xml:space="preserve">39.3557929992676</t>
   </si>
   <si>
     <t xml:space="preserve">40.0718269348145</t>
   </si>
   <si>
-    <t xml:space="preserve">39.8360595703125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.5566253662109</t>
+    <t xml:space="preserve">39.8360557556152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.5566329956055</t>
   </si>
   <si>
     <t xml:space="preserve">40.2551956176758</t>
@@ -3197,13 +3197,13 @@
     <t xml:space="preserve">40.6044883728027</t>
   </si>
   <si>
-    <t xml:space="preserve">39.6439552307129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.8797187805176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.5915603637695</t>
+    <t xml:space="preserve">39.6439590454102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.8797149658203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.5915641784668</t>
   </si>
   <si>
     <t xml:space="preserve">39.9845008850098</t>
@@ -3215,7 +3215,7 @@
     <t xml:space="preserve">38.7532691955566</t>
   </si>
   <si>
-    <t xml:space="preserve">39.4693069458008</t>
+    <t xml:space="preserve">39.469310760498</t>
   </si>
   <si>
     <t xml:space="preserve">38.3690605163574</t>
@@ -3224,16 +3224,16 @@
     <t xml:space="preserve">39.4518432617188</t>
   </si>
   <si>
-    <t xml:space="preserve">39.1636810302734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.416919708252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.4955139160156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.0588989257812</t>
+    <t xml:space="preserve">39.163688659668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.4169158935547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.4954986572266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.058895111084</t>
   </si>
   <si>
     <t xml:space="preserve">38.7358093261719</t>
@@ -3251,61 +3251,61 @@
     <t xml:space="preserve">39.2859344482422</t>
   </si>
   <si>
-    <t xml:space="preserve">38.9715766906738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.1944236755371</t>
+    <t xml:space="preserve">38.9715728759766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.1944198608398</t>
   </si>
   <si>
     <t xml:space="preserve">38.3253974914551</t>
   </si>
   <si>
-    <t xml:space="preserve">38.5087738037109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.8535194396973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40.0106964111328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40.7878684997559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40.4822387695312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40.5346298217773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40.2639350891113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.2594032287598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40.7005424499512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.3030471801758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40.9799690246582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.6960029602051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.6785469055176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.669807434082</t>
+    <t xml:space="preserve">38.5087776184082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.8535270690918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40.0107040405273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40.7878608703613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40.482234954834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40.5346336364746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40.2639389038086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.2593994140625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40.7005386352539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.303050994873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40.9799728393555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.6959991455078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.6785430908203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.6698112487793</t>
   </si>
   <si>
     <t xml:space="preserve">40.9537773132324</t>
   </si>
   <si>
-    <t xml:space="preserve">40.4560394287109</t>
+    <t xml:space="preserve">40.4560470581055</t>
   </si>
   <si>
     <t xml:space="preserve">38.8493309020996</t>
@@ -3314,25 +3314,25 @@
     <t xml:space="preserve">37.3561248779297</t>
   </si>
   <si>
-    <t xml:space="preserve">39.3383255004883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40.368724822998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40.4385795593262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40.0980186462402</t>
+    <t xml:space="preserve">39.3383293151855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40.3687171936035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40.4385833740234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40.0980224609375</t>
   </si>
   <si>
     <t xml:space="preserve">38.8405914306641</t>
   </si>
   <si>
-    <t xml:space="preserve">39.8273315429688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40.0892868041992</t>
+    <t xml:space="preserve">39.8273239135742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40.089282989502</t>
   </si>
   <si>
     <t xml:space="preserve">41.2943305969238</t>
@@ -3341,31 +3341,31 @@
     <t xml:space="preserve">40.7965965270996</t>
   </si>
   <si>
-    <t xml:space="preserve">40.3250617980957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40.3949165344238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.7151947021484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.6911964416504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.2120246887207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.6004333496094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.9976768493652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.397403717041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.6558876037598</t>
+    <t xml:space="preserve">40.3250579833984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40.3949127197266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.7151908874512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.6912002563477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.2120208740234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.6004409790039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.9976806640625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.3973999023438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.6558799743652</t>
   </si>
   <si>
     <t xml:space="preserve">37.993824005127</t>
@@ -3374,19 +3374,19 @@
     <t xml:space="preserve">37.9055480957031</t>
   </si>
   <si>
-    <t xml:space="preserve">38.1262321472168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.541130065918</t>
+    <t xml:space="preserve">38.1262283325195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.5411338806152</t>
   </si>
   <si>
     <t xml:space="preserve">38.947193145752</t>
   </si>
   <si>
-    <t xml:space="preserve">38.8147888183594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.8589172363281</t>
+    <t xml:space="preserve">38.8147850036621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.8589210510254</t>
   </si>
   <si>
     <t xml:space="preserve">39.5209846496582</t>
@@ -3395,7 +3395,7 @@
     <t xml:space="preserve">38.3469161987305</t>
   </si>
   <si>
-    <t xml:space="preserve">39.1855430603027</t>
+    <t xml:space="preserve">39.1855354309082</t>
   </si>
   <si>
     <t xml:space="preserve">38.8500938415527</t>
@@ -3407,7 +3407,7 @@
     <t xml:space="preserve">39.0972671508789</t>
   </si>
   <si>
-    <t xml:space="preserve">39.4768524169922</t>
+    <t xml:space="preserve">39.4768486022949</t>
   </si>
   <si>
     <t xml:space="preserve">39.7240257263184</t>
@@ -3416,31 +3416,31 @@
     <t xml:space="preserve">40.0153350830078</t>
   </si>
   <si>
-    <t xml:space="preserve">39.8652648925781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.4528541564941</t>
+    <t xml:space="preserve">39.8652572631836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.4528579711914</t>
   </si>
   <si>
     <t xml:space="preserve">37.0051307678223</t>
   </si>
   <si>
-    <t xml:space="preserve">37.7731323242188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.8172645568848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.8349227905273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.5058174133301</t>
+    <t xml:space="preserve">37.7731285095215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.817268371582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.8349266052246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.5058212280273</t>
   </si>
   <si>
     <t xml:space="preserve">38.6823692321777</t>
   </si>
   <si>
-    <t xml:space="preserve">38.5499572753906</t>
+    <t xml:space="preserve">38.5499496459961</t>
   </si>
   <si>
     <t xml:space="preserve">38.5852661132812</t>
@@ -3449,22 +3449,22 @@
     <t xml:space="preserve">38.4175453186035</t>
   </si>
   <si>
-    <t xml:space="preserve">37.5612678527832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.6495475769043</t>
+    <t xml:space="preserve">37.5612754821777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.649543762207</t>
   </si>
   <si>
     <t xml:space="preserve">37.8967170715332</t>
   </si>
   <si>
-    <t xml:space="preserve">37.4465065002441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.5259552001953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.5171279907227</t>
+    <t xml:space="preserve">37.4465103149414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.5259590148926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.5171318054199</t>
   </si>
   <si>
     <t xml:space="preserve">37.1905136108398</t>
@@ -3476,19 +3476,19 @@
     <t xml:space="preserve">38.3822326660156</t>
   </si>
   <si>
-    <t xml:space="preserve">38.9030609130859</t>
+    <t xml:space="preserve">38.9030570983887</t>
   </si>
   <si>
     <t xml:space="preserve">38.7883033752441</t>
   </si>
   <si>
-    <t xml:space="preserve">38.3557510375977</t>
+    <t xml:space="preserve">38.3557472229004</t>
   </si>
   <si>
     <t xml:space="preserve">39.618091583252</t>
   </si>
   <si>
-    <t xml:space="preserve">40.0771217346191</t>
+    <t xml:space="preserve">40.0771255493164</t>
   </si>
   <si>
     <t xml:space="preserve">40.2360229492188</t>
@@ -3500,34 +3500,34 @@
     <t xml:space="preserve">39.9800224304199</t>
   </si>
   <si>
-    <t xml:space="preserve">39.5827789306641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.0619506835938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.8412628173828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.6117515563965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.6647071838379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.3582305908203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.4729919433594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.8437423706055</t>
+    <t xml:space="preserve">39.5827827453613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.0619583129883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.8412666320801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.6117553710938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.6647148132324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.3582344055176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.4729995727539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.84375</t>
   </si>
   <si>
     <t xml:space="preserve">37.7819595336914</t>
   </si>
   <si>
-    <t xml:space="preserve">37.1993370056152</t>
+    <t xml:space="preserve">37.1993408203125</t>
   </si>
   <si>
     <t xml:space="preserve">37.4641647338867</t>
@@ -3539,10 +3539,10 @@
     <t xml:space="preserve">37.9673347473145</t>
   </si>
   <si>
-    <t xml:space="preserve">38.5764427185059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.2674674987793</t>
+    <t xml:space="preserve">38.5764350891113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.2674713134766</t>
   </si>
   <si>
     <t xml:space="preserve">39.5298156738281</t>
@@ -3554,70 +3554,70 @@
     <t xml:space="preserve">39.1325798034668</t>
   </si>
   <si>
-    <t xml:space="preserve">39.8387870788574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.3091239929199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.9182357788086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.6710510253906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.6622314453125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.4945068359375</t>
+    <t xml:space="preserve">39.8387794494629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.3091278076172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.9182281494141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.6710586547852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.6622276306152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.494514465332</t>
   </si>
   <si>
     <t xml:space="preserve">39.9094009399414</t>
   </si>
   <si>
-    <t xml:space="preserve">40.1477470397949</t>
+    <t xml:space="preserve">40.1477394104004</t>
   </si>
   <si>
     <t xml:space="preserve">39.8917465209961</t>
   </si>
   <si>
-    <t xml:space="preserve">39.8740882873535</t>
+    <t xml:space="preserve">39.8740921020508</t>
   </si>
   <si>
     <t xml:space="preserve">40.2889862060547</t>
   </si>
   <si>
-    <t xml:space="preserve">40.4920196533203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.383602142334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40.7480278015137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40.5361557006836</t>
+    <t xml:space="preserve">40.492015838623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.3836059570312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40.7480163574219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40.5361518859863</t>
   </si>
   <si>
     <t xml:space="preserve">40.1300888061523</t>
   </si>
   <si>
-    <t xml:space="preserve">40.0506362915039</t>
+    <t xml:space="preserve">40.0506401062012</t>
   </si>
   <si>
     <t xml:space="preserve">40.2183647155762</t>
   </si>
   <si>
-    <t xml:space="preserve">40.2007102966309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40.3596153259277</t>
+    <t xml:space="preserve">40.2007141113281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40.3596076965332</t>
   </si>
   <si>
     <t xml:space="preserve">40.5096740722656</t>
   </si>
   <si>
-    <t xml:space="preserve">40.5626373291016</t>
+    <t xml:space="preserve">40.5626449584961</t>
   </si>
   <si>
     <t xml:space="preserve">41.6042938232422</t>
@@ -3632,13 +3632,13 @@
     <t xml:space="preserve">41.0128402709961</t>
   </si>
   <si>
-    <t xml:space="preserve">40.7568511962891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40.6509132385254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40.3684310913086</t>
+    <t xml:space="preserve">40.7568473815918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40.6509170532227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40.3684349060059</t>
   </si>
   <si>
     <t xml:space="preserve">40.4655418395996</t>
@@ -3647,34 +3647,34 @@
     <t xml:space="preserve">40.4302291870117</t>
   </si>
   <si>
-    <t xml:space="preserve">40.4831924438477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.7416801452637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.5474739074707</t>
+    <t xml:space="preserve">40.4831962585449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.7416763305664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.5474700927734</t>
   </si>
   <si>
     <t xml:space="preserve">38.6470565795898</t>
   </si>
   <si>
-    <t xml:space="preserve">38.5676116943359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.8942337036133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.017822265625</t>
+    <t xml:space="preserve">38.5676078796387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.8942375183105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.0178184509277</t>
   </si>
   <si>
     <t xml:space="preserve">39.6975402832031</t>
   </si>
   <si>
-    <t xml:space="preserve">40.0065078735352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40.3331260681152</t>
+    <t xml:space="preserve">40.0065040588379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40.3331184387207</t>
   </si>
   <si>
     <t xml:space="preserve">41.0393295288086</t>
@@ -3683,13 +3683,13 @@
     <t xml:space="preserve">41.128662109375</t>
   </si>
   <si>
-    <t xml:space="preserve">41.378791809082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40.4854698181152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40.9053268432617</t>
+    <t xml:space="preserve">41.3787956237793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40.4854621887207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40.905330657959</t>
   </si>
   <si>
     <t xml:space="preserve">40.6373329162598</t>
@@ -3698,154 +3698,154 @@
     <t xml:space="preserve">40.6015968322754</t>
   </si>
   <si>
-    <t xml:space="preserve">40.4050712585449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40.8606643676758</t>
+    <t xml:space="preserve">40.4050674438477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40.860668182373</t>
   </si>
   <si>
     <t xml:space="preserve">41.2001304626465</t>
   </si>
   <si>
-    <t xml:space="preserve">41.9505233764648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.289981842041</t>
+    <t xml:space="preserve">41.9505157470703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.2899856567383</t>
   </si>
   <si>
     <t xml:space="preserve">42.7009124755859</t>
   </si>
   <si>
-    <t xml:space="preserve">42.3167877197266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.5311813354492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.6205101013184</t>
+    <t xml:space="preserve">42.316780090332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.531177520752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.6205062866211</t>
   </si>
   <si>
     <t xml:space="preserve">42.8527793884277</t>
   </si>
   <si>
-    <t xml:space="preserve">43.2458343505859</t>
+    <t xml:space="preserve">43.2458419799805</t>
   </si>
   <si>
     <t xml:space="preserve">43.3262405395508</t>
   </si>
   <si>
-    <t xml:space="preserve">43.031436920166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.9510459899902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.4865226745605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43.1029052734375</t>
+    <t xml:space="preserve">43.0314445495605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.9510383605957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.4865188598633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43.1029090881348</t>
   </si>
   <si>
     <t xml:space="preserve">43.120777130127</t>
   </si>
   <si>
-    <t xml:space="preserve">43.2637100219727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43.254768371582</t>
+    <t xml:space="preserve">43.2637023925781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43.2547721862793</t>
   </si>
   <si>
     <t xml:space="preserve">43.0582427978516</t>
   </si>
   <si>
-    <t xml:space="preserve">43.540641784668</t>
+    <t xml:space="preserve">43.5406379699707</t>
   </si>
   <si>
     <t xml:space="preserve">43.4781036376953</t>
   </si>
   <si>
-    <t xml:space="preserve">43.4602432250977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">44.7555656433105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.2206192016602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">44.8448905944824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.9888687133789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.2563400268555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.8811492919922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.1307525634766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.1486206054688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">44.630485534668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">44.4786262512207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.2200889587402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.3272933959961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.7739524841309</t>
+    <t xml:space="preserve">43.4602394104004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44.7555503845215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.2206153869629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44.8448944091797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.9888725280762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.2563438415527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.8811454772949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.1307563781738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.148624420166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44.6304931640625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44.4786338806152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.220085144043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.3272895812988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.7739448547363</t>
   </si>
   <si>
     <t xml:space="preserve">45.2915534973145</t>
   </si>
   <si>
-    <t xml:space="preserve">45.5595512390137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.4528770446777</t>
+    <t xml:space="preserve">45.5595474243164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.4528694152832</t>
   </si>
   <si>
     <t xml:space="preserve">45.9883460998535</t>
   </si>
   <si>
-    <t xml:space="preserve">46.6136703491211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">47.0424728393555</t>
+    <t xml:space="preserve">46.6136779785156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">47.0424690246582</t>
   </si>
   <si>
     <t xml:space="preserve">47.6141929626465</t>
   </si>
   <si>
-    <t xml:space="preserve">48.1501922607422</t>
+    <t xml:space="preserve">48.1501884460449</t>
   </si>
   <si>
     <t xml:space="preserve">48.0608596801758</t>
   </si>
   <si>
-    <t xml:space="preserve">49.0792503356934</t>
+    <t xml:space="preserve">49.0792427062988</t>
   </si>
   <si>
     <t xml:space="preserve">49.0435180664062</t>
   </si>
   <si>
-    <t xml:space="preserve">50.1869773864746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50.4192352294922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50.7765693664551</t>
+    <t xml:space="preserve">50.1869697570801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50.4192390441895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50.7765655517578</t>
   </si>
   <si>
     <t xml:space="preserve">51.0624313354492</t>
@@ -3854,22 +3854,22 @@
     <t xml:space="preserve">50.5085716247559</t>
   </si>
   <si>
-    <t xml:space="preserve">50.7944374084473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50.9730949401855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">51.3125610351562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50.6693687438965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">49.9904403686523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">49.579517364502</t>
+    <t xml:space="preserve">50.79443359375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50.9730987548828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">51.3125648498535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50.6693725585938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">49.9904365539551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">49.5795135498047</t>
   </si>
   <si>
     <t xml:space="preserve">50.151237487793</t>
@@ -3878,28 +3878,28 @@
     <t xml:space="preserve">49.9011077880859</t>
   </si>
   <si>
-    <t xml:space="preserve">49.6331214904785</t>
+    <t xml:space="preserve">49.6331100463867</t>
   </si>
   <si>
     <t xml:space="preserve">49.7581787109375</t>
   </si>
   <si>
-    <t xml:space="preserve">49.5437812805176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">49.9547119140625</t>
+    <t xml:space="preserve">49.5437774658203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">49.9547004699707</t>
   </si>
   <si>
     <t xml:space="preserve">48.8291206359863</t>
   </si>
   <si>
-    <t xml:space="preserve">48.1144638061523</t>
+    <t xml:space="preserve">48.1144599914551</t>
   </si>
   <si>
     <t xml:space="preserve">47.2568740844727</t>
   </si>
   <si>
-    <t xml:space="preserve">46.9531402587891</t>
+    <t xml:space="preserve">46.9531364440918</t>
   </si>
   <si>
     <t xml:space="preserve">46.8816680908203</t>
@@ -3911,148 +3911,148 @@
     <t xml:space="preserve">46.3278121948242</t>
   </si>
   <si>
-    <t xml:space="preserve">45.202220916748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">44.6840896606445</t>
+    <t xml:space="preserve">45.2022247314453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44.6840972900391</t>
   </si>
   <si>
     <t xml:space="preserve">45.613151550293</t>
   </si>
   <si>
-    <t xml:space="preserve">45.1843605041504</t>
+    <t xml:space="preserve">45.1843566894531</t>
   </si>
   <si>
     <t xml:space="preserve">45.7203483581543</t>
   </si>
   <si>
-    <t xml:space="preserve">45.4344825744629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43.7014350891113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43.7639694213867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">44.9163551330566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">44.1034278869629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43.6925010681152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43.9426345825195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43.7460975646973</t>
+    <t xml:space="preserve">45.4344902038574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43.7014389038086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43.763973236084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44.9163589477539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44.1034317016602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43.6925048828125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43.9426307678223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43.7461051940918</t>
   </si>
   <si>
     <t xml:space="preserve">43.6746368408203</t>
   </si>
   <si>
-    <t xml:space="preserve">44.1391639709473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">44.2731666564941</t>
+    <t xml:space="preserve">44.1391677856445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44.2731704711914</t>
   </si>
   <si>
     <t xml:space="preserve">45.4166221618652</t>
   </si>
   <si>
-    <t xml:space="preserve">45.6846160888672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.6310234069824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.9168815612793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.1848831176758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.4886169433594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">47.0960731506348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.8280639648438</t>
+    <t xml:space="preserve">45.6846199035645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.6310157775879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.9168853759766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.1848793029785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.4886131286621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">47.0960693359375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.8280754089355</t>
   </si>
   <si>
     <t xml:space="preserve">47.221134185791</t>
   </si>
   <si>
-    <t xml:space="preserve">48.3467216491699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">49.2043190002441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50.3120307922363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50.4728393554688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50.3299026489258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50.0261688232422</t>
+    <t xml:space="preserve">48.3467178344727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">49.2043228149414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50.3120384216309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50.4728355407715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50.3299102783203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50.0261726379395</t>
   </si>
   <si>
     <t xml:space="preserve">50.2227096557617</t>
   </si>
   <si>
-    <t xml:space="preserve">50.4371032714844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">51.0802955627441</t>
+    <t xml:space="preserve">50.4371070861816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">51.0802993774414</t>
   </si>
   <si>
     <t xml:space="preserve">50.6515007019043</t>
   </si>
   <si>
-    <t xml:space="preserve">50.1155052185059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">49.1685752868652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50.4907035827637</t>
+    <t xml:space="preserve">50.1155090332031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">49.1685829162598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50.4907073974609</t>
   </si>
   <si>
     <t xml:space="preserve">50.7522163391113</t>
   </si>
   <si>
-    <t xml:space="preserve">49.9586524963379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50.1209754943848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50.4997177124023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">49.3815116882324</t>
+    <t xml:space="preserve">49.9586563110352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50.1209716796875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50.4997215270996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">49.3815155029297</t>
   </si>
   <si>
     <t xml:space="preserve">49.5618705749512</t>
   </si>
   <si>
-    <t xml:space="preserve">49.9947166442871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">49.6159820556641</t>
+    <t xml:space="preserve">49.9947204589844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">49.6159744262695</t>
   </si>
   <si>
     <t xml:space="preserve">48.4436645507812</t>
   </si>
   <si>
-    <t xml:space="preserve">48.191162109375</t>
+    <t xml:space="preserve">48.1911582946777</t>
   </si>
   <si>
     <t xml:space="preserve">48.5338363647461</t>
@@ -4067,40 +4067,40 @@
     <t xml:space="preserve">48.6240158081055</t>
   </si>
   <si>
-    <t xml:space="preserve">48.299373626709</t>
+    <t xml:space="preserve">48.2993774414062</t>
   </si>
   <si>
     <t xml:space="preserve">49.0027656555176</t>
   </si>
   <si>
-    <t xml:space="preserve">48.2091941833496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">49.4716873168945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">49.7602653503418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50.0668640136719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50.1029472351074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50.9686508178711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50.2832908630371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50.445613861084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50.8243637084961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50.986686706543</t>
+    <t xml:space="preserve">48.2091979980469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">49.4716911315918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">49.7602615356445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50.0668716430664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50.1029434204102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50.9686470031738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50.2832984924316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50.4456100463867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50.8243675231934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50.9866828918457</t>
   </si>
   <si>
     <t xml:space="preserve">50.9506149291992</t>
@@ -4115,13 +4115,13 @@
     <t xml:space="preserve">49.2913360595703</t>
   </si>
   <si>
-    <t xml:space="preserve">49.0207977294922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">48.7683067321777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">49.1290168762207</t>
+    <t xml:space="preserve">49.0208015441895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">48.768310546875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">49.1290130615234</t>
   </si>
   <si>
     <t xml:space="preserve">49.5257987976074</t>
@@ -4130,46 +4130,46 @@
     <t xml:space="preserve">48.3174133300781</t>
   </si>
   <si>
-    <t xml:space="preserve">47.0909957885742</t>
+    <t xml:space="preserve">47.090991973877</t>
   </si>
   <si>
     <t xml:space="preserve">46.1711769104004</t>
   </si>
   <si>
-    <t xml:space="preserve">46.8926010131836</t>
+    <t xml:space="preserve">46.8925933837891</t>
   </si>
   <si>
     <t xml:space="preserve">46.4417114257812</t>
   </si>
   <si>
-    <t xml:space="preserve">45.5579605102539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.0439491271973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">44.6201133728027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">44.6471633911133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">44.6742172241211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">44.8726119995117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.0529594421387</t>
+    <t xml:space="preserve">45.5579643249512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.0439414978027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44.6201095581055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44.647159576416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44.6742210388184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44.8726081848145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.0529632568359</t>
   </si>
   <si>
     <t xml:space="preserve">43.7724380493164</t>
   </si>
   <si>
-    <t xml:space="preserve">42.6993141174316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.3025398254395</t>
+    <t xml:space="preserve">42.6993179321289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.3025321960449</t>
   </si>
   <si>
     <t xml:space="preserve">41.5630798339844</t>
@@ -4178,10 +4178,10 @@
     <t xml:space="preserve">41.9778938293457</t>
   </si>
   <si>
-    <t xml:space="preserve">41.3015632629395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40.940845489502</t>
+    <t xml:space="preserve">41.3015556335449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40.9408493041992</t>
   </si>
   <si>
     <t xml:space="preserve">40.3817405700684</t>
@@ -4193,76 +4193,76 @@
     <t xml:space="preserve">41.0400428771973</t>
   </si>
   <si>
-    <t xml:space="preserve">41.3105773925781</t>
+    <t xml:space="preserve">41.3105735778809</t>
   </si>
   <si>
     <t xml:space="preserve">41.6622734069824</t>
   </si>
   <si>
-    <t xml:space="preserve">41.581111907959</t>
+    <t xml:space="preserve">41.5811157226562</t>
   </si>
   <si>
     <t xml:space="preserve">41.7434310913086</t>
   </si>
   <si>
-    <t xml:space="preserve">41.5720863342285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.0921897888184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40.2645111083984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.4619216918945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.2715759277344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.9298706054688</t>
+    <t xml:space="preserve">41.572093963623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.0921974182129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40.2645149230957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.4619255065918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.2715721130371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.9298782348633</t>
   </si>
   <si>
     <t xml:space="preserve">38.6232681274414</t>
   </si>
   <si>
-    <t xml:space="preserve">37.9198799133301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.7395210266113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36.386848449707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.8947868347168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.7946128845215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.2545166015625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40.399772644043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.8496856689453</t>
+    <t xml:space="preserve">37.9198837280273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.7395172119141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.3868560791016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.8947792053223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.794605255127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.2545127868652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40.3997802734375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.8496932983398</t>
   </si>
   <si>
     <t xml:space="preserve">40.9678993225098</t>
   </si>
   <si>
-    <t xml:space="preserve">41.1753120422363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.1662940979004</t>
+    <t xml:space="preserve">41.1753082275391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.1662902832031</t>
   </si>
   <si>
     <t xml:space="preserve">41.229419708252</t>
   </si>
   <si>
-    <t xml:space="preserve">41.6262016296387</t>
+    <t xml:space="preserve">41.6261978149414</t>
   </si>
   <si>
     <t xml:space="preserve">41.3646850585938</t>
@@ -4271,13 +4271,13 @@
     <t xml:space="preserve">40.9588775634766</t>
   </si>
   <si>
-    <t xml:space="preserve">40.5891532897949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.3566398620605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.2754821777344</t>
+    <t xml:space="preserve">40.5891494750977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.3566474914551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.2754859924316</t>
   </si>
   <si>
     <t xml:space="preserve">41.1572723388672</t>
@@ -4286,88 +4286,88 @@
     <t xml:space="preserve">42.5911064147949</t>
   </si>
   <si>
-    <t xml:space="preserve">44.079044342041</t>
+    <t xml:space="preserve">44.0790481567383</t>
   </si>
   <si>
     <t xml:space="preserve">43.0870819091797</t>
   </si>
   <si>
-    <t xml:space="preserve">44.2954711914062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">44.3766288757324</t>
+    <t xml:space="preserve">44.295467376709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44.3766326904297</t>
   </si>
   <si>
     <t xml:space="preserve">43.8445777893066</t>
   </si>
   <si>
-    <t xml:space="preserve">42.9969062805176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43.3846778869629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43.4568214416504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43.4117279052734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43.9167213439941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43.1772613525391</t>
+    <t xml:space="preserve">42.9969139099121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43.3846740722656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43.4568138122559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43.4117240905762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43.9167289733887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43.1772689819336</t>
   </si>
   <si>
     <t xml:space="preserve">41.7163772583008</t>
   </si>
   <si>
-    <t xml:space="preserve">41.1843299865723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40.5350494384766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40.3366508483887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.4729042053223</t>
+    <t xml:space="preserve">41.1843185424805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40.5350456237793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40.3366470336914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.472900390625</t>
   </si>
   <si>
     <t xml:space="preserve">40.1021919250488</t>
   </si>
   <si>
-    <t xml:space="preserve">39.1282691955566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.6322822570801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.9739952087402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.3697929382324</t>
+    <t xml:space="preserve">39.1282730102539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.6322898864746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.9739837646484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.3697967529297</t>
   </si>
   <si>
     <t xml:space="preserve">38.2445220947266</t>
   </si>
   <si>
-    <t xml:space="preserve">37.8838081359863</t>
+    <t xml:space="preserve">37.8838043212891</t>
   </si>
   <si>
     <t xml:space="preserve">35.9810562133789</t>
   </si>
   <si>
-    <t xml:space="preserve">37.279613494873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.721492767334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.7575531005859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.2976493835449</t>
+    <t xml:space="preserve">37.2796173095703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.7214889526367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.7575569152832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.2976531982422</t>
   </si>
   <si>
     <t xml:space="preserve">37.4329147338867</t>
@@ -4379,16 +4379,16 @@
     <t xml:space="preserve">38.690559387207</t>
   </si>
   <si>
-    <t xml:space="preserve">37.9319114685059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.8222389221191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.2152709960938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.4711875915527</t>
+    <t xml:space="preserve">37.9319152832031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.8222351074219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.2152671813965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.4711952209473</t>
   </si>
   <si>
     <t xml:space="preserve">39.1110038757324</t>
@@ -4400,16 +4400,16 @@
     <t xml:space="preserve">37.2555389404297</t>
   </si>
   <si>
-    <t xml:space="preserve">37.2189865112305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36.140438079834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36.4146423339844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.8662261962891</t>
+    <t xml:space="preserve">37.2189788818359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.1404342651367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.4146385192871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.8662338256836</t>
   </si>
   <si>
     <t xml:space="preserve">36.067310333252</t>
@@ -4418,109 +4418,109 @@
     <t xml:space="preserve">35.4092178344727</t>
   </si>
   <si>
-    <t xml:space="preserve">33.8462409973145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.3398056030273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.348949432373</t>
+    <t xml:space="preserve">33.8462371826172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.3398132324219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.3489532470703</t>
   </si>
   <si>
     <t xml:space="preserve">34.5683174133301</t>
   </si>
   <si>
-    <t xml:space="preserve">34.4769172668457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.6651458740234</t>
+    <t xml:space="preserve">34.4769134521484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.6651420593262</t>
   </si>
   <si>
     <t xml:space="preserve">36.0490303039551</t>
   </si>
   <si>
-    <t xml:space="preserve">34.8242416381836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.2849655151367</t>
+    <t xml:space="preserve">34.8242454528809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.2849731445312</t>
   </si>
   <si>
     <t xml:space="preserve">35.5463218688965</t>
   </si>
   <si>
-    <t xml:space="preserve">38.2609710693359</t>
+    <t xml:space="preserve">38.2609672546387</t>
   </si>
   <si>
     <t xml:space="preserve">37.5754508972168</t>
   </si>
   <si>
-    <t xml:space="preserve">37.6394348144531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.9045028686523</t>
+    <t xml:space="preserve">37.6394271850586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.9044990539551</t>
   </si>
   <si>
     <t xml:space="preserve">37.9410552978516</t>
   </si>
   <si>
-    <t xml:space="preserve">39.3395118713379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.3212280273438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.2206878662109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.5223236083984</t>
+    <t xml:space="preserve">39.3395156860352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.3212356567383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.2206840515137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.5223159790039</t>
   </si>
   <si>
     <t xml:space="preserve">39.7691040039062</t>
   </si>
   <si>
-    <t xml:space="preserve">39.7782402038574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40.0433082580566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.4766159057617</t>
+    <t xml:space="preserve">39.7782440185547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40.0433120727539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.4766082763672</t>
   </si>
   <si>
     <t xml:space="preserve">39.3029518127441</t>
   </si>
   <si>
-    <t xml:space="preserve">38.5351715087891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.2846717834473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.440055847168</t>
+    <t xml:space="preserve">38.5351791381836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.2846755981445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.4400596618652</t>
   </si>
   <si>
     <t xml:space="preserve">39.6777038574219</t>
   </si>
   <si>
-    <t xml:space="preserve">39.8605003356934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.211555480957</t>
+    <t xml:space="preserve">39.8605041503906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.2115478515625</t>
   </si>
   <si>
     <t xml:space="preserve">39.165843963623</t>
   </si>
   <si>
-    <t xml:space="preserve">38.8185157775879</t>
+    <t xml:space="preserve">38.8185195922852</t>
   </si>
   <si>
     <t xml:space="preserve">38.5625915527344</t>
   </si>
   <si>
-    <t xml:space="preserve">38.1147193908691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.5131721496582</t>
+    <t xml:space="preserve">38.1147270202637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.5131759643555</t>
   </si>
   <si>
     <t xml:space="preserve">39.0104637145996</t>
@@ -4535,19 +4535,19 @@
     <t xml:space="preserve">38.7271156311035</t>
   </si>
   <si>
-    <t xml:space="preserve">38.6174354553223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.0872993469238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.0835838317871</t>
+    <t xml:space="preserve">38.617431640625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.0873031616211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.0835876464844</t>
   </si>
   <si>
     <t xml:space="preserve">39.1567077636719</t>
   </si>
   <si>
-    <t xml:space="preserve">38.6357154846191</t>
+    <t xml:space="preserve">38.6357192993164</t>
   </si>
   <si>
     <t xml:space="preserve">38.6631317138672</t>
@@ -4562,10 +4562,10 @@
     <t xml:space="preserve">39.5680198669434</t>
   </si>
   <si>
-    <t xml:space="preserve">40.2261123657227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.8787879943848</t>
+    <t xml:space="preserve">40.2261085510254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.878791809082</t>
   </si>
   <si>
     <t xml:space="preserve">40.4454803466797</t>
@@ -4577,7 +4577,7 @@
     <t xml:space="preserve">38.4986114501953</t>
   </si>
   <si>
-    <t xml:space="preserve">37.5480346679688</t>
+    <t xml:space="preserve">37.5480308532715</t>
   </si>
   <si>
     <t xml:space="preserve">37.0361785888672</t>
@@ -4586,43 +4586,43 @@
     <t xml:space="preserve">37.2372627258301</t>
   </si>
   <si>
-    <t xml:space="preserve">37.1915588378906</t>
+    <t xml:space="preserve">37.1915626525879</t>
   </si>
   <si>
     <t xml:space="preserve">37.8313751220703</t>
   </si>
   <si>
-    <t xml:space="preserve">36.7619705200195</t>
+    <t xml:space="preserve">36.7619743347168</t>
   </si>
   <si>
     <t xml:space="preserve">37.3743667602539</t>
   </si>
   <si>
-    <t xml:space="preserve">37.0087623596191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.4657707214355</t>
+    <t xml:space="preserve">37.0087585449219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.4657669067383</t>
   </si>
   <si>
     <t xml:space="preserve">37.1367225646973</t>
   </si>
   <si>
-    <t xml:space="preserve">37.5937347412109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.0453109741211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36.6522827148438</t>
+    <t xml:space="preserve">37.5937271118164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.0453147888184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.6522903442383</t>
   </si>
   <si>
     <t xml:space="preserve">36.7071304321289</t>
   </si>
   <si>
-    <t xml:space="preserve">36.3415145874023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36.1769905090332</t>
+    <t xml:space="preserve">36.3415222167969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.177001953125</t>
   </si>
   <si>
     <t xml:space="preserve">35.6468620300293</t>
@@ -4631,13 +4631,13 @@
     <t xml:space="preserve">35.6011619567871</t>
   </si>
   <si>
-    <t xml:space="preserve">33.9102210998535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.3161010742188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.0930213928223</t>
+    <t xml:space="preserve">33.9102249145508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.316104888916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.0930290222168</t>
   </si>
   <si>
     <t xml:space="preserve">33.5811729431152</t>
@@ -4649,49 +4649,49 @@
     <t xml:space="preserve">35.1532897949219</t>
   </si>
   <si>
-    <t xml:space="preserve">32.9962005615234</t>
+    <t xml:space="preserve">32.9961967468262</t>
   </si>
   <si>
     <t xml:space="preserve">32.2649841308594</t>
   </si>
   <si>
-    <t xml:space="preserve">32.3198165893555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.7494163513184</t>
+    <t xml:space="preserve">32.3198280334473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.7494201660156</t>
   </si>
   <si>
     <t xml:space="preserve">32.4752044677734</t>
   </si>
   <si>
-    <t xml:space="preserve">32.3929443359375</t>
+    <t xml:space="preserve">32.3929405212402</t>
   </si>
   <si>
     <t xml:space="preserve">33.4257888793945</t>
   </si>
   <si>
-    <t xml:space="preserve">33.6360130310059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.6542930603027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.8590927124023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.9596366882324</t>
+    <t xml:space="preserve">33.6360092163086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.654296875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.8590965270996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.9596405029297</t>
   </si>
   <si>
     <t xml:space="preserve">32.4020805358887</t>
   </si>
   <si>
-    <t xml:space="preserve">33.5171928405762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.6688613891602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.7328414916992</t>
+    <t xml:space="preserve">33.5171890258789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.6688575744629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.7328453063965</t>
   </si>
   <si>
     <t xml:space="preserve">34.4586334228516</t>
@@ -4700,46 +4700,46 @@
     <t xml:space="preserve">35.0710296630859</t>
   </si>
   <si>
-    <t xml:space="preserve">34.7602653503418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.8059577941895</t>
+    <t xml:space="preserve">34.7602577209473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.8059616088867</t>
   </si>
   <si>
     <t xml:space="preserve">35.1624336242676</t>
   </si>
   <si>
-    <t xml:space="preserve">34.6048774719238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.171573638916</t>
+    <t xml:space="preserve">34.6048812866211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.1715660095215</t>
   </si>
   <si>
     <t xml:space="preserve">34.6140174865723</t>
   </si>
   <si>
-    <t xml:space="preserve">35.1441497802734</t>
+    <t xml:space="preserve">35.144157409668</t>
   </si>
   <si>
     <t xml:space="preserve">37.0910186767578</t>
   </si>
   <si>
-    <t xml:space="preserve">37.9593315124512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.2463989257812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36.8168106079102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36.4055023193359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.9393501281738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.8296661376953</t>
+    <t xml:space="preserve">37.9593353271484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.2464027404785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.8168067932129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.4054985046387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.9393463134766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.8296699523926</t>
   </si>
   <si>
     <t xml:space="preserve">36.0947341918945</t>
@@ -4748,7 +4748,7 @@
     <t xml:space="preserve">36.2152366638184</t>
   </si>
   <si>
-    <t xml:space="preserve">35.7981185913086</t>
+    <t xml:space="preserve">35.7981147766113</t>
   </si>
   <si>
     <t xml:space="preserve">36.2893867492676</t>
@@ -4757,28 +4757,28 @@
     <t xml:space="preserve">37.2626686096191</t>
   </si>
   <si>
-    <t xml:space="preserve">37.2904777526855</t>
+    <t xml:space="preserve">37.2904739379883</t>
   </si>
   <si>
     <t xml:space="preserve">37.2533988952637</t>
   </si>
   <si>
-    <t xml:space="preserve">37.0865478515625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.6705131530762</t>
+    <t xml:space="preserve">37.0865516662598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.6705169677734</t>
   </si>
   <si>
     <t xml:space="preserve">38.5603713989258</t>
   </si>
   <si>
-    <t xml:space="preserve">38.4584159851074</t>
+    <t xml:space="preserve">38.4584083557129</t>
   </si>
   <si>
     <t xml:space="preserve">38.3749885559082</t>
   </si>
   <si>
-    <t xml:space="preserve">37.4665908813477</t>
+    <t xml:space="preserve">37.4665870666504</t>
   </si>
   <si>
     <t xml:space="preserve">37.5407485961914</t>
@@ -4787,19 +4787,19 @@
     <t xml:space="preserve">37.8559036254883</t>
   </si>
   <si>
-    <t xml:space="preserve">38.8291778564453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.8199157714844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.5881805419922</t>
+    <t xml:space="preserve">38.8291816711426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.8199195861816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.5881843566895</t>
   </si>
   <si>
     <t xml:space="preserve">37.4944000244141</t>
   </si>
   <si>
-    <t xml:space="preserve">36.7065086364746</t>
+    <t xml:space="preserve">36.7065124511719</t>
   </si>
   <si>
     <t xml:space="preserve">36.3542747497559</t>
@@ -4808,34 +4808,34 @@
     <t xml:space="preserve">35.6590728759766</t>
   </si>
   <si>
-    <t xml:space="preserve">36.3171997070312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.9000778198242</t>
+    <t xml:space="preserve">36.317195892334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.900074005127</t>
   </si>
   <si>
     <t xml:space="preserve">36.2615814208984</t>
   </si>
   <si>
-    <t xml:space="preserve">35.8073844909668</t>
+    <t xml:space="preserve">35.8073883056641</t>
   </si>
   <si>
     <t xml:space="preserve">36.1966972351074</t>
   </si>
   <si>
-    <t xml:space="preserve">36.7713928222656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.9186172485352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.9835014343262</t>
+    <t xml:space="preserve">36.7713966369629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.9186210632324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.9835052490234</t>
   </si>
   <si>
     <t xml:space="preserve">36.0761909484863</t>
   </si>
   <si>
-    <t xml:space="preserve">35.5941886901855</t>
+    <t xml:space="preserve">35.5941925048828</t>
   </si>
   <si>
     <t xml:space="preserve">35.8537330627441</t>
@@ -4844,97 +4844,97 @@
     <t xml:space="preserve">36.4655075073242</t>
   </si>
   <si>
-    <t xml:space="preserve">36.1874313354492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.9649696350098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36.5118560791016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.2348556518555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.1514320373535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.7921028137207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.1536140441895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.4027976989746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.291561126709</t>
+    <t xml:space="preserve">36.187427520752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.964958190918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.5118522644043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.23486328125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.1514434814453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.7921104431152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.1536102294922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.4027938842773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.2915649414062</t>
   </si>
   <si>
     <t xml:space="preserve">38.0227508544922</t>
   </si>
   <si>
-    <t xml:space="preserve">37.6056365966797</t>
+    <t xml:space="preserve">37.6056327819824</t>
   </si>
   <si>
     <t xml:space="preserve">37.7817459106445</t>
   </si>
   <si>
-    <t xml:space="preserve">38.2359466552734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.1977844238281</t>
+    <t xml:space="preserve">38.2359504699707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.1977806091309</t>
   </si>
   <si>
     <t xml:space="preserve">36.252311706543</t>
   </si>
   <si>
-    <t xml:space="preserve">37.0587463378906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.3182792663574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.6519813537598</t>
+    <t xml:space="preserve">37.0587425231934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.3182830810547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.6519737243652</t>
   </si>
   <si>
     <t xml:space="preserve">37.9300575256348</t>
   </si>
   <si>
-    <t xml:space="preserve">38.2452125549316</t>
+    <t xml:space="preserve">38.2452163696289</t>
   </si>
   <si>
     <t xml:space="preserve">38.0876350402832</t>
   </si>
   <si>
-    <t xml:space="preserve">37.3090171813965</t>
+    <t xml:space="preserve">37.3090133666992</t>
   </si>
   <si>
     <t xml:space="preserve">37.7724800109863</t>
   </si>
   <si>
-    <t xml:space="preserve">38.0505599975586</t>
+    <t xml:space="preserve">38.0505561828613</t>
   </si>
   <si>
     <t xml:space="preserve">37.9764060974121</t>
   </si>
   <si>
-    <t xml:space="preserve">38.3564529418945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.0969085693359</t>
+    <t xml:space="preserve">38.3564491271973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.0969047546387</t>
   </si>
   <si>
     <t xml:space="preserve">37.6241722106934</t>
   </si>
   <si>
-    <t xml:space="preserve">36.6601638793945</t>
+    <t xml:space="preserve">36.6601600646973</t>
   </si>
   <si>
     <t xml:space="preserve">37.1050872802734</t>
   </si>
   <si>
-    <t xml:space="preserve">36.5674705505371</t>
+    <t xml:space="preserve">36.5674743652344</t>
   </si>
   <si>
     <t xml:space="preserve">37.1885108947754</t>
@@ -4943,16 +4943,16 @@
     <t xml:space="preserve">37.2070541381836</t>
   </si>
   <si>
-    <t xml:space="preserve">36.4284324645996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36.7250442504883</t>
+    <t xml:space="preserve">36.4284286499023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.725040435791</t>
   </si>
   <si>
     <t xml:space="preserve">36.4098892211914</t>
   </si>
   <si>
-    <t xml:space="preserve">35.8815422058105</t>
+    <t xml:space="preserve">35.8815383911133</t>
   </si>
   <si>
     <t xml:space="preserve">35.8166542053223</t>
@@ -4961,19 +4961,19 @@
     <t xml:space="preserve">35.2234191894531</t>
   </si>
   <si>
-    <t xml:space="preserve">36.0205841064453</t>
+    <t xml:space="preserve">36.020580291748</t>
   </si>
   <si>
     <t xml:space="preserve">35.4829635620117</t>
   </si>
   <si>
-    <t xml:space="preserve">35.7239646911621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.8629951477051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.0402030944824</t>
+    <t xml:space="preserve">35.7239570617676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.8629989624023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.0402069091797</t>
   </si>
   <si>
     <t xml:space="preserve">36.3728141784668</t>
@@ -4991,49 +4991,49 @@
     <t xml:space="preserve">36.4840469360352</t>
   </si>
   <si>
-    <t xml:space="preserve">36.9382400512695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36.9938583374023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.3646354675293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.7539443969727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.8466339111328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.4758644104004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.2997436523438</t>
+    <t xml:space="preserve">36.9382362365723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.9938545227051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.364631652832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.7539405822754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.8466300964355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.4758682250977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.299747467041</t>
   </si>
   <si>
     <t xml:space="preserve">36.9475135803223</t>
   </si>
   <si>
-    <t xml:space="preserve">38.9589500427246</t>
+    <t xml:space="preserve">38.9589538574219</t>
   </si>
   <si>
     <t xml:space="preserve">37.7261352539062</t>
   </si>
   <si>
-    <t xml:space="preserve">37.095817565918</t>
+    <t xml:space="preserve">37.0958213806152</t>
   </si>
   <si>
     <t xml:space="preserve">38.6808738708496</t>
   </si>
   <si>
-    <t xml:space="preserve">37.9393272399902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.1061820983887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.3760719299316</t>
+    <t xml:space="preserve">37.9393310546875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.1061782836914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.3760681152344</t>
   </si>
   <si>
     <t xml:space="preserve">39.0053024291992</t>
@@ -5042,37 +5042,37 @@
     <t xml:space="preserve">38.9311447143555</t>
   </si>
   <si>
-    <t xml:space="preserve">39.1721496582031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.9878463745117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40.8684310913086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.5461807250977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.2866439819336</t>
+    <t xml:space="preserve">39.1721458435059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.9878540039062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40.8684349060059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.5461845397949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.2866363525391</t>
   </si>
   <si>
     <t xml:space="preserve">41.7119407653809</t>
   </si>
   <si>
-    <t xml:space="preserve">41.3040962219238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.3831329345703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.655574798584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40.5188331604004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40.0960731506348</t>
+    <t xml:space="preserve">41.3040924072266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.383129119873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.6555709838867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40.5188293457031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40.096076965332</t>
   </si>
   <si>
     <t xml:space="preserve">40.5564079284668</t>
@@ -5081,46 +5081,46 @@
     <t xml:space="preserve">40.0866775512695</t>
   </si>
   <si>
-    <t xml:space="preserve">39.4290618896484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.1607894897461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.983341217041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40.2463874816895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40.3967018127441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.4488906860352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.9186248779297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.1346969604492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.7025451660156</t>
+    <t xml:space="preserve">39.4290580749512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.1607818603516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.9833374023438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40.2463836669922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40.3966979980469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.4488945007324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.9186210632324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.134693145752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.7025489807129</t>
   </si>
   <si>
     <t xml:space="preserve">42.7453460693359</t>
   </si>
   <si>
-    <t xml:space="preserve">42.2568244934082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.2098579406738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.5198745727539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.3925285339355</t>
+    <t xml:space="preserve">42.2568321228027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.2098541259766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.5198783874512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.3925247192383</t>
   </si>
   <si>
     <t xml:space="preserve">40.6597442626953</t>
@@ -5129,7 +5129,7 @@
     <t xml:space="preserve">40.190013885498</t>
   </si>
   <si>
-    <t xml:space="preserve">40.330940246582</t>
+    <t xml:space="preserve">40.3309364318848</t>
   </si>
   <si>
     <t xml:space="preserve">40.1242561340332</t>
@@ -5138,10 +5138,10 @@
     <t xml:space="preserve">40.4906463623047</t>
   </si>
   <si>
-    <t xml:space="preserve">40.6973266601562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.1012954711914</t>
+    <t xml:space="preserve">40.6973304748535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.1012916564941</t>
   </si>
   <si>
     <t xml:space="preserve">40.7442970275879</t>
@@ -5150,7 +5150,7 @@
     <t xml:space="preserve">40.9415893554688</t>
   </si>
   <si>
-    <t xml:space="preserve">41.0449295043945</t>
+    <t xml:space="preserve">41.0449256896973</t>
   </si>
   <si>
     <t xml:space="preserve">39.6639251708984</t>
@@ -5162,61 +5162,61 @@
     <t xml:space="preserve">39.757869720459</t>
   </si>
   <si>
-    <t xml:space="preserve">39.6921081542969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40.3121490478516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40.2933578491211</t>
+    <t xml:space="preserve">39.6921043395996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40.3121452331543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40.2933616638184</t>
   </si>
   <si>
     <t xml:space="preserve">40.4718589782715</t>
   </si>
   <si>
-    <t xml:space="preserve">40.4060974121094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40.6691436767578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40.8476371765137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40.5470123291016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.5856437683105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.3319816589355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.7589149475098</t>
+    <t xml:space="preserve">40.4060935974121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40.6691474914551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40.8476409912109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40.5470085144043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.5856399536133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.3319854736328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.758918762207</t>
   </si>
   <si>
     <t xml:space="preserve">42.5386657714844</t>
   </si>
   <si>
-    <t xml:space="preserve">43.6754035949707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43.9760398864746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">44.1075630187988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43.1962852478027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.8392906188965</t>
+    <t xml:space="preserve">43.6754112243652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43.9760360717773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44.1075592041016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43.1962890625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.8392868041992</t>
   </si>
   <si>
     <t xml:space="preserve">41.881046295166</t>
   </si>
   <si>
-    <t xml:space="preserve">40.8758239746094</t>
+    <t xml:space="preserve">40.8758277893066</t>
   </si>
   <si>
     <t xml:space="preserve">42.228645324707</t>
@@ -5231,7 +5231,7 @@
     <t xml:space="preserve">42.698371887207</t>
   </si>
   <si>
-    <t xml:space="preserve">42.6138191223145</t>
+    <t xml:space="preserve">42.6138229370117</t>
   </si>
   <si>
     <t xml:space="preserve">42.0971183776855</t>
@@ -5243,25 +5243,25 @@
     <t xml:space="preserve">41.9749908447266</t>
   </si>
   <si>
-    <t xml:space="preserve">42.9896049499512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.8017120361328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43.0647583007812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43.3935737609863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">44.0511932373047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43.656623840332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43.5720710754395</t>
+    <t xml:space="preserve">42.9896011352539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.8017158508301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43.0647621154785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43.3935699462891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44.0511894226074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43.6566200256348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43.5720672607422</t>
   </si>
   <si>
     <t xml:space="preserve">43.0177879333496</t>
@@ -5279,25 +5279,25 @@
     <t xml:space="preserve">42.8298950195312</t>
   </si>
   <si>
-    <t xml:space="preserve">42.4822959899902</t>
+    <t xml:space="preserve">42.4822998046875</t>
   </si>
   <si>
     <t xml:space="preserve">42.7171592712402</t>
   </si>
   <si>
-    <t xml:space="preserve">42.8768653869629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43.5438842773438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43.9854316711426</t>
+    <t xml:space="preserve">42.8768692016602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43.5438804626465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43.985424041748</t>
   </si>
   <si>
     <t xml:space="preserve">44.0887718200684</t>
   </si>
   <si>
-    <t xml:space="preserve">44.1357421875</t>
+    <t xml:space="preserve">44.1357460021973</t>
   </si>
   <si>
     <t xml:space="preserve">44.5303192138672</t>
@@ -5306,28 +5306,28 @@
     <t xml:space="preserve">42.1816711425781</t>
   </si>
   <si>
-    <t xml:space="preserve">42.5574531555176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.0783271789551</t>
+    <t xml:space="preserve">42.5574569702148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.0783309936523</t>
   </si>
   <si>
     <t xml:space="preserve">42.0689353942871</t>
   </si>
   <si>
-    <t xml:space="preserve">41.3643417358398</t>
+    <t xml:space="preserve">41.3643379211426</t>
   </si>
   <si>
     <t xml:space="preserve">41.4770812988281</t>
   </si>
   <si>
-    <t xml:space="preserve">42.0031700134277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.4019203186035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.0919036865234</t>
+    <t xml:space="preserve">42.003173828125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.4019241333008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.0918998718262</t>
   </si>
   <si>
     <t xml:space="preserve">41.3549461364746</t>
@@ -5336,13 +5336,13 @@
     <t xml:space="preserve">41.9843864440918</t>
   </si>
   <si>
-    <t xml:space="preserve">41.9374122619629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.8580856323242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.7829208374023</t>
+    <t xml:space="preserve">41.9374084472656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.8580780029297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.7829246520996</t>
   </si>
   <si>
     <t xml:space="preserve">42.7359504699707</t>
@@ -5351,10 +5351,10 @@
     <t xml:space="preserve">42.1159133911133</t>
   </si>
   <si>
-    <t xml:space="preserve">41.3455505371094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.3267707824707</t>
+    <t xml:space="preserve">41.3455581665039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.3267669677734</t>
   </si>
   <si>
     <t xml:space="preserve">41.6837577819824</t>
@@ -5363,31 +5363,31 @@
     <t xml:space="preserve">41.307975769043</t>
   </si>
   <si>
-    <t xml:space="preserve">41.0637092590332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40.7912712097168</t>
+    <t xml:space="preserve">41.0637168884277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40.7912750244141</t>
   </si>
   <si>
     <t xml:space="preserve">40.6127738952637</t>
   </si>
   <si>
-    <t xml:space="preserve">40.960376739502</t>
+    <t xml:space="preserve">40.9603729248047</t>
   </si>
   <si>
     <t xml:space="preserve">41.4582862854004</t>
   </si>
   <si>
-    <t xml:space="preserve">41.6179962158203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.2891845703125</t>
+    <t xml:space="preserve">41.6180000305176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.2891883850098</t>
   </si>
   <si>
     <t xml:space="preserve">41.430103302002</t>
   </si>
   <si>
-    <t xml:space="preserve">41.1482696533203</t>
+    <t xml:space="preserve">41.148265838623</t>
   </si>
   <si>
     <t xml:space="preserve">42.0501480102539</t>
@@ -5399,79 +5399,79 @@
     <t xml:space="preserve">42.1910629272461</t>
   </si>
   <si>
-    <t xml:space="preserve">43.0741539001465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.8434638977051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.4447212219238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.4542350769043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.7016105651855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.2353935241699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.3876304626465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.2639427185059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.2163696289062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.1687927246094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.0260772705078</t>
+    <t xml:space="preserve">43.0741500854492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.8434715270996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.4447174072266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.454231262207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.7016143798828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.2354011535645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.3876266479492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.2639389038086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.216365814209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.1687965393066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.0260734558105</t>
   </si>
   <si>
     <t xml:space="preserve">42.0451049804688</t>
   </si>
   <si>
-    <t xml:space="preserve">43.0251121520996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43.6721038818359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43.9956016540527</t>
+    <t xml:space="preserve">43.0251159667969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43.6721115112305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43.99560546875</t>
   </si>
   <si>
     <t xml:space="preserve">43.4437522888184</t>
   </si>
   <si>
-    <t xml:space="preserve">44.4332733154297</t>
+    <t xml:space="preserve">44.4332809448242</t>
   </si>
   <si>
     <t xml:space="preserve">44.3857002258301</t>
   </si>
   <si>
-    <t xml:space="preserve">44.928035736084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">44.7282257080078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.0326957702637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.5559997558594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.5464859008789</t>
+    <t xml:space="preserve">44.9280395507812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44.7282295227051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.0326995849609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.5560035705566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.5464820861816</t>
   </si>
   <si>
     <t xml:space="preserve">45.6606636047363</t>
   </si>
   <si>
-    <t xml:space="preserve">45.2800750732422</t>
+    <t xml:space="preserve">45.2800712585449</t>
   </si>
   <si>
     <t xml:space="preserve">45.7938652038574</t>
@@ -5483,10 +5483,10 @@
     <t xml:space="preserve">45.9841575622559</t>
   </si>
   <si>
-    <t xml:space="preserve">46.0888137817383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.4598922729492</t>
+    <t xml:space="preserve">46.0888175964355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.459888458252</t>
   </si>
   <si>
     <t xml:space="preserve">46.621639251709</t>
@@ -5495,7 +5495,7 @@
     <t xml:space="preserve">45.6892051696777</t>
   </si>
   <si>
-    <t xml:space="preserve">46.1649360656738</t>
+    <t xml:space="preserve">46.1649398803711</t>
   </si>
   <si>
     <t xml:space="preserve">45.4989166259766</t>
@@ -5507,34 +5507,34 @@
     <t xml:space="preserve">46.5455169677734</t>
   </si>
   <si>
-    <t xml:space="preserve">46.7167778015137</t>
+    <t xml:space="preserve">46.7167816162109</t>
   </si>
   <si>
     <t xml:space="preserve">46.8309593200684</t>
   </si>
   <si>
-    <t xml:space="preserve">48.486499786377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">47.5635871887207</t>
+    <t xml:space="preserve">48.4865036010742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">47.5635833740234</t>
   </si>
   <si>
     <t xml:space="preserve">47.8204803466797</t>
   </si>
   <si>
-    <t xml:space="preserve">48.0488357543945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">47.3732948303223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">47.3447456359863</t>
+    <t xml:space="preserve">48.0488319396973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">47.373291015625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">47.3447494506836</t>
   </si>
   <si>
     <t xml:space="preserve">47.1639709472656</t>
   </si>
   <si>
-    <t xml:space="preserve">47.3066940307617</t>
+    <t xml:space="preserve">47.3066902160645</t>
   </si>
   <si>
     <t xml:space="preserve">47.5160102844238</t>
@@ -5543,7 +5543,7 @@
     <t xml:space="preserve">47.554069519043</t>
   </si>
   <si>
-    <t xml:space="preserve">48.4294204711914</t>
+    <t xml:space="preserve">48.4294128417969</t>
   </si>
   <si>
     <t xml:space="preserve">48.1820335388184</t>
@@ -5558,13 +5558,13 @@
     <t xml:space="preserve">48.2391242980957</t>
   </si>
   <si>
-    <t xml:space="preserve">48.3532943725586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">48.6197052001953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">47.9917373657227</t>
+    <t xml:space="preserve">48.3532981872559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">48.6197090148926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">47.9917449951172</t>
   </si>
   <si>
     <t xml:space="preserve">48.0107688903809</t>
@@ -5573,16 +5573,16 @@
     <t xml:space="preserve">48.1059188842773</t>
   </si>
   <si>
-    <t xml:space="preserve">47.9346580505371</t>
+    <t xml:space="preserve">47.9346542358398</t>
   </si>
   <si>
     <t xml:space="preserve">48.0298004150391</t>
   </si>
   <si>
-    <t xml:space="preserve">48.5435943603516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">48.7529144287109</t>
+    <t xml:space="preserve">48.5435905456543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">48.7529182434082</t>
   </si>
   <si>
     <t xml:space="preserve">49.5901985168457</t>
@@ -5591,31 +5591,31 @@
     <t xml:space="preserve">49.5521430969238</t>
   </si>
   <si>
-    <t xml:space="preserve">49.1715545654297</t>
+    <t xml:space="preserve">49.171558380127</t>
   </si>
   <si>
     <t xml:space="preserve">50.3133125305176</t>
   </si>
   <si>
-    <t xml:space="preserve">49.1525268554688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">48.5055313110352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">48.2581520080566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">49.247673034668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">49.4379615783691</t>
+    <t xml:space="preserve">49.152530670166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">48.5055351257324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">48.2581558227539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">49.2476692199707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">49.4379653930664</t>
   </si>
   <si>
     <t xml:space="preserve">49.2096176147461</t>
   </si>
   <si>
-    <t xml:space="preserve">50.0278739929199</t>
+    <t xml:space="preserve">50.0278701782227</t>
   </si>
   <si>
     <t xml:space="preserve">50.2942810058594</t>
@@ -5624,28 +5624,28 @@
     <t xml:space="preserve">50.1801071166992</t>
   </si>
   <si>
-    <t xml:space="preserve">50.503604888916</t>
+    <t xml:space="preserve">50.5036010742188</t>
   </si>
   <si>
     <t xml:space="preserve">50.2181663513184</t>
   </si>
   <si>
-    <t xml:space="preserve">50.2752494812012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">49.3428230285645</t>
+    <t xml:space="preserve">50.2752532958984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">49.3428192138672</t>
   </si>
   <si>
     <t xml:space="preserve">48.7338829040527</t>
   </si>
   <si>
-    <t xml:space="preserve">48.391357421875</t>
+    <t xml:space="preserve">48.3913612365723</t>
   </si>
   <si>
     <t xml:space="preserve">48.8861198425293</t>
   </si>
   <si>
-    <t xml:space="preserve">49.8185501098633</t>
+    <t xml:space="preserve">49.8185539245605</t>
   </si>
   <si>
     <t xml:space="preserve">49.4760208129883</t>
@@ -5669,25 +5669,25 @@
     <t xml:space="preserve">46.3361968994141</t>
   </si>
   <si>
-    <t xml:space="preserve">47.4969825744629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">47.1544570922852</t>
+    <t xml:space="preserve">47.4969787597656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">47.1544609069824</t>
   </si>
   <si>
     <t xml:space="preserve">47.5731010437012</t>
   </si>
   <si>
-    <t xml:space="preserve">47.0212516784668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.9451332092285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.5645484924316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">47.3257217407227</t>
+    <t xml:space="preserve">47.0212478637695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.9451370239258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.5645523071289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">47.3257255554199</t>
   </si>
   <si>
     <t xml:space="preserve">47.4398956298828</t>
@@ -5702,16 +5702,16 @@
     <t xml:space="preserve">47.6206703186035</t>
   </si>
   <si>
-    <t xml:space="preserve">47.7633934020996</t>
+    <t xml:space="preserve">47.7633895874023</t>
   </si>
   <si>
     <t xml:space="preserve">47.9061088562012</t>
   </si>
   <si>
-    <t xml:space="preserve">48.7148513793945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">49.2857284545898</t>
+    <t xml:space="preserve">48.7148551940918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">49.2857322692871</t>
   </si>
   <si>
     <t xml:space="preserve">48.5029220581055</t>
@@ -5720,25 +5720,25 @@
     <t xml:space="preserve">47.029052734375</t>
   </si>
   <si>
-    <t xml:space="preserve">47.3565826416016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.7400550842285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.5666580200195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.8941879272461</t>
+    <t xml:space="preserve">47.356575012207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.7400588989258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.5666618347168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.8941841125488</t>
   </si>
   <si>
     <t xml:space="preserve">46.3354644775391</t>
   </si>
   <si>
-    <t xml:space="preserve">45.950138092041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.7189407348633</t>
+    <t xml:space="preserve">45.9501419067383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.7189445495605</t>
   </si>
   <si>
     <t xml:space="preserve">46.6244621276855</t>
@@ -5753,13 +5753,13 @@
     <t xml:space="preserve">46.8171195983887</t>
   </si>
   <si>
-    <t xml:space="preserve">47.4336471557617</t>
+    <t xml:space="preserve">47.4336433410645</t>
   </si>
   <si>
     <t xml:space="preserve">47.8767700195312</t>
   </si>
   <si>
-    <t xml:space="preserve">47.7226409912109</t>
+    <t xml:space="preserve">47.7226371765137</t>
   </si>
   <si>
     <t xml:space="preserve">46.6437187194824</t>
@@ -5774,16 +5774,16 @@
     <t xml:space="preserve">45.6804084777832</t>
   </si>
   <si>
-    <t xml:space="preserve">46.0849990844727</t>
+    <t xml:space="preserve">46.0850028991699</t>
   </si>
   <si>
     <t xml:space="preserve">47.3951110839844</t>
   </si>
   <si>
-    <t xml:space="preserve">48.262092590332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">47.587776184082</t>
+    <t xml:space="preserve">48.2620887756348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">47.5877723693848</t>
   </si>
   <si>
     <t xml:space="preserve">47.7997016906738</t>
@@ -5798,7 +5798,7 @@
     <t xml:space="preserve">47.1639137268066</t>
   </si>
   <si>
-    <t xml:space="preserve">47.2795143127441</t>
+    <t xml:space="preserve">47.2795181274414</t>
   </si>
   <si>
     <t xml:space="preserve">47.3373107910156</t>
@@ -5807,7 +5807,7 @@
     <t xml:space="preserve">48.1657638549805</t>
   </si>
   <si>
-    <t xml:space="preserve">48.4065933227539</t>
+    <t xml:space="preserve">48.4065895080566</t>
   </si>
   <si>
     <t xml:space="preserve">49.0809135437012</t>
@@ -5816,25 +5816,25 @@
     <t xml:space="preserve">49.1772422790527</t>
   </si>
   <si>
-    <t xml:space="preserve">49.2254066467285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">49.8515663146973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">49.3699073791504</t>
+    <t xml:space="preserve">49.2254104614258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">49.8515625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">49.3699035644531</t>
   </si>
   <si>
     <t xml:space="preserve">49.514404296875</t>
   </si>
   <si>
-    <t xml:space="preserve">49.9478988647461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50.3332214355469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50.0442314147949</t>
+    <t xml:space="preserve">49.9478950500488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50.3332252502441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50.0442276000977</t>
   </si>
   <si>
     <t xml:space="preserve">50.4777221679688</t>
@@ -5843,7 +5843,7 @@
     <t xml:space="preserve">48.8882484436035</t>
   </si>
   <si>
-    <t xml:space="preserve">48.3102607727051</t>
+    <t xml:space="preserve">48.3102645874023</t>
   </si>
   <si>
     <t xml:space="preserve">46.7207908630371</t>
@@ -5855,7 +5855,7 @@
     <t xml:space="preserve">47.6263046264648</t>
   </si>
   <si>
-    <t xml:space="preserve">47.1831855773926</t>
+    <t xml:space="preserve">47.183177947998</t>
   </si>
   <si>
     <t xml:space="preserve">47.5299758911133</t>
@@ -5870,25 +5870,25 @@
     <t xml:space="preserve">48.1272277832031</t>
   </si>
   <si>
-    <t xml:space="preserve">48.7437553405762</t>
+    <t xml:space="preserve">48.7437477111816</t>
   </si>
   <si>
     <t xml:space="preserve">48.5510902404785</t>
   </si>
   <si>
-    <t xml:space="preserve">48.791919708252</t>
+    <t xml:space="preserve">48.7919235229492</t>
   </si>
   <si>
     <t xml:space="preserve">49.7070655822754</t>
   </si>
   <si>
-    <t xml:space="preserve">50.8148803710938</t>
+    <t xml:space="preserve">50.814884185791</t>
   </si>
   <si>
     <t xml:space="preserve">50.6222152709961</t>
   </si>
   <si>
-    <t xml:space="preserve">51.0557098388672</t>
+    <t xml:space="preserve">51.0557060241699</t>
   </si>
   <si>
     <t xml:space="preserve">50.7185478210449</t>
@@ -5903,10 +5903,10 @@
     <t xml:space="preserve">49.4180717468262</t>
   </si>
   <si>
-    <t xml:space="preserve">49.5625686645508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">49.0327491760254</t>
+    <t xml:space="preserve">49.562572479248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">49.0327453613281</t>
   </si>
   <si>
     <t xml:space="preserve">48.9845809936523</t>
@@ -5918,25 +5918,25 @@
     <t xml:space="preserve">48.1079635620117</t>
   </si>
   <si>
-    <t xml:space="preserve">47.9730987548828</t>
+    <t xml:space="preserve">47.9731025695801</t>
   </si>
   <si>
     <t xml:space="preserve">48.8400840759277</t>
   </si>
   <si>
-    <t xml:space="preserve">48.9364166259766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">47.6841049194336</t>
+    <t xml:space="preserve">48.9364128112793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">47.6841087341309</t>
   </si>
   <si>
     <t xml:space="preserve">50.1887245178223</t>
   </si>
   <si>
-    <t xml:space="preserve">52.1153526306152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">51.441032409668</t>
+    <t xml:space="preserve">52.1153564453125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">51.4410400390625</t>
   </si>
   <si>
     <t xml:space="preserve">51.5855331420898</t>
@@ -5948,22 +5948,22 @@
     <t xml:space="preserve">52.2116889953613</t>
   </si>
   <si>
-    <t xml:space="preserve">51.7781944274902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">51.3928680419922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">51.7300300598145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">51.8263626098633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">51.8745269775391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">51.152042388916</t>
+    <t xml:space="preserve">51.7781982421875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">51.3928642272949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">51.7300262451172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">51.826358795166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">51.8745231628418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">51.1520385742188</t>
   </si>
   <si>
     <t xml:space="preserve">49.9960632324219</t>
@@ -5975,76 +5975,76 @@
     <t xml:space="preserve">50.4295501708984</t>
   </si>
   <si>
+    <t xml:space="preserve">49.3217430114746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">48.7369003295898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">48.6394271850586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">49.1755294799805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">49.3704795837402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50.7838478088379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50.930061340332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50.4426918029785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50.3939552307129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50.0527954101562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50.2477416992188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">49.8578491210938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50.1015319824219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50.637638092041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">49.7603721618652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">49.8091087341309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">49.9065856933594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">49.5654258728027</t>
+  </si>
+  <si>
     <t xml:space="preserve">49.3217391967773</t>
   </si>
   <si>
-    <t xml:space="preserve">48.7369003295898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">48.6394271850586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">49.1755294799805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">49.3704795837402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50.7838478088379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50.9300575256348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50.4426918029785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50.3939514160156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50.0527954101562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50.2477416992188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">49.8578491210938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50.1015319824219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50.6376419067383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">49.7603721618652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">49.8091087341309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">49.9065818786621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">49.5654258728027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">49.3217430114746</t>
-  </si>
-  <si>
     <t xml:space="preserve">49.4679527282715</t>
   </si>
   <si>
     <t xml:space="preserve">49.0780563354492</t>
   </si>
   <si>
-    <t xml:space="preserve">49.1267967224121</t>
+    <t xml:space="preserve">49.1267929077148</t>
   </si>
   <si>
     <t xml:space="preserve">49.2242698669434</t>
   </si>
   <si>
-    <t xml:space="preserve">49.6141662597656</t>
+    <t xml:space="preserve">49.6141624450684</t>
   </si>
   <si>
     <t xml:space="preserve">50.4914245605469</t>
@@ -6068,10 +6068,10 @@
     <t xml:space="preserve">53.1719551086426</t>
   </si>
   <si>
-    <t xml:space="preserve">53.5131187438965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">53.2206916809082</t>
+    <t xml:space="preserve">53.5131149291992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">53.2206954956055</t>
   </si>
   <si>
     <t xml:space="preserve">53.7568016052246</t>
@@ -6083,13 +6083,13 @@
     <t xml:space="preserve">54.3903770446777</t>
   </si>
   <si>
-    <t xml:space="preserve">54.5853233337402</t>
+    <t xml:space="preserve">54.5853271484375</t>
   </si>
   <si>
     <t xml:space="preserve">55.3651161193848</t>
   </si>
   <si>
-    <t xml:space="preserve">56.047435760498</t>
+    <t xml:space="preserve">56.0474319458008</t>
   </si>
   <si>
     <t xml:space="preserve">56.6810150146484</t>
@@ -6101,7 +6101,7 @@
     <t xml:space="preserve">57.2658576965332</t>
   </si>
   <si>
-    <t xml:space="preserve">57.7532272338867</t>
+    <t xml:space="preserve">57.7532234191895</t>
   </si>
   <si>
     <t xml:space="preserve">57.6070137023926</t>
@@ -6110,7 +6110,7 @@
     <t xml:space="preserve">57.9481735229492</t>
   </si>
   <si>
-    <t xml:space="preserve">58.1431198120117</t>
+    <t xml:space="preserve">58.143123626709</t>
   </si>
   <si>
     <t xml:space="preserve">57.1196441650391</t>
@@ -6125,10 +6125,10 @@
     <t xml:space="preserve">57.558277130127</t>
   </si>
   <si>
-    <t xml:space="preserve">59.4102821350098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">58.0943832397461</t>
+    <t xml:space="preserve">59.4102783203125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">58.0943794250488</t>
   </si>
   <si>
     <t xml:space="preserve">58.240592956543</t>
@@ -6140,10 +6140,10 @@
     <t xml:space="preserve">54.4391136169434</t>
   </si>
   <si>
-    <t xml:space="preserve">53.4643745422363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">52.7333221435547</t>
+    <t xml:space="preserve">53.4643783569336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">52.733325958252</t>
   </si>
   <si>
     <t xml:space="preserve">52.3434295654297</t>
@@ -6158,28 +6158,28 @@
     <t xml:space="preserve">52.9282722473145</t>
   </si>
   <si>
-    <t xml:space="preserve">53.5618515014648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">52.8795356750488</t>
+    <t xml:space="preserve">53.5618553161621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">52.8795318603516</t>
   </si>
   <si>
     <t xml:space="preserve">52.4896392822266</t>
   </si>
   <si>
-    <t xml:space="preserve">52.1972198486328</t>
+    <t xml:space="preserve">52.1972160339355</t>
   </si>
   <si>
     <t xml:space="preserve">50.9787940979004</t>
   </si>
   <si>
-    <t xml:space="preserve">51.6611137390137</t>
+    <t xml:space="preserve">51.6611099243164</t>
   </si>
   <si>
     <t xml:space="preserve">51.612377166748</t>
   </si>
   <si>
-    <t xml:space="preserve">51.3686943054199</t>
+    <t xml:space="preserve">51.3686904907227</t>
   </si>
   <si>
     <t xml:space="preserve">52.0997467041016</t>
@@ -6212,10 +6212,10 @@
     <t xml:space="preserve">44.7014846801758</t>
   </si>
   <si>
-    <t xml:space="preserve">45.4617805480957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.4365196228027</t>
+    <t xml:space="preserve">45.4617767333984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.4365158081055</t>
   </si>
   <si>
     <t xml:space="preserve">47.1383285522461</t>
@@ -6224,16 +6224,16 @@
     <t xml:space="preserve">47.2747917175293</t>
   </si>
   <si>
-    <t xml:space="preserve">47.0798454284668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">47.7426681518555</t>
+    <t xml:space="preserve">47.0798416137695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">47.7426643371582</t>
   </si>
   <si>
     <t xml:space="preserve">47.9766044616699</t>
   </si>
   <si>
-    <t xml:space="preserve">48.2105407714844</t>
+    <t xml:space="preserve">48.2105369567871</t>
   </si>
   <si>
     <t xml:space="preserve">47.8011512756348</t>
@@ -6245,7 +6245,7 @@
     <t xml:space="preserve">50.5401649475098</t>
   </si>
   <si>
-    <t xml:space="preserve">51.8560638427734</t>
+    <t xml:space="preserve">51.8560600280762</t>
   </si>
   <si>
     <t xml:space="preserve">51.1737442016602</t>
@@ -6254,10 +6254,10 @@
     <t xml:space="preserve">50.8325843811035</t>
   </si>
   <si>
-    <t xml:space="preserve">50.3452186584473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50.1990051269531</t>
+    <t xml:space="preserve">50.34521484375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50.1990089416504</t>
   </si>
   <si>
     <t xml:space="preserve">50.8113098144531</t>
@@ -6683,10 +6683,13 @@
     <t xml:space="preserve">44.9799995422363</t>
   </si>
   <si>
+    <t xml:space="preserve">45.0400009155273</t>
+  </si>
+  <si>
     <t xml:space="preserve"/>
   </si>
   <si>
-    <t xml:space="preserve">45.0400009155273</t>
+    <t xml:space="preserve">44.6599998474121</t>
   </si>
 </sst>
 </file>
@@ -74457,7 +74460,9 @@
       <c r="E2594" t="n">
         <v>45.2200012207031</v>
       </c>
-      <c r="F2594"/>
+      <c r="F2594" t="n">
+        <v>45.0400009155273</v>
+      </c>
       <c r="G2594" t="s">
         <v>2223</v>
       </c>
@@ -74467,27 +74472,51 @@
     </row>
     <row r="2595">
       <c r="A2595" s="1" t="n">
-        <v>46098.6911226852</v>
+        <v>46099.3333333333</v>
       </c>
       <c r="B2595" t="n">
-        <v>248554</v>
+        <v>269758</v>
       </c>
       <c r="C2595" t="n">
-        <v>45.3400001525879</v>
+        <v>45.4000015258789</v>
       </c>
       <c r="D2595" t="n">
-        <v>44.7799987792969</v>
+        <v>44.6399993896484</v>
       </c>
       <c r="E2595" t="n">
-        <v>45.2200012207031</v>
-      </c>
-      <c r="F2595" t="n">
-        <v>45.0400009155273</v>
-      </c>
+        <v>45.1800003051758</v>
+      </c>
+      <c r="F2595"/>
       <c r="G2595" t="s">
         <v>2224</v>
       </c>
       <c r="H2595" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2596">
+      <c r="A2596" s="1" t="n">
+        <v>46099.691712963</v>
+      </c>
+      <c r="B2596" t="n">
+        <v>269758</v>
+      </c>
+      <c r="C2596" t="n">
+        <v>45.4000015258789</v>
+      </c>
+      <c r="D2596" t="n">
+        <v>44.6399993896484</v>
+      </c>
+      <c r="E2596" t="n">
+        <v>45.1800003051758</v>
+      </c>
+      <c r="F2596" t="n">
+        <v>44.6599998474121</v>
+      </c>
+      <c r="G2596" t="s">
+        <v>2225</v>
+      </c>
+      <c r="H2596" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/REC.MI.xlsx
+++ b/data/REC.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2251" uniqueCount="2251">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2252" uniqueCount="2252">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -44,49 +44,49 @@
     <t xml:space="preserve">REC.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">18.9363479614258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.6177635192871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2680969238281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.1204566955566</t>
+    <t xml:space="preserve">18.9363460540771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6177597045898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2680950164795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.1204586029053</t>
   </si>
   <si>
     <t xml:space="preserve">17.9728240966797</t>
   </si>
   <si>
-    <t xml:space="preserve">18.0116748809814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4444389343262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.5609951019287</t>
+    <t xml:space="preserve">18.0116767883301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4444446563721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.5609912872314</t>
   </si>
   <si>
     <t xml:space="preserve">16.9626789093018</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9005165100098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.884973526001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.623161315918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.8484954833984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.817419052124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.1359977722168</t>
+    <t xml:space="preserve">16.9005146026611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8849716186523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6231555938721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.8485012054443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.8174171447754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.1360034942627</t>
   </si>
   <si>
     <t xml:space="preserve">17.3667392730713</t>
@@ -95,10 +95,10 @@
     <t xml:space="preserve">17.7164001464844</t>
   </si>
   <si>
-    <t xml:space="preserve">18.066068649292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4677505493164</t>
+    <t xml:space="preserve">18.0660648345947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4677486419678</t>
   </si>
   <si>
     <t xml:space="preserve">17.2424125671387</t>
@@ -110,73 +110,73 @@
     <t xml:space="preserve">15.5407028198242</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0977964401245</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2143516540527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7815837860107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9136800765991</t>
+    <t xml:space="preserve">15.0977973937988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2143449783325</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7815818786621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9136810302734</t>
   </si>
   <si>
     <t xml:space="preserve">16.5042304992676</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1647033691406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0326118469238</t>
+    <t xml:space="preserve">17.1647090911865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0326137542725</t>
   </si>
   <si>
     <t xml:space="preserve">17.3511962890625</t>
   </si>
   <si>
-    <t xml:space="preserve">17.7474842071533</t>
+    <t xml:space="preserve">17.747486114502</t>
   </si>
   <si>
     <t xml:space="preserve">17.7707977294922</t>
   </si>
   <si>
-    <t xml:space="preserve">18.0349884033203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4342956542969</t>
+    <t xml:space="preserve">18.0349826812744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4342918395996</t>
   </si>
   <si>
     <t xml:space="preserve">16.379903793335</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8772029876709</t>
+    <t xml:space="preserve">16.8772048950195</t>
   </si>
   <si>
     <t xml:space="preserve">17.0403842926025</t>
   </si>
   <si>
-    <t xml:space="preserve">17.2579479217529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4055843353271</t>
+    <t xml:space="preserve">17.2579517364502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4055862426758</t>
   </si>
   <si>
     <t xml:space="preserve">17.0248413085938</t>
   </si>
   <si>
-    <t xml:space="preserve">16.799503326416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7295684814453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5508518218994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8616619110107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5353107452393</t>
+    <t xml:space="preserve">16.7995052337646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7295665740967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.550853729248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8616638183594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.535306930542</t>
   </si>
   <si>
     <t xml:space="preserve">16.8072662353516</t>
@@ -188,259 +188,259 @@
     <t xml:space="preserve">16.9937591552734</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9315986633301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7217979431152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7684192657471</t>
+    <t xml:space="preserve">16.9315929412842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7217998504639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7684154510498</t>
   </si>
   <si>
     <t xml:space="preserve">16.8694305419922</t>
   </si>
   <si>
-    <t xml:space="preserve">16.6829452514648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9782199859619</t>
+    <t xml:space="preserve">16.6829414367676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9782238006592</t>
   </si>
   <si>
     <t xml:space="preserve">17.0947761535645</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1025428771973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2191009521484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1336231231689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4832954406738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.5454540252686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.459981918335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4366683959961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4522075653076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.3822803497314</t>
+    <t xml:space="preserve">17.1025447845459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2190990447998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1336250305176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4832935333252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.5454521179199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4599800109863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4366703033447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4522113800049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3822765350342</t>
   </si>
   <si>
     <t xml:space="preserve">17.4133586883545</t>
   </si>
   <si>
-    <t xml:space="preserve">17.7677707672119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6968822479248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.5314979553223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6102561950684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.381856918335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4448623657227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.5078659057617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6811370849609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4763660430908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4291133880615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6023750305176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.8937797546387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9804153442383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.6734848022461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.9648914337158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.9018821716309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.7286148071289</t>
+    <t xml:space="preserve">17.7677726745605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6968879699707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.5314960479736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6102523803711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3818531036377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4448642730713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.507869720459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6811389923096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4763641357422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4291076660156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6023826599121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.8937854766846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9804191589355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6734828948975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.9648857116699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.9018859863281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.7286186218262</t>
   </si>
   <si>
     <t xml:space="preserve">19.0436458587646</t>
   </si>
   <si>
-    <t xml:space="preserve">19.02001953125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.0672721862793</t>
+    <t xml:space="preserve">19.0200214385986</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.0672702789307</t>
   </si>
   <si>
     <t xml:space="preserve">19.2169151306152</t>
   </si>
   <si>
-    <t xml:space="preserve">19.2720432281494</t>
+    <t xml:space="preserve">19.272045135498</t>
   </si>
   <si>
     <t xml:space="preserve">20.0911273956299</t>
   </si>
   <si>
-    <t xml:space="preserve">20.232889175415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.421911239624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3274002075195</t>
+    <t xml:space="preserve">20.2328929901123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.4219093322754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3273983001709</t>
   </si>
   <si>
     <t xml:space="preserve">20.4691638946533</t>
   </si>
   <si>
-    <t xml:space="preserve">20.7605686187744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.8944549560547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.9023303985596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.2488632202148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.4142570495605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.0677280426025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.9968414306641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.4930152893066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.4536361694336</t>
+    <t xml:space="preserve">20.7605667114258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.8944568634033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.9023361206055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.2488651275635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.4142608642578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.0677242279053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.9968433380127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.4930171966553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.4536380767822</t>
   </si>
   <si>
     <t xml:space="preserve">21.1464824676514</t>
   </si>
   <si>
-    <t xml:space="preserve">20.4770374298096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.4297885894775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.6266822814941</t>
+    <t xml:space="preserve">20.4770393371582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.4297828674316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.6266765594482</t>
   </si>
   <si>
     <t xml:space="preserve">20.3667774200439</t>
   </si>
   <si>
-    <t xml:space="preserve">19.9729919433594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.642427444458</t>
+    <t xml:space="preserve">19.9729900360107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.6424293518066</t>
   </si>
   <si>
     <t xml:space="preserve">20.9102058410645</t>
   </si>
   <si>
-    <t xml:space="preserve">20.8156986236572</t>
+    <t xml:space="preserve">20.81569480896</t>
   </si>
   <si>
     <t xml:space="preserve">21.1386051177979</t>
   </si>
   <si>
-    <t xml:space="preserve">20.0438747406006</t>
+    <t xml:space="preserve">20.0438709259033</t>
   </si>
   <si>
     <t xml:space="preserve">20.8708267211914</t>
   </si>
   <si>
-    <t xml:space="preserve">21.154354095459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.2646198272705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.2882404327393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.2803707122803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.1858577728271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.0519714355469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.3748836517334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.0758266448975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.2884712219238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.1545829772949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.918306350708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.7292823791504</t>
+    <t xml:space="preserve">21.1543560028076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.2646160125732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.2882480621338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.280366897583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.1858596801758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.0519695281982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.3748817443848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.0758247375488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.2884731292725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.1545810699463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.9183082580566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.7292900085449</t>
   </si>
   <si>
     <t xml:space="preserve">21.9104309082031</t>
   </si>
   <si>
-    <t xml:space="preserve">21.8001708984375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.217586517334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.6507568359375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.6192512512207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.6586322784424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.3751049041748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.8161468505859</t>
+    <t xml:space="preserve">21.8001689910889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.2175903320312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.6507511138916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.619255065918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.6586303710938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.3751010894775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.81614112854</t>
   </si>
   <si>
     <t xml:space="preserve">22.7925186157227</t>
@@ -452,37 +452,37 @@
     <t xml:space="preserve">22.8476505279541</t>
   </si>
   <si>
-    <t xml:space="preserve">23.1233043670654</t>
+    <t xml:space="preserve">23.1233024597168</t>
   </si>
   <si>
     <t xml:space="preserve">22.7216396331787</t>
   </si>
   <si>
-    <t xml:space="preserve">22.1230754852295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.4932403564453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.2412166595459</t>
+    <t xml:space="preserve">22.1230792999268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.4932384490967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.2412128448486</t>
   </si>
   <si>
     <t xml:space="preserve">22.1782112121582</t>
   </si>
   <si>
-    <t xml:space="preserve">22.4066143035889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.3672256469727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.51686668396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.902551651001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.8946800231934</t>
+    <t xml:space="preserve">22.4066047668457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.3672218322754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.5168685913086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.9025573730469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.894681930542</t>
   </si>
   <si>
     <t xml:space="preserve">21.4772663116455</t>
@@ -491,40 +491,40 @@
     <t xml:space="preserve">21.6111526489258</t>
   </si>
   <si>
-    <t xml:space="preserve">21.3355007171631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.4851379394531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.6032752990723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.6977844238281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.2094898223877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.2331142425537</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.5402717590332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.3591270446777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.1228542327881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.382755279541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.2724914550781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.9655590057373</t>
+    <t xml:space="preserve">21.3354988098145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.4851398468018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.6032791137695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.6977825164795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.2094879150391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.2331123352051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.5402736663818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.3591289520264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.1228504180908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.3827514648438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.2724933624268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.9655609130859</t>
   </si>
   <si>
     <t xml:space="preserve">21.6899089813232</t>
@@ -536,28 +536,28 @@
     <t xml:space="preserve">21.0047168731689</t>
   </si>
   <si>
-    <t xml:space="preserve">20.9495849609375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.398509979248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.5481452941895</t>
+    <t xml:space="preserve">20.9495830535889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.3985042572021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.5481433868408</t>
   </si>
   <si>
     <t xml:space="preserve">21.1779823303223</t>
   </si>
   <si>
-    <t xml:space="preserve">21.3906269073486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.406379699707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.6190299987793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.6584091186523</t>
+    <t xml:space="preserve">21.3906307220459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.4063816070557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.619026184082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.6584033966064</t>
   </si>
   <si>
     <t xml:space="preserve">22.3908557891846</t>
@@ -566,184 +566,184 @@
     <t xml:space="preserve">22.5956268310547</t>
   </si>
   <si>
-    <t xml:space="preserve">22.5326156616211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.4223594665527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.3514785766602</t>
+    <t xml:space="preserve">22.5326194763184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.4223556518555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.3514728546143</t>
   </si>
   <si>
     <t xml:space="preserve">22.3042240142822</t>
   </si>
   <si>
-    <t xml:space="preserve">22.1860866546631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.0836982727051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.2648429870605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.5166435241699</t>
+    <t xml:space="preserve">22.1860828399658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.0837001800537</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.2648410797119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.5166454315186</t>
   </si>
   <si>
     <t xml:space="preserve">21.6820373535156</t>
   </si>
   <si>
-    <t xml:space="preserve">21.2252426147461</t>
+    <t xml:space="preserve">21.2252445220947</t>
   </si>
   <si>
     <t xml:space="preserve">21.3512516021729</t>
   </si>
   <si>
-    <t xml:space="preserve">21.2567443847656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.1070995330811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.0913543701172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3037757873535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.8627300262451</t>
+    <t xml:space="preserve">21.2567348480225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.1070976257324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.0913486480713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3037719726562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.8627243041992</t>
   </si>
   <si>
     <t xml:space="preserve">20.1620082855225</t>
   </si>
   <si>
-    <t xml:space="preserve">20.256519317627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.8154716491699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3116493225098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.193733215332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.5164165496826</t>
+    <t xml:space="preserve">20.2565174102783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.8154678344727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3116455078125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.1937313079834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.5164203643799</t>
   </si>
   <si>
     <t xml:space="preserve">20.5557975769043</t>
   </si>
   <si>
-    <t xml:space="preserve">20.1383800506592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.0202484130859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.2643928527832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.2164916992188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.7134666442871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.0168743133545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.2564105987549</t>
+    <t xml:space="preserve">20.1383838653564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.0202465057373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.2643909454346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.2164859771729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.7134685516357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.0168762207031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.2564086914062</t>
   </si>
   <si>
     <t xml:space="preserve">20.3282661437988</t>
   </si>
   <si>
-    <t xml:space="preserve">20.0887355804443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3602046966553</t>
+    <t xml:space="preserve">20.0887298583984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3602066040039</t>
   </si>
   <si>
     <t xml:space="preserve">20.5119113922119</t>
   </si>
   <si>
-    <t xml:space="preserve">19.8092803955078</t>
+    <t xml:space="preserve">19.8092842102051</t>
   </si>
   <si>
     <t xml:space="preserve">20.1286563873291</t>
   </si>
   <si>
-    <t xml:space="preserve">20.3442344665527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.5598125457764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.5039215087891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3841590881348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.7594223022461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.4719886779785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.7354736328125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.4240798950195</t>
+    <t xml:space="preserve">20.3442325592041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.5598163604736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.503927230835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3841609954834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.759428024292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.4719848632812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.7354679107666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.4240837097168</t>
   </si>
   <si>
     <t xml:space="preserve">21.1107406616211</t>
   </si>
   <si>
-    <t xml:space="preserve">21.3582572937012</t>
+    <t xml:space="preserve">21.3582534790039</t>
   </si>
   <si>
     <t xml:space="preserve">21.5179481506348</t>
   </si>
   <si>
-    <t xml:space="preserve">21.294376373291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.1027545928955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.9270973205566</t>
+    <t xml:space="preserve">21.2943782806396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.1027526855469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.927095413208</t>
   </si>
   <si>
     <t xml:space="preserve">21.5019760131836</t>
   </si>
   <si>
-    <t xml:space="preserve">21.6057720184326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.3502655029297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.4939918518066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.8053817749023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.7335186004639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.8453006744385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.1966152191162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.180643081665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.7095642089844</t>
+    <t xml:space="preserve">21.605770111084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.3502731323242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.493989944458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.8053779602051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.7335205078125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.8452987670898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.1966190338135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.1806468963623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.7095718383789</t>
   </si>
   <si>
     <t xml:space="preserve">22.2205696105957</t>
@@ -752,49 +752,49 @@
     <t xml:space="preserve">21.7894134521484</t>
   </si>
   <si>
-    <t xml:space="preserve">22.1087913513184</t>
+    <t xml:space="preserve">22.1087875366211</t>
   </si>
   <si>
     <t xml:space="preserve">21.9570808410645</t>
   </si>
   <si>
-    <t xml:space="preserve">21.9890232086182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.7734432220459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.7814311981201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.749490737915</t>
+    <t xml:space="preserve">21.9890213012695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.7734451293945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.7814254760742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.7494926452637</t>
   </si>
   <si>
     <t xml:space="preserve">21.4620513916016</t>
   </si>
   <si>
-    <t xml:space="preserve">21.6377105712891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.6137523651123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.0069446563721</t>
+    <t xml:space="preserve">21.6377067565918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.6137580871582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.0069408416748</t>
   </si>
   <si>
     <t xml:space="preserve">21.0867824554443</t>
   </si>
   <si>
-    <t xml:space="preserve">21.2544574737549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.4380950927734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.0708160400391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.4540710449219</t>
+    <t xml:space="preserve">21.2544593811035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.4381008148193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.0708179473877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.454065322876</t>
   </si>
   <si>
     <t xml:space="preserve">21.5578651428223</t>
@@ -803,7 +803,7 @@
     <t xml:space="preserve">22.4281635284424</t>
   </si>
   <si>
-    <t xml:space="preserve">22.5399417877197</t>
+    <t xml:space="preserve">22.539945602417</t>
   </si>
   <si>
     <t xml:space="preserve">22.5958366394043</t>
@@ -812,70 +812,70 @@
     <t xml:space="preserve">22.8193969726562</t>
   </si>
   <si>
-    <t xml:space="preserve">22.5638961791992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.0509490966797</t>
+    <t xml:space="preserve">22.5638942718506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.0509433746338</t>
   </si>
   <si>
     <t xml:space="preserve">23.1467609405518</t>
   </si>
   <si>
-    <t xml:space="preserve">23.5539588928223</t>
+    <t xml:space="preserve">23.5539627075195</t>
   </si>
   <si>
     <t xml:space="preserve">23.5220241546631</t>
   </si>
   <si>
-    <t xml:space="preserve">23.4501647949219</t>
+    <t xml:space="preserve">23.4501686096191</t>
   </si>
   <si>
     <t xml:space="preserve">23.8733386993408</t>
   </si>
   <si>
-    <t xml:space="preserve">23.9292278289795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.8653526306152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.1687641143799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.2326354980469</t>
+    <t xml:space="preserve">23.9292335510254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.8653545379639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.1687622070312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.2326335906982</t>
   </si>
   <si>
     <t xml:space="preserve">24.0889186859131</t>
   </si>
   <si>
-    <t xml:space="preserve">24.1847267150879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.3444194793701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.6158885955811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.6078987121582</t>
+    <t xml:space="preserve">24.1847324371338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.3444175720215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.6158905029297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.6079063415527</t>
   </si>
   <si>
     <t xml:space="preserve">24.8554191589355</t>
   </si>
   <si>
-    <t xml:space="preserve">24.9751873016357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.2466526031494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.4382801055908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.47021484375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.0071220397949</t>
+    <t xml:space="preserve">24.9751834869385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.246654510498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.4382781982422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.4702167510986</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.0071239471436</t>
   </si>
   <si>
     <t xml:space="preserve">24.9272785186768</t>
@@ -887,10 +887,10 @@
     <t xml:space="preserve">25.3344821929932</t>
   </si>
   <si>
-    <t xml:space="preserve">25.2785930633545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.629903793335</t>
+    <t xml:space="preserve">25.2785911560059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.6299076080322</t>
   </si>
   <si>
     <t xml:space="preserve">25.3983554840088</t>
@@ -899,7 +899,7 @@
     <t xml:space="preserve">25.2067317962646</t>
   </si>
   <si>
-    <t xml:space="preserve">25.2865772247314</t>
+    <t xml:space="preserve">25.2865753173828</t>
   </si>
   <si>
     <t xml:space="preserve">25.3664226531982</t>
@@ -908,55 +908,55 @@
     <t xml:space="preserve">25.5899829864502</t>
   </si>
   <si>
-    <t xml:space="preserve">25.9492797851562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.9652481079102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.2207527160645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.0450973510742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.0211410522461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.4043884277344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.6598930358887</t>
+    <t xml:space="preserve">25.9492855072021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.9652519226074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.2207508087158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.0450897216797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.0211429595947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.4043941497803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.65989112854</t>
   </si>
   <si>
     <t xml:space="preserve">26.611988067627</t>
   </si>
   <si>
-    <t xml:space="preserve">26.3804378509521</t>
+    <t xml:space="preserve">26.3804416656494</t>
   </si>
   <si>
     <t xml:space="preserve">26.6439228057861</t>
   </si>
   <si>
-    <t xml:space="preserve">27.0351600646973</t>
+    <t xml:space="preserve">27.0351581573486</t>
   </si>
   <si>
     <t xml:space="preserve">26.5002002716064</t>
   </si>
   <si>
-    <t xml:space="preserve">27.6864204406738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.4685459136963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.4362602233887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.7187004089355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.4443321228027</t>
+    <t xml:space="preserve">27.6864185333252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.4685478210449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.4362640380859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.7186946868896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.4443359375</t>
   </si>
   <si>
     <t xml:space="preserve">27.7832508087158</t>
@@ -965,97 +965,97 @@
     <t xml:space="preserve">27.5573120117188</t>
   </si>
   <si>
-    <t xml:space="preserve">27.6218605041504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.3481178283691</t>
+    <t xml:space="preserve">27.6218681335449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.3481197357178</t>
   </si>
   <si>
     <t xml:space="preserve">28.743522644043</t>
   </si>
   <si>
-    <t xml:space="preserve">28.7193164825439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.4455718994141</t>
+    <t xml:space="preserve">28.7193183898926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.4455680847168</t>
   </si>
   <si>
     <t xml:space="preserve">29.5343322753906</t>
   </si>
   <si>
-    <t xml:space="preserve">29.4536380767822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.6628265380859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.8403587341309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.9291191101074</t>
+    <t xml:space="preserve">29.4536399841309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.6628341674805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.8403511047363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.9291172027588</t>
   </si>
   <si>
     <t xml:space="preserve">28.8322830200195</t>
   </si>
   <si>
-    <t xml:space="preserve">28.7758026123047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.9452610015869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.800012588501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.1389293670654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.388463973999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.4853000640869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.896842956543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.5833625793457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.6231002807617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.7441368103027</t>
+    <t xml:space="preserve">28.7758045196533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.9452571868896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.8000068664551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.1389274597168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.3884658813477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.4853057861328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.8968486785889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.5833644866943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.6230964660645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.744140625</t>
   </si>
   <si>
     <t xml:space="preserve">29.2680377960205</t>
   </si>
   <si>
-    <t xml:space="preserve">29.4375019073486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.4697799682617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.9371929168701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.4052219390869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.0749912261963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.8893966674805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.1072654724121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.3412857055664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.0265789031982</t>
+    <t xml:space="preserve">29.4375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.4697742462158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.9371948242188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.405216217041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.074987411499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.8894023895264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.107271194458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.3412780761719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.026575088501</t>
   </si>
   <si>
     <t xml:space="preserve">30.1798934936523</t>
@@ -1064,31 +1064,31 @@
     <t xml:space="preserve">29.2519016265869</t>
   </si>
   <si>
-    <t xml:space="preserve">28.4610977172852</t>
+    <t xml:space="preserve">28.4610958099365</t>
   </si>
   <si>
     <t xml:space="preserve">28.081823348999</t>
   </si>
   <si>
-    <t xml:space="preserve">28.5659980773926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.6386184692383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.2109355926514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.1544570922852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.436882019043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.2593593597412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.6063480377197</t>
+    <t xml:space="preserve">28.5659961700439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.6386203765869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.2109375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.1544551849365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.4368839263916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.2593517303467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.6063385009766</t>
   </si>
   <si>
     <t xml:space="preserve">28.3158397674561</t>
@@ -1097,28 +1097,28 @@
     <t xml:space="preserve">28.5902042388916</t>
   </si>
   <si>
-    <t xml:space="preserve">28.6547622680664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.1147155761719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.1308555603027</t>
+    <t xml:space="preserve">28.6547565460205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.114725112915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.1308631896973</t>
   </si>
   <si>
     <t xml:space="preserve">29.0663032531738</t>
   </si>
   <si>
-    <t xml:space="preserve">28.8080749511719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.6789646148682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.8565006256104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.6951065063477</t>
+    <t xml:space="preserve">28.8080825805664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.6789722442627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.8564929962158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.695104598999</t>
   </si>
   <si>
     <t xml:space="preserve">28.6305522918701</t>
@@ -1127,130 +1127,130 @@
     <t xml:space="preserve">28.7596645355225</t>
   </si>
   <si>
-    <t xml:space="preserve">28.2512798309326</t>
+    <t xml:space="preserve">28.2512874603271</t>
   </si>
   <si>
     <t xml:space="preserve">27.9769229888916</t>
   </si>
   <si>
-    <t xml:space="preserve">28.3561897277832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.4126739501953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.1786632537842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.2028675079346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.5337162017822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.2835578918457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.5982723236084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.5014419555664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.3804016113281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.7677345275879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.0340251922607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.332592010498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.2115478515625</t>
+    <t xml:space="preserve">28.3561935424805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.4126777648926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.1786556243896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.2028636932373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.533712387085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.2835655212402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.5982704162598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.5014400482178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.3803939819336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.7677326202393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.0340309143066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.3325958251953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.2115535736084</t>
   </si>
   <si>
     <t xml:space="preserve">29.1873474121094</t>
   </si>
   <si>
-    <t xml:space="preserve">29.3971576690674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.8409767150879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.0346450805664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.9942932128906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.0992050170898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.2202396392822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.8490428924561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.0830593109131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.405834197998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.5995063781738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.0352573394775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.5274982452393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.4387283325195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.3499755859375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.793794631958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.4710121154785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.7695846557617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.5839805603027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.8018589019775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.9067649841309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.9309749603271</t>
+    <t xml:space="preserve">29.3971519470215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.8409729003906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.0346393585205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.9943008422852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.0991973876953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.2202491760254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.849048614502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.0830554962158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.4058361053467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.5995044708252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.0352535247803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.527494430542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.4387340545654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.3499660491943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.7937984466553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.4710178375244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.7695789337158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.5839824676514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.8018608093262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.906759262085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.9309787750244</t>
   </si>
   <si>
     <t xml:space="preserve">32.1649894714355</t>
   </si>
   <si>
-    <t xml:space="preserve">32.1407852172852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.3425254821777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.1085014343262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.3586463928223</t>
+    <t xml:space="preserve">32.1407775878906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.3425216674805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.1084976196289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.3586540222168</t>
   </si>
   <si>
     <t xml:space="preserve">31.963249206543</t>
@@ -1259,43 +1259,43 @@
     <t xml:space="preserve">32.0116691589355</t>
   </si>
   <si>
-    <t xml:space="preserve">31.8986968994141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.0439453125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.2295417785645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.4232139587402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.9551811218262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.0358810424805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.1891937255859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.3667297363281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.2053375244141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.4877700805664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.1246452331543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.7621269226074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.6491546630859</t>
+    <t xml:space="preserve">31.8986930847168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.0439567565918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.2295379638672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.423210144043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.9551792144775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.0358695983887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.1891975402832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.3667221069336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.2053413391113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.4877662658691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.124641418457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.7621307373047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.6491584777832</t>
   </si>
   <si>
     <t xml:space="preserve">32.1004257202148</t>
@@ -1307,244 +1307,244 @@
     <t xml:space="preserve">31.4064540863037</t>
   </si>
   <si>
-    <t xml:space="preserve">31.3176898956299</t>
+    <t xml:space="preserve">31.3176956176758</t>
   </si>
   <si>
     <t xml:space="preserve">31.1563034057617</t>
   </si>
   <si>
-    <t xml:space="preserve">31.4145278930664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.8012447357178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.1805038452148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.6963424682617</t>
+    <t xml:space="preserve">31.4145259857178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.8012390136719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.1805095672607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.6963405609131</t>
   </si>
   <si>
     <t xml:space="preserve">31.2348728179932</t>
   </si>
   <si>
-    <t xml:space="preserve">31.275671005249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.1614284515381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.210391998291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.9982433319092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.9900875091553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.6963348388672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.8432083129883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.7045059204102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.916654586792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.6020469665527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.2593574523926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.0472011566162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.5612545013428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.5204563140869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.5857276916504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.8350582122803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.20676612854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.83957862854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.3944320678711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.3781070709229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.8477363586426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.7416610717773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.1904430389404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.4597187042236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.5086631774902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.2394027709961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.4352397918701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.2883605957031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.7616119384766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.3001518249512</t>
+    <t xml:space="preserve">31.2756671905518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.1614360809326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.2103900909424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.9982471466064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.990083694458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.6963386535645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.8432140350342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.704496383667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.9166488647461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.6020545959473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.2593555450439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.0471992492676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.56125831604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.5204544067383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.5857410430908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.8350563049316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.2067680358887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.8395843505859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.3944339752197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.3781147003174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.8477439880371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.7416667938232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.1904449462891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.4597148895264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.5086650848389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.2394065856934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.4352340698242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.2883567810059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.7616195678711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.3001461029053</t>
   </si>
   <si>
     <t xml:space="preserve">31.4307041168213</t>
   </si>
   <si>
-    <t xml:space="preserve">31.5775699615479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.3491039276123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.1695899963379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.4959754943848</t>
+    <t xml:space="preserve">31.5775718688965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.349100112915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.1695957183838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.4959812164307</t>
   </si>
   <si>
     <t xml:space="preserve">31.1043148040771</t>
   </si>
   <si>
-    <t xml:space="preserve">30.9411296844482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.549467086792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.7942523956299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.4633483886719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.8595371246338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.3327865600586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.3128395080566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.921178817749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.5540008544922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.7869987487793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.1505470275879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.1550807952881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.362699508667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.0780162811279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.1886253356934</t>
+    <t xml:space="preserve">30.9411239624023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.5494651794434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.7942562103271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.4633407592773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.8595352172852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.33278465271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.3128356933594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.9211769104004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.5539989471436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.786994934082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.1505527496338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.1550788879395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.3626956939697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.0780143737793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.1886234283447</t>
   </si>
   <si>
     <t xml:space="preserve">24.6337738037109</t>
   </si>
   <si>
-    <t xml:space="preserve">24.1686744689941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.3518142700195</t>
+    <t xml:space="preserve">24.1686763763428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.3518104553223</t>
   </si>
   <si>
     <t xml:space="preserve">25.0335922241211</t>
   </si>
   <si>
-    <t xml:space="preserve">25.4007682800293</t>
+    <t xml:space="preserve">25.4007701873779</t>
   </si>
   <si>
     <t xml:space="preserve">24.495059967041</t>
   </si>
   <si>
-    <t xml:space="preserve">24.0707626342773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.9075679779053</t>
+    <t xml:space="preserve">24.0707588195801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.9075660705566</t>
   </si>
   <si>
     <t xml:space="preserve">23.7117366790771</t>
   </si>
   <si>
-    <t xml:space="preserve">24.3971462249756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.2339496612549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.0299644470215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.7199001312256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.1405735015869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.5730266571045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.6464653015137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.4216175079346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.3155460357666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.5521793365479</t>
+    <t xml:space="preserve">24.3971424102783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.2339553833008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.0299625396729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.719898223877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.1405696868896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.5730228424072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.6464614868164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.4216213226318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.3155498504639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.552173614502</t>
   </si>
   <si>
     <t xml:space="preserve">24.2013149261475</t>
   </si>
   <si>
-    <t xml:space="preserve">23.7933330535889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.0626029968262</t>
+    <t xml:space="preserve">23.7933349609375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.0626010894775</t>
   </si>
   <si>
     <t xml:space="preserve">23.9238910675049</t>
@@ -1553,7 +1553,7 @@
     <t xml:space="preserve">23.7035808563232</t>
   </si>
   <si>
-    <t xml:space="preserve">23.3364009857178</t>
+    <t xml:space="preserve">23.3363971710205</t>
   </si>
   <si>
     <t xml:space="preserve">23.2384834289551</t>
@@ -1562,49 +1562,49 @@
     <t xml:space="preserve">23.1895275115967</t>
   </si>
   <si>
-    <t xml:space="preserve">23.1568908691406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.4551620483398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.8468189239502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.548547744751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.4624195098877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.087085723877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.3808212280273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.3563442230225</t>
+    <t xml:space="preserve">23.1568870544434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.4551677703857</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.8468246459961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.5485439300537</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.4624214172363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.0870780944824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.3808250427246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.3563480377197</t>
   </si>
   <si>
     <t xml:space="preserve">24.0952396392822</t>
   </si>
   <si>
-    <t xml:space="preserve">24.1278781890869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.9157238006592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.20947265625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.1523571014404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.3481884002686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.5551586151123</t>
+    <t xml:space="preserve">24.1278762817383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.9157257080078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.2094707489014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.1523590087891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.3481864929199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.5551605224609</t>
   </si>
   <si>
     <t xml:space="preserve">24.2902336120605</t>
@@ -1616,28 +1616,28 @@
     <t xml:space="preserve">24.4558124542236</t>
   </si>
   <si>
-    <t xml:space="preserve">24.5468788146973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.5403442382812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.308536529541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.3747673034668</t>
+    <t xml:space="preserve">24.5468807220459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.5403461456299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.3085346221924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.3747692108154</t>
   </si>
   <si>
     <t xml:space="preserve">25.5982990264893</t>
   </si>
   <si>
-    <t xml:space="preserve">25.3333778381348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.4244422912598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.151237487793</t>
+    <t xml:space="preserve">25.3333721160889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.4244384765625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.1512393951416</t>
   </si>
   <si>
     <t xml:space="preserve">25.2505836486816</t>
@@ -1646,40 +1646,40 @@
     <t xml:space="preserve">25.5320663452148</t>
   </si>
   <si>
-    <t xml:space="preserve">25.4161643981934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.9277114868164</t>
+    <t xml:space="preserve">25.4161605834961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.9277095794678</t>
   </si>
   <si>
     <t xml:space="preserve">26.6248760223389</t>
   </si>
   <si>
-    <t xml:space="preserve">26.4261856079102</t>
+    <t xml:space="preserve">26.4261875152588</t>
   </si>
   <si>
     <t xml:space="preserve">26.6828308105469</t>
   </si>
   <si>
-    <t xml:space="preserve">26.5503730773926</t>
+    <t xml:space="preserve">26.5503673553467</t>
   </si>
   <si>
     <t xml:space="preserve">26.5089740753174</t>
   </si>
   <si>
-    <t xml:space="preserve">26.5669269561768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.6000423431396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.2440509796143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.1115894317627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.2606105804443</t>
+    <t xml:space="preserve">26.5669250488281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.600040435791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.2440528869629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.1115913391113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.2606029510498</t>
   </si>
   <si>
     <t xml:space="preserve">26.3433952331543</t>
@@ -1688,70 +1688,70 @@
     <t xml:space="preserve">26.2937259674072</t>
   </si>
   <si>
-    <t xml:space="preserve">27.2540702819824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.3203067779541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.2789115905762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.9477519989014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.1298866271973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.1878452301025</t>
+    <t xml:space="preserve">27.2540683746338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.3203086853027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.2789096832275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.94775390625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.1298923492432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.1878414154053</t>
   </si>
   <si>
     <t xml:space="preserve">27.5686702728271</t>
   </si>
   <si>
-    <t xml:space="preserve">27.1961231231689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.0636596679688</t>
+    <t xml:space="preserve">27.1961193084717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.0636539459229</t>
   </si>
   <si>
     <t xml:space="preserve">27.7839241027832</t>
   </si>
   <si>
-    <t xml:space="preserve">28.5455780029297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.2806529998779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.346887588501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.5024394989014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.4527683258057</t>
+    <t xml:space="preserve">28.545581817627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.2806549072266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.3468894958496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.5024433135986</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.4527645111084</t>
   </si>
   <si>
     <t xml:space="preserve">27.8004817962646</t>
   </si>
   <si>
-    <t xml:space="preserve">27.7673625946045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.1978664398193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.6876201629639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.7024326324463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.0418720245361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.3399066925049</t>
+    <t xml:space="preserve">27.7673645019531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.197868347168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.6876182556152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.7024345397949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.0418701171875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.3399047851562</t>
   </si>
   <si>
     <t xml:space="preserve">24.803524017334</t>
@@ -1766,109 +1766,109 @@
     <t xml:space="preserve">25.6728076934814</t>
   </si>
   <si>
-    <t xml:space="preserve">25.358211517334</t>
+    <t xml:space="preserve">25.3582057952881</t>
   </si>
   <si>
     <t xml:space="preserve">25.4492778778076</t>
   </si>
   <si>
-    <t xml:space="preserve">24.8780326843262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.7538528442383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.861478805542</t>
+    <t xml:space="preserve">24.8780345916748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.7538509368896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.8614768981934</t>
   </si>
   <si>
     <t xml:space="preserve">25.8301048278809</t>
   </si>
   <si>
-    <t xml:space="preserve">25.6893653869629</t>
+    <t xml:space="preserve">25.6893672943115</t>
   </si>
   <si>
     <t xml:space="preserve">25.9046192169189</t>
   </si>
   <si>
-    <t xml:space="preserve">26.0619163513184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.0453586578369</t>
+    <t xml:space="preserve">26.0619125366211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.0453548431396</t>
   </si>
   <si>
     <t xml:space="preserve">25.7555999755859</t>
   </si>
   <si>
-    <t xml:space="preserve">25.9128932952881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.4758567810059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.5006942749023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.2357711791992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.5752048492432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.6993865966797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.9725971221924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.9891452789307</t>
+    <t xml:space="preserve">25.9128913879395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.4758548736572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.500696182251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.2357730865479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.5752010345459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.6993846893311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.9725952148438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.9891510009766</t>
   </si>
   <si>
     <t xml:space="preserve">26.8732452392578</t>
   </si>
   <si>
-    <t xml:space="preserve">26.4924144744873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.2274951934814</t>
+    <t xml:space="preserve">26.4924125671387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.2274913787842</t>
   </si>
   <si>
     <t xml:space="preserve">25.6396923065186</t>
   </si>
   <si>
-    <t xml:space="preserve">25.2754230499268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.590015411377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.4327182769775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.1926326751709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.9773807525635</t>
+    <t xml:space="preserve">25.2754192352295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.5900211334229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.4327220916748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.1926307678223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.9773826599121</t>
   </si>
   <si>
     <t xml:space="preserve">25.0022201538086</t>
   </si>
   <si>
-    <t xml:space="preserve">25.109842300415</t>
+    <t xml:space="preserve">25.1098403930664</t>
   </si>
   <si>
     <t xml:space="preserve">24.9691009521484</t>
   </si>
   <si>
-    <t xml:space="preserve">25.2423038482666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.159517288208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.2919769287109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.8863143920898</t>
+    <t xml:space="preserve">25.2423057556152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.1595134735107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.2919788360596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.8863124847412</t>
   </si>
   <si>
     <t xml:space="preserve">25.2588634490967</t>
@@ -1877,40 +1877,40 @@
     <t xml:space="preserve">24.811803817749</t>
   </si>
   <si>
-    <t xml:space="preserve">24.6296710968018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.6710643768311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.5634346008301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.3895797729492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.2985153198242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.1081008911133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.3067951202393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.4475326538086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.6131114959717</t>
+    <t xml:space="preserve">24.6296691894531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.6710624694824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.5634384155273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.3895778656006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.2985134124756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.1080989837646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.3067932128906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.4475345611572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.613109588623</t>
   </si>
   <si>
     <t xml:space="preserve">24.1412124633789</t>
   </si>
   <si>
-    <t xml:space="preserve">24.356466293335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.4889278411865</t>
+    <t xml:space="preserve">24.3564624786377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.4889316558838</t>
   </si>
   <si>
     <t xml:space="preserve">25.3830451965332</t>
@@ -1919,70 +1919,70 @@
     <t xml:space="preserve">25.1181240081787</t>
   </si>
   <si>
-    <t xml:space="preserve">24.720739364624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.8532009124756</t>
+    <t xml:space="preserve">24.7207355499268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.853199005127</t>
   </si>
   <si>
     <t xml:space="preserve">25.0187740325928</t>
   </si>
   <si>
-    <t xml:space="preserve">24.0915412902832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.9507999420166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.8183403015137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.0004749298096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.1494903564453</t>
+    <t xml:space="preserve">24.0915431976318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.9508018493652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.8183345794678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.0004768371582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.1494941711426</t>
   </si>
   <si>
     <t xml:space="preserve">24.5220432281494</t>
   </si>
   <si>
-    <t xml:space="preserve">24.8283596038818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.5882759094238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.6627826690674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.2488403320312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.0850028991699</t>
+    <t xml:space="preserve">24.8283615112305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.5882740020752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.662784576416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.248836517334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.0850067138672</t>
   </si>
   <si>
     <t xml:space="preserve">25.6065769195557</t>
   </si>
   <si>
-    <t xml:space="preserve">24.7704105377197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.9111518859863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.960823059082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.7952480316162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.9194278717041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.6958999633789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.0270576477051</t>
+    <t xml:space="preserve">24.7704086303711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.9111461639404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.9608249664307</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.7952461242676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.9194297790527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.6958980560303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.0270538330078</t>
   </si>
   <si>
     <t xml:space="preserve">24.7124576568604</t>
@@ -1994,13 +1994,13 @@
     <t xml:space="preserve">23.9425201416016</t>
   </si>
   <si>
-    <t xml:space="preserve">24.0087509155273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.1246566772461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.2087440490723</t>
+    <t xml:space="preserve">24.008752822876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.1246547698975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.208740234375</t>
   </si>
   <si>
     <t xml:space="preserve">23.8639850616455</t>
@@ -2009,31 +2009,31 @@
     <t xml:space="preserve">23.8555774688721</t>
   </si>
   <si>
-    <t xml:space="preserve">23.4855899810791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.4771842956543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.5360450744629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.3426456451416</t>
+    <t xml:space="preserve">23.4855880737305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.477180480957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.5360431671143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.3426418304443</t>
   </si>
   <si>
     <t xml:space="preserve">23.8892116546631</t>
   </si>
   <si>
-    <t xml:space="preserve">24.2171516418457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.1919288635254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.048978805542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.544454574585</t>
+    <t xml:space="preserve">24.2171535491943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.1919250488281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.0489826202393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.5444526672363</t>
   </si>
   <si>
     <t xml:space="preserve">23.6285419464111</t>
@@ -2045,346 +2045,346 @@
     <t xml:space="preserve">23.4603652954102</t>
   </si>
   <si>
-    <t xml:space="preserve">23.9060287475586</t>
+    <t xml:space="preserve">23.90602684021</t>
   </si>
   <si>
     <t xml:space="preserve">23.8808002471924</t>
   </si>
   <si>
-    <t xml:space="preserve">24.1330623626709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.385326385498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.5534992218018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.9318943023682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.478458404541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.0754833221436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.4700565338135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.2430210113525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.0580272674561</t>
+    <t xml:space="preserve">24.1330661773682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.3853282928467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.5535011291504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.9318981170654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.4784603118896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.0754852294922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.4700584411621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.2430152893066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.0580253601074</t>
   </si>
   <si>
     <t xml:space="preserve">25.3271064758301</t>
   </si>
   <si>
-    <t xml:space="preserve">25.0159854888916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.8898506164551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.1589317321777</t>
+    <t xml:space="preserve">25.0159816741943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.8898525238037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.1589298248291</t>
   </si>
   <si>
     <t xml:space="preserve">24.915075302124</t>
   </si>
   <si>
-    <t xml:space="preserve">25.7979965209961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.8568572998047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.9913921356201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.588415145874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.2352466583252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.8148136138916</t>
+    <t xml:space="preserve">25.7979946136475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.8568553924561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.9913940429688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.5884113311768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.2352485656738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.814811706543</t>
   </si>
   <si>
     <t xml:space="preserve">25.3691482543945</t>
   </si>
   <si>
-    <t xml:space="preserve">25.175745010376</t>
+    <t xml:space="preserve">25.1757469177246</t>
   </si>
   <si>
     <t xml:space="preserve">25.2009735107422</t>
   </si>
   <si>
-    <t xml:space="preserve">25.2766532897949</t>
+    <t xml:space="preserve">25.2766513824463</t>
   </si>
   <si>
     <t xml:space="preserve">25.587776184082</t>
   </si>
   <si>
-    <t xml:space="preserve">26.6052284240723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.386604309082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.0004425048828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.8749523162842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.8329086303711</t>
+    <t xml:space="preserve">26.6052322387695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.3866024017334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.0004463195801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.8749504089355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.8329105377197</t>
   </si>
   <si>
     <t xml:space="preserve">27.1433887481689</t>
   </si>
   <si>
-    <t xml:space="preserve">26.6556854248047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.9415855407715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.3115673065186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.1188068389893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.1860752105713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.4467525482178</t>
+    <t xml:space="preserve">26.6556873321533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.9415836334229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.3115653991699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.1188049316406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.1860771179199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.4467468261719</t>
   </si>
   <si>
     <t xml:space="preserve">28.556058883667</t>
   </si>
   <si>
-    <t xml:space="preserve">28.0431232452393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.1944789886475</t>
+    <t xml:space="preserve">28.0431251525879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.1944828033447</t>
   </si>
   <si>
     <t xml:space="preserve">27.7992744445801</t>
   </si>
   <si>
-    <t xml:space="preserve">27.6058692932129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.5806446075439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.8160934448242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.681547164917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.8076782226562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.0094966888428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.4635581970215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.5896911621094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.530834197998</t>
+    <t xml:space="preserve">27.6058731079102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.5806465148926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.8160915374756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.6815452575684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.8076858520508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.0094909667969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.4635620117188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.5897006988525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.5308322906494</t>
   </si>
   <si>
     <t xml:space="preserve">28.3962917327881</t>
   </si>
   <si>
-    <t xml:space="preserve">28.3626575469971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.9008159637451</t>
+    <t xml:space="preserve">28.3626594543457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.9008121490479</t>
   </si>
   <si>
     <t xml:space="preserve">29.0269451141357</t>
   </si>
   <si>
-    <t xml:space="preserve">29.3801136016846</t>
+    <t xml:space="preserve">29.3801116943359</t>
   </si>
   <si>
     <t xml:space="preserve">30.296667098999</t>
   </si>
   <si>
-    <t xml:space="preserve">30.4143924713135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.8348236083984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.9020919799805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.7423305511475</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.9687232971191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.0612239837646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.1789436340332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.9014587402344</t>
+    <t xml:space="preserve">30.4143867492676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.8348293304443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.9021015167236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.7423343658447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.968729019165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.0612201690674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.1789417266846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.901460647583</t>
   </si>
   <si>
     <t xml:space="preserve">28.8671836853027</t>
   </si>
   <si>
-    <t xml:space="preserve">29.1867160797119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.3885269165039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.926685333252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.1368980407715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.8341865539551</t>
+    <t xml:space="preserve">29.1867141723633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.388521194458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.9266815185547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.1369018554688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.8341884613037</t>
   </si>
   <si>
     <t xml:space="preserve">30.3471183776855</t>
   </si>
   <si>
-    <t xml:space="preserve">30.3891696929932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.1200828552246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.321891784668</t>
+    <t xml:space="preserve">30.38916015625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.120080947876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.3218936920166</t>
   </si>
   <si>
     <t xml:space="preserve">30.40598487854</t>
   </si>
   <si>
-    <t xml:space="preserve">30.5152969360352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.3555278778076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.8510093688965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.6181755065918</t>
+    <t xml:space="preserve">30.5152912139893</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.3555240631104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.8510036468506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.6181774139404</t>
   </si>
   <si>
     <t xml:space="preserve">30.2602691650391</t>
   </si>
   <si>
-    <t xml:space="preserve">30.2858371734619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.8567810058594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.6522674560547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.6693058013916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.8226890563965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.8397331237793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.2091388702393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.3880920410156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.0783462524414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.140962600708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.9705276489258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.8627147674561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.4081020355225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.1068840026855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.1720771789551</t>
+    <t xml:space="preserve">30.2858333587646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.856782913208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.6522655487061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.6693077087402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.8226909637451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.8397350311279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.209135055542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.388090133667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.0783443450928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.1409683227539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.970531463623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.8627243041992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.4081058502197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.106876373291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.1720809936523</t>
   </si>
   <si>
     <t xml:space="preserve">31.1379909515381</t>
   </si>
   <si>
-    <t xml:space="preserve">31.1465148925781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.5981636047363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.2572937011719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.8312129974365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.2658138275146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.9760856628418</t>
+    <t xml:space="preserve">31.1465167999268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.5981616973877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.257287979126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.8312187194824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.2658233642578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.9760837554932</t>
   </si>
   <si>
     <t xml:space="preserve">31.2061672210693</t>
   </si>
   <si>
-    <t xml:space="preserve">31.4021606445312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.4958972930908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.5299911499023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.9731121063232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.9645919799805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.3821487426758</t>
+    <t xml:space="preserve">31.4021625518799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.4959049224854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.529993057251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.9731101989746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.9645881652832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.3821411132812</t>
   </si>
   <si>
     <t xml:space="preserve">32.3480567932129</t>
   </si>
   <si>
-    <t xml:space="preserve">32.4673652648926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.450325012207</t>
+    <t xml:space="preserve">32.467357635498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.4503173828125</t>
   </si>
   <si>
     <t xml:space="preserve">32.0668525695801</t>
@@ -2396,73 +2396,73 @@
     <t xml:space="preserve">31.8708572387695</t>
   </si>
   <si>
-    <t xml:space="preserve">31.5725917816162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.0527801513672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.5129432678223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.7856407165527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.8623332977295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.9420013427734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.7630405426025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.2402496337891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.3510341644287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.69189453125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.0327606201172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.1520690917969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.5951919555664</t>
+    <t xml:space="preserve">31.5725994110107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.0527744293213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.5129451751709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.7856330871582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.8623371124268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.9419975280762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.7630386352539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.2402534484863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.3510398864746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.6919040679932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.0327644348145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.1520614624023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.5951957702637</t>
   </si>
   <si>
     <t xml:space="preserve">32.1435432434082</t>
   </si>
   <si>
-    <t xml:space="preserve">32.8252716064453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.8082275390625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.4899559020996</t>
+    <t xml:space="preserve">32.8252754211426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.8082313537598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.4899635314941</t>
   </si>
   <si>
     <t xml:space="preserve">33.5155296325684</t>
   </si>
   <si>
-    <t xml:space="preserve">33.4132614135742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.7882194519043</t>
+    <t xml:space="preserve">33.4132690429688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.788215637207</t>
   </si>
   <si>
     <t xml:space="preserve">33.7626495361328</t>
   </si>
   <si>
-    <t xml:space="preserve">33.8904762268066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.0268211364746</t>
+    <t xml:space="preserve">33.8904800415039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.0268249511719</t>
   </si>
   <si>
     <t xml:space="preserve">34.418815612793</t>
@@ -2471,70 +2471,70 @@
     <t xml:space="preserve">34.1716842651367</t>
   </si>
   <si>
-    <t xml:space="preserve">34.2483825683594</t>
+    <t xml:space="preserve">34.2483863830566</t>
   </si>
   <si>
     <t xml:space="preserve">34.2057762145996</t>
   </si>
   <si>
-    <t xml:space="preserve">33.9075164794922</t>
+    <t xml:space="preserve">33.9075202941895</t>
   </si>
   <si>
     <t xml:space="preserve">34.5381164550781</t>
   </si>
   <si>
-    <t xml:space="preserve">34.5551605224609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.7541351318359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.0894470214844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.1746673583984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.8308258056641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.9927368164062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.3877067565918</t>
+    <t xml:space="preserve">34.5551643371582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.7541313171387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.0894393920898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.1746635437012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.8308296203613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.992733001709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.3877029418945</t>
   </si>
   <si>
     <t xml:space="preserve">33.1150093078613</t>
   </si>
   <si>
-    <t xml:space="preserve">32.5525817871094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.0638732910156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.2854385375977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.9275283813477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.9586448669434</t>
+    <t xml:space="preserve">32.5525779724121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.0638809204102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.2854423522949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.9275360107422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.9586486816406</t>
   </si>
   <si>
     <t xml:space="preserve">33.6689186096191</t>
   </si>
   <si>
-    <t xml:space="preserve">34.0694389343262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.0012474060059</t>
+    <t xml:space="preserve">34.0694351196289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.0012550354004</t>
   </si>
   <si>
     <t xml:space="preserve">34.9130744934082</t>
   </si>
   <si>
-    <t xml:space="preserve">34.2995109558105</t>
+    <t xml:space="preserve">34.2995147705078</t>
   </si>
   <si>
     <t xml:space="preserve">33.9671745300293</t>
@@ -2546,58 +2546,58 @@
     <t xml:space="preserve">34.4784698486328</t>
   </si>
   <si>
-    <t xml:space="preserve">34.529598236084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.035343170166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.0523948669434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.5696258544922</t>
+    <t xml:space="preserve">34.5295944213867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.0353355407715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.0523910522461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.5696296691895</t>
   </si>
   <si>
     <t xml:space="preserve">33.6263046264648</t>
   </si>
   <si>
-    <t xml:space="preserve">32.544059753418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.1064872741699</t>
+    <t xml:space="preserve">32.5440521240234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.1064834594727</t>
   </si>
   <si>
     <t xml:space="preserve">33.6177787780762</t>
   </si>
   <si>
-    <t xml:space="preserve">33.8393478393555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.9160346984863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.302490234375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.6433448791504</t>
+    <t xml:space="preserve">33.8393440246582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.9160385131836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.3024864196777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.6433486938477</t>
   </si>
   <si>
     <t xml:space="preserve">33.5325622558594</t>
   </si>
   <si>
-    <t xml:space="preserve">33.5410919189453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.9360580444336</t>
+    <t xml:space="preserve">33.5410842895508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.9360542297363</t>
   </si>
   <si>
     <t xml:space="preserve">31.6578159332275</t>
   </si>
   <si>
-    <t xml:space="preserve">31.8282451629639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.3766021728516</t>
+    <t xml:space="preserve">31.8282432556152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.3765983581543</t>
   </si>
   <si>
     <t xml:space="preserve">31.8112010955811</t>
@@ -2606,31 +2606,31 @@
     <t xml:space="preserve">31.274341583252</t>
   </si>
   <si>
-    <t xml:space="preserve">31.5811157226562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.9305038452148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.5270080566406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.9219760894775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.1265068054199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.3425140380859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.1294689178467</t>
+    <t xml:space="preserve">31.5811195373535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.9305076599121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.5270118713379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.9219856262207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.1264991760254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.3425178527832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.1294746398926</t>
   </si>
   <si>
     <t xml:space="preserve">31.1550407409668</t>
   </si>
   <si>
-    <t xml:space="preserve">31.4106903076172</t>
+    <t xml:space="preserve">31.4106922149658</t>
   </si>
   <si>
     <t xml:space="preserve">31.6066875457764</t>
@@ -2639,31 +2639,31 @@
     <t xml:space="preserve">32.3991928100586</t>
   </si>
   <si>
-    <t xml:space="preserve">32.1009292602539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.1891326904297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.7174663543701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.4618148803711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.9390277862549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.8964157104492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.2372856140137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.2969360351562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.0725288391113</t>
+    <t xml:space="preserve">32.1009330749512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.1891250610352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.7174644470215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.4618110656738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.9390296936035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.8964176177979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.2372894287109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.296932220459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.0725326538086</t>
   </si>
   <si>
     <t xml:space="preserve">31.934440612793</t>
@@ -2672,121 +2672,121 @@
     <t xml:space="preserve">32.8752059936523</t>
   </si>
   <si>
-    <t xml:space="preserve">32.7112197875977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.089786529541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.3055686950684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.6162796020508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.210620880127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.8579521179199</t>
+    <t xml:space="preserve">32.7112159729004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.0897979736328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.3055648803711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.6162757873535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.2106246948242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.8579406738281</t>
   </si>
   <si>
     <t xml:space="preserve">31.2094402313232</t>
   </si>
   <si>
-    <t xml:space="preserve">31.6841354370117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.7445602416992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.589204788208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.5287761688232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.5793762207031</t>
+    <t xml:space="preserve">31.6841373443604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.7445583343506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.5891990661621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.5287837982178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.5793781280518</t>
   </si>
   <si>
     <t xml:space="preserve">31.0972366333008</t>
   </si>
   <si>
-    <t xml:space="preserve">31.2871131896973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.4597396850586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.4079494476318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.9862194061279</t>
+    <t xml:space="preserve">31.2871150970459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.45973777771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.4079475402832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.9862213134766</t>
   </si>
   <si>
     <t xml:space="preserve">32.573127746582</t>
   </si>
   <si>
-    <t xml:space="preserve">32.7543678283691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.4350357055664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.9701499938965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.7630043029785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.426399230957</t>
+    <t xml:space="preserve">32.7543716430664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.4350318908691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.9701461791992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.7630004882812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.4263954162598</t>
   </si>
   <si>
     <t xml:space="preserve">33.0823516845703</t>
   </si>
   <si>
-    <t xml:space="preserve">32.590389251709</t>
+    <t xml:space="preserve">32.5903816223145</t>
   </si>
   <si>
     <t xml:space="preserve">32.7025871276855</t>
   </si>
   <si>
-    <t xml:space="preserve">33.4793663024902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.4621124267578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.453483581543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.8505020141602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.3856201171875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.6778831481934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.0835380554199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.1612167358398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.5237121582031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.7999038696289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.7740135192871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.4632949829102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.2832298278809</t>
+    <t xml:space="preserve">33.4793701171875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.4621086120605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.4534721374512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.8505058288574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.3856163024902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.6778869628906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.0835418701172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.1612205505371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.5237159729004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.7999000549316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.7740058898926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.4633026123047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.2832336425781</t>
   </si>
   <si>
     <t xml:space="preserve">34.2561531066895</t>
@@ -2798,139 +2798,139 @@
     <t xml:space="preserve">33.9540710449219</t>
   </si>
   <si>
-    <t xml:space="preserve">34.5496063232422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.5409774780273</t>
+    <t xml:space="preserve">34.5496025085449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.5409736633301</t>
   </si>
   <si>
     <t xml:space="preserve">34.9552612304688</t>
   </si>
   <si>
-    <t xml:space="preserve">34.6877021789551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.0329399108887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.317756652832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.6543617248535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.3868064880371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.8257942199707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.4731101989746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.8442420959473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36.3879928588867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.0674629211426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.2204437255859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.3499031066895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.3424606323242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.3597259521484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.3844261169434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.203182220459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.8677673339844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.9713401794434</t>
+    <t xml:space="preserve">34.6877059936523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.0329360961914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.3177604675293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.654369354248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.3868141174316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.8258056640625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.4731140136719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.8442459106445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.3879890441895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.0674667358398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.2204399108887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.349910736084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.3424644470215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.3597297668457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.3844299316406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.2031860351562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.8677558898926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.9713287353516</t>
   </si>
   <si>
     <t xml:space="preserve">33.3067512512207</t>
   </si>
   <si>
-    <t xml:space="preserve">31.7790794372559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.6472396850586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.1984329223633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.3910026550293</t>
+    <t xml:space="preserve">31.7790775299072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.64723777771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.1984348297119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.3910045623779</t>
   </si>
   <si>
     <t xml:space="preserve">28.9567642211914</t>
   </si>
   <si>
-    <t xml:space="preserve">28.5597438812256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.4918804168701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.0356292724609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.4067630767822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.4153938293457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.1478309631348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.1835460662842</t>
+    <t xml:space="preserve">28.559741973877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.4918785095215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.0356311798096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.4067573547363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.4153881072998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.1478328704834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.1835479736328</t>
   </si>
   <si>
     <t xml:space="preserve">31.3734264373779</t>
   </si>
   <si>
-    <t xml:space="preserve">33.772819519043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.2636032104492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.5386009216309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.9615135192871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.99485206604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.4954490661621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.2537803649902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.7100276947021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.6076507568359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.2290687561035</t>
+    <t xml:space="preserve">33.7728157043457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.2635955810547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.5385971069336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.9615097045898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.9948577880859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.4954452514648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.2537841796875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.7100410461426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.6076393127441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.2290725708008</t>
   </si>
   <si>
     <t xml:space="preserve">33.039192199707</t>
@@ -2939,10 +2939,10 @@
     <t xml:space="preserve">32.5817527770996</t>
   </si>
   <si>
-    <t xml:space="preserve">33.4966354370117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.935619354248</t>
+    <t xml:space="preserve">33.4966316223145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.9356231689453</t>
   </si>
   <si>
     <t xml:space="preserve">33.3240165710449</t>
@@ -2951,64 +2951,64 @@
     <t xml:space="preserve">33.056453704834</t>
   </si>
   <si>
-    <t xml:space="preserve">33.7296714782715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.2573356628418</t>
+    <t xml:space="preserve">33.7296676635742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.2573432922363</t>
   </si>
   <si>
     <t xml:space="preserve">34.2388916015625</t>
   </si>
   <si>
-    <t xml:space="preserve">34.074893951416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.9466323852539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.4201469421387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.3091278076172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.732048034668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.9760818481445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.2165603637695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.7085189819336</t>
+    <t xml:space="preserve">34.0749053955078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.9466247558594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.4201431274414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.3091239929199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.7320518493652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.9760856628418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.2165679931641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.7085266113281</t>
   </si>
   <si>
     <t xml:space="preserve">36.5088233947754</t>
   </si>
   <si>
-    <t xml:space="preserve">38.7183494567871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.8231353759766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.6882820129395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36.2908134460449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.9589881896973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36.8147315979004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36.7623481750488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36.9719123840332</t>
+    <t xml:space="preserve">38.7183456420898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.8231315612793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.688289642334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.2908058166504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.958984375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.8147277832031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.7623405456543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.9719161987305</t>
   </si>
   <si>
     <t xml:space="preserve">36.0899696350098</t>
@@ -3017,25 +3017,25 @@
     <t xml:space="preserve">36.4829177856445</t>
   </si>
   <si>
-    <t xml:space="preserve">35.7319450378418</t>
+    <t xml:space="preserve">35.7319526672363</t>
   </si>
   <si>
     <t xml:space="preserve">35.4961853027344</t>
   </si>
   <si>
-    <t xml:space="preserve">35.9065933227539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.827995300293</t>
+    <t xml:space="preserve">35.9065971374512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.8280067443848</t>
   </si>
   <si>
     <t xml:space="preserve">36.3955955505371</t>
   </si>
   <si>
-    <t xml:space="preserve">36.1074295043945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.9939117431641</t>
+    <t xml:space="preserve">36.1074371337891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.9939193725586</t>
   </si>
   <si>
     <t xml:space="preserve">36.220947265625</t>
@@ -3044,22 +3044,22 @@
     <t xml:space="preserve">36.5789680480957</t>
   </si>
   <si>
-    <t xml:space="preserve">35.4001274108887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.417594909668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36.2820701599121</t>
+    <t xml:space="preserve">35.4001350402832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.4175987243652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.2820739746094</t>
   </si>
   <si>
     <t xml:space="preserve">37.1814880371094</t>
   </si>
   <si>
-    <t xml:space="preserve">39.5129661560059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.6222877502441</t>
+    <t xml:space="preserve">39.5129699707031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.6222915649414</t>
   </si>
   <si>
     <t xml:space="preserve">39.6352233886719</t>
@@ -3071,25 +3071,25 @@
     <t xml:space="preserve">40.2901306152344</t>
   </si>
   <si>
-    <t xml:space="preserve">39.2946739196777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.4605751037598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.2160758972168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.8144035339355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.6614151000977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.9321022033691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40.0281715393066</t>
+    <t xml:space="preserve">39.2946624755859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.460578918457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.2160797119141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.814395904541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.6614189147949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.9321174621582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40.0281753540039</t>
   </si>
   <si>
     <t xml:space="preserve">40.7267379760742</t>
@@ -3098,10 +3098,10 @@
     <t xml:space="preserve">40.1591491699219</t>
   </si>
   <si>
-    <t xml:space="preserve">40.1678771972656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40.2988662719727</t>
+    <t xml:space="preserve">40.1678886413574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40.2988624572754</t>
   </si>
   <si>
     <t xml:space="preserve">39.8185958862305</t>
@@ -3110,16 +3110,16 @@
     <t xml:space="preserve">40.7616691589355</t>
   </si>
   <si>
-    <t xml:space="preserve">41.0585594177246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.3903846740723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.5737571716309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.1937370300293</t>
+    <t xml:space="preserve">41.0585517883301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.390380859375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.5737533569336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.1937446594238</t>
   </si>
   <si>
     <t xml:space="preserve">42.577953338623</t>
@@ -3128,37 +3128,37 @@
     <t xml:space="preserve">42.2024765014648</t>
   </si>
   <si>
-    <t xml:space="preserve">41.6174163818359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.0365600585938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.0061683654785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.3205299377441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.3292541503906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.1371459960938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.8884544372559</t>
+    <t xml:space="preserve">41.6174201965332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.036563873291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.0061645507812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.3205223083496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.3292617797852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.137149810791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.8884506225586</t>
   </si>
   <si>
     <t xml:space="preserve">39.5042419433594</t>
   </si>
   <si>
-    <t xml:space="preserve">40.0019683837891</t>
+    <t xml:space="preserve">40.0019721984863</t>
   </si>
   <si>
     <t xml:space="preserve">39.0501670837402</t>
   </si>
   <si>
-    <t xml:space="preserve">38.9977684020996</t>
+    <t xml:space="preserve">38.9977798461914</t>
   </si>
   <si>
     <t xml:space="preserve">38.9628448486328</t>
@@ -3170,193 +3170,193 @@
     <t xml:space="preserve">38.8929862976074</t>
   </si>
   <si>
-    <t xml:space="preserve">40.3425331115723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.3557891845703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40.0718231201172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.836051940918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.5566253662109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40.2552070617676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40.6044921875</t>
+    <t xml:space="preserve">40.3425254821777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.3557929992676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40.0718307495117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.8360595703125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.5566368103027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40.2552032470703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40.6044883728027</t>
   </si>
   <si>
     <t xml:space="preserve">39.6439552307129</t>
   </si>
   <si>
-    <t xml:space="preserve">39.8797225952148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.5915603637695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.984504699707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.2422714233398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.7532768249512</t>
+    <t xml:space="preserve">39.8797149658203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.5915641784668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.9845085144043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.2422676086426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.7532691955566</t>
   </si>
   <si>
     <t xml:space="preserve">39.4693145751953</t>
   </si>
   <si>
-    <t xml:space="preserve">38.3690605163574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.4518394470215</t>
+    <t xml:space="preserve">38.3690567016602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.451847076416</t>
   </si>
   <si>
     <t xml:space="preserve">39.1636848449707</t>
   </si>
   <si>
-    <t xml:space="preserve">39.4169158935547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.4955024719238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.0589027404785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.7358055114746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.198616027832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.154956817627</t>
+    <t xml:space="preserve">39.4169235229492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.4955062866211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.0588912963867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.7358131408691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.1986083984375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.1549530029297</t>
   </si>
   <si>
     <t xml:space="preserve">39.0938262939453</t>
   </si>
   <si>
-    <t xml:space="preserve">39.2859306335449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.9715805053711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.1944122314453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.3253936767578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.5087738037109</t>
+    <t xml:space="preserve">39.2859382629395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.9715766906738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.1944198608398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.3253974914551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.5087661743164</t>
   </si>
   <si>
     <t xml:space="preserve">39.8535194396973</t>
   </si>
   <si>
-    <t xml:space="preserve">40.0107002258301</t>
+    <t xml:space="preserve">40.0107078552246</t>
   </si>
   <si>
     <t xml:space="preserve">40.7878608703613</t>
   </si>
   <si>
-    <t xml:space="preserve">40.4822425842285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40.5346336364746</t>
+    <t xml:space="preserve">40.4822387695312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40.5346298217773</t>
   </si>
   <si>
     <t xml:space="preserve">40.2639350891113</t>
   </si>
   <si>
-    <t xml:space="preserve">41.259407043457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40.7005424499512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.303050994873</t>
+    <t xml:space="preserve">41.2593955993652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40.7005348205566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.3030586242676</t>
   </si>
   <si>
     <t xml:space="preserve">40.9799690246582</t>
   </si>
   <si>
-    <t xml:space="preserve">41.6960067749023</t>
+    <t xml:space="preserve">41.6960105895996</t>
   </si>
   <si>
     <t xml:space="preserve">41.6785430908203</t>
   </si>
   <si>
-    <t xml:space="preserve">41.6698112487793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40.9537811279297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40.4560432434082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.8493347167969</t>
+    <t xml:space="preserve">41.6698150634766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40.9537696838379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40.4560508728027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.8493232727051</t>
   </si>
   <si>
     <t xml:space="preserve">37.356128692627</t>
   </si>
   <si>
-    <t xml:space="preserve">39.3383255004883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40.3687210083008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40.4385795593262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40.0980224609375</t>
+    <t xml:space="preserve">39.3383293151855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40.368724822998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40.4385833740234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40.098030090332</t>
   </si>
   <si>
     <t xml:space="preserve">38.8405914306641</t>
   </si>
   <si>
-    <t xml:space="preserve">39.8273239135742</t>
+    <t xml:space="preserve">39.827335357666</t>
   </si>
   <si>
     <t xml:space="preserve">40.0892906188965</t>
   </si>
   <si>
-    <t xml:space="preserve">41.2943344116211</t>
+    <t xml:space="preserve">41.2943267822266</t>
   </si>
   <si>
     <t xml:space="preserve">40.7965965270996</t>
   </si>
   <si>
-    <t xml:space="preserve">40.3250617980957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40.3949127197266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.7151947021484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.6911964416504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.2120170593262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.6004371643066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.9976806640625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.3973999023438</t>
+    <t xml:space="preserve">40.325065612793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40.3949165344238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.7151985168457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.6912040710449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.2120208740234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.6004409790039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.9976768493652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.3974075317383</t>
   </si>
   <si>
     <t xml:space="preserve">38.655891418457</t>
@@ -3365,19 +3365,19 @@
     <t xml:space="preserve">37.9938201904297</t>
   </si>
   <si>
-    <t xml:space="preserve">37.9055366516113</t>
+    <t xml:space="preserve">37.9055404663086</t>
   </si>
   <si>
     <t xml:space="preserve">38.1262283325195</t>
   </si>
   <si>
-    <t xml:space="preserve">38.5411338806152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.947193145752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.8147850036621</t>
+    <t xml:space="preserve">38.5411262512207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.9471969604492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.8147888183594</t>
   </si>
   <si>
     <t xml:space="preserve">38.8589248657227</t>
@@ -3389,16 +3389,16 @@
     <t xml:space="preserve">38.346923828125</t>
   </si>
   <si>
-    <t xml:space="preserve">39.1855430603027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.8500938415527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.2561645507812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.0972671508789</t>
+    <t xml:space="preserve">39.1855392456055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.8500900268555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.256160736084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.0972595214844</t>
   </si>
   <si>
     <t xml:space="preserve">39.4768447875977</t>
@@ -3410,22 +3410,22 @@
     <t xml:space="preserve">40.0153312683105</t>
   </si>
   <si>
-    <t xml:space="preserve">39.8652610778809</t>
+    <t xml:space="preserve">39.8652648925781</t>
   </si>
   <si>
     <t xml:space="preserve">38.4528541564941</t>
   </si>
   <si>
-    <t xml:space="preserve">37.0051307678223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.7731285095215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.8172721862793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.8349227905273</t>
+    <t xml:space="preserve">37.005126953125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.7731323242188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.817268371582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.8349304199219</t>
   </si>
   <si>
     <t xml:space="preserve">38.5058174133301</t>
@@ -3440,34 +3440,34 @@
     <t xml:space="preserve">38.5852661132812</t>
   </si>
   <si>
-    <t xml:space="preserve">38.4175453186035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.5612678527832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.6495513916016</t>
+    <t xml:space="preserve">38.4175491333008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.5612640380859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.6495475769043</t>
   </si>
   <si>
     <t xml:space="preserve">37.8967170715332</t>
   </si>
   <si>
-    <t xml:space="preserve">37.4465065002441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.5259590148926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.5171356201172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.1905136108398</t>
+    <t xml:space="preserve">37.4465141296387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.525951385498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.5171318054199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.1905097961426</t>
   </si>
   <si>
     <t xml:space="preserve">37.7113380432129</t>
   </si>
   <si>
-    <t xml:space="preserve">38.3822326660156</t>
+    <t xml:space="preserve">38.3822364807129</t>
   </si>
   <si>
     <t xml:space="preserve">38.9030532836914</t>
@@ -3482,64 +3482,64 @@
     <t xml:space="preserve">39.618091583252</t>
   </si>
   <si>
-    <t xml:space="preserve">40.0771255493164</t>
+    <t xml:space="preserve">40.0771331787109</t>
   </si>
   <si>
     <t xml:space="preserve">40.2360191345215</t>
   </si>
   <si>
-    <t xml:space="preserve">39.9447135925293</t>
+    <t xml:space="preserve">39.9447059631348</t>
   </si>
   <si>
     <t xml:space="preserve">39.9800224304199</t>
   </si>
   <si>
-    <t xml:space="preserve">39.5827865600586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.061954498291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.8412704467773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.6117515563965</t>
+    <t xml:space="preserve">39.5827789306641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.0619468688965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.8412628173828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.6117553710938</t>
   </si>
   <si>
     <t xml:space="preserve">38.6647109985352</t>
   </si>
   <si>
-    <t xml:space="preserve">37.3582382202148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.4729957580566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.8437461853027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.7819557189941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.1993408203125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.464168548584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.6671943664551</t>
+    <t xml:space="preserve">37.3582305908203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.4729995727539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.8437538146973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.7819595336914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.1993370056152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.4641723632812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.6672058105469</t>
   </si>
   <si>
     <t xml:space="preserve">37.9673347473145</t>
   </si>
   <si>
-    <t xml:space="preserve">38.5764465332031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.2674713134766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.5298156738281</t>
+    <t xml:space="preserve">38.5764427185059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.2674674987793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.5298080444336</t>
   </si>
   <si>
     <t xml:space="preserve">39.8564376831055</t>
@@ -3548,79 +3548,79 @@
     <t xml:space="preserve">39.1325759887695</t>
   </si>
   <si>
-    <t xml:space="preserve">39.8387832641602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.3091201782227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.9182281494141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.6710548400879</t>
+    <t xml:space="preserve">39.8387718200684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.3091278076172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.9182319641113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.6710510253906</t>
   </si>
   <si>
     <t xml:space="preserve">39.6622276306152</t>
   </si>
   <si>
-    <t xml:space="preserve">39.4945106506348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.9093971252441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40.1477432250977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.8917503356934</t>
+    <t xml:space="preserve">39.4945068359375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.9094009399414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40.1477470397949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.8917388916016</t>
   </si>
   <si>
     <t xml:space="preserve">39.8740882873535</t>
   </si>
   <si>
-    <t xml:space="preserve">40.2889862060547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40.4920196533203</t>
+    <t xml:space="preserve">40.2889823913574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40.4920234680176</t>
   </si>
   <si>
     <t xml:space="preserve">41.3836059570312</t>
   </si>
   <si>
-    <t xml:space="preserve">40.7480201721191</t>
+    <t xml:space="preserve">40.7480163574219</t>
   </si>
   <si>
     <t xml:space="preserve">40.5361557006836</t>
   </si>
   <si>
-    <t xml:space="preserve">40.1300926208496</t>
+    <t xml:space="preserve">40.1300888061523</t>
   </si>
   <si>
     <t xml:space="preserve">40.0506439208984</t>
   </si>
   <si>
-    <t xml:space="preserve">40.2183723449707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40.2007102966309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40.3596076965332</t>
+    <t xml:space="preserve">40.2183647155762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40.2007026672363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40.3596000671387</t>
   </si>
   <si>
     <t xml:space="preserve">40.5096778869629</t>
   </si>
   <si>
-    <t xml:space="preserve">40.5626449584961</t>
+    <t xml:space="preserve">40.5626373291016</t>
   </si>
   <si>
     <t xml:space="preserve">41.6042938232422</t>
   </si>
   <si>
-    <t xml:space="preserve">41.507194519043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.0834693908691</t>
+    <t xml:space="preserve">41.5071868896484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.0834655761719</t>
   </si>
   <si>
     <t xml:space="preserve">41.0128440856934</t>
@@ -3632,46 +3632,46 @@
     <t xml:space="preserve">40.6509170532227</t>
   </si>
   <si>
-    <t xml:space="preserve">40.3684272766113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40.4655380249023</t>
+    <t xml:space="preserve">40.3684349060059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40.4655456542969</t>
   </si>
   <si>
     <t xml:space="preserve">40.4302291870117</t>
   </si>
   <si>
-    <t xml:space="preserve">40.4831924438477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.7416763305664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.5474739074707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.6470642089844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.5676116943359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.8942375183105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.017822265625</t>
+    <t xml:space="preserve">40.4831962585449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.7416801452637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.5474700927734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.6470527648926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.5676155090332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.8942337036133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.0178146362305</t>
   </si>
   <si>
     <t xml:space="preserve">39.6975440979004</t>
   </si>
   <si>
-    <t xml:space="preserve">40.0065002441406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40.3331146240234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.0393333435059</t>
+    <t xml:space="preserve">40.0065040588379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40.3331260681152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.0393371582031</t>
   </si>
   <si>
     <t xml:space="preserve">41.128662109375</t>
@@ -3680,22 +3680,22 @@
     <t xml:space="preserve">41.378791809082</t>
   </si>
   <si>
-    <t xml:space="preserve">41.0393257141113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40.4854698181152</t>
+    <t xml:space="preserve">41.0393295288086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40.485466003418</t>
   </si>
   <si>
     <t xml:space="preserve">40.905330657959</t>
   </si>
   <si>
-    <t xml:space="preserve">40.637336730957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40.6016044616699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40.4050636291504</t>
+    <t xml:space="preserve">40.6373329162598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40.6016006469727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40.4050674438477</t>
   </si>
   <si>
     <t xml:space="preserve">40.8606643676758</t>
@@ -3713,25 +3713,25 @@
     <t xml:space="preserve">42.7009124755859</t>
   </si>
   <si>
-    <t xml:space="preserve">42.316780090332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.5311851501465</t>
+    <t xml:space="preserve">42.3167877197266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.5311813354492</t>
   </si>
   <si>
     <t xml:space="preserve">42.6205139160156</t>
   </si>
   <si>
-    <t xml:space="preserve">42.852783203125</t>
+    <t xml:space="preserve">42.8527793884277</t>
   </si>
   <si>
     <t xml:space="preserve">43.2458381652832</t>
   </si>
   <si>
-    <t xml:space="preserve">43.3262405395508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43.0314407348633</t>
+    <t xml:space="preserve">43.3262367248535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43.0314445495605</t>
   </si>
   <si>
     <t xml:space="preserve">42.951042175293</t>
@@ -3740,25 +3740,25 @@
     <t xml:space="preserve">42.486515045166</t>
   </si>
   <si>
-    <t xml:space="preserve">43.102912902832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43.120777130127</t>
+    <t xml:space="preserve">43.1029090881348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43.1207695007324</t>
   </si>
   <si>
     <t xml:space="preserve">43.2637100219727</t>
   </si>
   <si>
-    <t xml:space="preserve">43.2547760009766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43.0582389831543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43.540641784668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43.4781074523926</t>
+    <t xml:space="preserve">43.2547721862793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43.0582427978516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43.5406379699707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43.478099822998</t>
   </si>
   <si>
     <t xml:space="preserve">43.4602394104004</t>
@@ -3767,49 +3767,49 @@
     <t xml:space="preserve">44.755558013916</t>
   </si>
   <si>
-    <t xml:space="preserve">46.2206115722656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">44.8448944091797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.9888687133789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.2563438415527</t>
+    <t xml:space="preserve">46.2206192016602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44.8448905944824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.9888725280762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.25634765625</t>
   </si>
   <si>
     <t xml:space="preserve">45.8811454772949</t>
   </si>
   <si>
-    <t xml:space="preserve">45.1307525634766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.1486206054688</t>
+    <t xml:space="preserve">45.1307563781738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.148624420166</t>
   </si>
   <si>
     <t xml:space="preserve">44.6304931640625</t>
   </si>
   <si>
-    <t xml:space="preserve">44.4786262512207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.2200889587402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.3272895812988</t>
+    <t xml:space="preserve">44.478630065918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.220085144043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.3272857666016</t>
   </si>
   <si>
     <t xml:space="preserve">45.7739524841309</t>
   </si>
   <si>
-    <t xml:space="preserve">45.2915534973145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.5595474243164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.4528770446777</t>
+    <t xml:space="preserve">45.2915496826172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.5595512390137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.4528732299805</t>
   </si>
   <si>
     <t xml:space="preserve">45.9883460998535</t>
@@ -3821,28 +3821,28 @@
     <t xml:space="preserve">47.0424690246582</t>
   </si>
   <si>
-    <t xml:space="preserve">47.6141891479492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">48.1501960754395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">48.0608558654785</t>
+    <t xml:space="preserve">47.614200592041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">48.1501922607422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">48.060863494873</t>
   </si>
   <si>
     <t xml:space="preserve">49.0792427062988</t>
   </si>
   <si>
-    <t xml:space="preserve">49.043514251709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50.1869735717773</t>
+    <t xml:space="preserve">49.0435180664062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50.1869697570801</t>
   </si>
   <si>
     <t xml:space="preserve">50.4192352294922</t>
   </si>
   <si>
-    <t xml:space="preserve">50.7765655517578</t>
+    <t xml:space="preserve">50.7765693664551</t>
   </si>
   <si>
     <t xml:space="preserve">51.0624313354492</t>
@@ -3860,13 +3860,13 @@
     <t xml:space="preserve">51.3125610351562</t>
   </si>
   <si>
-    <t xml:space="preserve">50.6693725585938</t>
+    <t xml:space="preserve">50.6693649291992</t>
   </si>
   <si>
     <t xml:space="preserve">49.9904403686523</t>
   </si>
   <si>
-    <t xml:space="preserve">49.5795097351074</t>
+    <t xml:space="preserve">49.5795135498047</t>
   </si>
   <si>
     <t xml:space="preserve">50.151237487793</t>
@@ -3875,13 +3875,13 @@
     <t xml:space="preserve">49.9011077880859</t>
   </si>
   <si>
-    <t xml:space="preserve">49.633113861084</t>
+    <t xml:space="preserve">49.6331062316895</t>
   </si>
   <si>
     <t xml:space="preserve">49.7581787109375</t>
   </si>
   <si>
-    <t xml:space="preserve">49.543773651123</t>
+    <t xml:space="preserve">49.5437812805176</t>
   </si>
   <si>
     <t xml:space="preserve">49.954704284668</t>
@@ -3890,10 +3890,10 @@
     <t xml:space="preserve">48.8291206359863</t>
   </si>
   <si>
-    <t xml:space="preserve">48.1144561767578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">47.2568664550781</t>
+    <t xml:space="preserve">48.1144599914551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">47.2568702697754</t>
   </si>
   <si>
     <t xml:space="preserve">46.9531402587891</t>
@@ -3902,13 +3902,13 @@
     <t xml:space="preserve">46.8816719055176</t>
   </si>
   <si>
-    <t xml:space="preserve">45.6488800048828</t>
+    <t xml:space="preserve">45.6488838195801</t>
   </si>
   <si>
     <t xml:space="preserve">46.3278121948242</t>
   </si>
   <si>
-    <t xml:space="preserve">45.2022247314453</t>
+    <t xml:space="preserve">45.202220916748</t>
   </si>
   <si>
     <t xml:space="preserve">44.6840972900391</t>
@@ -3920,61 +3920,61 @@
     <t xml:space="preserve">45.1843566894531</t>
   </si>
   <si>
-    <t xml:space="preserve">45.7203483581543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.4344902038574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43.7014389038086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43.763973236084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">44.9163589477539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">44.1034317016602</t>
+    <t xml:space="preserve">45.720344543457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.4344825744629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43.7014350891113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43.7639694213867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44.9163551330566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44.1034355163574</t>
   </si>
   <si>
     <t xml:space="preserve">43.6925010681152</t>
   </si>
   <si>
-    <t xml:space="preserve">43.9426307678223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43.7461013793945</t>
+    <t xml:space="preserve">43.9426345825195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43.7461051940918</t>
   </si>
   <si>
     <t xml:space="preserve">43.6746368408203</t>
   </si>
   <si>
-    <t xml:space="preserve">44.1391639709473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">44.2731704711914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.4166221618652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.6846199035645</t>
+    <t xml:space="preserve">44.13916015625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44.2731666564941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.416618347168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.6846160888672</t>
   </si>
   <si>
     <t xml:space="preserve">45.6310195922852</t>
   </si>
   <si>
-    <t xml:space="preserve">45.916877746582</t>
+    <t xml:space="preserve">45.9168815612793</t>
   </si>
   <si>
     <t xml:space="preserve">46.1848793029785</t>
   </si>
   <si>
-    <t xml:space="preserve">46.4886054992676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">47.0960731506348</t>
+    <t xml:space="preserve">46.4886131286621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">47.096076965332</t>
   </si>
   <si>
     <t xml:space="preserve">46.8280715942383</t>
@@ -3989,13 +3989,13 @@
     <t xml:space="preserve">49.2043190002441</t>
   </si>
   <si>
-    <t xml:space="preserve">50.3120307922363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50.4728355407715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50.3299026489258</t>
+    <t xml:space="preserve">50.3120384216309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50.4728317260742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50.329906463623</t>
   </si>
   <si>
     <t xml:space="preserve">50.0261764526367</t>
@@ -4004,16 +4004,16 @@
     <t xml:space="preserve">50.2227058410645</t>
   </si>
   <si>
-    <t xml:space="preserve">50.4371032714844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">51.0802955627441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50.6515045166016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50.1154975891113</t>
+    <t xml:space="preserve">50.4370956420898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">51.0802993774414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50.651496887207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50.1155052185059</t>
   </si>
   <si>
     <t xml:space="preserve">49.1685829162598</t>
@@ -4031,28 +4031,28 @@
     <t xml:space="preserve">50.1209754943848</t>
   </si>
   <si>
-    <t xml:space="preserve">50.4997291564941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">49.3815078735352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">49.5618667602539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">49.9947204589844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">49.6159782409668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">48.4436645507812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">48.1911659240723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">48.5338439941406</t>
+    <t xml:space="preserve">50.4997215270996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">49.3815116882324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">49.5618705749512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">49.9947166442871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">49.6159744262695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">48.4436683654785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">48.191162109375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">48.5338363647461</t>
   </si>
   <si>
     <t xml:space="preserve">49.8324012756348</t>
@@ -4061,28 +4061,28 @@
     <t xml:space="preserve">48.6420516967773</t>
   </si>
   <si>
-    <t xml:space="preserve">48.6240196228027</t>
+    <t xml:space="preserve">48.6240119934082</t>
   </si>
   <si>
     <t xml:space="preserve">48.2993774414062</t>
   </si>
   <si>
-    <t xml:space="preserve">49.0027694702148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">48.2092018127441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">49.4716949462891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">49.7602653503418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50.0668716430664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50.1029472351074</t>
+    <t xml:space="preserve">49.0027618408203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">48.2091979980469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">49.4716873168945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">49.7602615356445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50.0668678283691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50.1029396057129</t>
   </si>
   <si>
     <t xml:space="preserve">50.9686470031738</t>
@@ -4094,19 +4094,19 @@
     <t xml:space="preserve">50.445613861084</t>
   </si>
   <si>
-    <t xml:space="preserve">50.8243637084961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50.9866828918457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50.9506149291992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50.084903717041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">49.2552642822266</t>
+    <t xml:space="preserve">50.8243675231934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50.986686706543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50.950611114502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50.0849075317383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">49.2552604675293</t>
   </si>
   <si>
     <t xml:space="preserve">49.2913360595703</t>
@@ -4115,52 +4115,52 @@
     <t xml:space="preserve">49.0208015441895</t>
   </si>
   <si>
-    <t xml:space="preserve">48.7683029174805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">49.1290130615234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">49.5257987976074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">48.3174171447754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">47.0909881591797</t>
+    <t xml:space="preserve">48.7683067321777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">49.129020690918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">49.5257949829102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">48.3174133300781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">47.090991973877</t>
   </si>
   <si>
     <t xml:space="preserve">46.1711769104004</t>
   </si>
   <si>
-    <t xml:space="preserve">46.8926010131836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.441707611084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.5579643249512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.0439453125</t>
+    <t xml:space="preserve">46.8925933837891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.4417114257812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.5579681396484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.0439491271973</t>
   </si>
   <si>
     <t xml:space="preserve">44.6201133728027</t>
   </si>
   <si>
-    <t xml:space="preserve">44.6471633911133</t>
+    <t xml:space="preserve">44.647159576416</t>
   </si>
   <si>
     <t xml:space="preserve">44.6742210388184</t>
   </si>
   <si>
-    <t xml:space="preserve">44.8726081848145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.0529670715332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43.7724342346191</t>
+    <t xml:space="preserve">44.8726005554199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.0529632568359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43.7724380493164</t>
   </si>
   <si>
     <t xml:space="preserve">42.6993179321289</t>
@@ -4178,31 +4178,31 @@
     <t xml:space="preserve">41.3015556335449</t>
   </si>
   <si>
-    <t xml:space="preserve">40.9408493041992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40.3817405700684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.2564697265625</t>
+    <t xml:space="preserve">40.9408531188965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40.3817367553711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.2564735412598</t>
   </si>
   <si>
     <t xml:space="preserve">41.0400390625</t>
   </si>
   <si>
-    <t xml:space="preserve">41.3105735778809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.6622695922852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.581111907959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.7434310913086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.5720901489258</t>
+    <t xml:space="preserve">41.3105812072754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.6622734069824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.5811080932617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.7434272766113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.572093963623</t>
   </si>
   <si>
     <t xml:space="preserve">39.0921936035156</t>
@@ -4211,151 +4211,151 @@
     <t xml:space="preserve">40.2645111083984</t>
   </si>
   <si>
-    <t xml:space="preserve">39.4619178771973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.2715721130371</t>
+    <t xml:space="preserve">39.4619216918945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.2715797424316</t>
   </si>
   <si>
     <t xml:space="preserve">38.929874420166</t>
   </si>
   <si>
-    <t xml:space="preserve">38.6232681274414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.9198722839355</t>
+    <t xml:space="preserve">38.6232719421387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.9198799133301</t>
   </si>
   <si>
     <t xml:space="preserve">37.7395248413086</t>
   </si>
   <si>
-    <t xml:space="preserve">36.386848449707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.894775390625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.7946090698242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.2545166015625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40.3997764587402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.8496894836426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40.9678993225098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.1753044128418</t>
+    <t xml:space="preserve">36.3868560791016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.8947792053223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.794605255127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.2545127868652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40.399772644043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.8496856689453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40.967903137207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.1753082275391</t>
   </si>
   <si>
     <t xml:space="preserve">41.1662940979004</t>
   </si>
   <si>
-    <t xml:space="preserve">41.2294158935547</t>
+    <t xml:space="preserve">41.2294120788574</t>
   </si>
   <si>
     <t xml:space="preserve">41.6261978149414</t>
   </si>
   <si>
-    <t xml:space="preserve">41.3646812438965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40.9588813781738</t>
+    <t xml:space="preserve">41.3646850585938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40.9588775634766</t>
   </si>
   <si>
     <t xml:space="preserve">40.5891494750977</t>
   </si>
   <si>
-    <t xml:space="preserve">42.3566398620605</t>
+    <t xml:space="preserve">42.3566474914551</t>
   </si>
   <si>
     <t xml:space="preserve">42.2754859924316</t>
   </si>
   <si>
-    <t xml:space="preserve">41.1572761535645</t>
+    <t xml:space="preserve">41.1572685241699</t>
   </si>
   <si>
     <t xml:space="preserve">42.5911026000977</t>
   </si>
   <si>
-    <t xml:space="preserve">44.0790481567383</t>
+    <t xml:space="preserve">44.079044342041</t>
   </si>
   <si>
     <t xml:space="preserve">43.0870819091797</t>
   </si>
   <si>
-    <t xml:space="preserve">44.2954635620117</t>
+    <t xml:space="preserve">44.295467376709</t>
   </si>
   <si>
     <t xml:space="preserve">44.3766288757324</t>
   </si>
   <si>
-    <t xml:space="preserve">43.8445854187012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.9969062805176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43.3846664428711</t>
+    <t xml:space="preserve">43.8445816040039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.9969024658203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43.3846740722656</t>
   </si>
   <si>
     <t xml:space="preserve">43.4568099975586</t>
   </si>
   <si>
-    <t xml:space="preserve">43.4117202758789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43.9167289733887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43.1772689819336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.7163734436035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.1843299865723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40.5350456237793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40.3366470336914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.472900390625</t>
+    <t xml:space="preserve">43.4117279052734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43.9167175292969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43.1772613525391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.716381072998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.184326171875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40.5350494384766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40.3366546630859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.4728927612305</t>
   </si>
   <si>
     <t xml:space="preserve">40.1021881103516</t>
   </si>
   <si>
-    <t xml:space="preserve">39.1282653808594</t>
+    <t xml:space="preserve">39.1282691955566</t>
   </si>
   <si>
     <t xml:space="preserve">38.6322860717773</t>
   </si>
   <si>
-    <t xml:space="preserve">37.9739875793457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.3697891235352</t>
+    <t xml:space="preserve">37.9739837646484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.369800567627</t>
   </si>
   <si>
     <t xml:space="preserve">38.2445220947266</t>
   </si>
   <si>
-    <t xml:space="preserve">37.8838005065918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.9810562133789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.2796211242676</t>
+    <t xml:space="preserve">37.8838081359863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.9810523986816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.2796173095703</t>
   </si>
   <si>
     <t xml:space="preserve">37.721492767334</t>
@@ -4364,34 +4364,34 @@
     <t xml:space="preserve">37.7575607299805</t>
   </si>
   <si>
-    <t xml:space="preserve">37.2976531982422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.4329147338867</t>
+    <t xml:space="preserve">37.2976493835449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.432918548584</t>
   </si>
   <si>
     <t xml:space="preserve">38.3797912597656</t>
   </si>
   <si>
-    <t xml:space="preserve">38.6905555725098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.9319190979004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.8222389221191</t>
+    <t xml:space="preserve">38.690559387207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.9319229125977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.8222427368164</t>
   </si>
   <si>
     <t xml:space="preserve">38.2152633666992</t>
   </si>
   <si>
-    <t xml:space="preserve">38.4711990356445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.1110076904297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.0964431762695</t>
+    <t xml:space="preserve">38.4711952209473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.111011505127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.0964393615723</t>
   </si>
   <si>
     <t xml:space="preserve">37.255542755127</t>
@@ -4403,19 +4403,19 @@
     <t xml:space="preserve">36.1404342651367</t>
   </si>
   <si>
-    <t xml:space="preserve">36.4146385192871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.8662338256836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36.0673141479492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.4092254638672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.8462409973145</t>
+    <t xml:space="preserve">36.4146347045898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.8662300109863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.067310333252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.4092216491699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.8462448120117</t>
   </si>
   <si>
     <t xml:space="preserve">34.3398094177246</t>
@@ -4424,19 +4424,19 @@
     <t xml:space="preserve">34.3489532470703</t>
   </si>
   <si>
-    <t xml:space="preserve">34.5683174133301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.4769172668457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.6651458740234</t>
+    <t xml:space="preserve">34.5683212280273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.4769134521484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.6651420593262</t>
   </si>
   <si>
     <t xml:space="preserve">36.0490341186523</t>
   </si>
   <si>
-    <t xml:space="preserve">34.8242454528809</t>
+    <t xml:space="preserve">34.8242416381836</t>
   </si>
   <si>
     <t xml:space="preserve">34.284969329834</t>
@@ -4445,55 +4445,55 @@
     <t xml:space="preserve">35.5463256835938</t>
   </si>
   <si>
-    <t xml:space="preserve">38.2609634399414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.5754470825195</t>
+    <t xml:space="preserve">38.2609672546387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.5754508972168</t>
   </si>
   <si>
     <t xml:space="preserve">37.6394309997559</t>
   </si>
   <si>
-    <t xml:space="preserve">37.9045028686523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.9410552978516</t>
+    <t xml:space="preserve">37.9044952392578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.9410591125488</t>
   </si>
   <si>
     <t xml:space="preserve">39.3395118713379</t>
   </si>
   <si>
-    <t xml:space="preserve">39.321231842041</t>
+    <t xml:space="preserve">39.3212280273438</t>
   </si>
   <si>
     <t xml:space="preserve">39.2206878662109</t>
   </si>
   <si>
-    <t xml:space="preserve">39.5223159790039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.769100189209</t>
+    <t xml:space="preserve">39.5223197937012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.7691040039062</t>
   </si>
   <si>
     <t xml:space="preserve">39.7782440185547</t>
   </si>
   <si>
-    <t xml:space="preserve">40.0433158874512</t>
+    <t xml:space="preserve">40.0433082580566</t>
   </si>
   <si>
     <t xml:space="preserve">39.4766120910645</t>
   </si>
   <si>
-    <t xml:space="preserve">39.3029518127441</t>
+    <t xml:space="preserve">39.3029479980469</t>
   </si>
   <si>
     <t xml:space="preserve">38.5351715087891</t>
   </si>
   <si>
-    <t xml:space="preserve">39.28466796875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.4400520324707</t>
+    <t xml:space="preserve">39.2846717834473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.4400596618652</t>
   </si>
   <si>
     <t xml:space="preserve">39.6776962280273</t>
@@ -4511,7 +4511,7 @@
     <t xml:space="preserve">38.8185195922852</t>
   </si>
   <si>
-    <t xml:space="preserve">38.5625915527344</t>
+    <t xml:space="preserve">38.5625839233398</t>
   </si>
   <si>
     <t xml:space="preserve">38.1147232055664</t>
@@ -4529,7 +4529,7 @@
     <t xml:space="preserve">39.7965240478516</t>
   </si>
   <si>
-    <t xml:space="preserve">38.7271194458008</t>
+    <t xml:space="preserve">38.7271156311035</t>
   </si>
   <si>
     <t xml:space="preserve">38.6174354553223</t>
@@ -4538,10 +4538,10 @@
     <t xml:space="preserve">38.0873031616211</t>
   </si>
   <si>
-    <t xml:space="preserve">39.0835876464844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.1567115783691</t>
+    <t xml:space="preserve">39.0835838317871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.1567039489746</t>
   </si>
   <si>
     <t xml:space="preserve">38.6357154846191</t>
@@ -4550,22 +4550,22 @@
     <t xml:space="preserve">38.6631355285645</t>
   </si>
   <si>
-    <t xml:space="preserve">38.443775177002</t>
+    <t xml:space="preserve">38.4437713623047</t>
   </si>
   <si>
     <t xml:space="preserve">38.7636795043945</t>
   </si>
   <si>
-    <t xml:space="preserve">39.5680198669434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40.2261161804199</t>
+    <t xml:space="preserve">39.5680160522461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40.2261085510254</t>
   </si>
   <si>
     <t xml:space="preserve">39.8787879943848</t>
   </si>
   <si>
-    <t xml:space="preserve">40.4454803466797</t>
+    <t xml:space="preserve">40.4454765319824</t>
   </si>
   <si>
     <t xml:space="preserve">39.8330879211426</t>
@@ -4583,19 +4583,19 @@
     <t xml:space="preserve">37.2372627258301</t>
   </si>
   <si>
-    <t xml:space="preserve">37.1915588378906</t>
+    <t xml:space="preserve">37.1915626525879</t>
   </si>
   <si>
     <t xml:space="preserve">37.8313789367676</t>
   </si>
   <si>
-    <t xml:space="preserve">36.7619667053223</t>
+    <t xml:space="preserve">36.7619743347168</t>
   </si>
   <si>
     <t xml:space="preserve">37.3743667602539</t>
   </si>
   <si>
-    <t xml:space="preserve">37.0087585449219</t>
+    <t xml:space="preserve">37.0087547302246</t>
   </si>
   <si>
     <t xml:space="preserve">37.4657707214355</t>
@@ -4604,19 +4604,19 @@
     <t xml:space="preserve">37.1367225646973</t>
   </si>
   <si>
-    <t xml:space="preserve">37.5937309265137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.0453186035156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36.6522827148438</t>
+    <t xml:space="preserve">37.5937271118164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.0453147888184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.652286529541</t>
   </si>
   <si>
     <t xml:space="preserve">36.7071304321289</t>
   </si>
   <si>
-    <t xml:space="preserve">36.3415145874023</t>
+    <t xml:space="preserve">36.3415222167969</t>
   </si>
   <si>
     <t xml:space="preserve">36.1769943237305</t>
@@ -4628,103 +4628,103 @@
     <t xml:space="preserve">35.6011619567871</t>
   </si>
   <si>
-    <t xml:space="preserve">33.9102249145508</t>
+    <t xml:space="preserve">33.9102172851562</t>
   </si>
   <si>
     <t xml:space="preserve">33.3161087036133</t>
   </si>
   <si>
-    <t xml:space="preserve">34.0930213928223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.5811729431152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.4494972229004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.1532859802246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.9961929321289</t>
+    <t xml:space="preserve">34.0930252075195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.5811767578125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.4494934082031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.1532936096191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.9961967468262</t>
   </si>
   <si>
     <t xml:space="preserve">32.2649803161621</t>
   </si>
   <si>
-    <t xml:space="preserve">32.3198204040527</t>
+    <t xml:space="preserve">32.31982421875</t>
   </si>
   <si>
     <t xml:space="preserve">32.7494163513184</t>
   </si>
   <si>
-    <t xml:space="preserve">32.4752082824707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.3929405212402</t>
+    <t xml:space="preserve">32.4752006530762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.3929443359375</t>
   </si>
   <si>
     <t xml:space="preserve">33.4257926940918</t>
   </si>
   <si>
-    <t xml:space="preserve">33.6360092163086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.6542892456055</t>
+    <t xml:space="preserve">33.6360168457031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.6542930603027</t>
   </si>
   <si>
     <t xml:space="preserve">32.8590965270996</t>
   </si>
   <si>
-    <t xml:space="preserve">32.9596405029297</t>
+    <t xml:space="preserve">32.9596366882324</t>
   </si>
   <si>
     <t xml:space="preserve">32.4020843505859</t>
   </si>
   <si>
-    <t xml:space="preserve">33.5171890258789</t>
+    <t xml:space="preserve">33.5171852111816</t>
   </si>
   <si>
     <t xml:space="preserve">34.6688613891602</t>
   </si>
   <si>
-    <t xml:space="preserve">34.7328414916992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.4586334228516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.0710296630859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.7602615356445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.805965423584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.1624298095703</t>
+    <t xml:space="preserve">34.7328338623047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.4586372375488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.0710258483887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.7602653503418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.8059616088867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.1624336242676</t>
   </si>
   <si>
     <t xml:space="preserve">34.6048812866211</t>
   </si>
   <si>
-    <t xml:space="preserve">35.171573638916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.6140174865723</t>
+    <t xml:space="preserve">35.1715698242188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.6140213012695</t>
   </si>
   <si>
     <t xml:space="preserve">35.144157409668</t>
   </si>
   <si>
-    <t xml:space="preserve">37.0910186767578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.9593391418457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.2463989257812</t>
+    <t xml:space="preserve">37.0910224914551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.9593353271484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.2464027404785</t>
   </si>
   <si>
     <t xml:space="preserve">36.8168067932129</t>
@@ -4733,16 +4733,16 @@
     <t xml:space="preserve">36.4055061340332</t>
   </si>
   <si>
-    <t xml:space="preserve">35.9393463134766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.8296699523926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36.0947380065918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36.2152366638184</t>
+    <t xml:space="preserve">35.9393501281738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.829662322998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.0947341918945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.2152328491211</t>
   </si>
   <si>
     <t xml:space="preserve">35.7981147766113</t>
@@ -4751,49 +4751,49 @@
     <t xml:space="preserve">36.2893943786621</t>
   </si>
   <si>
-    <t xml:space="preserve">37.2626724243164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.2904777526855</t>
+    <t xml:space="preserve">37.2626647949219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.2904739379883</t>
   </si>
   <si>
     <t xml:space="preserve">37.2533988952637</t>
   </si>
   <si>
-    <t xml:space="preserve">37.0865516662598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.670524597168</t>
+    <t xml:space="preserve">37.0865478515625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.6705169677734</t>
   </si>
   <si>
     <t xml:space="preserve">38.5603713989258</t>
   </si>
   <si>
-    <t xml:space="preserve">38.4584121704102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.3749847412109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.4665946960449</t>
+    <t xml:space="preserve">38.4584083557129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.3749923706055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.4665908813477</t>
   </si>
   <si>
     <t xml:space="preserve">37.5407485961914</t>
   </si>
   <si>
-    <t xml:space="preserve">37.8559074401855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.8291816711426</t>
+    <t xml:space="preserve">37.8559036254883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.8291854858398</t>
   </si>
   <si>
     <t xml:space="preserve">38.8199157714844</t>
   </si>
   <si>
-    <t xml:space="preserve">38.5881805419922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.4944076538086</t>
+    <t xml:space="preserve">38.5881881713867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.4944038391113</t>
   </si>
   <si>
     <t xml:space="preserve">36.7065086364746</t>
@@ -4802,25 +4802,25 @@
     <t xml:space="preserve">36.3542747497559</t>
   </si>
   <si>
-    <t xml:space="preserve">35.6590728759766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36.3172035217285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.900074005127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36.2615814208984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.8073883056641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36.1966934204102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36.7713890075684</t>
+    <t xml:space="preserve">35.6590766906738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.317195892334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.9000778198242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.2615852355957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.8073844909668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.1966972351074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.7713928222656</t>
   </si>
   <si>
     <t xml:space="preserve">35.9186172485352</t>
@@ -4829,7 +4829,7 @@
     <t xml:space="preserve">35.9834976196289</t>
   </si>
   <si>
-    <t xml:space="preserve">36.0761985778809</t>
+    <t xml:space="preserve">36.0761947631836</t>
   </si>
   <si>
     <t xml:space="preserve">35.5941886901855</t>
@@ -4847,10 +4847,10 @@
     <t xml:space="preserve">35.9649620056152</t>
   </si>
   <si>
-    <t xml:space="preserve">36.5118560791016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.2348556518555</t>
+    <t xml:space="preserve">36.5118522644043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.2348594665527</t>
   </si>
   <si>
     <t xml:space="preserve">37.1514358520508</t>
@@ -4859,19 +4859,19 @@
     <t xml:space="preserve">38.792106628418</t>
   </si>
   <si>
-    <t xml:space="preserve">39.1536140441895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.4027976989746</t>
+    <t xml:space="preserve">39.1536102294922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.4027938842773</t>
   </si>
   <si>
     <t xml:space="preserve">38.291561126709</t>
   </si>
   <si>
-    <t xml:space="preserve">38.0227546691895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.6056327819824</t>
+    <t xml:space="preserve">38.0227508544922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.6056365966797</t>
   </si>
   <si>
     <t xml:space="preserve">37.7817497253418</t>
@@ -4880,22 +4880,22 @@
     <t xml:space="preserve">38.2359466552734</t>
   </si>
   <si>
-    <t xml:space="preserve">37.1977844238281</t>
+    <t xml:space="preserve">37.1977806091309</t>
   </si>
   <si>
     <t xml:space="preserve">36.2523155212402</t>
   </si>
   <si>
-    <t xml:space="preserve">37.0587387084961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.318286895752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.6519775390625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.9300537109375</t>
+    <t xml:space="preserve">37.0587425231934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.3182830810547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.6519813537598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.9300575256348</t>
   </si>
   <si>
     <t xml:space="preserve">38.2452163696289</t>
@@ -4904,7 +4904,7 @@
     <t xml:space="preserve">38.0876426696777</t>
   </si>
   <si>
-    <t xml:space="preserve">37.3090171813965</t>
+    <t xml:space="preserve">37.3090133666992</t>
   </si>
   <si>
     <t xml:space="preserve">37.7724800109863</t>
@@ -4916,7 +4916,7 @@
     <t xml:space="preserve">37.9764099121094</t>
   </si>
   <si>
-    <t xml:space="preserve">38.3564491271973</t>
+    <t xml:space="preserve">38.3564529418945</t>
   </si>
   <si>
     <t xml:space="preserve">38.0969047546387</t>
@@ -4931,7 +4931,7 @@
     <t xml:space="preserve">37.1050910949707</t>
   </si>
   <si>
-    <t xml:space="preserve">36.5674705505371</t>
+    <t xml:space="preserve">36.5674667358398</t>
   </si>
   <si>
     <t xml:space="preserve">37.1885147094727</t>
@@ -4943,28 +4943,28 @@
     <t xml:space="preserve">36.4284286499023</t>
   </si>
   <si>
-    <t xml:space="preserve">36.7250480651855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36.4098854064941</t>
+    <t xml:space="preserve">36.7250442504883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.4098930358887</t>
   </si>
   <si>
     <t xml:space="preserve">35.8815383911133</t>
   </si>
   <si>
-    <t xml:space="preserve">35.816650390625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.2234153747559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36.020580291748</t>
+    <t xml:space="preserve">35.8166580200195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.2234115600586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.0205841064453</t>
   </si>
   <si>
     <t xml:space="preserve">35.4829597473145</t>
   </si>
   <si>
-    <t xml:space="preserve">35.7239646911621</t>
+    <t xml:space="preserve">35.7239608764648</t>
   </si>
   <si>
     <t xml:space="preserve">35.8629989624023</t>
@@ -4973,31 +4973,31 @@
     <t xml:space="preserve">37.0402030944824</t>
   </si>
   <si>
-    <t xml:space="preserve">36.3728179931641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36.3913497924805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36.1132736206055</t>
+    <t xml:space="preserve">36.3728141784668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.3913459777832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.1132698059082</t>
   </si>
   <si>
     <t xml:space="preserve">36.2059669494629</t>
   </si>
   <si>
-    <t xml:space="preserve">36.4840469360352</t>
+    <t xml:space="preserve">36.4840431213379</t>
   </si>
   <si>
     <t xml:space="preserve">36.9382400512695</t>
   </si>
   <si>
-    <t xml:space="preserve">36.9938545227051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.364631652832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.7539405822754</t>
+    <t xml:space="preserve">36.9938621520996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.3646278381348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.7539443969727</t>
   </si>
   <si>
     <t xml:space="preserve">37.8466377258301</t>
@@ -5006,40 +5006,40 @@
     <t xml:space="preserve">37.4758605957031</t>
   </si>
   <si>
-    <t xml:space="preserve">37.299747467041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36.947509765625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.9589538574219</t>
+    <t xml:space="preserve">37.2997436523438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.9475135803223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.9589576721191</t>
   </si>
   <si>
     <t xml:space="preserve">37.7261352539062</t>
   </si>
   <si>
-    <t xml:space="preserve">37.0958213806152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.6808700561523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.939323425293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.1061744689941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.3760719299316</t>
+    <t xml:space="preserve">37.095817565918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.6808738708496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.9393310546875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.1061782836914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.3760681152344</t>
   </si>
   <si>
     <t xml:space="preserve">39.005298614502</t>
   </si>
   <si>
-    <t xml:space="preserve">38.9311447143555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.1721458435059</t>
+    <t xml:space="preserve">38.9311485290527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.1721496582031</t>
   </si>
   <si>
     <t xml:space="preserve">39.987850189209</t>
@@ -5051,7 +5051,7 @@
     <t xml:space="preserve">42.5461845397949</t>
   </si>
   <si>
-    <t xml:space="preserve">42.2866363525391</t>
+    <t xml:space="preserve">42.2866401672363</t>
   </si>
   <si>
     <t xml:space="preserve">41.7119407653809</t>
@@ -5063,10 +5063,10 @@
     <t xml:space="preserve">41.3831253051758</t>
   </si>
   <si>
-    <t xml:space="preserve">41.6555786132812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40.5188331604004</t>
+    <t xml:space="preserve">41.655574798584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40.5188293457031</t>
   </si>
   <si>
     <t xml:space="preserve">40.0960731506348</t>
@@ -5078,19 +5078,19 @@
     <t xml:space="preserve">40.0866775512695</t>
   </si>
   <si>
-    <t xml:space="preserve">39.4290580749512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.1607894897461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.983341217041</t>
+    <t xml:space="preserve">39.4290542602539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.1607856750488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.9833374023438</t>
   </si>
   <si>
     <t xml:space="preserve">40.2463912963867</t>
   </si>
   <si>
-    <t xml:space="preserve">40.3967018127441</t>
+    <t xml:space="preserve">40.3966979980469</t>
   </si>
   <si>
     <t xml:space="preserve">41.4488906860352</t>
@@ -5102,16 +5102,16 @@
     <t xml:space="preserve">42.1346969604492</t>
   </si>
   <si>
-    <t xml:space="preserve">41.7025489807129</t>
+    <t xml:space="preserve">41.7025451660156</t>
   </si>
   <si>
     <t xml:space="preserve">42.7453460693359</t>
   </si>
   <si>
-    <t xml:space="preserve">42.2568244934082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.2098541259766</t>
+    <t xml:space="preserve">42.2568283081055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.2098503112793</t>
   </si>
   <si>
     <t xml:space="preserve">42.5198745727539</t>
@@ -5120,43 +5120,43 @@
     <t xml:space="preserve">41.3925285339355</t>
   </si>
   <si>
-    <t xml:space="preserve">40.6597518920898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40.1900215148926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40.330940246582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40.1242599487305</t>
+    <t xml:space="preserve">40.6597480773926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40.1900177001953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40.3309364318848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40.1242561340332</t>
   </si>
   <si>
     <t xml:space="preserve">40.4906463623047</t>
   </si>
   <si>
-    <t xml:space="preserve">40.697322845459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.1012916564941</t>
+    <t xml:space="preserve">40.6973266601562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.1012954711914</t>
   </si>
   <si>
     <t xml:space="preserve">40.7442970275879</t>
   </si>
   <si>
-    <t xml:space="preserve">40.9415855407715</t>
+    <t xml:space="preserve">40.9415893554688</t>
   </si>
   <si>
     <t xml:space="preserve">41.0449256896973</t>
   </si>
   <si>
-    <t xml:space="preserve">39.6639251708984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.4196624755859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.757869720459</t>
+    <t xml:space="preserve">39.6639213562012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.4196662902832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.7578659057617</t>
   </si>
   <si>
     <t xml:space="preserve">39.6921043395996</t>
@@ -5177,16 +5177,16 @@
     <t xml:space="preserve">40.6691436767578</t>
   </si>
   <si>
-    <t xml:space="preserve">40.8476371765137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40.5470123291016</t>
+    <t xml:space="preserve">40.8476409912109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40.5470085144043</t>
   </si>
   <si>
     <t xml:space="preserve">42.5856399536133</t>
   </si>
   <si>
-    <t xml:space="preserve">42.3319892883301</t>
+    <t xml:space="preserve">42.3319854736328</t>
   </si>
   <si>
     <t xml:space="preserve">41.758918762207</t>
@@ -5198,25 +5198,25 @@
     <t xml:space="preserve">43.6754112243652</t>
   </si>
   <si>
-    <t xml:space="preserve">43.9760360717773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">44.1075630187988</t>
+    <t xml:space="preserve">43.9760398864746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44.1075592041016</t>
   </si>
   <si>
     <t xml:space="preserve">43.1962814331055</t>
   </si>
   <si>
-    <t xml:space="preserve">42.8392906188965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.8810424804688</t>
+    <t xml:space="preserve">42.8392868041992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.881046295166</t>
   </si>
   <si>
     <t xml:space="preserve">40.8758201599121</t>
   </si>
   <si>
-    <t xml:space="preserve">42.228645324707</t>
+    <t xml:space="preserve">42.2286491394043</t>
   </si>
   <si>
     <t xml:space="preserve">42.7077674865723</t>
@@ -5231,16 +5231,16 @@
     <t xml:space="preserve">42.6138229370117</t>
   </si>
   <si>
-    <t xml:space="preserve">42.0971260070801</t>
+    <t xml:space="preserve">42.0971221923828</t>
   </si>
   <si>
     <t xml:space="preserve">41.9468078613281</t>
   </si>
   <si>
-    <t xml:space="preserve">41.9749870300293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.9896049499512</t>
+    <t xml:space="preserve">41.9749908447266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.9896011352539</t>
   </si>
   <si>
     <t xml:space="preserve">42.8017158508301</t>
@@ -5249,13 +5249,13 @@
     <t xml:space="preserve">43.0647621154785</t>
   </si>
   <si>
-    <t xml:space="preserve">43.3935661315918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">44.0511894226074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43.6566162109375</t>
+    <t xml:space="preserve">43.3935699462891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44.0511932373047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43.6566200256348</t>
   </si>
   <si>
     <t xml:space="preserve">43.5720710754395</t>
@@ -5264,22 +5264,22 @@
     <t xml:space="preserve">43.0177879333496</t>
   </si>
   <si>
-    <t xml:space="preserve">42.811107635498</t>
+    <t xml:space="preserve">42.8111038208008</t>
   </si>
   <si>
     <t xml:space="preserve">41.6743659973145</t>
   </si>
   <si>
-    <t xml:space="preserve">42.2850074768066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.8298950195312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.4822998046875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.7171630859375</t>
+    <t xml:space="preserve">42.2850112915039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.8298988342285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.4822959899902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.7171592712402</t>
   </si>
   <si>
     <t xml:space="preserve">42.8768692016602</t>
@@ -5288,16 +5288,16 @@
     <t xml:space="preserve">43.5438842773438</t>
   </si>
   <si>
-    <t xml:space="preserve">43.9854316711426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">44.0887718200684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">44.1357421875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">44.5303192138672</t>
+    <t xml:space="preserve">43.9854278564453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44.0887680053711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44.1357383728027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44.5303153991699</t>
   </si>
   <si>
     <t xml:space="preserve">42.1816711425781</t>
@@ -5309,19 +5309,19 @@
     <t xml:space="preserve">42.0783309936523</t>
   </si>
   <si>
-    <t xml:space="preserve">42.0689353942871</t>
+    <t xml:space="preserve">42.0689315795898</t>
   </si>
   <si>
     <t xml:space="preserve">41.3643417358398</t>
   </si>
   <si>
-    <t xml:space="preserve">41.4770812988281</t>
+    <t xml:space="preserve">41.4770774841309</t>
   </si>
   <si>
     <t xml:space="preserve">42.003173828125</t>
   </si>
   <si>
-    <t xml:space="preserve">41.4019203186035</t>
+    <t xml:space="preserve">41.4019241333008</t>
   </si>
   <si>
     <t xml:space="preserve">41.0918998718262</t>
@@ -5333,13 +5333,13 @@
     <t xml:space="preserve">41.9843788146973</t>
   </si>
   <si>
-    <t xml:space="preserve">41.9374160766602</t>
+    <t xml:space="preserve">41.9374122619629</t>
   </si>
   <si>
     <t xml:space="preserve">42.858081817627</t>
   </si>
   <si>
-    <t xml:space="preserve">42.7829246520996</t>
+    <t xml:space="preserve">42.7829208374023</t>
   </si>
   <si>
     <t xml:space="preserve">42.735954284668</t>
@@ -5351,16 +5351,16 @@
     <t xml:space="preserve">41.3455505371094</t>
   </si>
   <si>
-    <t xml:space="preserve">41.3267631530762</t>
+    <t xml:space="preserve">41.3267669677734</t>
   </si>
   <si>
     <t xml:space="preserve">41.6837539672852</t>
   </si>
   <si>
-    <t xml:space="preserve">41.307975769043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.0637168884277</t>
+    <t xml:space="preserve">41.3079719543457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.0637130737305</t>
   </si>
   <si>
     <t xml:space="preserve">40.7912750244141</t>
@@ -5369,13 +5369,13 @@
     <t xml:space="preserve">40.6127738952637</t>
   </si>
   <si>
-    <t xml:space="preserve">40.9603691101074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.4582862854004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.617992401123</t>
+    <t xml:space="preserve">40.960376739502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.4582901000977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.6179962158203</t>
   </si>
   <si>
     <t xml:space="preserve">41.2891883850098</t>
@@ -5390,19 +5390,19 @@
     <t xml:space="preserve">42.0501441955566</t>
   </si>
   <si>
-    <t xml:space="preserve">41.5804138183594</t>
+    <t xml:space="preserve">41.5804176330566</t>
   </si>
   <si>
     <t xml:space="preserve">42.1910629272461</t>
   </si>
   <si>
-    <t xml:space="preserve">43.0741539001465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.8434600830078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.4447174072266</t>
+    <t xml:space="preserve">43.0741577148438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.8434715270996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.4447212219238</t>
   </si>
   <si>
     <t xml:space="preserve">42.454231262207</t>
@@ -5411,7 +5411,7 @@
     <t xml:space="preserve">42.7016181945801</t>
   </si>
   <si>
-    <t xml:space="preserve">42.2354011535645</t>
+    <t xml:space="preserve">42.2353973388672</t>
   </si>
   <si>
     <t xml:space="preserve">42.3876266479492</t>
@@ -5420,16 +5420,16 @@
     <t xml:space="preserve">42.2639389038086</t>
   </si>
   <si>
-    <t xml:space="preserve">42.216365814209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.1687965393066</t>
+    <t xml:space="preserve">42.2163696289062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.1687927246094</t>
   </si>
   <si>
     <t xml:space="preserve">42.0260734558105</t>
   </si>
   <si>
-    <t xml:space="preserve">42.0451011657715</t>
+    <t xml:space="preserve">42.0451049804688</t>
   </si>
   <si>
     <t xml:space="preserve">43.0251121520996</t>
@@ -5441,7 +5441,7 @@
     <t xml:space="preserve">43.99560546875</t>
   </si>
   <si>
-    <t xml:space="preserve">43.4437484741211</t>
+    <t xml:space="preserve">43.4437522888184</t>
   </si>
   <si>
     <t xml:space="preserve">44.4332809448242</t>
@@ -5456,7 +5456,7 @@
     <t xml:space="preserve">44.7282295227051</t>
   </si>
   <si>
-    <t xml:space="preserve">45.0326995849609</t>
+    <t xml:space="preserve">45.0326957702637</t>
   </si>
   <si>
     <t xml:space="preserve">45.5560035705566</t>
@@ -5471,16 +5471,16 @@
     <t xml:space="preserve">45.2800750732422</t>
   </si>
   <si>
-    <t xml:space="preserve">45.7938690185547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.8794975280762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.9841575622559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.0888175964355</t>
+    <t xml:space="preserve">45.7938652038574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.8795013427734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.9841613769531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.0888137817383</t>
   </si>
   <si>
     <t xml:space="preserve">46.459888458252</t>
@@ -5489,16 +5489,16 @@
     <t xml:space="preserve">46.621639251709</t>
   </si>
   <si>
-    <t xml:space="preserve">45.6892051696777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.1649398803711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.4989166259766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.8604736328125</t>
+    <t xml:space="preserve">45.689208984375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.1649360656738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.4989128112793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.8604698181152</t>
   </si>
   <si>
     <t xml:space="preserve">46.5455207824707</t>
@@ -5519,7 +5519,7 @@
     <t xml:space="preserve">47.8204765319824</t>
   </si>
   <si>
-    <t xml:space="preserve">48.0488319396973</t>
+    <t xml:space="preserve">48.048828125</t>
   </si>
   <si>
     <t xml:space="preserve">47.373291015625</t>
@@ -5528,19 +5528,19 @@
     <t xml:space="preserve">47.3447456359863</t>
   </si>
   <si>
-    <t xml:space="preserve">47.1639747619629</t>
+    <t xml:space="preserve">47.1639709472656</t>
   </si>
   <si>
     <t xml:space="preserve">47.3066902160645</t>
   </si>
   <si>
-    <t xml:space="preserve">47.5160102844238</t>
+    <t xml:space="preserve">47.5160064697266</t>
   </si>
   <si>
     <t xml:space="preserve">47.554069519043</t>
   </si>
   <si>
-    <t xml:space="preserve">48.4294128417969</t>
+    <t xml:space="preserve">48.4294166564941</t>
   </si>
   <si>
     <t xml:space="preserve">48.1820335388184</t>
@@ -5552,7 +5552,7 @@
     <t xml:space="preserve">48.8099975585938</t>
   </si>
   <si>
-    <t xml:space="preserve">48.2391242980957</t>
+    <t xml:space="preserve">48.239128112793</t>
   </si>
   <si>
     <t xml:space="preserve">48.3532981872559</t>
@@ -5561,7 +5561,7 @@
     <t xml:space="preserve">48.6197090148926</t>
   </si>
   <si>
-    <t xml:space="preserve">47.9917449951172</t>
+    <t xml:space="preserve">47.9917411804199</t>
   </si>
   <si>
     <t xml:space="preserve">48.0107688903809</t>
@@ -5582,7 +5582,7 @@
     <t xml:space="preserve">48.7529182434082</t>
   </si>
   <si>
-    <t xml:space="preserve">49.5901985168457</t>
+    <t xml:space="preserve">49.5901947021484</t>
   </si>
   <si>
     <t xml:space="preserve">49.5521430969238</t>
@@ -5594,13 +5594,13 @@
     <t xml:space="preserve">50.3133125305176</t>
   </si>
   <si>
-    <t xml:space="preserve">49.1525268554688</t>
+    <t xml:space="preserve">49.1525230407715</t>
   </si>
   <si>
     <t xml:space="preserve">48.5055313110352</t>
   </si>
   <si>
-    <t xml:space="preserve">48.2581558227539</t>
+    <t xml:space="preserve">48.2581520080566</t>
   </si>
   <si>
     <t xml:space="preserve">49.2476692199707</t>
@@ -5618,13 +5618,13 @@
     <t xml:space="preserve">50.2942810058594</t>
   </si>
   <si>
-    <t xml:space="preserve">50.1801109313965</t>
+    <t xml:space="preserve">50.1801071166992</t>
   </si>
   <si>
     <t xml:space="preserve">50.5036010742188</t>
   </si>
   <si>
-    <t xml:space="preserve">50.2181663513184</t>
+    <t xml:space="preserve">50.2181625366211</t>
   </si>
   <si>
     <t xml:space="preserve">50.2752532958984</t>
@@ -5642,34 +5642,34 @@
     <t xml:space="preserve">48.8861198425293</t>
   </si>
   <si>
-    <t xml:space="preserve">49.8185539245605</t>
+    <t xml:space="preserve">49.8185501098633</t>
   </si>
   <si>
     <t xml:space="preserve">49.4760208129883</t>
   </si>
   <si>
-    <t xml:space="preserve">48.9051475524902</t>
+    <t xml:space="preserve">48.9051513671875</t>
   </si>
   <si>
     <t xml:space="preserve">49.228645324707</t>
   </si>
   <si>
-    <t xml:space="preserve">48.2866973876953</t>
+    <t xml:space="preserve">48.286693572998</t>
   </si>
   <si>
     <t xml:space="preserve">48.0964012145996</t>
   </si>
   <si>
-    <t xml:space="preserve">47.4018325805664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.3361968994141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">47.4969787597656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">47.1544609069824</t>
+    <t xml:space="preserve">47.4018363952637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.3362007141113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">47.4969825744629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">47.1544570922852</t>
   </si>
   <si>
     <t xml:space="preserve">47.5731010437012</t>
@@ -5678,10 +5678,10 @@
     <t xml:space="preserve">47.0212516784668</t>
   </si>
   <si>
-    <t xml:space="preserve">46.9451370239258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.5645523071289</t>
+    <t xml:space="preserve">46.945140838623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.5645484924316</t>
   </si>
   <si>
     <t xml:space="preserve">47.3257255554199</t>
@@ -5699,28 +5699,28 @@
     <t xml:space="preserve">47.6206703186035</t>
   </si>
   <si>
-    <t xml:space="preserve">47.7633895874023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">47.9061088562012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">48.7148551940918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">49.2857322692871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">48.5029220581055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">47.029052734375</t>
+    <t xml:space="preserve">47.7633934020996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">47.9061126708984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">48.7148590087891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">49.2857284545898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">48.5029258728027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">47.0290489196777</t>
   </si>
   <si>
     <t xml:space="preserve">47.356575012207</t>
   </si>
   <si>
-    <t xml:space="preserve">46.7400588989258</t>
+    <t xml:space="preserve">46.7400550842285</t>
   </si>
   <si>
     <t xml:space="preserve">46.5666618347168</t>
@@ -5732,7 +5732,7 @@
     <t xml:space="preserve">46.3354644775391</t>
   </si>
   <si>
-    <t xml:space="preserve">45.9501419067383</t>
+    <t xml:space="preserve">45.950138092041</t>
   </si>
   <si>
     <t xml:space="preserve">45.7189407348633</t>
@@ -5744,10 +5744,10 @@
     <t xml:space="preserve">46.5859260559082</t>
   </si>
   <si>
-    <t xml:space="preserve">46.4318008422852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.8171195983887</t>
+    <t xml:space="preserve">46.4317970275879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.8171234130859</t>
   </si>
   <si>
     <t xml:space="preserve">47.4336471557617</t>
@@ -5756,10 +5756,10 @@
     <t xml:space="preserve">47.8767700195312</t>
   </si>
   <si>
-    <t xml:space="preserve">47.7226371765137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.6437225341797</t>
+    <t xml:space="preserve">47.7226409912109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.643726348877</t>
   </si>
   <si>
     <t xml:space="preserve">47.4529075622559</t>
@@ -5774,7 +5774,7 @@
     <t xml:space="preserve">46.0850028991699</t>
   </si>
   <si>
-    <t xml:space="preserve">47.3951110839844</t>
+    <t xml:space="preserve">47.3951148986816</t>
   </si>
   <si>
     <t xml:space="preserve">48.262092590332</t>
@@ -5786,7 +5786,7 @@
     <t xml:space="preserve">47.7997016906738</t>
   </si>
   <si>
-    <t xml:space="preserve">46.9134521484375</t>
+    <t xml:space="preserve">46.9134559631348</t>
   </si>
   <si>
     <t xml:space="preserve">47.0097846984863</t>
@@ -5816,28 +5816,28 @@
     <t xml:space="preserve">49.2254104614258</t>
   </si>
   <si>
-    <t xml:space="preserve">49.8515625</t>
+    <t xml:space="preserve">49.8515663146973</t>
   </si>
   <si>
     <t xml:space="preserve">49.3699073791504</t>
   </si>
   <si>
-    <t xml:space="preserve">49.514404296875</t>
+    <t xml:space="preserve">49.5144081115723</t>
   </si>
   <si>
     <t xml:space="preserve">49.9478950500488</t>
   </si>
   <si>
-    <t xml:space="preserve">50.3332214355469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50.0442276000977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50.4777221679688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">48.8882522583008</t>
+    <t xml:space="preserve">50.3332252502441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50.0442314147949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50.4777183532715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">48.8882484436035</t>
   </si>
   <si>
     <t xml:space="preserve">48.3102607727051</t>
@@ -5855,16 +5855,16 @@
     <t xml:space="preserve">47.183177947998</t>
   </si>
   <si>
-    <t xml:space="preserve">47.5299758911133</t>
+    <t xml:space="preserve">47.5299797058105</t>
   </si>
   <si>
     <t xml:space="preserve">47.6455726623535</t>
   </si>
   <si>
-    <t xml:space="preserve">47.9923629760742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">48.1272277832031</t>
+    <t xml:space="preserve">47.9923667907715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">48.1272315979004</t>
   </si>
   <si>
     <t xml:space="preserve">48.7437515258789</t>
@@ -5873,19 +5873,19 @@
     <t xml:space="preserve">48.5510902404785</t>
   </si>
   <si>
-    <t xml:space="preserve">48.791919708252</t>
+    <t xml:space="preserve">48.7919158935547</t>
   </si>
   <si>
     <t xml:space="preserve">49.7070655822754</t>
   </si>
   <si>
-    <t xml:space="preserve">50.8148803710938</t>
+    <t xml:space="preserve">50.8148765563965</t>
   </si>
   <si>
     <t xml:space="preserve">50.6222152709961</t>
   </si>
   <si>
-    <t xml:space="preserve">51.0557060241699</t>
+    <t xml:space="preserve">51.0557098388672</t>
   </si>
   <si>
     <t xml:space="preserve">50.7185478210449</t>
@@ -5894,7 +5894,7 @@
     <t xml:space="preserve">50.8630447387695</t>
   </si>
   <si>
-    <t xml:space="preserve">50.1405601501465</t>
+    <t xml:space="preserve">50.1405563354492</t>
   </si>
   <si>
     <t xml:space="preserve">49.4180717468262</t>
@@ -5903,7 +5903,7 @@
     <t xml:space="preserve">49.562572479248</t>
   </si>
   <si>
-    <t xml:space="preserve">49.0327453613281</t>
+    <t xml:space="preserve">49.0327491760254</t>
   </si>
   <si>
     <t xml:space="preserve">48.9845809936523</t>
@@ -5912,34 +5912,34 @@
     <t xml:space="preserve">48.6955833435059</t>
   </si>
   <si>
-    <t xml:space="preserve">48.1079635620117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">47.9730987548828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">48.8400840759277</t>
+    <t xml:space="preserve">48.1079597473145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">47.9730949401855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">48.840087890625</t>
   </si>
   <si>
     <t xml:space="preserve">48.9364128112793</t>
   </si>
   <si>
-    <t xml:space="preserve">47.6841087341309</t>
+    <t xml:space="preserve">47.6841049194336</t>
   </si>
   <si>
     <t xml:space="preserve">50.1887245178223</t>
   </si>
   <si>
-    <t xml:space="preserve">52.1153564453125</t>
+    <t xml:space="preserve">52.1153526306152</t>
   </si>
   <si>
     <t xml:space="preserve">51.4410362243652</t>
   </si>
   <si>
-    <t xml:space="preserve">51.5855331420898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">52.5006790161133</t>
+    <t xml:space="preserve">51.5855293273926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">52.5006828308105</t>
   </si>
   <si>
     <t xml:space="preserve">52.2116889953613</t>
@@ -5951,7 +5951,7 @@
     <t xml:space="preserve">51.3928680419922</t>
   </si>
   <si>
-    <t xml:space="preserve">51.7300300598145</t>
+    <t xml:space="preserve">51.7300338745117</t>
   </si>
   <si>
     <t xml:space="preserve">51.826358795166</t>
@@ -5960,7 +5960,7 @@
     <t xml:space="preserve">51.8745269775391</t>
   </si>
   <si>
-    <t xml:space="preserve">51.1520385742188</t>
+    <t xml:space="preserve">51.152042388916</t>
   </si>
   <si>
     <t xml:space="preserve">49.9960632324219</t>
@@ -5972,76 +5972,76 @@
     <t xml:space="preserve">50.4295539855957</t>
   </si>
   <si>
+    <t xml:space="preserve">49.3217468261719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">48.7369003295898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">48.6394271850586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">49.1755294799805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">49.3704795837402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50.7838478088379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50.9300575256348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50.4426918029785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50.3939514160156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50.0527954101562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50.2477416992188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">49.8578491210938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50.1015319824219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50.6376419067383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">49.7603721618652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">49.8091087341309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">49.9065818786621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">49.5654258728027</t>
+  </si>
+  <si>
     <t xml:space="preserve">49.3217430114746</t>
   </si>
   <si>
-    <t xml:space="preserve">48.7369003295898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">48.6394271850586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">49.1755294799805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">49.3704795837402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50.7838478088379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50.930061340332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50.4426918029785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50.3939552307129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50.0527954101562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50.2477416992188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">49.8578491210938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50.1015319824219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50.637638092041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">49.7603721618652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">49.8091087341309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">49.9065856933594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">49.5654258728027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">49.3217391967773</t>
-  </si>
-  <si>
     <t xml:space="preserve">49.4679527282715</t>
   </si>
   <si>
     <t xml:space="preserve">49.0780563354492</t>
   </si>
   <si>
-    <t xml:space="preserve">49.1267929077148</t>
+    <t xml:space="preserve">49.1267967224121</t>
   </si>
   <si>
     <t xml:space="preserve">49.2242698669434</t>
   </si>
   <si>
-    <t xml:space="preserve">49.6141624450684</t>
+    <t xml:space="preserve">49.6141662597656</t>
   </si>
   <si>
     <t xml:space="preserve">50.4914245605469</t>
@@ -6065,10 +6065,10 @@
     <t xml:space="preserve">53.1719551086426</t>
   </si>
   <si>
-    <t xml:space="preserve">53.5131149291992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">53.2206954956055</t>
+    <t xml:space="preserve">53.5131187438965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">53.2206916809082</t>
   </si>
   <si>
     <t xml:space="preserve">53.7568016052246</t>
@@ -6080,13 +6080,13 @@
     <t xml:space="preserve">54.3903770446777</t>
   </si>
   <si>
-    <t xml:space="preserve">54.5853271484375</t>
+    <t xml:space="preserve">54.5853233337402</t>
   </si>
   <si>
     <t xml:space="preserve">55.3651161193848</t>
   </si>
   <si>
-    <t xml:space="preserve">56.0474319458008</t>
+    <t xml:space="preserve">56.047435760498</t>
   </si>
   <si>
     <t xml:space="preserve">56.6810150146484</t>
@@ -6098,7 +6098,7 @@
     <t xml:space="preserve">57.2658576965332</t>
   </si>
   <si>
-    <t xml:space="preserve">57.7532234191895</t>
+    <t xml:space="preserve">57.7532272338867</t>
   </si>
   <si>
     <t xml:space="preserve">57.6070137023926</t>
@@ -6107,7 +6107,7 @@
     <t xml:space="preserve">57.9481735229492</t>
   </si>
   <si>
-    <t xml:space="preserve">58.143123626709</t>
+    <t xml:space="preserve">58.1431198120117</t>
   </si>
   <si>
     <t xml:space="preserve">57.1196441650391</t>
@@ -6122,10 +6122,10 @@
     <t xml:space="preserve">57.558277130127</t>
   </si>
   <si>
-    <t xml:space="preserve">59.4102783203125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">58.0943794250488</t>
+    <t xml:space="preserve">59.4102821350098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">58.0943832397461</t>
   </si>
   <si>
     <t xml:space="preserve">58.240592956543</t>
@@ -6137,10 +6137,10 @@
     <t xml:space="preserve">54.4391136169434</t>
   </si>
   <si>
-    <t xml:space="preserve">53.4643783569336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">52.733325958252</t>
+    <t xml:space="preserve">53.4643745422363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">52.7333221435547</t>
   </si>
   <si>
     <t xml:space="preserve">52.3434295654297</t>
@@ -6155,28 +6155,28 @@
     <t xml:space="preserve">52.9282722473145</t>
   </si>
   <si>
-    <t xml:space="preserve">53.5618553161621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">52.8795318603516</t>
+    <t xml:space="preserve">53.5618515014648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">52.8795356750488</t>
   </si>
   <si>
     <t xml:space="preserve">52.4896392822266</t>
   </si>
   <si>
-    <t xml:space="preserve">52.1972160339355</t>
+    <t xml:space="preserve">52.1972198486328</t>
   </si>
   <si>
     <t xml:space="preserve">50.9787940979004</t>
   </si>
   <si>
-    <t xml:space="preserve">51.6611099243164</t>
+    <t xml:space="preserve">51.6611137390137</t>
   </si>
   <si>
     <t xml:space="preserve">51.612377166748</t>
   </si>
   <si>
-    <t xml:space="preserve">51.3686904907227</t>
+    <t xml:space="preserve">51.3686943054199</t>
   </si>
   <si>
     <t xml:space="preserve">52.0997467041016</t>
@@ -6209,10 +6209,10 @@
     <t xml:space="preserve">44.7014846801758</t>
   </si>
   <si>
-    <t xml:space="preserve">45.4617767333984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.4365158081055</t>
+    <t xml:space="preserve">45.4617805480957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.4365196228027</t>
   </si>
   <si>
     <t xml:space="preserve">47.1383285522461</t>
@@ -6221,16 +6221,16 @@
     <t xml:space="preserve">47.2747917175293</t>
   </si>
   <si>
-    <t xml:space="preserve">47.0798416137695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">47.7426643371582</t>
+    <t xml:space="preserve">47.0798454284668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">47.7426681518555</t>
   </si>
   <si>
     <t xml:space="preserve">47.9766044616699</t>
   </si>
   <si>
-    <t xml:space="preserve">48.2105369567871</t>
+    <t xml:space="preserve">48.2105407714844</t>
   </si>
   <si>
     <t xml:space="preserve">47.8011512756348</t>
@@ -6242,7 +6242,7 @@
     <t xml:space="preserve">50.5401649475098</t>
   </si>
   <si>
-    <t xml:space="preserve">51.8560600280762</t>
+    <t xml:space="preserve">51.8560638427734</t>
   </si>
   <si>
     <t xml:space="preserve">51.1737442016602</t>
@@ -6251,10 +6251,10 @@
     <t xml:space="preserve">50.8325843811035</t>
   </si>
   <si>
-    <t xml:space="preserve">50.34521484375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50.1990089416504</t>
+    <t xml:space="preserve">50.3452186584473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50.1990051269531</t>
   </si>
   <si>
     <t xml:space="preserve">50.8113098144531</t>
@@ -6765,6 +6765,9 @@
   </si>
   <si>
     <t xml:space="preserve">49.9000015258789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">49.7999992370605</t>
   </si>
 </sst>
 </file>
@@ -75403,6 +75406,32 @@
         <v>9</v>
       </c>
     </row>
+    <row r="2628">
+      <c r="A2628" s="1" t="n">
+        <v>46149.2916666667</v>
+      </c>
+      <c r="B2628" t="n">
+        <v>394716</v>
+      </c>
+      <c r="C2628" t="n">
+        <v>50.25</v>
+      </c>
+      <c r="D2628" t="n">
+        <v>49.3800010681152</v>
+      </c>
+      <c r="E2628" t="n">
+        <v>50.0999984741211</v>
+      </c>
+      <c r="F2628" t="n">
+        <v>49.7999992370605</v>
+      </c>
+      <c r="G2628" t="s">
+        <v>2251</v>
+      </c>
+      <c r="H2628" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/REC.MI.xlsx
+++ b/data/REC.MI.xlsx
@@ -61692,24 +61692,47 @@
     </row>
     <row r="2667">
       <c r="A2667" s="1" t="n">
-        <v>46205.2916666667</v>
+        <v>46204.2916666667</v>
       </c>
       <c r="B2667" t="n">
-        <v>270079</v>
+        <v>264575</v>
       </c>
       <c r="C2667" t="n">
-        <v>51.5999984741211</v>
+        <v>51.4500007629395</v>
       </c>
       <c r="D2667" t="n">
+        <v>51.25</v>
+      </c>
+      <c r="E2667" t="n">
         <v>51.2999992370605</v>
       </c>
-      <c r="E2667" t="n">
-        <v>51.4500007629395</v>
-      </c>
       <c r="F2667" t="n">
-        <v>51.5999984741211</v>
+        <v>51.3499984741211</v>
       </c>
       <c r="G2667" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2668">
+      <c r="A2668" s="1" t="n">
+        <v>46206.2916666667</v>
+      </c>
+      <c r="B2668" t="n">
+        <v>144729</v>
+      </c>
+      <c r="C2668" t="n">
+        <v>51.5</v>
+      </c>
+      <c r="D2668" t="n">
+        <v>51.2999992370605</v>
+      </c>
+      <c r="E2668" t="n">
+        <v>51.3499984741211</v>
+      </c>
+      <c r="F2668" t="n">
+        <v>51.3499984741211</v>
+      </c>
+      <c r="G2668" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/REC.MI.xlsx
+++ b/data/REC.MI.xlsx
@@ -62198,19 +62198,19 @@
     </row>
     <row r="2689">
       <c r="A2689" s="1" t="n">
-        <v>46237.2916666667</v>
+        <v>46234.2916666667</v>
       </c>
       <c r="B2689" t="n">
-        <v>261482</v>
+        <v>436966</v>
       </c>
       <c r="C2689" t="n">
-        <v>51.75</v>
+        <v>51.7999992370605</v>
       </c>
       <c r="D2689" t="n">
-        <v>51.5499992370605</v>
+        <v>51.4000015258789</v>
       </c>
       <c r="E2689" t="n">
-        <v>51.5499992370605</v>
+        <v>51.4500007629395</v>
       </c>
       <c r="F2689" t="n">
         <v>51.6500015258789</v>
@@ -62221,22 +62221,22 @@
     </row>
     <row r="2690">
       <c r="A2690" s="1" t="n">
-        <v>46238.2916666667</v>
+        <v>46237.2916666667</v>
       </c>
       <c r="B2690" t="n">
-        <v>159270</v>
+        <v>261482</v>
       </c>
       <c r="C2690" t="n">
-        <v>52.0999984741211</v>
+        <v>51.75</v>
       </c>
       <c r="D2690" t="n">
-        <v>51.4500007629395</v>
+        <v>51.5499992370605</v>
       </c>
       <c r="E2690" t="n">
-        <v>51.4500007629395</v>
+        <v>51.5499992370605</v>
       </c>
       <c r="F2690" t="n">
-        <v>52.0999984741211</v>
+        <v>51.6500015258789</v>
       </c>
       <c r="G2690" t="s">
         <v>7</v>
@@ -62244,24 +62244,68 @@
     </row>
     <row r="2691">
       <c r="A2691" s="1" t="n">
+        <v>46238.2916666667</v>
+      </c>
+      <c r="B2691" t="n">
+        <v>159270</v>
+      </c>
+      <c r="C2691" t="n">
+        <v>52.0999984741211</v>
+      </c>
+      <c r="D2691" t="n">
+        <v>51.4500007629395</v>
+      </c>
+      <c r="E2691" t="n">
+        <v>51.4500007629395</v>
+      </c>
+      <c r="F2691" t="n">
+        <v>52.0999984741211</v>
+      </c>
+      <c r="G2691" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2692">
+      <c r="A2692" s="1" t="n">
         <v>46239.2916666667</v>
       </c>
-      <c r="B2691" t="n">
+      <c r="B2692" t="n">
         <v>249490</v>
       </c>
-      <c r="C2691" t="n">
+      <c r="C2692" t="n">
         <v>52.2000007629395</v>
       </c>
-      <c r="D2691" t="n">
+      <c r="D2692" t="n">
         <v>51.7999992370605</v>
       </c>
-      <c r="E2691" t="n">
+      <c r="E2692" t="n">
         <v>51.7999992370605</v>
       </c>
-      <c r="F2691" t="n">
+      <c r="F2692" t="n">
         <v>52.2000007629395</v>
       </c>
-      <c r="G2691" t="s">
+      <c r="G2692" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2693">
+      <c r="A2693" s="1" t="n">
+        <v>46240.2916666667</v>
+      </c>
+      <c r="B2693" t="n">
+        <v>236206</v>
+      </c>
+      <c r="C2693" t="n">
+        <v>52.7999992370605</v>
+      </c>
+      <c r="D2693" t="n">
+        <v>52.1500015258789</v>
+      </c>
+      <c r="E2693" t="n">
+        <v>52.2999992370605</v>
+      </c>
+      <c r="F2693"/>
+      <c r="G2693" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/REC.MI.xlsx
+++ b/data/REC.MI.xlsx
@@ -62357,6 +62357,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2696">
+      <c r="A2696" s="1" t="n">
+        <v>46246.2916666667</v>
+      </c>
+      <c r="B2696" t="n">
+        <v>188395</v>
+      </c>
+      <c r="C2696" t="n">
+        <v>52.75</v>
+      </c>
+      <c r="D2696" t="n">
+        <v>52.5999984741211</v>
+      </c>
+      <c r="E2696" t="n">
+        <v>52.6500015258789</v>
+      </c>
+      <c r="F2696" t="n">
+        <v>52.5999984741211</v>
+      </c>
+      <c r="G2696" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/REC.MI.xlsx
+++ b/data/REC.MI.xlsx
@@ -61991,22 +61991,22 @@
     </row>
     <row r="2680">
       <c r="A2680" s="1" t="n">
-        <v>46224.2916666667</v>
+        <v>46223.2916666667</v>
       </c>
       <c r="B2680" t="n">
-        <v>387781</v>
+        <v>200950</v>
       </c>
       <c r="C2680" t="n">
         <v>51.4000015258789</v>
       </c>
       <c r="D2680" t="n">
-        <v>51.25</v>
+        <v>51.2999992370605</v>
       </c>
       <c r="E2680" t="n">
         <v>51.2999992370605</v>
       </c>
       <c r="F2680" t="n">
-        <v>51.3499984741211</v>
+        <v>51.2999992370605</v>
       </c>
       <c r="G2680" t="s">
         <v>7</v>
@@ -62014,22 +62014,22 @@
     </row>
     <row r="2681">
       <c r="A2681" s="1" t="n">
-        <v>46225.2916666667</v>
+        <v>46224.2916666667</v>
       </c>
       <c r="B2681" t="n">
-        <v>289354</v>
+        <v>387781</v>
       </c>
       <c r="C2681" t="n">
         <v>51.4000015258789</v>
       </c>
       <c r="D2681" t="n">
+        <v>51.25</v>
+      </c>
+      <c r="E2681" t="n">
         <v>51.2999992370605</v>
       </c>
-      <c r="E2681" t="n">
+      <c r="F2681" t="n">
         <v>51.3499984741211</v>
-      </c>
-      <c r="F2681" t="n">
-        <v>51.4000015258789</v>
       </c>
       <c r="G2681" t="s">
         <v>7</v>
@@ -62037,10 +62037,10 @@
     </row>
     <row r="2682">
       <c r="A2682" s="1" t="n">
-        <v>46226.2916666667</v>
+        <v>46225.2916666667</v>
       </c>
       <c r="B2682" t="n">
-        <v>324615</v>
+        <v>289354</v>
       </c>
       <c r="C2682" t="n">
         <v>51.4000015258789</v>
@@ -62049,10 +62049,10 @@
         <v>51.2999992370605</v>
       </c>
       <c r="E2682" t="n">
-        <v>51.2999992370605</v>
+        <v>51.3499984741211</v>
       </c>
       <c r="F2682" t="n">
-        <v>51.3499984741211</v>
+        <v>51.4000015258789</v>
       </c>
       <c r="G2682" t="s">
         <v>7</v>
@@ -62060,10 +62060,10 @@
     </row>
     <row r="2683">
       <c r="A2683" s="1" t="n">
-        <v>46227.2916666667</v>
+        <v>46226.2916666667</v>
       </c>
       <c r="B2683" t="n">
-        <v>260289</v>
+        <v>324615</v>
       </c>
       <c r="C2683" t="n">
         <v>51.4000015258789</v>
@@ -62072,7 +62072,7 @@
         <v>51.2999992370605</v>
       </c>
       <c r="E2683" t="n">
-        <v>51.4000015258789</v>
+        <v>51.2999992370605</v>
       </c>
       <c r="F2683" t="n">
         <v>51.3499984741211</v>
@@ -62083,22 +62083,22 @@
     </row>
     <row r="2684">
       <c r="A2684" s="1" t="n">
-        <v>46230.2916666667</v>
+        <v>46227.2916666667</v>
       </c>
       <c r="B2684" t="n">
-        <v>469692</v>
+        <v>260289</v>
       </c>
       <c r="C2684" t="n">
-        <v>51.4500007629395</v>
+        <v>51.4000015258789</v>
       </c>
       <c r="D2684" t="n">
+        <v>51.2999992370605</v>
+      </c>
+      <c r="E2684" t="n">
+        <v>51.4000015258789</v>
+      </c>
+      <c r="F2684" t="n">
         <v>51.3499984741211</v>
-      </c>
-      <c r="E2684" t="n">
-        <v>51.4500007629395</v>
-      </c>
-      <c r="F2684" t="n">
-        <v>51.4500007629395</v>
       </c>
       <c r="G2684" t="s">
         <v>7</v>
@@ -62106,22 +62106,22 @@
     </row>
     <row r="2685">
       <c r="A2685" s="1" t="n">
-        <v>46231.2916666667</v>
+        <v>46230.2916666667</v>
       </c>
       <c r="B2685" t="n">
-        <v>193462</v>
+        <v>469692</v>
       </c>
       <c r="C2685" t="n">
-        <v>51.5</v>
+        <v>51.4500007629395</v>
       </c>
       <c r="D2685" t="n">
-        <v>51.2999992370605</v>
+        <v>51.3499984741211</v>
       </c>
       <c r="E2685" t="n">
-        <v>51.5</v>
+        <v>51.4500007629395</v>
       </c>
       <c r="F2685" t="n">
-        <v>51.2999992370605</v>
+        <v>51.4500007629395</v>
       </c>
       <c r="G2685" t="s">
         <v>7</v>
@@ -62129,22 +62129,22 @@
     </row>
     <row r="2686">
       <c r="A2686" s="1" t="n">
-        <v>46232.2916666667</v>
+        <v>46231.2916666667</v>
       </c>
       <c r="B2686" t="n">
-        <v>507144</v>
+        <v>193462</v>
       </c>
       <c r="C2686" t="n">
-        <v>51.5999984741211</v>
+        <v>51.5</v>
       </c>
       <c r="D2686" t="n">
-        <v>51.3499984741211</v>
+        <v>51.2999992370605</v>
       </c>
       <c r="E2686" t="n">
-        <v>51.3499984741211</v>
+        <v>51.5</v>
       </c>
       <c r="F2686" t="n">
-        <v>51.4000015258789</v>
+        <v>51.2999992370605</v>
       </c>
       <c r="G2686" t="s">
         <v>7</v>
@@ -62152,22 +62152,22 @@
     </row>
     <row r="2687">
       <c r="A2687" s="1" t="n">
-        <v>46233.2916666667</v>
+        <v>46232.2916666667</v>
       </c>
       <c r="B2687" t="n">
-        <v>413506</v>
+        <v>507144</v>
       </c>
       <c r="C2687" t="n">
-        <v>51.5</v>
+        <v>51.5999984741211</v>
       </c>
       <c r="D2687" t="n">
-        <v>51.2999992370605</v>
+        <v>51.3499984741211</v>
       </c>
       <c r="E2687" t="n">
         <v>51.3499984741211</v>
       </c>
       <c r="F2687" t="n">
-        <v>51.5</v>
+        <v>51.4000015258789</v>
       </c>
       <c r="G2687" t="s">
         <v>7</v>
@@ -62175,22 +62175,22 @@
     </row>
     <row r="2688">
       <c r="A2688" s="1" t="n">
-        <v>46237.2916666667</v>
+        <v>46233.2916666667</v>
       </c>
       <c r="B2688" t="n">
-        <v>261482</v>
+        <v>413506</v>
       </c>
       <c r="C2688" t="n">
-        <v>51.75</v>
+        <v>51.5</v>
       </c>
       <c r="D2688" t="n">
-        <v>51.5499992370605</v>
+        <v>51.2999992370605</v>
       </c>
       <c r="E2688" t="n">
-        <v>51.5499992370605</v>
+        <v>51.3499984741211</v>
       </c>
       <c r="F2688" t="n">
-        <v>51.6500015258789</v>
+        <v>51.5</v>
       </c>
       <c r="G2688" t="s">
         <v>7</v>
@@ -62198,22 +62198,22 @@
     </row>
     <row r="2689">
       <c r="A2689" s="1" t="n">
-        <v>46238.2916666667</v>
+        <v>46237.2916666667</v>
       </c>
       <c r="B2689" t="n">
-        <v>159270</v>
+        <v>261482</v>
       </c>
       <c r="C2689" t="n">
-        <v>52.0999984741211</v>
+        <v>51.75</v>
       </c>
       <c r="D2689" t="n">
-        <v>51.4500007629395</v>
+        <v>51.5499992370605</v>
       </c>
       <c r="E2689" t="n">
-        <v>51.4500007629395</v>
+        <v>51.5499992370605</v>
       </c>
       <c r="F2689" t="n">
-        <v>52.0999984741211</v>
+        <v>51.6500015258789</v>
       </c>
       <c r="G2689" t="s">
         <v>7</v>
@@ -62221,22 +62221,22 @@
     </row>
     <row r="2690">
       <c r="A2690" s="1" t="n">
-        <v>46239.2916666667</v>
+        <v>46238.2916666667</v>
       </c>
       <c r="B2690" t="n">
-        <v>249490</v>
+        <v>159270</v>
       </c>
       <c r="C2690" t="n">
-        <v>52.2000007629395</v>
+        <v>52.0999984741211</v>
       </c>
       <c r="D2690" t="n">
-        <v>51.7999992370605</v>
+        <v>51.4500007629395</v>
       </c>
       <c r="E2690" t="n">
-        <v>51.7999992370605</v>
+        <v>51.4500007629395</v>
       </c>
       <c r="F2690" t="n">
-        <v>52.2000007629395</v>
+        <v>52.0999984741211</v>
       </c>
       <c r="G2690" t="s">
         <v>7</v>
@@ -62244,22 +62244,22 @@
     </row>
     <row r="2691">
       <c r="A2691" s="1" t="n">
-        <v>46240.2916666667</v>
+        <v>46239.2916666667</v>
       </c>
       <c r="B2691" t="n">
-        <v>236206</v>
+        <v>249490</v>
       </c>
       <c r="C2691" t="n">
-        <v>52.7999992370605</v>
+        <v>52.2000007629395</v>
       </c>
       <c r="D2691" t="n">
-        <v>52.1500015258789</v>
+        <v>51.7999992370605</v>
       </c>
       <c r="E2691" t="n">
-        <v>52.2999992370605</v>
+        <v>51.7999992370605</v>
       </c>
       <c r="F2691" t="n">
-        <v>52.6500015258789</v>
+        <v>52.2000007629395</v>
       </c>
       <c r="G2691" t="s">
         <v>7</v>
@@ -62267,22 +62267,22 @@
     </row>
     <row r="2692">
       <c r="A2692" s="1" t="n">
-        <v>46241.2916666667</v>
+        <v>46240.2916666667</v>
       </c>
       <c r="B2692" t="n">
-        <v>357572</v>
+        <v>236206</v>
       </c>
       <c r="C2692" t="n">
-        <v>53.7000007629395</v>
+        <v>52.7999992370605</v>
       </c>
       <c r="D2692" t="n">
-        <v>52.5999984741211</v>
+        <v>52.1500015258789</v>
       </c>
       <c r="E2692" t="n">
-        <v>52.5999984741211</v>
+        <v>52.2999992370605</v>
       </c>
       <c r="F2692" t="n">
-        <v>53.25</v>
+        <v>52.6500015258789</v>
       </c>
       <c r="G2692" t="s">
         <v>7</v>
@@ -62290,22 +62290,22 @@
     </row>
     <row r="2693">
       <c r="A2693" s="1" t="n">
-        <v>46244.2916666667</v>
+        <v>46241.2916666667</v>
       </c>
       <c r="B2693" t="n">
-        <v>209520</v>
+        <v>357572</v>
       </c>
       <c r="C2693" t="n">
-        <v>53.1500015258789</v>
+        <v>53.7000007629395</v>
       </c>
       <c r="D2693" t="n">
-        <v>52.6500015258789</v>
+        <v>52.5999984741211</v>
       </c>
       <c r="E2693" t="n">
-        <v>53</v>
+        <v>52.5999984741211</v>
       </c>
       <c r="F2693" t="n">
-        <v>52.6500015258789</v>
+        <v>53.25</v>
       </c>
       <c r="G2693" t="s">
         <v>7</v>
@@ -62313,22 +62313,22 @@
     </row>
     <row r="2694">
       <c r="A2694" s="1" t="n">
-        <v>46245.2916666667</v>
+        <v>46244.2916666667</v>
       </c>
       <c r="B2694" t="n">
-        <v>217842</v>
+        <v>209520</v>
       </c>
       <c r="C2694" t="n">
-        <v>52.9000015258789</v>
+        <v>53.1500015258789</v>
       </c>
       <c r="D2694" t="n">
-        <v>52.5999984741211</v>
+        <v>52.6500015258789</v>
       </c>
       <c r="E2694" t="n">
-        <v>52.7000007629395</v>
+        <v>53</v>
       </c>
       <c r="F2694" t="n">
-        <v>52.7000007629395</v>
+        <v>52.6500015258789</v>
       </c>
       <c r="G2694" t="s">
         <v>7</v>
@@ -62336,22 +62336,22 @@
     </row>
     <row r="2695">
       <c r="A2695" s="1" t="n">
-        <v>46246.2916666667</v>
+        <v>46245.2916666667</v>
       </c>
       <c r="B2695" t="n">
-        <v>188395</v>
+        <v>217842</v>
       </c>
       <c r="C2695" t="n">
-        <v>52.75</v>
+        <v>52.9000015258789</v>
       </c>
       <c r="D2695" t="n">
         <v>52.5999984741211</v>
       </c>
       <c r="E2695" t="n">
-        <v>52.6500015258789</v>
+        <v>52.7000007629395</v>
       </c>
       <c r="F2695" t="n">
-        <v>52.5999984741211</v>
+        <v>52.7000007629395</v>
       </c>
       <c r="G2695" t="s">
         <v>7</v>
@@ -62359,22 +62359,22 @@
     </row>
     <row r="2696">
       <c r="A2696" s="1" t="n">
-        <v>46247.2916666667</v>
+        <v>46246.2916666667</v>
       </c>
       <c r="B2696" t="n">
-        <v>158403</v>
+        <v>188395</v>
       </c>
       <c r="C2696" t="n">
-        <v>52.7999992370605</v>
+        <v>52.75</v>
       </c>
       <c r="D2696" t="n">
-        <v>52.7000007629395</v>
+        <v>52.5999984741211</v>
       </c>
       <c r="E2696" t="n">
-        <v>52.75</v>
+        <v>52.6500015258789</v>
       </c>
       <c r="F2696" t="n">
-        <v>52.7999992370605</v>
+        <v>52.5999984741211</v>
       </c>
       <c r="G2696" t="s">
         <v>7</v>
@@ -62382,22 +62382,22 @@
     </row>
     <row r="2697">
       <c r="A2697" s="1" t="n">
-        <v>46248.2916666667</v>
+        <v>46247.2916666667</v>
       </c>
       <c r="B2697" t="n">
-        <v>151630</v>
+        <v>158403</v>
       </c>
       <c r="C2697" t="n">
-        <v>52.8499984741211</v>
+        <v>52.7999992370605</v>
       </c>
       <c r="D2697" t="n">
-        <v>52.5</v>
+        <v>52.7000007629395</v>
       </c>
       <c r="E2697" t="n">
-        <v>52.8499984741211</v>
+        <v>52.75</v>
       </c>
       <c r="F2697" t="n">
-        <v>52.5</v>
+        <v>52.7999992370605</v>
       </c>
       <c r="G2697" t="s">
         <v>7</v>
@@ -62405,19 +62405,19 @@
     </row>
     <row r="2698">
       <c r="A2698" s="1" t="n">
-        <v>46251.2916666667</v>
+        <v>46248.2916666667</v>
       </c>
       <c r="B2698" t="n">
-        <v>238516</v>
+        <v>151630</v>
       </c>
       <c r="C2698" t="n">
-        <v>52.75</v>
+        <v>52.8499984741211</v>
       </c>
       <c r="D2698" t="n">
         <v>52.5</v>
       </c>
       <c r="E2698" t="n">
-        <v>52.7000007629395</v>
+        <v>52.8499984741211</v>
       </c>
       <c r="F2698" t="n">
         <v>52.5</v>
@@ -62428,22 +62428,22 @@
     </row>
     <row r="2699">
       <c r="A2699" s="1" t="n">
-        <v>46252.2916666667</v>
+        <v>46251.2916666667</v>
       </c>
       <c r="B2699" t="n">
-        <v>233062</v>
+        <v>238516</v>
       </c>
       <c r="C2699" t="n">
-        <v>52.7999992370605</v>
+        <v>52.75</v>
       </c>
       <c r="D2699" t="n">
-        <v>52.5499992370605</v>
+        <v>52.5</v>
       </c>
       <c r="E2699" t="n">
-        <v>52.7999992370605</v>
+        <v>52.7000007629395</v>
       </c>
       <c r="F2699" t="n">
-        <v>52.5499992370605</v>
+        <v>52.5</v>
       </c>
       <c r="G2699" t="s">
         <v>7</v>
@@ -62451,24 +62451,70 @@
     </row>
     <row r="2700">
       <c r="A2700" s="1" t="n">
+        <v>46252.2916666667</v>
+      </c>
+      <c r="B2700" t="n">
+        <v>233062</v>
+      </c>
+      <c r="C2700" t="n">
+        <v>52.7999992370605</v>
+      </c>
+      <c r="D2700" t="n">
+        <v>52.5499992370605</v>
+      </c>
+      <c r="E2700" t="n">
+        <v>52.7999992370605</v>
+      </c>
+      <c r="F2700" t="n">
+        <v>52.5499992370605</v>
+      </c>
+      <c r="G2700" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2701">
+      <c r="A2701" s="1" t="n">
         <v>46253.2916666667</v>
       </c>
-      <c r="B2700" t="n">
+      <c r="B2701" t="n">
         <v>169280</v>
       </c>
-      <c r="C2700" t="n">
+      <c r="C2701" t="n">
         <v>53.0999984741211</v>
       </c>
-      <c r="D2700" t="n">
+      <c r="D2701" t="n">
         <v>52.5999984741211</v>
       </c>
-      <c r="E2700" t="n">
+      <c r="E2701" t="n">
         <v>52.6500015258789</v>
       </c>
-      <c r="F2700" t="n">
+      <c r="F2701" t="n">
         <v>53.0499992370605</v>
       </c>
-      <c r="G2700" t="s">
+      <c r="G2701" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2702">
+      <c r="A2702" s="1" t="n">
+        <v>46254.2916666667</v>
+      </c>
+      <c r="B2702" t="n">
+        <v>167637</v>
+      </c>
+      <c r="C2702" t="n">
+        <v>53.2000007629395</v>
+      </c>
+      <c r="D2702" t="n">
+        <v>52.7000007629395</v>
+      </c>
+      <c r="E2702" t="n">
+        <v>53.0499992370605</v>
+      </c>
+      <c r="F2702" t="n">
+        <v>53</v>
+      </c>
+      <c r="G2702" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/REC.MI.xlsx
+++ b/data/REC.MI.xlsx
@@ -62649,8 +62649,31 @@
       <c r="E2708" t="n">
         <v>52.75</v>
       </c>
-      <c r="F2708"/>
+      <c r="F2708" t="n">
+        <v>52.6500015258789</v>
+      </c>
       <c r="G2708" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2709">
+      <c r="A2709" s="1" t="n">
+        <v>46262.2916666667</v>
+      </c>
+      <c r="B2709" t="n">
+        <v>155833</v>
+      </c>
+      <c r="C2709" t="n">
+        <v>52.7000007629395</v>
+      </c>
+      <c r="D2709" t="n">
+        <v>52.6500015258789</v>
+      </c>
+      <c r="E2709" t="n">
+        <v>52.7000007629395</v>
+      </c>
+      <c r="F2709"/>
+      <c r="G2709" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/REC.MI.xlsx
+++ b/data/REC.MI.xlsx
@@ -62672,8 +62672,31 @@
       <c r="E2709" t="n">
         <v>52.7000007629395</v>
       </c>
-      <c r="F2709"/>
+      <c r="F2709" t="n">
+        <v>52.6500015258789</v>
+      </c>
       <c r="G2709" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2710">
+      <c r="A2710" s="1" t="n">
+        <v>46265.2916666667</v>
+      </c>
+      <c r="B2710" t="n">
+        <v>2036154</v>
+      </c>
+      <c r="C2710" t="n">
+        <v>52.7000007629395</v>
+      </c>
+      <c r="D2710" t="n">
+        <v>52.4000015258789</v>
+      </c>
+      <c r="E2710" t="n">
+        <v>52.6500015258789</v>
+      </c>
+      <c r="F2710"/>
+      <c r="G2710" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/REC.MI.xlsx
+++ b/data/REC.MI.xlsx
@@ -62817,6 +62817,52 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2716">
+      <c r="A2716" s="1" t="n">
+        <v>46274.2916666667</v>
+      </c>
+      <c r="B2716" t="n">
+        <v>491761</v>
+      </c>
+      <c r="C2716" t="n">
+        <v>52.0999984741211</v>
+      </c>
+      <c r="D2716" t="n">
+        <v>51.8499984741211</v>
+      </c>
+      <c r="E2716" t="n">
+        <v>51.8499984741211</v>
+      </c>
+      <c r="F2716" t="n">
+        <v>52</v>
+      </c>
+      <c r="G2716" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2717">
+      <c r="A2717" s="1" t="n">
+        <v>46275.2916666667</v>
+      </c>
+      <c r="B2717" t="n">
+        <v>588688</v>
+      </c>
+      <c r="C2717" t="n">
+        <v>52.0999984741211</v>
+      </c>
+      <c r="D2717" t="n">
+        <v>51.9000015258789</v>
+      </c>
+      <c r="E2717" t="n">
+        <v>51.9000015258789</v>
+      </c>
+      <c r="F2717" t="n">
+        <v>52</v>
+      </c>
+      <c r="G2717" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/REC.MI.xlsx
+++ b/data/REC.MI.xlsx
@@ -62863,6 +62863,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2718">
+      <c r="A2718" s="1" t="n">
+        <v>46276.2916666667</v>
+      </c>
+      <c r="B2718" t="n">
+        <v>555326</v>
+      </c>
+      <c r="C2718" t="n">
+        <v>52.2000007629395</v>
+      </c>
+      <c r="D2718" t="n">
+        <v>52</v>
+      </c>
+      <c r="E2718" t="n">
+        <v>52</v>
+      </c>
+      <c r="F2718" t="n">
+        <v>52</v>
+      </c>
+      <c r="G2718" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
